--- a/avito.xlsx
+++ b/avito.xlsx
@@ -2519,10 +2519,18 @@
       <ns0:c r="AA5"/>
       <ns0:c r="AB5"/>
       <ns0:c r="AC5"/>
-      <ns0:c r="AD5"/>
-      <ns0:c r="AE5"/>
-      <ns0:c r="AF5"/>
-      <ns0:c r="AG5"/>
+      <ns0:c r="AD5">
+        <ns0:v>6.5</ns0:v>
+      </ns0:c>
+      <ns0:c r="AE5">
+        <ns0:v>15</ns0:v>
+      </ns0:c>
+      <ns0:c r="AF5">
+        <ns0:v>120</ns0:v>
+      </ns0:c>
+      <ns0:c r="AG5">
+        <ns0:v>15</ns0:v>
+      </ns0:c>
       <ns0:c r="AH5"/>
       <ns0:c r="AI5">
         <ns0:v>3921</ns0:v>
@@ -2648,10 +2656,18 @@
       <ns0:c r="AA6"/>
       <ns0:c r="AB6"/>
       <ns0:c r="AC6"/>
-      <ns0:c r="AD6"/>
-      <ns0:c r="AE6"/>
-      <ns0:c r="AF6"/>
-      <ns0:c r="AG6"/>
+      <ns0:c r="AD6">
+        <ns0:v>6.5</ns0:v>
+      </ns0:c>
+      <ns0:c r="AE6">
+        <ns0:v>15</ns0:v>
+      </ns0:c>
+      <ns0:c r="AF6">
+        <ns0:v>120</ns0:v>
+      </ns0:c>
+      <ns0:c r="AG6">
+        <ns0:v>15</ns0:v>
+      </ns0:c>
       <ns0:c r="AH6"/>
       <ns0:c r="AI6">
         <ns0:v>3921</ns0:v>
@@ -2777,10 +2793,18 @@
       <ns0:c r="AA7"/>
       <ns0:c r="AB7"/>
       <ns0:c r="AC7"/>
-      <ns0:c r="AD7"/>
-      <ns0:c r="AE7"/>
-      <ns0:c r="AF7"/>
-      <ns0:c r="AG7"/>
+      <ns0:c r="AD7">
+        <ns0:v>6.5</ns0:v>
+      </ns0:c>
+      <ns0:c r="AE7">
+        <ns0:v>15</ns0:v>
+      </ns0:c>
+      <ns0:c r="AF7">
+        <ns0:v>120</ns0:v>
+      </ns0:c>
+      <ns0:c r="AG7">
+        <ns0:v>15</ns0:v>
+      </ns0:c>
       <ns0:c r="AH7"/>
       <ns0:c r="AI7">
         <ns0:v>3921</ns0:v>
@@ -2906,10 +2930,18 @@
       <ns0:c r="AA8"/>
       <ns0:c r="AB8"/>
       <ns0:c r="AC8"/>
-      <ns0:c r="AD8"/>
-      <ns0:c r="AE8"/>
-      <ns0:c r="AF8"/>
-      <ns0:c r="AG8"/>
+      <ns0:c r="AD8">
+        <ns0:v>6.5</ns0:v>
+      </ns0:c>
+      <ns0:c r="AE8">
+        <ns0:v>15</ns0:v>
+      </ns0:c>
+      <ns0:c r="AF8">
+        <ns0:v>120</ns0:v>
+      </ns0:c>
+      <ns0:c r="AG8">
+        <ns0:v>15</ns0:v>
+      </ns0:c>
       <ns0:c r="AH8"/>
       <ns0:c r="AI8">
         <ns0:v>3921</ns0:v>
@@ -3035,10 +3067,18 @@
       <ns0:c r="AA9"/>
       <ns0:c r="AB9"/>
       <ns0:c r="AC9"/>
-      <ns0:c r="AD9"/>
-      <ns0:c r="AE9"/>
-      <ns0:c r="AF9"/>
-      <ns0:c r="AG9"/>
+      <ns0:c r="AD9">
+        <ns0:v>6.5</ns0:v>
+      </ns0:c>
+      <ns0:c r="AE9">
+        <ns0:v>15</ns0:v>
+      </ns0:c>
+      <ns0:c r="AF9">
+        <ns0:v>120</ns0:v>
+      </ns0:c>
+      <ns0:c r="AG9">
+        <ns0:v>15</ns0:v>
+      </ns0:c>
       <ns0:c r="AH9"/>
       <ns0:c r="AI9">
         <ns0:v>3921</ns0:v>
@@ -3164,10 +3204,18 @@
       <ns0:c r="AA10"/>
       <ns0:c r="AB10"/>
       <ns0:c r="AC10"/>
-      <ns0:c r="AD10"/>
-      <ns0:c r="AE10"/>
-      <ns0:c r="AF10"/>
-      <ns0:c r="AG10"/>
+      <ns0:c r="AD10">
+        <ns0:v>6.5</ns0:v>
+      </ns0:c>
+      <ns0:c r="AE10">
+        <ns0:v>15</ns0:v>
+      </ns0:c>
+      <ns0:c r="AF10">
+        <ns0:v>120</ns0:v>
+      </ns0:c>
+      <ns0:c r="AG10">
+        <ns0:v>15</ns0:v>
+      </ns0:c>
       <ns0:c r="AH10"/>
       <ns0:c r="AI10">
         <ns0:v>3921</ns0:v>
@@ -3293,10 +3341,18 @@
       <ns0:c r="AA11"/>
       <ns0:c r="AB11"/>
       <ns0:c r="AC11"/>
-      <ns0:c r="AD11"/>
-      <ns0:c r="AE11"/>
-      <ns0:c r="AF11"/>
-      <ns0:c r="AG11"/>
+      <ns0:c r="AD11">
+        <ns0:v>6.5</ns0:v>
+      </ns0:c>
+      <ns0:c r="AE11">
+        <ns0:v>15</ns0:v>
+      </ns0:c>
+      <ns0:c r="AF11">
+        <ns0:v>120</ns0:v>
+      </ns0:c>
+      <ns0:c r="AG11">
+        <ns0:v>15</ns0:v>
+      </ns0:c>
       <ns0:c r="AH11"/>
       <ns0:c r="AI11">
         <ns0:v>3921</ns0:v>
@@ -3422,10 +3478,18 @@
       <ns0:c r="AA12"/>
       <ns0:c r="AB12"/>
       <ns0:c r="AC12"/>
-      <ns0:c r="AD12"/>
-      <ns0:c r="AE12"/>
-      <ns0:c r="AF12"/>
-      <ns0:c r="AG12"/>
+      <ns0:c r="AD12">
+        <ns0:v>6.5</ns0:v>
+      </ns0:c>
+      <ns0:c r="AE12">
+        <ns0:v>15</ns0:v>
+      </ns0:c>
+      <ns0:c r="AF12">
+        <ns0:v>120</ns0:v>
+      </ns0:c>
+      <ns0:c r="AG12">
+        <ns0:v>15</ns0:v>
+      </ns0:c>
       <ns0:c r="AH12"/>
       <ns0:c r="AI12">
         <ns0:v>3921</ns0:v>
@@ -3551,10 +3615,18 @@
       <ns0:c r="AA13"/>
       <ns0:c r="AB13"/>
       <ns0:c r="AC13"/>
-      <ns0:c r="AD13"/>
-      <ns0:c r="AE13"/>
-      <ns0:c r="AF13"/>
-      <ns0:c r="AG13"/>
+      <ns0:c r="AD13">
+        <ns0:v>6.5</ns0:v>
+      </ns0:c>
+      <ns0:c r="AE13">
+        <ns0:v>15</ns0:v>
+      </ns0:c>
+      <ns0:c r="AF13">
+        <ns0:v>120</ns0:v>
+      </ns0:c>
+      <ns0:c r="AG13">
+        <ns0:v>15</ns0:v>
+      </ns0:c>
       <ns0:c r="AH13"/>
       <ns0:c r="AI13">
         <ns0:v>3921</ns0:v>
@@ -3680,10 +3752,18 @@
       <ns0:c r="AA14"/>
       <ns0:c r="AB14"/>
       <ns0:c r="AC14"/>
-      <ns0:c r="AD14"/>
-      <ns0:c r="AE14"/>
-      <ns0:c r="AF14"/>
-      <ns0:c r="AG14"/>
+      <ns0:c r="AD14">
+        <ns0:v>6.5</ns0:v>
+      </ns0:c>
+      <ns0:c r="AE14">
+        <ns0:v>15</ns0:v>
+      </ns0:c>
+      <ns0:c r="AF14">
+        <ns0:v>120</ns0:v>
+      </ns0:c>
+      <ns0:c r="AG14">
+        <ns0:v>15</ns0:v>
+      </ns0:c>
       <ns0:c r="AH14"/>
       <ns0:c r="AI14">
         <ns0:v>3921</ns0:v>
@@ -3810,10 +3890,18 @@
       <ns0:c r="AA15"/>
       <ns0:c r="AB15"/>
       <ns0:c r="AC15"/>
-      <ns0:c r="AD15"/>
-      <ns0:c r="AE15"/>
-      <ns0:c r="AF15"/>
-      <ns0:c r="AG15"/>
+      <ns0:c r="AD15">
+        <ns0:v>6.5</ns0:v>
+      </ns0:c>
+      <ns0:c r="AE15">
+        <ns0:v>15</ns0:v>
+      </ns0:c>
+      <ns0:c r="AF15">
+        <ns0:v>120</ns0:v>
+      </ns0:c>
+      <ns0:c r="AG15">
+        <ns0:v>15</ns0:v>
+      </ns0:c>
       <ns0:c r="AH15"/>
       <ns0:c r="AI15">
         <ns0:v>3921</ns0:v>
@@ -3942,10 +4030,18 @@
       <ns0:c r="AA16"/>
       <ns0:c r="AB16"/>
       <ns0:c r="AC16"/>
-      <ns0:c r="AD16"/>
-      <ns0:c r="AE16"/>
-      <ns0:c r="AF16"/>
-      <ns0:c r="AG16"/>
+      <ns0:c r="AD16">
+        <ns0:v>6.5</ns0:v>
+      </ns0:c>
+      <ns0:c r="AE16">
+        <ns0:v>15</ns0:v>
+      </ns0:c>
+      <ns0:c r="AF16">
+        <ns0:v>120</ns0:v>
+      </ns0:c>
+      <ns0:c r="AG16">
+        <ns0:v>15</ns0:v>
+      </ns0:c>
       <ns0:c r="AH16"/>
       <ns0:c r="AI16">
         <ns0:v>3921</ns0:v>
@@ -4074,10 +4170,18 @@
       <ns0:c r="AA17"/>
       <ns0:c r="AB17"/>
       <ns0:c r="AC17"/>
-      <ns0:c r="AD17"/>
-      <ns0:c r="AE17"/>
-      <ns0:c r="AF17"/>
-      <ns0:c r="AG17"/>
+      <ns0:c r="AD17">
+        <ns0:v>6.5</ns0:v>
+      </ns0:c>
+      <ns0:c r="AE17">
+        <ns0:v>15</ns0:v>
+      </ns0:c>
+      <ns0:c r="AF17">
+        <ns0:v>120</ns0:v>
+      </ns0:c>
+      <ns0:c r="AG17">
+        <ns0:v>15</ns0:v>
+      </ns0:c>
       <ns0:c r="AH17"/>
       <ns0:c r="AI17">
         <ns0:v>3950</ns0:v>
@@ -4206,10 +4310,18 @@
       <ns0:c r="AA18"/>
       <ns0:c r="AB18"/>
       <ns0:c r="AC18"/>
-      <ns0:c r="AD18"/>
-      <ns0:c r="AE18"/>
-      <ns0:c r="AF18"/>
-      <ns0:c r="AG18"/>
+      <ns0:c r="AD18">
+        <ns0:v>6.5</ns0:v>
+      </ns0:c>
+      <ns0:c r="AE18">
+        <ns0:v>15</ns0:v>
+      </ns0:c>
+      <ns0:c r="AF18">
+        <ns0:v>120</ns0:v>
+      </ns0:c>
+      <ns0:c r="AG18">
+        <ns0:v>15</ns0:v>
+      </ns0:c>
       <ns0:c r="AH18"/>
       <ns0:c r="AI18">
         <ns0:v>3950</ns0:v>
@@ -4338,10 +4450,18 @@
       <ns0:c r="AA19"/>
       <ns0:c r="AB19"/>
       <ns0:c r="AC19"/>
-      <ns0:c r="AD19"/>
-      <ns0:c r="AE19"/>
-      <ns0:c r="AF19"/>
-      <ns0:c r="AG19"/>
+      <ns0:c r="AD19">
+        <ns0:v>6.5</ns0:v>
+      </ns0:c>
+      <ns0:c r="AE19">
+        <ns0:v>15</ns0:v>
+      </ns0:c>
+      <ns0:c r="AF19">
+        <ns0:v>120</ns0:v>
+      </ns0:c>
+      <ns0:c r="AG19">
+        <ns0:v>15</ns0:v>
+      </ns0:c>
       <ns0:c r="AH19"/>
       <ns0:c r="AI19">
         <ns0:v>3950</ns0:v>
@@ -4470,10 +4590,18 @@
       <ns0:c r="AA20"/>
       <ns0:c r="AB20"/>
       <ns0:c r="AC20"/>
-      <ns0:c r="AD20"/>
-      <ns0:c r="AE20"/>
-      <ns0:c r="AF20"/>
-      <ns0:c r="AG20"/>
+      <ns0:c r="AD20">
+        <ns0:v>6.5</ns0:v>
+      </ns0:c>
+      <ns0:c r="AE20">
+        <ns0:v>15</ns0:v>
+      </ns0:c>
+      <ns0:c r="AF20">
+        <ns0:v>120</ns0:v>
+      </ns0:c>
+      <ns0:c r="AG20">
+        <ns0:v>15</ns0:v>
+      </ns0:c>
       <ns0:c r="AH20"/>
       <ns0:c r="AI20">
         <ns0:v>3950</ns0:v>
@@ -4602,10 +4730,18 @@
       <ns0:c r="AA21"/>
       <ns0:c r="AB21"/>
       <ns0:c r="AC21"/>
-      <ns0:c r="AD21"/>
-      <ns0:c r="AE21"/>
-      <ns0:c r="AF21"/>
-      <ns0:c r="AG21"/>
+      <ns0:c r="AD21">
+        <ns0:v>6.5</ns0:v>
+      </ns0:c>
+      <ns0:c r="AE21">
+        <ns0:v>15</ns0:v>
+      </ns0:c>
+      <ns0:c r="AF21">
+        <ns0:v>120</ns0:v>
+      </ns0:c>
+      <ns0:c r="AG21">
+        <ns0:v>15</ns0:v>
+      </ns0:c>
       <ns0:c r="AH21"/>
       <ns0:c r="AI21">
         <ns0:v>3950</ns0:v>
@@ -4734,10 +4870,18 @@
       <ns0:c r="AA22"/>
       <ns0:c r="AB22"/>
       <ns0:c r="AC22"/>
-      <ns0:c r="AD22"/>
-      <ns0:c r="AE22"/>
-      <ns0:c r="AF22"/>
-      <ns0:c r="AG22"/>
+      <ns0:c r="AD22">
+        <ns0:v>6.5</ns0:v>
+      </ns0:c>
+      <ns0:c r="AE22">
+        <ns0:v>15</ns0:v>
+      </ns0:c>
+      <ns0:c r="AF22">
+        <ns0:v>120</ns0:v>
+      </ns0:c>
+      <ns0:c r="AG22">
+        <ns0:v>15</ns0:v>
+      </ns0:c>
       <ns0:c r="AH22"/>
       <ns0:c r="AI22">
         <ns0:v>3950</ns0:v>
@@ -4866,10 +5010,18 @@
       <ns0:c r="AA23"/>
       <ns0:c r="AB23"/>
       <ns0:c r="AC23"/>
-      <ns0:c r="AD23"/>
-      <ns0:c r="AE23"/>
-      <ns0:c r="AF23"/>
-      <ns0:c r="AG23"/>
+      <ns0:c r="AD23">
+        <ns0:v>6.5</ns0:v>
+      </ns0:c>
+      <ns0:c r="AE23">
+        <ns0:v>15</ns0:v>
+      </ns0:c>
+      <ns0:c r="AF23">
+        <ns0:v>120</ns0:v>
+      </ns0:c>
+      <ns0:c r="AG23">
+        <ns0:v>15</ns0:v>
+      </ns0:c>
       <ns0:c r="AH23"/>
       <ns0:c r="AI23">
         <ns0:v>3950</ns0:v>
@@ -4998,10 +5150,18 @@
       <ns0:c r="AA24"/>
       <ns0:c r="AB24"/>
       <ns0:c r="AC24"/>
-      <ns0:c r="AD24"/>
-      <ns0:c r="AE24"/>
-      <ns0:c r="AF24"/>
-      <ns0:c r="AG24"/>
+      <ns0:c r="AD24">
+        <ns0:v>6.5</ns0:v>
+      </ns0:c>
+      <ns0:c r="AE24">
+        <ns0:v>15</ns0:v>
+      </ns0:c>
+      <ns0:c r="AF24">
+        <ns0:v>120</ns0:v>
+      </ns0:c>
+      <ns0:c r="AG24">
+        <ns0:v>15</ns0:v>
+      </ns0:c>
       <ns0:c r="AH24"/>
       <ns0:c r="AI24">
         <ns0:v>3950</ns0:v>
@@ -5130,10 +5290,18 @@
       <ns0:c r="AA25"/>
       <ns0:c r="AB25"/>
       <ns0:c r="AC25"/>
-      <ns0:c r="AD25"/>
-      <ns0:c r="AE25"/>
-      <ns0:c r="AF25"/>
-      <ns0:c r="AG25"/>
+      <ns0:c r="AD25">
+        <ns0:v>6.5</ns0:v>
+      </ns0:c>
+      <ns0:c r="AE25">
+        <ns0:v>15</ns0:v>
+      </ns0:c>
+      <ns0:c r="AF25">
+        <ns0:v>120</ns0:v>
+      </ns0:c>
+      <ns0:c r="AG25">
+        <ns0:v>15</ns0:v>
+      </ns0:c>
       <ns0:c r="AH25"/>
       <ns0:c r="AI25">
         <ns0:v>3950</ns0:v>
@@ -5262,10 +5430,18 @@
       <ns0:c r="AA26"/>
       <ns0:c r="AB26"/>
       <ns0:c r="AC26"/>
-      <ns0:c r="AD26"/>
-      <ns0:c r="AE26"/>
-      <ns0:c r="AF26"/>
-      <ns0:c r="AG26"/>
+      <ns0:c r="AD26">
+        <ns0:v>6.5</ns0:v>
+      </ns0:c>
+      <ns0:c r="AE26">
+        <ns0:v>15</ns0:v>
+      </ns0:c>
+      <ns0:c r="AF26">
+        <ns0:v>120</ns0:v>
+      </ns0:c>
+      <ns0:c r="AG26">
+        <ns0:v>15</ns0:v>
+      </ns0:c>
       <ns0:c r="AH26"/>
       <ns0:c r="AI26">
         <ns0:v>3950</ns0:v>
@@ -5394,10 +5570,18 @@
       <ns0:c r="AA27"/>
       <ns0:c r="AB27"/>
       <ns0:c r="AC27"/>
-      <ns0:c r="AD27"/>
-      <ns0:c r="AE27"/>
-      <ns0:c r="AF27"/>
-      <ns0:c r="AG27"/>
+      <ns0:c r="AD27">
+        <ns0:v>6.5</ns0:v>
+      </ns0:c>
+      <ns0:c r="AE27">
+        <ns0:v>15</ns0:v>
+      </ns0:c>
+      <ns0:c r="AF27">
+        <ns0:v>120</ns0:v>
+      </ns0:c>
+      <ns0:c r="AG27">
+        <ns0:v>15</ns0:v>
+      </ns0:c>
       <ns0:c r="AH27"/>
       <ns0:c r="AI27">
         <ns0:v>3950</ns0:v>
@@ -5526,10 +5710,18 @@
       <ns0:c r="AA28"/>
       <ns0:c r="AB28"/>
       <ns0:c r="AC28"/>
-      <ns0:c r="AD28"/>
-      <ns0:c r="AE28"/>
-      <ns0:c r="AF28"/>
-      <ns0:c r="AG28"/>
+      <ns0:c r="AD28">
+        <ns0:v>6.5</ns0:v>
+      </ns0:c>
+      <ns0:c r="AE28">
+        <ns0:v>15</ns0:v>
+      </ns0:c>
+      <ns0:c r="AF28">
+        <ns0:v>120</ns0:v>
+      </ns0:c>
+      <ns0:c r="AG28">
+        <ns0:v>15</ns0:v>
+      </ns0:c>
       <ns0:c r="AH28"/>
       <ns0:c r="AI28">
         <ns0:v>3950</ns0:v>
@@ -5658,10 +5850,18 @@
       <ns0:c r="AA29"/>
       <ns0:c r="AB29"/>
       <ns0:c r="AC29"/>
-      <ns0:c r="AD29"/>
-      <ns0:c r="AE29"/>
-      <ns0:c r="AF29"/>
-      <ns0:c r="AG29"/>
+      <ns0:c r="AD29">
+        <ns0:v>6.5</ns0:v>
+      </ns0:c>
+      <ns0:c r="AE29">
+        <ns0:v>15</ns0:v>
+      </ns0:c>
+      <ns0:c r="AF29">
+        <ns0:v>120</ns0:v>
+      </ns0:c>
+      <ns0:c r="AG29">
+        <ns0:v>15</ns0:v>
+      </ns0:c>
       <ns0:c r="AH29"/>
       <ns0:c r="AI29">
         <ns0:v>3950</ns0:v>
@@ -5790,10 +5990,18 @@
       <ns0:c r="AA30"/>
       <ns0:c r="AB30"/>
       <ns0:c r="AC30"/>
-      <ns0:c r="AD30"/>
-      <ns0:c r="AE30"/>
-      <ns0:c r="AF30"/>
-      <ns0:c r="AG30"/>
+      <ns0:c r="AD30">
+        <ns0:v>6.5</ns0:v>
+      </ns0:c>
+      <ns0:c r="AE30">
+        <ns0:v>15</ns0:v>
+      </ns0:c>
+      <ns0:c r="AF30">
+        <ns0:v>120</ns0:v>
+      </ns0:c>
+      <ns0:c r="AG30">
+        <ns0:v>15</ns0:v>
+      </ns0:c>
       <ns0:c r="AH30"/>
       <ns0:c r="AI30">
         <ns0:v>3950</ns0:v>
@@ -5922,10 +6130,18 @@
       <ns0:c r="AA31"/>
       <ns0:c r="AB31"/>
       <ns0:c r="AC31"/>
-      <ns0:c r="AD31"/>
-      <ns0:c r="AE31"/>
-      <ns0:c r="AF31"/>
-      <ns0:c r="AG31"/>
+      <ns0:c r="AD31">
+        <ns0:v>6.5</ns0:v>
+      </ns0:c>
+      <ns0:c r="AE31">
+        <ns0:v>15</ns0:v>
+      </ns0:c>
+      <ns0:c r="AF31">
+        <ns0:v>120</ns0:v>
+      </ns0:c>
+      <ns0:c r="AG31">
+        <ns0:v>15</ns0:v>
+      </ns0:c>
       <ns0:c r="AH31"/>
       <ns0:c r="AI31">
         <ns0:v>3950</ns0:v>

--- a/avito.xlsx
+++ b/avito.xlsx
@@ -2533,7 +2533,7 @@
       </ns0:c>
       <ns0:c r="AH5"/>
       <ns0:c r="AI5">
-        <ns0:v>3921</ns0:v>
+        <ns0:v>4900</ns0:v>
       </ns0:c>
       <ns0:c r="AJ5" t="str">
         <ns0:v>Стройматериалы</ns0:v>
@@ -2670,7 +2670,7 @@
       </ns0:c>
       <ns0:c r="AH6"/>
       <ns0:c r="AI6">
-        <ns0:v>3921</ns0:v>
+        <ns0:v>4900</ns0:v>
       </ns0:c>
       <ns0:c r="AJ6" t="str">
         <ns0:v>Стройматериалы</ns0:v>
@@ -2807,7 +2807,7 @@
       </ns0:c>
       <ns0:c r="AH7"/>
       <ns0:c r="AI7">
-        <ns0:v>3921</ns0:v>
+        <ns0:v>4900</ns0:v>
       </ns0:c>
       <ns0:c r="AJ7" t="str">
         <ns0:v>Стройматериалы</ns0:v>
@@ -2944,7 +2944,7 @@
       </ns0:c>
       <ns0:c r="AH8"/>
       <ns0:c r="AI8">
-        <ns0:v>3921</ns0:v>
+        <ns0:v>4900</ns0:v>
       </ns0:c>
       <ns0:c r="AJ8" t="str">
         <ns0:v>Стройматериалы</ns0:v>
@@ -3081,7 +3081,7 @@
       </ns0:c>
       <ns0:c r="AH9"/>
       <ns0:c r="AI9">
-        <ns0:v>3921</ns0:v>
+        <ns0:v>4900</ns0:v>
       </ns0:c>
       <ns0:c r="AJ9" t="str">
         <ns0:v>Стройматериалы</ns0:v>
@@ -3218,7 +3218,7 @@
       </ns0:c>
       <ns0:c r="AH10"/>
       <ns0:c r="AI10">
-        <ns0:v>3921</ns0:v>
+        <ns0:v>4900</ns0:v>
       </ns0:c>
       <ns0:c r="AJ10" t="str">
         <ns0:v>Стройматериалы</ns0:v>
@@ -3355,7 +3355,7 @@
       </ns0:c>
       <ns0:c r="AH11"/>
       <ns0:c r="AI11">
-        <ns0:v>3921</ns0:v>
+        <ns0:v>4900</ns0:v>
       </ns0:c>
       <ns0:c r="AJ11" t="str">
         <ns0:v>Стройматериалы</ns0:v>
@@ -3492,7 +3492,7 @@
       </ns0:c>
       <ns0:c r="AH12"/>
       <ns0:c r="AI12">
-        <ns0:v>3921</ns0:v>
+        <ns0:v>4900</ns0:v>
       </ns0:c>
       <ns0:c r="AJ12" t="str">
         <ns0:v>Стройматериалы</ns0:v>
@@ -3629,7 +3629,7 @@
       </ns0:c>
       <ns0:c r="AH13"/>
       <ns0:c r="AI13">
-        <ns0:v>3921</ns0:v>
+        <ns0:v>4900</ns0:v>
       </ns0:c>
       <ns0:c r="AJ13" t="str">
         <ns0:v>Стройматериалы</ns0:v>
@@ -3766,7 +3766,7 @@
       </ns0:c>
       <ns0:c r="AH14"/>
       <ns0:c r="AI14">
-        <ns0:v>3921</ns0:v>
+        <ns0:v>4900</ns0:v>
       </ns0:c>
       <ns0:c r="AJ14" t="str">
         <ns0:v>Стройматериалы</ns0:v>
@@ -3904,7 +3904,7 @@
       </ns0:c>
       <ns0:c r="AH15"/>
       <ns0:c r="AI15">
-        <ns0:v>3921</ns0:v>
+        <ns0:v>4900</ns0:v>
       </ns0:c>
       <ns0:c r="AJ15" t="str">
         <ns0:v>Стройматериалы</ns0:v>
@@ -4044,7 +4044,7 @@
       </ns0:c>
       <ns0:c r="AH16"/>
       <ns0:c r="AI16">
-        <ns0:v>3921</ns0:v>
+        <ns0:v>4900</ns0:v>
       </ns0:c>
       <ns0:c r="AJ16" t="str">
         <ns0:v>Стройматериалы</ns0:v>
@@ -4184,7 +4184,7 @@
       </ns0:c>
       <ns0:c r="AH17"/>
       <ns0:c r="AI17">
-        <ns0:v>3950</ns0:v>
+        <ns0:v>4900</ns0:v>
       </ns0:c>
       <ns0:c r="AJ17" t="str">
         <ns0:v>Стройматериалы</ns0:v>
@@ -4324,7 +4324,7 @@
       </ns0:c>
       <ns0:c r="AH18"/>
       <ns0:c r="AI18">
-        <ns0:v>3950</ns0:v>
+        <ns0:v>4900</ns0:v>
       </ns0:c>
       <ns0:c r="AJ18" t="str">
         <ns0:v>Стройматериалы</ns0:v>
@@ -4464,7 +4464,7 @@
       </ns0:c>
       <ns0:c r="AH19"/>
       <ns0:c r="AI19">
-        <ns0:v>3950</ns0:v>
+        <ns0:v>4900</ns0:v>
       </ns0:c>
       <ns0:c r="AJ19" t="str">
         <ns0:v>Стройматериалы</ns0:v>
@@ -4604,7 +4604,7 @@
       </ns0:c>
       <ns0:c r="AH20"/>
       <ns0:c r="AI20">
-        <ns0:v>3950</ns0:v>
+        <ns0:v>4900</ns0:v>
       </ns0:c>
       <ns0:c r="AJ20" t="str">
         <ns0:v>Стройматериалы</ns0:v>
@@ -4744,7 +4744,7 @@
       </ns0:c>
       <ns0:c r="AH21"/>
       <ns0:c r="AI21">
-        <ns0:v>3950</ns0:v>
+        <ns0:v>4900</ns0:v>
       </ns0:c>
       <ns0:c r="AJ21" t="str">
         <ns0:v>Стройматериалы</ns0:v>
@@ -4884,7 +4884,7 @@
       </ns0:c>
       <ns0:c r="AH22"/>
       <ns0:c r="AI22">
-        <ns0:v>3950</ns0:v>
+        <ns0:v>4900</ns0:v>
       </ns0:c>
       <ns0:c r="AJ22" t="str">
         <ns0:v>Стройматериалы</ns0:v>
@@ -5024,7 +5024,7 @@
       </ns0:c>
       <ns0:c r="AH23"/>
       <ns0:c r="AI23">
-        <ns0:v>3950</ns0:v>
+        <ns0:v>4900</ns0:v>
       </ns0:c>
       <ns0:c r="AJ23" t="str">
         <ns0:v>Стройматериалы</ns0:v>
@@ -5164,7 +5164,7 @@
       </ns0:c>
       <ns0:c r="AH24"/>
       <ns0:c r="AI24">
-        <ns0:v>3950</ns0:v>
+        <ns0:v>4900</ns0:v>
       </ns0:c>
       <ns0:c r="AJ24" t="str">
         <ns0:v>Стройматериалы</ns0:v>
@@ -5304,7 +5304,7 @@
       </ns0:c>
       <ns0:c r="AH25"/>
       <ns0:c r="AI25">
-        <ns0:v>3950</ns0:v>
+        <ns0:v>4900</ns0:v>
       </ns0:c>
       <ns0:c r="AJ25" t="str">
         <ns0:v>Стройматериалы</ns0:v>
@@ -5444,7 +5444,7 @@
       </ns0:c>
       <ns0:c r="AH26"/>
       <ns0:c r="AI26">
-        <ns0:v>3950</ns0:v>
+        <ns0:v>4900</ns0:v>
       </ns0:c>
       <ns0:c r="AJ26" t="str">
         <ns0:v>Стройматериалы</ns0:v>
@@ -5584,7 +5584,7 @@
       </ns0:c>
       <ns0:c r="AH27"/>
       <ns0:c r="AI27">
-        <ns0:v>3950</ns0:v>
+        <ns0:v>4900</ns0:v>
       </ns0:c>
       <ns0:c r="AJ27" t="str">
         <ns0:v>Стройматериалы</ns0:v>
@@ -5724,7 +5724,7 @@
       </ns0:c>
       <ns0:c r="AH28"/>
       <ns0:c r="AI28">
-        <ns0:v>3950</ns0:v>
+        <ns0:v>4900</ns0:v>
       </ns0:c>
       <ns0:c r="AJ28" t="str">
         <ns0:v>Стройматериалы</ns0:v>
@@ -5864,7 +5864,7 @@
       </ns0:c>
       <ns0:c r="AH29"/>
       <ns0:c r="AI29">
-        <ns0:v>3950</ns0:v>
+        <ns0:v>4900</ns0:v>
       </ns0:c>
       <ns0:c r="AJ29" t="str">
         <ns0:v>Стройматериалы</ns0:v>
@@ -6004,7 +6004,7 @@
       </ns0:c>
       <ns0:c r="AH30"/>
       <ns0:c r="AI30">
-        <ns0:v>3950</ns0:v>
+        <ns0:v>4900</ns0:v>
       </ns0:c>
       <ns0:c r="AJ30" t="str">
         <ns0:v>Стройматериалы</ns0:v>
@@ -6144,7 +6144,7 @@
       </ns0:c>
       <ns0:c r="AH31"/>
       <ns0:c r="AI31">
-        <ns0:v>3950</ns0:v>
+        <ns0:v>4900</ns0:v>
       </ns0:c>
       <ns0:c r="AJ31" t="str">
         <ns0:v>Стройматериалы</ns0:v>
@@ -6276,7 +6276,7 @@
       <ns0:c r="AG32"/>
       <ns0:c r="AH32"/>
       <ns0:c r="AI32">
-        <ns0:v>490</ns0:v>
+        <ns0:v>4900</ns0:v>
       </ns0:c>
       <ns0:c r="AJ32" t="str">
         <ns0:v>Стройматериалы</ns0:v>

--- a/avito.xlsx
+++ b/avito.xlsx
@@ -2533,7 +2533,7 @@
       </ns0:c>
       <ns0:c r="AH5"/>
       <ns0:c r="AI5">
-        <ns0:v>4900</ns0:v>
+        <ns0:v>3921</ns0:v>
       </ns0:c>
       <ns0:c r="AJ5" t="str">
         <ns0:v>Стройматериалы</ns0:v>
@@ -2670,7 +2670,7 @@
       </ns0:c>
       <ns0:c r="AH6"/>
       <ns0:c r="AI6">
-        <ns0:v>4900</ns0:v>
+        <ns0:v>3921</ns0:v>
       </ns0:c>
       <ns0:c r="AJ6" t="str">
         <ns0:v>Стройматериалы</ns0:v>
@@ -2807,7 +2807,7 @@
       </ns0:c>
       <ns0:c r="AH7"/>
       <ns0:c r="AI7">
-        <ns0:v>4900</ns0:v>
+        <ns0:v>3921</ns0:v>
       </ns0:c>
       <ns0:c r="AJ7" t="str">
         <ns0:v>Стройматериалы</ns0:v>
@@ -2944,7 +2944,7 @@
       </ns0:c>
       <ns0:c r="AH8"/>
       <ns0:c r="AI8">
-        <ns0:v>4900</ns0:v>
+        <ns0:v>3921</ns0:v>
       </ns0:c>
       <ns0:c r="AJ8" t="str">
         <ns0:v>Стройматериалы</ns0:v>
@@ -3081,7 +3081,7 @@
       </ns0:c>
       <ns0:c r="AH9"/>
       <ns0:c r="AI9">
-        <ns0:v>4900</ns0:v>
+        <ns0:v>3921</ns0:v>
       </ns0:c>
       <ns0:c r="AJ9" t="str">
         <ns0:v>Стройматериалы</ns0:v>
@@ -3218,7 +3218,7 @@
       </ns0:c>
       <ns0:c r="AH10"/>
       <ns0:c r="AI10">
-        <ns0:v>4900</ns0:v>
+        <ns0:v>3921</ns0:v>
       </ns0:c>
       <ns0:c r="AJ10" t="str">
         <ns0:v>Стройматериалы</ns0:v>
@@ -3355,7 +3355,7 @@
       </ns0:c>
       <ns0:c r="AH11"/>
       <ns0:c r="AI11">
-        <ns0:v>4900</ns0:v>
+        <ns0:v>3921</ns0:v>
       </ns0:c>
       <ns0:c r="AJ11" t="str">
         <ns0:v>Стройматериалы</ns0:v>
@@ -3492,7 +3492,7 @@
       </ns0:c>
       <ns0:c r="AH12"/>
       <ns0:c r="AI12">
-        <ns0:v>4900</ns0:v>
+        <ns0:v>3921</ns0:v>
       </ns0:c>
       <ns0:c r="AJ12" t="str">
         <ns0:v>Стройматериалы</ns0:v>
@@ -3629,7 +3629,7 @@
       </ns0:c>
       <ns0:c r="AH13"/>
       <ns0:c r="AI13">
-        <ns0:v>4900</ns0:v>
+        <ns0:v>3921</ns0:v>
       </ns0:c>
       <ns0:c r="AJ13" t="str">
         <ns0:v>Стройматериалы</ns0:v>
@@ -3766,7 +3766,7 @@
       </ns0:c>
       <ns0:c r="AH14"/>
       <ns0:c r="AI14">
-        <ns0:v>4900</ns0:v>
+        <ns0:v>3921</ns0:v>
       </ns0:c>
       <ns0:c r="AJ14" t="str">
         <ns0:v>Стройматериалы</ns0:v>
@@ -3904,7 +3904,7 @@
       </ns0:c>
       <ns0:c r="AH15"/>
       <ns0:c r="AI15">
-        <ns0:v>4900</ns0:v>
+        <ns0:v>3921</ns0:v>
       </ns0:c>
       <ns0:c r="AJ15" t="str">
         <ns0:v>Стройматериалы</ns0:v>
@@ -4044,7 +4044,7 @@
       </ns0:c>
       <ns0:c r="AH16"/>
       <ns0:c r="AI16">
-        <ns0:v>4900</ns0:v>
+        <ns0:v>3921</ns0:v>
       </ns0:c>
       <ns0:c r="AJ16" t="str">
         <ns0:v>Стройматериалы</ns0:v>
@@ -4184,7 +4184,7 @@
       </ns0:c>
       <ns0:c r="AH17"/>
       <ns0:c r="AI17">
-        <ns0:v>4900</ns0:v>
+        <ns0:v>3950</ns0:v>
       </ns0:c>
       <ns0:c r="AJ17" t="str">
         <ns0:v>Стройматериалы</ns0:v>
@@ -4324,7 +4324,7 @@
       </ns0:c>
       <ns0:c r="AH18"/>
       <ns0:c r="AI18">
-        <ns0:v>4900</ns0:v>
+        <ns0:v>3950</ns0:v>
       </ns0:c>
       <ns0:c r="AJ18" t="str">
         <ns0:v>Стройматериалы</ns0:v>
@@ -4464,7 +4464,7 @@
       </ns0:c>
       <ns0:c r="AH19"/>
       <ns0:c r="AI19">
-        <ns0:v>4900</ns0:v>
+        <ns0:v>3950</ns0:v>
       </ns0:c>
       <ns0:c r="AJ19" t="str">
         <ns0:v>Стройматериалы</ns0:v>
@@ -4604,7 +4604,7 @@
       </ns0:c>
       <ns0:c r="AH20"/>
       <ns0:c r="AI20">
-        <ns0:v>4900</ns0:v>
+        <ns0:v>3950</ns0:v>
       </ns0:c>
       <ns0:c r="AJ20" t="str">
         <ns0:v>Стройматериалы</ns0:v>
@@ -4744,7 +4744,7 @@
       </ns0:c>
       <ns0:c r="AH21"/>
       <ns0:c r="AI21">
-        <ns0:v>4900</ns0:v>
+        <ns0:v>3950</ns0:v>
       </ns0:c>
       <ns0:c r="AJ21" t="str">
         <ns0:v>Стройматериалы</ns0:v>
@@ -4884,7 +4884,7 @@
       </ns0:c>
       <ns0:c r="AH22"/>
       <ns0:c r="AI22">
-        <ns0:v>4900</ns0:v>
+        <ns0:v>3950</ns0:v>
       </ns0:c>
       <ns0:c r="AJ22" t="str">
         <ns0:v>Стройматериалы</ns0:v>
@@ -5024,7 +5024,7 @@
       </ns0:c>
       <ns0:c r="AH23"/>
       <ns0:c r="AI23">
-        <ns0:v>4900</ns0:v>
+        <ns0:v>3950</ns0:v>
       </ns0:c>
       <ns0:c r="AJ23" t="str">
         <ns0:v>Стройматериалы</ns0:v>
@@ -5164,7 +5164,7 @@
       </ns0:c>
       <ns0:c r="AH24"/>
       <ns0:c r="AI24">
-        <ns0:v>4900</ns0:v>
+        <ns0:v>3950</ns0:v>
       </ns0:c>
       <ns0:c r="AJ24" t="str">
         <ns0:v>Стройматериалы</ns0:v>
@@ -5304,7 +5304,7 @@
       </ns0:c>
       <ns0:c r="AH25"/>
       <ns0:c r="AI25">
-        <ns0:v>4900</ns0:v>
+        <ns0:v>3950</ns0:v>
       </ns0:c>
       <ns0:c r="AJ25" t="str">
         <ns0:v>Стройматериалы</ns0:v>
@@ -5444,7 +5444,7 @@
       </ns0:c>
       <ns0:c r="AH26"/>
       <ns0:c r="AI26">
-        <ns0:v>4900</ns0:v>
+        <ns0:v>3950</ns0:v>
       </ns0:c>
       <ns0:c r="AJ26" t="str">
         <ns0:v>Стройматериалы</ns0:v>
@@ -5584,7 +5584,7 @@
       </ns0:c>
       <ns0:c r="AH27"/>
       <ns0:c r="AI27">
-        <ns0:v>4900</ns0:v>
+        <ns0:v>3950</ns0:v>
       </ns0:c>
       <ns0:c r="AJ27" t="str">
         <ns0:v>Стройматериалы</ns0:v>
@@ -5724,7 +5724,7 @@
       </ns0:c>
       <ns0:c r="AH28"/>
       <ns0:c r="AI28">
-        <ns0:v>4900</ns0:v>
+        <ns0:v>3950</ns0:v>
       </ns0:c>
       <ns0:c r="AJ28" t="str">
         <ns0:v>Стройматериалы</ns0:v>
@@ -5864,7 +5864,7 @@
       </ns0:c>
       <ns0:c r="AH29"/>
       <ns0:c r="AI29">
-        <ns0:v>4900</ns0:v>
+        <ns0:v>3950</ns0:v>
       </ns0:c>
       <ns0:c r="AJ29" t="str">
         <ns0:v>Стройматериалы</ns0:v>
@@ -6004,7 +6004,7 @@
       </ns0:c>
       <ns0:c r="AH30"/>
       <ns0:c r="AI30">
-        <ns0:v>4900</ns0:v>
+        <ns0:v>3950</ns0:v>
       </ns0:c>
       <ns0:c r="AJ30" t="str">
         <ns0:v>Стройматериалы</ns0:v>
@@ -6144,7 +6144,7 @@
       </ns0:c>
       <ns0:c r="AH31"/>
       <ns0:c r="AI31">
-        <ns0:v>4900</ns0:v>
+        <ns0:v>3950</ns0:v>
       </ns0:c>
       <ns0:c r="AJ31" t="str">
         <ns0:v>Стройматериалы</ns0:v>
@@ -6276,7 +6276,7 @@
       <ns0:c r="AG32"/>
       <ns0:c r="AH32"/>
       <ns0:c r="AI32">
-        <ns0:v>4900</ns0:v>
+        <ns0:v>490</ns0:v>
       </ns0:c>
       <ns0:c r="AJ32" t="str">
         <ns0:v>Стройматериалы</ns0:v>
@@ -6329,6 +6329,2806 @@
       <ns0:c r="BD32"/>
       <ns0:c r="BE32"/>
       <ns0:c r="BF32"/>
+    </ns0:row>
+    <ns0:row r="33">
+      <ns0:c r="A33" t="inlineStr">
+        <ns0:is>
+          <ns0:t>adamar-vlg-ДУБ БЕЛЕНЫЙ</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="B33"/>
+      <ns0:c r="C33"/>
+      <ns0:c r="D33"/>
+      <ns0:c r="E33"/>
+      <ns0:c r="F33"/>
+      <ns0:c r="G33" t="str">
+        <ns0:v>Adamar Group</ns0:v>
+      </ns0:c>
+      <ns0:c r="H33" t="str">
+        <ns0:v>79996244489</ns0:v>
+      </ns0:c>
+      <ns0:c r="I33" t="inlineStr">
+        <ns0:is>
+          <ns0:t>Гибкий мрамор 114х280 см — ДУБ БЕЛЕНЫЙ</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="J33" t="inlineStr">
+        <ns0:is>
+          <ns0:t xml:space="preserve">Гибкий мрамор «ДУБ БЕЛЕНЫЙ» — выразительная отделка для современного интерьера ✨
+Это широкоформатные панели 114×280 см, которые также называют гибким камнем и микрокальцитными панелями. Материал подходит для кухни, ванной, прихожей, гостиной, офиса и коммерческих помещений. Панели легко режутся и быстро монтируются на прочное основание.
+✅ Есть в наличии в Волгограде.
+🤝 Дилерам и монтажным бригадам предоставляем специальные скидки.
+📍 Приходите в шоурум: ТЦ «Новосрой», 2 этаж, г. Волгоград, ул. 25-летия Октября, д. 1, стр. 3. Посмотрите декоры вживую и получите расчёт количества панелей.</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="K33" t="inlineStr">
+        <ns0:is>
+          <ns0:t>https://avatars.mds.yandex.net/get-yastore/21044143/9vjbw4hhj7cjqzcb4qwft87tm7bdlb5d/orig | https://avatars.mds.yandex.net/get-yastore/20918687/lfck5pdxflgh5jxjvhj59x6584zgqtrd/orig | https://avatars.mds.yandex.net/get-yastore/20918687/4nxrrq9q62cwnv68swfhtmk546k8ktrl/orig</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="L33"/>
+      <ns0:c r="M33" t="str">
+        <ns0:v>По телефону и в сообщениях</ns0:v>
+      </ns0:c>
+      <ns0:c r="N33"/>
+      <ns0:c r="O33"/>
+      <ns0:c r="P33"/>
+      <ns0:c r="Q33" t="str">
+        <ns0:v>Ремонт и строительство</ns0:v>
+      </ns0:c>
+      <ns0:c r="R33" t="inlineStr">
+        <ns0:is>
+          <ns0:t>г. Волгоград, ул. 25-летия Октября, д. 1, стр. 3</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="S33"/>
+      <ns0:c r="T33"/>
+      <ns0:c r="U33"/>
+      <ns0:c r="V33" t="str">
+        <ns0:v>Поштучно</ns0:v>
+      </ns0:c>
+      <ns0:c r="W33">
+        <ns0:v>200</ns0:v>
+      </ns0:c>
+      <ns0:c r="X33" t="n">
+        <ns0:v>1</ns0:v>
+      </ns0:c>
+      <ns0:c r="Y33" t="n">
+        <ns0:v>1</ns0:v>
+      </ns0:c>
+      <ns0:c r="Z33" t="str">
+        <ns0:v>Штуку</ns0:v>
+      </ns0:c>
+      <ns0:c r="AA33"/>
+      <ns0:c r="AB33"/>
+      <ns0:c r="AC33"/>
+      <ns0:c r="AD33">
+        <ns0:v>6.5</ns0:v>
+      </ns0:c>
+      <ns0:c r="AE33">
+        <ns0:v>15</ns0:v>
+      </ns0:c>
+      <ns0:c r="AF33">
+        <ns0:v>120</ns0:v>
+      </ns0:c>
+      <ns0:c r="AG33">
+        <ns0:v>15</ns0:v>
+      </ns0:c>
+      <ns0:c r="AH33"/>
+      <ns0:c r="AI33">
+        <ns0:v>4900</ns0:v>
+      </ns0:c>
+      <ns0:c r="AJ33" t="str">
+        <ns0:v>Стройматериалы</ns0:v>
+      </ns0:c>
+      <ns0:c r="AK33" t="str">
+        <ns0:v>Товар от производителя</ns0:v>
+      </ns0:c>
+      <ns0:c r="AL33" t="str">
+        <ns0:v>Новое</ns0:v>
+      </ns0:c>
+      <ns0:c r="AM33" t="inlineStr">
+        <ns0:is>
+          <ns0:t>В наличии</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="AN33" t="str">
+        <ns0:v>Отделка</ns0:v>
+      </ns0:c>
+      <ns0:c r="AO33"/>
+      <ns0:c r="AP33" t="str">
+        <ns0:v>Стеновые панели, рейки и элементы декора</ns0:v>
+      </ns0:c>
+      <ns0:c r="AQ33" t="str">
+        <ns0:v>Стеновые панели</ns0:v>
+      </ns0:c>
+      <ns0:c r="AR33" t="str">
+        <ns0:v>ПВХ</ns0:v>
+      </ns0:c>
+      <ns0:c r="AS33" t="str">
+        <ns0:v>Стены | Двери</ns0:v>
+      </ns0:c>
+      <ns0:c r="AT33" t="str">
+        <ns0:v>Нет</ns0:v>
+      </ns0:c>
+      <ns0:c r="AU33" t="n">
+        <ns0:v>2800</ns0:v>
+      </ns0:c>
+      <ns0:c r="AV33" t="n">
+        <ns0:v>1140</ns0:v>
+      </ns0:c>
+      <ns0:c r="AW33"/>
+      <ns0:c r="AX33" t="str">
+        <ns0:v>Нет</ns0:v>
+      </ns0:c>
+      <ns0:c r="AY33"/>
+      <ns0:c r="AZ33"/>
+      <ns0:c r="BA33"/>
+      <ns0:c r="BB33"/>
+      <ns0:c r="BC33"/>
+      <ns0:c r="BD33"/>
+      <ns0:c r="BE33"/>
+      <ns0:c r="BF33"/>
+    </ns0:row>
+    <ns0:row r="34">
+      <ns0:c r="A34" t="inlineStr">
+        <ns0:is>
+          <ns0:t>adamar-vlg-FONDAMENTO BLUE</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="B34"/>
+      <ns0:c r="C34"/>
+      <ns0:c r="D34"/>
+      <ns0:c r="E34"/>
+      <ns0:c r="F34"/>
+      <ns0:c r="G34" t="str">
+        <ns0:v>Adamar Group</ns0:v>
+      </ns0:c>
+      <ns0:c r="H34" t="str">
+        <ns0:v>79996244489</ns0:v>
+      </ns0:c>
+      <ns0:c r="I34" t="inlineStr">
+        <ns0:is>
+          <ns0:t>Гибкий мрамор 114х280 см — FONDAMENTO BLUE</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="J34" t="inlineStr">
+        <ns0:is>
+          <ns0:t xml:space="preserve">Гибкий мрамор «FONDAMENTO BLUE» — выразительная отделка для современного интерьера ✨
+Это широкоформатные панели 114×280 см, которые также называют гибким камнем и микрокальцитными панелями. Материал подходит для кухни, ванной, прихожей, гостиной, офиса и коммерческих помещений. Панели легко режутся и быстро монтируются на прочное основание.
+✅ Есть в наличии в Волгограде.
+🤝 Дилерам и монтажным бригадам предоставляем специальные скидки.
+📍 Приходите в шоурум: ТЦ «Новосрой», 2 этаж, г. Волгоград, ул. 25-летия Октября, д. 1, стр. 3. Посмотрите декоры вживую и получите расчёт количества панелей.</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="K34" t="inlineStr">
+        <ns0:is>
+          <ns0:t>https://avatars.mds.yandex.net/get-yastore/20760651/znswqj9q9pd95zkm6477mrhc86wgbxkf/orig | https://avatars.mds.yandex.net/get-yastore/20760651/k9tgsvwpl7fdnkgqnzmfscrrvfxrff2j/orig | https://avatars.mds.yandex.net/get-yastore/21104660/w28jjl9k4mbx5rz2hf4j9cf7rttmjpwh/orig | https://avatars.mds.yandex.net/get-yastore/20760651/gmb7ddls4m2mwzk8blt4rgchgfn9ntp2/orig</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="L34"/>
+      <ns0:c r="M34" t="str">
+        <ns0:v>По телефону и в сообщениях</ns0:v>
+      </ns0:c>
+      <ns0:c r="N34"/>
+      <ns0:c r="O34"/>
+      <ns0:c r="P34"/>
+      <ns0:c r="Q34" t="str">
+        <ns0:v>Ремонт и строительство</ns0:v>
+      </ns0:c>
+      <ns0:c r="R34" t="inlineStr">
+        <ns0:is>
+          <ns0:t>г. Волгоград, ул. 25-летия Октября, д. 1, стр. 3</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="S34"/>
+      <ns0:c r="T34"/>
+      <ns0:c r="U34"/>
+      <ns0:c r="V34" t="str">
+        <ns0:v>Поштучно</ns0:v>
+      </ns0:c>
+      <ns0:c r="W34">
+        <ns0:v>200</ns0:v>
+      </ns0:c>
+      <ns0:c r="X34" t="n">
+        <ns0:v>1</ns0:v>
+      </ns0:c>
+      <ns0:c r="Y34" t="n">
+        <ns0:v>1</ns0:v>
+      </ns0:c>
+      <ns0:c r="Z34" t="str">
+        <ns0:v>Штуку</ns0:v>
+      </ns0:c>
+      <ns0:c r="AA34"/>
+      <ns0:c r="AB34"/>
+      <ns0:c r="AC34"/>
+      <ns0:c r="AD34">
+        <ns0:v>6.5</ns0:v>
+      </ns0:c>
+      <ns0:c r="AE34">
+        <ns0:v>15</ns0:v>
+      </ns0:c>
+      <ns0:c r="AF34">
+        <ns0:v>120</ns0:v>
+      </ns0:c>
+      <ns0:c r="AG34">
+        <ns0:v>15</ns0:v>
+      </ns0:c>
+      <ns0:c r="AH34"/>
+      <ns0:c r="AI34">
+        <ns0:v>4900</ns0:v>
+      </ns0:c>
+      <ns0:c r="AJ34" t="str">
+        <ns0:v>Стройматериалы</ns0:v>
+      </ns0:c>
+      <ns0:c r="AK34" t="str">
+        <ns0:v>Товар от производителя</ns0:v>
+      </ns0:c>
+      <ns0:c r="AL34" t="str">
+        <ns0:v>Новое</ns0:v>
+      </ns0:c>
+      <ns0:c r="AM34" t="inlineStr">
+        <ns0:is>
+          <ns0:t>В наличии</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="AN34" t="str">
+        <ns0:v>Отделка</ns0:v>
+      </ns0:c>
+      <ns0:c r="AO34"/>
+      <ns0:c r="AP34" t="str">
+        <ns0:v>Стеновые панели, рейки и элементы декора</ns0:v>
+      </ns0:c>
+      <ns0:c r="AQ34" t="str">
+        <ns0:v>Стеновые панели</ns0:v>
+      </ns0:c>
+      <ns0:c r="AR34" t="str">
+        <ns0:v>ПВХ</ns0:v>
+      </ns0:c>
+      <ns0:c r="AS34" t="str">
+        <ns0:v>Стены | Двери</ns0:v>
+      </ns0:c>
+      <ns0:c r="AT34" t="str">
+        <ns0:v>Нет</ns0:v>
+      </ns0:c>
+      <ns0:c r="AU34" t="n">
+        <ns0:v>2800</ns0:v>
+      </ns0:c>
+      <ns0:c r="AV34" t="n">
+        <ns0:v>1140</ns0:v>
+      </ns0:c>
+      <ns0:c r="AW34"/>
+      <ns0:c r="AX34" t="str">
+        <ns0:v>Нет</ns0:v>
+      </ns0:c>
+      <ns0:c r="AY34"/>
+      <ns0:c r="AZ34"/>
+      <ns0:c r="BA34"/>
+      <ns0:c r="BB34"/>
+      <ns0:c r="BC34"/>
+      <ns0:c r="BD34"/>
+      <ns0:c r="BE34"/>
+      <ns0:c r="BF34"/>
+    </ns0:row>
+    <ns0:row r="35">
+      <ns0:c r="A35" t="inlineStr">
+        <ns0:is>
+          <ns0:t>adamar-vlg-Glossy_MARBLE_FLORENCE</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="B35"/>
+      <ns0:c r="C35"/>
+      <ns0:c r="D35"/>
+      <ns0:c r="E35"/>
+      <ns0:c r="F35"/>
+      <ns0:c r="G35" t="str">
+        <ns0:v>Adamar Group</ns0:v>
+      </ns0:c>
+      <ns0:c r="H35" t="str">
+        <ns0:v>79996244489</ns0:v>
+      </ns0:c>
+      <ns0:c r="I35" t="inlineStr">
+        <ns0:is>
+          <ns0:t>Гибкий мрамор 114х280 см — Glossy MARBLE FLORENCE</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="J35" t="inlineStr">
+        <ns0:is>
+          <ns0:t xml:space="preserve">Гибкий мрамор «Glossy MARBLE FLORENCE» — выразительная отделка для современного интерьера ✨
+Это широкоформатные панели 114×280 см, которые также называют гибким камнем и микрокальцитными панелями. Материал подходит для кухни, ванной, прихожей, гостиной, офиса и коммерческих помещений. Панели легко режутся и быстро монтируются на прочное основание.
+✅ Есть в наличии в Волгограде.
+🤝 Дилерам и монтажным бригадам предоставляем специальные скидки.
+📍 Приходите в шоурум: ТЦ «Новосрой», 2 этаж, г. Волгоград, ул. 25-летия Октября, д. 1, стр. 3. Посмотрите декоры вживую и получите расчёт количества панелей.</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="K35" t="inlineStr">
+        <ns0:is>
+          <ns0:t>https://avatars.mds.yandex.net/get-yastore/20760651/bjcwtcqtz6kcrwlg45pc2zv4sc4tmzr4/orig | https://avatars.mds.yandex.net/get-yastore/21069123/gt8fs88vhfp7c4p897jqvfbp8vjfdgq8/orig | https://avatars.mds.yandex.net/get-yastore/21069123/kkd64w7s64tbxd9f4jmbdtl42krkxqr6/orig | https://avatars.mds.yandex.net/get-yastore/16104656/8rjb7dc2wxpbw6fpcz9b9n8g6lcs2q9v/orig</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="L35"/>
+      <ns0:c r="M35" t="str">
+        <ns0:v>По телефону и в сообщениях</ns0:v>
+      </ns0:c>
+      <ns0:c r="N35"/>
+      <ns0:c r="O35"/>
+      <ns0:c r="P35"/>
+      <ns0:c r="Q35" t="str">
+        <ns0:v>Ремонт и строительство</ns0:v>
+      </ns0:c>
+      <ns0:c r="R35" t="inlineStr">
+        <ns0:is>
+          <ns0:t>г. Волгоград, ул. 25-летия Октября, д. 1, стр. 3</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="S35"/>
+      <ns0:c r="T35"/>
+      <ns0:c r="U35"/>
+      <ns0:c r="V35" t="str">
+        <ns0:v>Поштучно</ns0:v>
+      </ns0:c>
+      <ns0:c r="W35">
+        <ns0:v>200</ns0:v>
+      </ns0:c>
+      <ns0:c r="X35" t="n">
+        <ns0:v>1</ns0:v>
+      </ns0:c>
+      <ns0:c r="Y35" t="n">
+        <ns0:v>1</ns0:v>
+      </ns0:c>
+      <ns0:c r="Z35" t="str">
+        <ns0:v>Штуку</ns0:v>
+      </ns0:c>
+      <ns0:c r="AA35"/>
+      <ns0:c r="AB35"/>
+      <ns0:c r="AC35"/>
+      <ns0:c r="AD35">
+        <ns0:v>6.5</ns0:v>
+      </ns0:c>
+      <ns0:c r="AE35">
+        <ns0:v>15</ns0:v>
+      </ns0:c>
+      <ns0:c r="AF35">
+        <ns0:v>120</ns0:v>
+      </ns0:c>
+      <ns0:c r="AG35">
+        <ns0:v>15</ns0:v>
+      </ns0:c>
+      <ns0:c r="AH35"/>
+      <ns0:c r="AI35">
+        <ns0:v>4900</ns0:v>
+      </ns0:c>
+      <ns0:c r="AJ35" t="str">
+        <ns0:v>Стройматериалы</ns0:v>
+      </ns0:c>
+      <ns0:c r="AK35" t="str">
+        <ns0:v>Товар от производителя</ns0:v>
+      </ns0:c>
+      <ns0:c r="AL35" t="str">
+        <ns0:v>Новое</ns0:v>
+      </ns0:c>
+      <ns0:c r="AM35" t="inlineStr">
+        <ns0:is>
+          <ns0:t>В наличии</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="AN35" t="str">
+        <ns0:v>Отделка</ns0:v>
+      </ns0:c>
+      <ns0:c r="AO35"/>
+      <ns0:c r="AP35" t="str">
+        <ns0:v>Стеновые панели, рейки и элементы декора</ns0:v>
+      </ns0:c>
+      <ns0:c r="AQ35" t="str">
+        <ns0:v>Стеновые панели</ns0:v>
+      </ns0:c>
+      <ns0:c r="AR35" t="str">
+        <ns0:v>ПВХ</ns0:v>
+      </ns0:c>
+      <ns0:c r="AS35" t="str">
+        <ns0:v>Стены | Двери</ns0:v>
+      </ns0:c>
+      <ns0:c r="AT35" t="str">
+        <ns0:v>Нет</ns0:v>
+      </ns0:c>
+      <ns0:c r="AU35" t="n">
+        <ns0:v>2800</ns0:v>
+      </ns0:c>
+      <ns0:c r="AV35" t="n">
+        <ns0:v>1140</ns0:v>
+      </ns0:c>
+      <ns0:c r="AW35"/>
+      <ns0:c r="AX35" t="str">
+        <ns0:v>Нет</ns0:v>
+      </ns0:c>
+      <ns0:c r="AY35"/>
+      <ns0:c r="AZ35"/>
+      <ns0:c r="BA35"/>
+      <ns0:c r="BB35"/>
+      <ns0:c r="BC35"/>
+      <ns0:c r="BD35"/>
+      <ns0:c r="BE35"/>
+      <ns0:c r="BF35"/>
+    </ns0:row>
+    <ns0:row r="36">
+      <ns0:c r="A36" t="inlineStr">
+        <ns0:is>
+          <ns0:t>adamar-vlg-SKY</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="B36"/>
+      <ns0:c r="C36"/>
+      <ns0:c r="D36"/>
+      <ns0:c r="E36"/>
+      <ns0:c r="F36"/>
+      <ns0:c r="G36" t="str">
+        <ns0:v>Adamar Group</ns0:v>
+      </ns0:c>
+      <ns0:c r="H36" t="str">
+        <ns0:v>79996244489</ns0:v>
+      </ns0:c>
+      <ns0:c r="I36" t="inlineStr">
+        <ns0:is>
+          <ns0:t>Гибкий мрамор 114х280 см — SKY</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="J36" t="inlineStr">
+        <ns0:is>
+          <ns0:t xml:space="preserve">Гибкий мрамор «SKY» — выразительная отделка для современного интерьера ✨
+Это широкоформатные панели 114×280 см, которые также называют гибким камнем и микрокальцитными панелями. Материал подходит для кухни, ванной, прихожей, гостиной, офиса и коммерческих помещений. Панели легко режутся и быстро монтируются на прочное основание.
+✅ Есть в наличии в Волгограде.
+🤝 Дилерам и монтажным бригадам предоставляем специальные скидки.
+📍 Приходите в шоурум: ТЦ «Новосрой», 2 этаж, г. Волгоград, ул. 25-летия Октября, д. 1, стр. 3. Посмотрите декоры вживую и получите расчёт количества панелей.</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="K36" t="inlineStr">
+        <ns0:is>
+          <ns0:t>https://avatars.mds.yandex.net/get-yastore/20760651/v6dqzkbdpvjbhxhnwnxzdvnddd9w68pf/orig | https://avatars.mds.yandex.net/get-yastore/21104660/9cq7lxgsc2dgcmrzkxrbs4dwcbkhfv6s/orig | https://avatars.mds.yandex.net/get-yastore/21104660/gjvvs4vfb7b54s9trbvmxbt8468l2fft/orig | https://avatars.mds.yandex.net/get-yastore/21104660/gcbxfclzcc76zrlhdk68qrjqd8qz9772/orig</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="L36"/>
+      <ns0:c r="M36" t="str">
+        <ns0:v>По телефону и в сообщениях</ns0:v>
+      </ns0:c>
+      <ns0:c r="N36"/>
+      <ns0:c r="O36"/>
+      <ns0:c r="P36"/>
+      <ns0:c r="Q36" t="str">
+        <ns0:v>Ремонт и строительство</ns0:v>
+      </ns0:c>
+      <ns0:c r="R36" t="inlineStr">
+        <ns0:is>
+          <ns0:t>г. Волгоград, ул. 25-летия Октября, д. 1, стр. 3</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="S36"/>
+      <ns0:c r="T36"/>
+      <ns0:c r="U36"/>
+      <ns0:c r="V36" t="str">
+        <ns0:v>Поштучно</ns0:v>
+      </ns0:c>
+      <ns0:c r="W36">
+        <ns0:v>200</ns0:v>
+      </ns0:c>
+      <ns0:c r="X36" t="n">
+        <ns0:v>1</ns0:v>
+      </ns0:c>
+      <ns0:c r="Y36" t="n">
+        <ns0:v>1</ns0:v>
+      </ns0:c>
+      <ns0:c r="Z36" t="str">
+        <ns0:v>Штуку</ns0:v>
+      </ns0:c>
+      <ns0:c r="AA36"/>
+      <ns0:c r="AB36"/>
+      <ns0:c r="AC36"/>
+      <ns0:c r="AD36">
+        <ns0:v>6.5</ns0:v>
+      </ns0:c>
+      <ns0:c r="AE36">
+        <ns0:v>15</ns0:v>
+      </ns0:c>
+      <ns0:c r="AF36">
+        <ns0:v>120</ns0:v>
+      </ns0:c>
+      <ns0:c r="AG36">
+        <ns0:v>15</ns0:v>
+      </ns0:c>
+      <ns0:c r="AH36"/>
+      <ns0:c r="AI36">
+        <ns0:v>4900</ns0:v>
+      </ns0:c>
+      <ns0:c r="AJ36" t="str">
+        <ns0:v>Стройматериалы</ns0:v>
+      </ns0:c>
+      <ns0:c r="AK36" t="str">
+        <ns0:v>Товар от производителя</ns0:v>
+      </ns0:c>
+      <ns0:c r="AL36" t="str">
+        <ns0:v>Новое</ns0:v>
+      </ns0:c>
+      <ns0:c r="AM36" t="inlineStr">
+        <ns0:is>
+          <ns0:t>В наличии</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="AN36" t="str">
+        <ns0:v>Отделка</ns0:v>
+      </ns0:c>
+      <ns0:c r="AO36"/>
+      <ns0:c r="AP36" t="str">
+        <ns0:v>Стеновые панели, рейки и элементы декора</ns0:v>
+      </ns0:c>
+      <ns0:c r="AQ36" t="str">
+        <ns0:v>Стеновые панели</ns0:v>
+      </ns0:c>
+      <ns0:c r="AR36" t="str">
+        <ns0:v>ПВХ</ns0:v>
+      </ns0:c>
+      <ns0:c r="AS36" t="str">
+        <ns0:v>Стены | Двери</ns0:v>
+      </ns0:c>
+      <ns0:c r="AT36" t="str">
+        <ns0:v>Нет</ns0:v>
+      </ns0:c>
+      <ns0:c r="AU36" t="n">
+        <ns0:v>2800</ns0:v>
+      </ns0:c>
+      <ns0:c r="AV36" t="n">
+        <ns0:v>1140</ns0:v>
+      </ns0:c>
+      <ns0:c r="AW36"/>
+      <ns0:c r="AX36" t="str">
+        <ns0:v>Нет</ns0:v>
+      </ns0:c>
+      <ns0:c r="AY36"/>
+      <ns0:c r="AZ36"/>
+      <ns0:c r="BA36"/>
+      <ns0:c r="BB36"/>
+      <ns0:c r="BC36"/>
+      <ns0:c r="BD36"/>
+      <ns0:c r="BE36"/>
+      <ns0:c r="BF36"/>
+    </ns0:row>
+    <ns0:row r="37">
+      <ns0:c r="A37" t="inlineStr">
+        <ns0:is>
+          <ns0:t>adamar-vlg-SCRIBBLE GRAY</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="B37"/>
+      <ns0:c r="C37"/>
+      <ns0:c r="D37"/>
+      <ns0:c r="E37"/>
+      <ns0:c r="F37"/>
+      <ns0:c r="G37" t="str">
+        <ns0:v>Adamar Group</ns0:v>
+      </ns0:c>
+      <ns0:c r="H37" t="str">
+        <ns0:v>79996244489</ns0:v>
+      </ns0:c>
+      <ns0:c r="I37" t="inlineStr">
+        <ns0:is>
+          <ns0:t>Гибкий мрамор 114х280 см — SCRIBBLE GRAY</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="J37" t="inlineStr">
+        <ns0:is>
+          <ns0:t xml:space="preserve">Гибкий мрамор «SCRIBBLE GRAY» — выразительная отделка для современного интерьера ✨
+Это широкоформатные панели 114×280 см, которые также называют гибким камнем и микрокальцитными панелями. Материал подходит для кухни, ванной, прихожей, гостиной, офиса и коммерческих помещений. Панели легко режутся и быстро монтируются на прочное основание.
+✅ Есть в наличии в Волгограде.
+🤝 Дилерам и монтажным бригадам предоставляем специальные скидки.
+📍 Приходите в шоурум: ТЦ «Новосрой», 2 этаж, г. Волгоград, ул. 25-летия Октября, д. 1, стр. 3. Посмотрите декоры вживую и получите расчёт количества панелей.</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="K37" t="inlineStr">
+        <ns0:is>
+          <ns0:t>https://avatars.mds.yandex.net/get-yastore/21055393/9kkt59pv4mdn66w5bq7ts4s5s2zwvdcl/orig | https://avatars.mds.yandex.net/get-yastore/21055393/v89g7vkm4fpkcph8q5576xhg95kcchld/orig | https://avatars.mds.yandex.net/get-yastore/20918687/jfwnzj7czzdm72hsftfvfk5pzpwnjj2b/orig | https://avatars.mds.yandex.net/get-yastore/21055393/bk2tdvhntmz7zl25g9pzsxx2clkzxmwx/orig</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="L37"/>
+      <ns0:c r="M37" t="str">
+        <ns0:v>По телефону и в сообщениях</ns0:v>
+      </ns0:c>
+      <ns0:c r="N37"/>
+      <ns0:c r="O37"/>
+      <ns0:c r="P37"/>
+      <ns0:c r="Q37" t="str">
+        <ns0:v>Ремонт и строительство</ns0:v>
+      </ns0:c>
+      <ns0:c r="R37" t="inlineStr">
+        <ns0:is>
+          <ns0:t>г. Волгоград, ул. 25-летия Октября, д. 1, стр. 3</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="S37"/>
+      <ns0:c r="T37"/>
+      <ns0:c r="U37"/>
+      <ns0:c r="V37" t="str">
+        <ns0:v>Поштучно</ns0:v>
+      </ns0:c>
+      <ns0:c r="W37">
+        <ns0:v>200</ns0:v>
+      </ns0:c>
+      <ns0:c r="X37" t="n">
+        <ns0:v>1</ns0:v>
+      </ns0:c>
+      <ns0:c r="Y37" t="n">
+        <ns0:v>1</ns0:v>
+      </ns0:c>
+      <ns0:c r="Z37" t="str">
+        <ns0:v>Штуку</ns0:v>
+      </ns0:c>
+      <ns0:c r="AA37"/>
+      <ns0:c r="AB37"/>
+      <ns0:c r="AC37"/>
+      <ns0:c r="AD37">
+        <ns0:v>6.5</ns0:v>
+      </ns0:c>
+      <ns0:c r="AE37">
+        <ns0:v>15</ns0:v>
+      </ns0:c>
+      <ns0:c r="AF37">
+        <ns0:v>120</ns0:v>
+      </ns0:c>
+      <ns0:c r="AG37">
+        <ns0:v>15</ns0:v>
+      </ns0:c>
+      <ns0:c r="AH37"/>
+      <ns0:c r="AI37">
+        <ns0:v>4900</ns0:v>
+      </ns0:c>
+      <ns0:c r="AJ37" t="str">
+        <ns0:v>Стройматериалы</ns0:v>
+      </ns0:c>
+      <ns0:c r="AK37" t="str">
+        <ns0:v>Товар от производителя</ns0:v>
+      </ns0:c>
+      <ns0:c r="AL37" t="str">
+        <ns0:v>Новое</ns0:v>
+      </ns0:c>
+      <ns0:c r="AM37" t="inlineStr">
+        <ns0:is>
+          <ns0:t>В наличии</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="AN37" t="str">
+        <ns0:v>Отделка</ns0:v>
+      </ns0:c>
+      <ns0:c r="AO37"/>
+      <ns0:c r="AP37" t="str">
+        <ns0:v>Стеновые панели, рейки и элементы декора</ns0:v>
+      </ns0:c>
+      <ns0:c r="AQ37" t="str">
+        <ns0:v>Стеновые панели</ns0:v>
+      </ns0:c>
+      <ns0:c r="AR37" t="str">
+        <ns0:v>ПВХ</ns0:v>
+      </ns0:c>
+      <ns0:c r="AS37" t="str">
+        <ns0:v>Стены | Двери</ns0:v>
+      </ns0:c>
+      <ns0:c r="AT37" t="str">
+        <ns0:v>Нет</ns0:v>
+      </ns0:c>
+      <ns0:c r="AU37" t="n">
+        <ns0:v>2800</ns0:v>
+      </ns0:c>
+      <ns0:c r="AV37" t="n">
+        <ns0:v>1140</ns0:v>
+      </ns0:c>
+      <ns0:c r="AW37"/>
+      <ns0:c r="AX37" t="str">
+        <ns0:v>Нет</ns0:v>
+      </ns0:c>
+      <ns0:c r="AY37"/>
+      <ns0:c r="AZ37"/>
+      <ns0:c r="BA37"/>
+      <ns0:c r="BB37"/>
+      <ns0:c r="BC37"/>
+      <ns0:c r="BD37"/>
+      <ns0:c r="BE37"/>
+      <ns0:c r="BF37"/>
+    </ns0:row>
+    <ns0:row r="38">
+      <ns0:c r="A38" t="inlineStr">
+        <ns0:is>
+          <ns0:t>adamar-vlg-OCEAN_1</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="B38"/>
+      <ns0:c r="C38"/>
+      <ns0:c r="D38"/>
+      <ns0:c r="E38"/>
+      <ns0:c r="F38"/>
+      <ns0:c r="G38" t="str">
+        <ns0:v>Adamar Group</ns0:v>
+      </ns0:c>
+      <ns0:c r="H38" t="str">
+        <ns0:v>79996244489</ns0:v>
+      </ns0:c>
+      <ns0:c r="I38" t="inlineStr">
+        <ns0:is>
+          <ns0:t>Гибкий мрамор 114х280 см — OCEAN 1</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="J38" t="inlineStr">
+        <ns0:is>
+          <ns0:t xml:space="preserve">Гибкий мрамор «OCEAN 1» — выразительная отделка для современного интерьера ✨
+Это широкоформатные панели 114×280 см, которые также называют гибким камнем и микрокальцитными панелями. Материал подходит для кухни, ванной, прихожей, гостиной, офиса и коммерческих помещений. Панели легко режутся и быстро монтируются на прочное основание.
+✅ Есть в наличии в Волгограде.
+🤝 Дилерам и монтажным бригадам предоставляем специальные скидки.
+📍 Приходите в шоурум: ТЦ «Новосрой», 2 этаж, г. Волгоград, ул. 25-летия Октября, д. 1, стр. 3. Посмотрите декоры вживую и получите расчёт количества панелей.</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="K38" t="inlineStr">
+        <ns0:is>
+          <ns0:t>https://avatars.mds.yandex.net/get-yastore/21012869/qqd2bp2fsxjqbqnm75kwbsq9mlkqjxtp/orig | https://avatars.mds.yandex.net/get-yastore/20274467/btsmj4xjltbnxvml826r8wxbrhhlzrxn/orig | https://avatars.mds.yandex.net/get-yastore/20760651/czxdrm24dr9plkqp6h8k9wt9fjjx2gn8/orig | https://avatars.mds.yandex.net/get-yastore/20274467/zkkls5t6wlljhblwjvwpr8tnbwwz2hxk/orig</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="L38"/>
+      <ns0:c r="M38" t="str">
+        <ns0:v>По телефону и в сообщениях</ns0:v>
+      </ns0:c>
+      <ns0:c r="N38"/>
+      <ns0:c r="O38"/>
+      <ns0:c r="P38"/>
+      <ns0:c r="Q38" t="str">
+        <ns0:v>Ремонт и строительство</ns0:v>
+      </ns0:c>
+      <ns0:c r="R38" t="inlineStr">
+        <ns0:is>
+          <ns0:t>г. Волгоград, ул. 25-летия Октября, д. 1, стр. 3</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="S38"/>
+      <ns0:c r="T38"/>
+      <ns0:c r="U38"/>
+      <ns0:c r="V38" t="str">
+        <ns0:v>Поштучно</ns0:v>
+      </ns0:c>
+      <ns0:c r="W38">
+        <ns0:v>200</ns0:v>
+      </ns0:c>
+      <ns0:c r="X38" t="n">
+        <ns0:v>1</ns0:v>
+      </ns0:c>
+      <ns0:c r="Y38" t="n">
+        <ns0:v>1</ns0:v>
+      </ns0:c>
+      <ns0:c r="Z38" t="str">
+        <ns0:v>Штуку</ns0:v>
+      </ns0:c>
+      <ns0:c r="AA38"/>
+      <ns0:c r="AB38"/>
+      <ns0:c r="AC38"/>
+      <ns0:c r="AD38">
+        <ns0:v>6.5</ns0:v>
+      </ns0:c>
+      <ns0:c r="AE38">
+        <ns0:v>15</ns0:v>
+      </ns0:c>
+      <ns0:c r="AF38">
+        <ns0:v>120</ns0:v>
+      </ns0:c>
+      <ns0:c r="AG38">
+        <ns0:v>15</ns0:v>
+      </ns0:c>
+      <ns0:c r="AH38"/>
+      <ns0:c r="AI38">
+        <ns0:v>4900</ns0:v>
+      </ns0:c>
+      <ns0:c r="AJ38" t="str">
+        <ns0:v>Стройматериалы</ns0:v>
+      </ns0:c>
+      <ns0:c r="AK38" t="str">
+        <ns0:v>Товар от производителя</ns0:v>
+      </ns0:c>
+      <ns0:c r="AL38" t="str">
+        <ns0:v>Новое</ns0:v>
+      </ns0:c>
+      <ns0:c r="AM38" t="inlineStr">
+        <ns0:is>
+          <ns0:t>В наличии</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="AN38" t="str">
+        <ns0:v>Отделка</ns0:v>
+      </ns0:c>
+      <ns0:c r="AO38"/>
+      <ns0:c r="AP38" t="str">
+        <ns0:v>Стеновые панели, рейки и элементы декора</ns0:v>
+      </ns0:c>
+      <ns0:c r="AQ38" t="str">
+        <ns0:v>Стеновые панели</ns0:v>
+      </ns0:c>
+      <ns0:c r="AR38" t="str">
+        <ns0:v>ПВХ</ns0:v>
+      </ns0:c>
+      <ns0:c r="AS38" t="str">
+        <ns0:v>Стены | Двери</ns0:v>
+      </ns0:c>
+      <ns0:c r="AT38" t="str">
+        <ns0:v>Нет</ns0:v>
+      </ns0:c>
+      <ns0:c r="AU38" t="n">
+        <ns0:v>2800</ns0:v>
+      </ns0:c>
+      <ns0:c r="AV38" t="n">
+        <ns0:v>1140</ns0:v>
+      </ns0:c>
+      <ns0:c r="AW38"/>
+      <ns0:c r="AX38" t="str">
+        <ns0:v>Нет</ns0:v>
+      </ns0:c>
+      <ns0:c r="AY38"/>
+      <ns0:c r="AZ38"/>
+      <ns0:c r="BA38"/>
+      <ns0:c r="BB38"/>
+      <ns0:c r="BC38"/>
+      <ns0:c r="BD38"/>
+      <ns0:c r="BE38"/>
+      <ns0:c r="BF38"/>
+    </ns0:row>
+    <ns0:row r="39">
+      <ns0:c r="A39" t="inlineStr">
+        <ns0:is>
+          <ns0:t>adamar-vlg-Gerda_1</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="B39"/>
+      <ns0:c r="C39"/>
+      <ns0:c r="D39"/>
+      <ns0:c r="E39"/>
+      <ns0:c r="F39"/>
+      <ns0:c r="G39" t="str">
+        <ns0:v>Adamar Group</ns0:v>
+      </ns0:c>
+      <ns0:c r="H39" t="str">
+        <ns0:v>79996244489</ns0:v>
+      </ns0:c>
+      <ns0:c r="I39" t="inlineStr">
+        <ns0:is>
+          <ns0:t>Гибкий мрамор 114х280 см — Gerda 1</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="J39" t="inlineStr">
+        <ns0:is>
+          <ns0:t xml:space="preserve">Гибкий мрамор «Gerda 1» — выразительная отделка для современного интерьера ✨
+Это широкоформатные панели 114×280 см, которые также называют гибким камнем и микрокальцитными панелями. Материал подходит для кухни, ванной, прихожей, гостиной, офиса и коммерческих помещений. Панели легко режутся и быстро монтируются на прочное основание.
+✅ Есть в наличии в Волгограде.
+🤝 Дилерам и монтажным бригадам предоставляем специальные скидки.
+📍 Приходите в шоурум: ТЦ «Новосрой», 2 этаж, г. Волгоград, ул. 25-летия Октября, д. 1, стр. 3. Посмотрите декоры вживую и получите расчёт количества панелей.</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="K39" t="inlineStr">
+        <ns0:is>
+          <ns0:t>https://avatars.mds.yandex.net/get-yastore/20274467/vgf9tn8bz9zf6bvf79jwttbd8lgvrl87/orig | https://avatars.mds.yandex.net/get-yastore/20274467/86nfrzr9gmk4ct8c62pbk282lclqmrpg/orig | https://avatars.mds.yandex.net/get-yastore/20274467/grkksnr7rlmv9445rwt5prw2ht2hbc8p/orig | https://avatars.mds.yandex.net/get-yastore/20274467/lp2jlgpz7wv6nds9crs9pcslw4rgrwfv/orig</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="L39"/>
+      <ns0:c r="M39" t="str">
+        <ns0:v>По телефону и в сообщениях</ns0:v>
+      </ns0:c>
+      <ns0:c r="N39"/>
+      <ns0:c r="O39"/>
+      <ns0:c r="P39"/>
+      <ns0:c r="Q39" t="str">
+        <ns0:v>Ремонт и строительство</ns0:v>
+      </ns0:c>
+      <ns0:c r="R39" t="inlineStr">
+        <ns0:is>
+          <ns0:t>г. Волгоград, ул. 25-летия Октября, д. 1, стр. 3</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="S39"/>
+      <ns0:c r="T39"/>
+      <ns0:c r="U39"/>
+      <ns0:c r="V39" t="str">
+        <ns0:v>Поштучно</ns0:v>
+      </ns0:c>
+      <ns0:c r="W39">
+        <ns0:v>200</ns0:v>
+      </ns0:c>
+      <ns0:c r="X39" t="n">
+        <ns0:v>1</ns0:v>
+      </ns0:c>
+      <ns0:c r="Y39" t="n">
+        <ns0:v>1</ns0:v>
+      </ns0:c>
+      <ns0:c r="Z39" t="str">
+        <ns0:v>Штуку</ns0:v>
+      </ns0:c>
+      <ns0:c r="AA39"/>
+      <ns0:c r="AB39"/>
+      <ns0:c r="AC39"/>
+      <ns0:c r="AD39">
+        <ns0:v>6.5</ns0:v>
+      </ns0:c>
+      <ns0:c r="AE39">
+        <ns0:v>15</ns0:v>
+      </ns0:c>
+      <ns0:c r="AF39">
+        <ns0:v>120</ns0:v>
+      </ns0:c>
+      <ns0:c r="AG39">
+        <ns0:v>15</ns0:v>
+      </ns0:c>
+      <ns0:c r="AH39"/>
+      <ns0:c r="AI39">
+        <ns0:v>4900</ns0:v>
+      </ns0:c>
+      <ns0:c r="AJ39" t="str">
+        <ns0:v>Стройматериалы</ns0:v>
+      </ns0:c>
+      <ns0:c r="AK39" t="str">
+        <ns0:v>Товар от производителя</ns0:v>
+      </ns0:c>
+      <ns0:c r="AL39" t="str">
+        <ns0:v>Новое</ns0:v>
+      </ns0:c>
+      <ns0:c r="AM39" t="inlineStr">
+        <ns0:is>
+          <ns0:t>В наличии</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="AN39" t="str">
+        <ns0:v>Отделка</ns0:v>
+      </ns0:c>
+      <ns0:c r="AO39"/>
+      <ns0:c r="AP39" t="str">
+        <ns0:v>Стеновые панели, рейки и элементы декора</ns0:v>
+      </ns0:c>
+      <ns0:c r="AQ39" t="str">
+        <ns0:v>Стеновые панели</ns0:v>
+      </ns0:c>
+      <ns0:c r="AR39" t="str">
+        <ns0:v>ПВХ</ns0:v>
+      </ns0:c>
+      <ns0:c r="AS39" t="str">
+        <ns0:v>Стены | Двери</ns0:v>
+      </ns0:c>
+      <ns0:c r="AT39" t="str">
+        <ns0:v>Нет</ns0:v>
+      </ns0:c>
+      <ns0:c r="AU39" t="n">
+        <ns0:v>2800</ns0:v>
+      </ns0:c>
+      <ns0:c r="AV39" t="n">
+        <ns0:v>1140</ns0:v>
+      </ns0:c>
+      <ns0:c r="AW39"/>
+      <ns0:c r="AX39" t="str">
+        <ns0:v>Нет</ns0:v>
+      </ns0:c>
+      <ns0:c r="AY39"/>
+      <ns0:c r="AZ39"/>
+      <ns0:c r="BA39"/>
+      <ns0:c r="BB39"/>
+      <ns0:c r="BC39"/>
+      <ns0:c r="BD39"/>
+      <ns0:c r="BE39"/>
+      <ns0:c r="BF39"/>
+    </ns0:row>
+    <ns0:row r="40">
+      <ns0:c r="A40" t="inlineStr">
+        <ns0:is>
+          <ns0:t>adamar-vlg-Beton Blurry_1</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="B40"/>
+      <ns0:c r="C40"/>
+      <ns0:c r="D40"/>
+      <ns0:c r="E40"/>
+      <ns0:c r="F40"/>
+      <ns0:c r="G40" t="str">
+        <ns0:v>Adamar Group</ns0:v>
+      </ns0:c>
+      <ns0:c r="H40" t="str">
+        <ns0:v>79996244489</ns0:v>
+      </ns0:c>
+      <ns0:c r="I40" t="inlineStr">
+        <ns0:is>
+          <ns0:t>Гибкий мрамор 114х280 см — Beton Blurry 1</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="J40" t="inlineStr">
+        <ns0:is>
+          <ns0:t xml:space="preserve">Гибкий мрамор «Beton Blurry 1» — выразительная отделка для современного интерьера ✨
+Это широкоформатные панели 114×280 см, которые также называют гибким камнем и микрокальцитными панелями. Материал подходит для кухни, ванной, прихожей, гостиной, офиса и коммерческих помещений. Панели легко режутся и быстро монтируются на прочное основание.
+✅ Есть в наличии в Волгограде.
+🤝 Дилерам и монтажным бригадам предоставляем специальные скидки.
+📍 Приходите в шоурум: ТЦ «Новосрой», 2 этаж, г. Волгоград, ул. 25-летия Октября, д. 1, стр. 3. Посмотрите декоры вживую и получите расчёт количества панелей.</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="K40" t="inlineStr">
+        <ns0:is>
+          <ns0:t>https://avatars.mds.yandex.net/get-yastore/20918687/65tfpzcmtfgh2nw54b54phkjth8pfmdt/orig | https://avatars.mds.yandex.net/get-yastore/21055393/9j56s4dxrz9lp5xtqpm2wfjspjk54nvd/orig | https://avatars.mds.yandex.net/get-yastore/20918687/pfzrxv5stbw7prlfmsghplrcwk67mc47/orig</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="L40"/>
+      <ns0:c r="M40" t="str">
+        <ns0:v>По телефону и в сообщениях</ns0:v>
+      </ns0:c>
+      <ns0:c r="N40"/>
+      <ns0:c r="O40"/>
+      <ns0:c r="P40"/>
+      <ns0:c r="Q40" t="str">
+        <ns0:v>Ремонт и строительство</ns0:v>
+      </ns0:c>
+      <ns0:c r="R40" t="inlineStr">
+        <ns0:is>
+          <ns0:t>г. Волгоград, ул. 25-летия Октября, д. 1, стр. 3</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="S40"/>
+      <ns0:c r="T40"/>
+      <ns0:c r="U40"/>
+      <ns0:c r="V40" t="str">
+        <ns0:v>Поштучно</ns0:v>
+      </ns0:c>
+      <ns0:c r="W40">
+        <ns0:v>200</ns0:v>
+      </ns0:c>
+      <ns0:c r="X40" t="n">
+        <ns0:v>1</ns0:v>
+      </ns0:c>
+      <ns0:c r="Y40" t="n">
+        <ns0:v>1</ns0:v>
+      </ns0:c>
+      <ns0:c r="Z40" t="str">
+        <ns0:v>Штуку</ns0:v>
+      </ns0:c>
+      <ns0:c r="AA40"/>
+      <ns0:c r="AB40"/>
+      <ns0:c r="AC40"/>
+      <ns0:c r="AD40">
+        <ns0:v>6.5</ns0:v>
+      </ns0:c>
+      <ns0:c r="AE40">
+        <ns0:v>15</ns0:v>
+      </ns0:c>
+      <ns0:c r="AF40">
+        <ns0:v>120</ns0:v>
+      </ns0:c>
+      <ns0:c r="AG40">
+        <ns0:v>15</ns0:v>
+      </ns0:c>
+      <ns0:c r="AH40"/>
+      <ns0:c r="AI40">
+        <ns0:v>4900</ns0:v>
+      </ns0:c>
+      <ns0:c r="AJ40" t="str">
+        <ns0:v>Стройматериалы</ns0:v>
+      </ns0:c>
+      <ns0:c r="AK40" t="str">
+        <ns0:v>Товар от производителя</ns0:v>
+      </ns0:c>
+      <ns0:c r="AL40" t="str">
+        <ns0:v>Новое</ns0:v>
+      </ns0:c>
+      <ns0:c r="AM40" t="inlineStr">
+        <ns0:is>
+          <ns0:t>В наличии</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="AN40" t="str">
+        <ns0:v>Отделка</ns0:v>
+      </ns0:c>
+      <ns0:c r="AO40"/>
+      <ns0:c r="AP40" t="str">
+        <ns0:v>Стеновые панели, рейки и элементы декора</ns0:v>
+      </ns0:c>
+      <ns0:c r="AQ40" t="str">
+        <ns0:v>Стеновые панели</ns0:v>
+      </ns0:c>
+      <ns0:c r="AR40" t="str">
+        <ns0:v>ПВХ</ns0:v>
+      </ns0:c>
+      <ns0:c r="AS40" t="str">
+        <ns0:v>Стены | Двери</ns0:v>
+      </ns0:c>
+      <ns0:c r="AT40" t="str">
+        <ns0:v>Нет</ns0:v>
+      </ns0:c>
+      <ns0:c r="AU40" t="n">
+        <ns0:v>2800</ns0:v>
+      </ns0:c>
+      <ns0:c r="AV40" t="n">
+        <ns0:v>1140</ns0:v>
+      </ns0:c>
+      <ns0:c r="AW40"/>
+      <ns0:c r="AX40" t="str">
+        <ns0:v>Нет</ns0:v>
+      </ns0:c>
+      <ns0:c r="AY40"/>
+      <ns0:c r="AZ40"/>
+      <ns0:c r="BA40"/>
+      <ns0:c r="BB40"/>
+      <ns0:c r="BC40"/>
+      <ns0:c r="BD40"/>
+      <ns0:c r="BE40"/>
+      <ns0:c r="BF40"/>
+    </ns0:row>
+    <ns0:row r="41">
+      <ns0:c r="A41" t="inlineStr">
+        <ns0:is>
+          <ns0:t>adamar-vlg-MARBLE 10</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="B41"/>
+      <ns0:c r="C41"/>
+      <ns0:c r="D41"/>
+      <ns0:c r="E41"/>
+      <ns0:c r="F41"/>
+      <ns0:c r="G41" t="str">
+        <ns0:v>Adamar Group</ns0:v>
+      </ns0:c>
+      <ns0:c r="H41" t="str">
+        <ns0:v>79996244489</ns0:v>
+      </ns0:c>
+      <ns0:c r="I41" t="inlineStr">
+        <ns0:is>
+          <ns0:t>Гибкий мрамор 114х280 см — MARBLE 10</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="J41" t="inlineStr">
+        <ns0:is>
+          <ns0:t xml:space="preserve">Гибкий мрамор «MARBLE 10» — выразительная отделка для современного интерьера ✨
+Это широкоформатные панели 114×280 см, которые также называют гибким камнем и микрокальцитными панелями. Материал подходит для кухни, ванной, прихожей, гостиной, офиса и коммерческих помещений. Панели легко режутся и быстро монтируются на прочное основание.
+✅ Есть в наличии в Волгограде.
+🤝 Дилерам и монтажным бригадам предоставляем специальные скидки.
+📍 Приходите в шоурум: ТЦ «Новосрой», 2 этаж, г. Волгоград, ул. 25-летия Октября, д. 1, стр. 3. Посмотрите декоры вживую и получите расчёт количества панелей.</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="K41" t="inlineStr">
+        <ns0:is>
+          <ns0:t>https://avatars.mds.yandex.net/get-yastore/20760651/jdgk94lggnz2mdjcdxvlv8v9jt2fv4qs/orig | https://avatars.mds.yandex.net/get-yastore/20918687/fc6f786fxq9nhx4n2wwhzg7z2d97h6ld/orig | https://avatars.mds.yandex.net/get-yastore/20274467/fd4pj5crklkgv7dz6jxq2fq7qvmjfc47/orig | https://avatars.mds.yandex.net/get-yastore/20760651/zqfffdb4thrz2rmcqhvlbkb7swv5rj46/orig</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="L41"/>
+      <ns0:c r="M41" t="str">
+        <ns0:v>По телефону и в сообщениях</ns0:v>
+      </ns0:c>
+      <ns0:c r="N41"/>
+      <ns0:c r="O41"/>
+      <ns0:c r="P41"/>
+      <ns0:c r="Q41" t="str">
+        <ns0:v>Ремонт и строительство</ns0:v>
+      </ns0:c>
+      <ns0:c r="R41" t="inlineStr">
+        <ns0:is>
+          <ns0:t>г. Волгоград, ул. 25-летия Октября, д. 1, стр. 3</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="S41"/>
+      <ns0:c r="T41"/>
+      <ns0:c r="U41"/>
+      <ns0:c r="V41" t="str">
+        <ns0:v>Поштучно</ns0:v>
+      </ns0:c>
+      <ns0:c r="W41">
+        <ns0:v>200</ns0:v>
+      </ns0:c>
+      <ns0:c r="X41" t="n">
+        <ns0:v>1</ns0:v>
+      </ns0:c>
+      <ns0:c r="Y41" t="n">
+        <ns0:v>1</ns0:v>
+      </ns0:c>
+      <ns0:c r="Z41" t="str">
+        <ns0:v>Штуку</ns0:v>
+      </ns0:c>
+      <ns0:c r="AA41"/>
+      <ns0:c r="AB41"/>
+      <ns0:c r="AC41"/>
+      <ns0:c r="AD41">
+        <ns0:v>6.5</ns0:v>
+      </ns0:c>
+      <ns0:c r="AE41">
+        <ns0:v>15</ns0:v>
+      </ns0:c>
+      <ns0:c r="AF41">
+        <ns0:v>120</ns0:v>
+      </ns0:c>
+      <ns0:c r="AG41">
+        <ns0:v>15</ns0:v>
+      </ns0:c>
+      <ns0:c r="AH41"/>
+      <ns0:c r="AI41">
+        <ns0:v>4900</ns0:v>
+      </ns0:c>
+      <ns0:c r="AJ41" t="str">
+        <ns0:v>Стройматериалы</ns0:v>
+      </ns0:c>
+      <ns0:c r="AK41" t="str">
+        <ns0:v>Товар от производителя</ns0:v>
+      </ns0:c>
+      <ns0:c r="AL41" t="str">
+        <ns0:v>Новое</ns0:v>
+      </ns0:c>
+      <ns0:c r="AM41" t="inlineStr">
+        <ns0:is>
+          <ns0:t>В наличии</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="AN41" t="str">
+        <ns0:v>Отделка</ns0:v>
+      </ns0:c>
+      <ns0:c r="AO41"/>
+      <ns0:c r="AP41" t="str">
+        <ns0:v>Стеновые панели, рейки и элементы декора</ns0:v>
+      </ns0:c>
+      <ns0:c r="AQ41" t="str">
+        <ns0:v>Стеновые панели</ns0:v>
+      </ns0:c>
+      <ns0:c r="AR41" t="str">
+        <ns0:v>ПВХ</ns0:v>
+      </ns0:c>
+      <ns0:c r="AS41" t="str">
+        <ns0:v>Стены | Двери</ns0:v>
+      </ns0:c>
+      <ns0:c r="AT41" t="str">
+        <ns0:v>Нет</ns0:v>
+      </ns0:c>
+      <ns0:c r="AU41" t="n">
+        <ns0:v>2800</ns0:v>
+      </ns0:c>
+      <ns0:c r="AV41" t="n">
+        <ns0:v>1140</ns0:v>
+      </ns0:c>
+      <ns0:c r="AW41"/>
+      <ns0:c r="AX41" t="str">
+        <ns0:v>Нет</ns0:v>
+      </ns0:c>
+      <ns0:c r="AY41"/>
+      <ns0:c r="AZ41"/>
+      <ns0:c r="BA41"/>
+      <ns0:c r="BB41"/>
+      <ns0:c r="BC41"/>
+      <ns0:c r="BD41"/>
+      <ns0:c r="BE41"/>
+      <ns0:c r="BF41"/>
+    </ns0:row>
+    <ns0:row r="42">
+      <ns0:c r="A42" t="inlineStr">
+        <ns0:is>
+          <ns0:t>adamar-vlg-WHITE NIGHT</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="B42"/>
+      <ns0:c r="C42"/>
+      <ns0:c r="D42"/>
+      <ns0:c r="E42"/>
+      <ns0:c r="F42"/>
+      <ns0:c r="G42" t="str">
+        <ns0:v>Adamar Group</ns0:v>
+      </ns0:c>
+      <ns0:c r="H42" t="str">
+        <ns0:v>79996244489</ns0:v>
+      </ns0:c>
+      <ns0:c r="I42" t="inlineStr">
+        <ns0:is>
+          <ns0:t>Гибкий мрамор 114х280 см — WHITE NIGHT</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="J42" t="inlineStr">
+        <ns0:is>
+          <ns0:t xml:space="preserve">Гибкий мрамор «WHITE NIGHT» — выразительная отделка для современного интерьера ✨
+Это широкоформатные панели 114×280 см, которые также называют гибким камнем и микрокальцитными панелями. Материал подходит для кухни, ванной, прихожей, гостиной, офиса и коммерческих помещений. Панели легко режутся и быстро монтируются на прочное основание.
+✅ Есть в наличии в Волгограде.
+🤝 Дилерам и монтажным бригадам предоставляем специальные скидки.
+📍 Приходите в шоурум: ТЦ «Новосрой», 2 этаж, г. Волгоград, ул. 25-летия Октября, д. 1, стр. 3. Посмотрите декоры вживую и получите расчёт количества панелей.</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="K42" t="inlineStr">
+        <ns0:is>
+          <ns0:t>https://avatars.mds.yandex.net/get-yastore/20274467/vmk77jq2ks4hmzjfx4vv6dblzrswm4rl/orig | https://avatars.mds.yandex.net/get-yastore/20274467/677wqq2wb8s2cwhkckssh4d9g2lrxmsl/orig | https://avatars.mds.yandex.net/get-yastore/20274467/pkh99898g7qsc95krlm8mgt9q856mhjq/orig | https://avatars.mds.yandex.net/get-yastore/20274467/q8wjzqsrfqnbsr9qf68mnrf52xs5tfjd/orig</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="L42"/>
+      <ns0:c r="M42" t="str">
+        <ns0:v>По телефону и в сообщениях</ns0:v>
+      </ns0:c>
+      <ns0:c r="N42"/>
+      <ns0:c r="O42"/>
+      <ns0:c r="P42"/>
+      <ns0:c r="Q42" t="str">
+        <ns0:v>Ремонт и строительство</ns0:v>
+      </ns0:c>
+      <ns0:c r="R42" t="inlineStr">
+        <ns0:is>
+          <ns0:t>г. Волгоград, ул. 25-летия Октября, д. 1, стр. 3</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="S42"/>
+      <ns0:c r="T42"/>
+      <ns0:c r="U42"/>
+      <ns0:c r="V42" t="str">
+        <ns0:v>Поштучно</ns0:v>
+      </ns0:c>
+      <ns0:c r="W42">
+        <ns0:v>200</ns0:v>
+      </ns0:c>
+      <ns0:c r="X42" t="n">
+        <ns0:v>1</ns0:v>
+      </ns0:c>
+      <ns0:c r="Y42" t="n">
+        <ns0:v>1</ns0:v>
+      </ns0:c>
+      <ns0:c r="Z42" t="str">
+        <ns0:v>Штуку</ns0:v>
+      </ns0:c>
+      <ns0:c r="AA42"/>
+      <ns0:c r="AB42"/>
+      <ns0:c r="AC42"/>
+      <ns0:c r="AD42">
+        <ns0:v>6.5</ns0:v>
+      </ns0:c>
+      <ns0:c r="AE42">
+        <ns0:v>15</ns0:v>
+      </ns0:c>
+      <ns0:c r="AF42">
+        <ns0:v>120</ns0:v>
+      </ns0:c>
+      <ns0:c r="AG42">
+        <ns0:v>15</ns0:v>
+      </ns0:c>
+      <ns0:c r="AH42"/>
+      <ns0:c r="AI42">
+        <ns0:v>4900</ns0:v>
+      </ns0:c>
+      <ns0:c r="AJ42" t="str">
+        <ns0:v>Стройматериалы</ns0:v>
+      </ns0:c>
+      <ns0:c r="AK42" t="str">
+        <ns0:v>Товар от производителя</ns0:v>
+      </ns0:c>
+      <ns0:c r="AL42" t="str">
+        <ns0:v>Новое</ns0:v>
+      </ns0:c>
+      <ns0:c r="AM42" t="inlineStr">
+        <ns0:is>
+          <ns0:t>В наличии</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="AN42" t="str">
+        <ns0:v>Отделка</ns0:v>
+      </ns0:c>
+      <ns0:c r="AO42"/>
+      <ns0:c r="AP42" t="str">
+        <ns0:v>Стеновые панели, рейки и элементы декора</ns0:v>
+      </ns0:c>
+      <ns0:c r="AQ42" t="str">
+        <ns0:v>Стеновые панели</ns0:v>
+      </ns0:c>
+      <ns0:c r="AR42" t="str">
+        <ns0:v>ПВХ</ns0:v>
+      </ns0:c>
+      <ns0:c r="AS42" t="str">
+        <ns0:v>Стены | Двери</ns0:v>
+      </ns0:c>
+      <ns0:c r="AT42" t="str">
+        <ns0:v>Нет</ns0:v>
+      </ns0:c>
+      <ns0:c r="AU42" t="n">
+        <ns0:v>2800</ns0:v>
+      </ns0:c>
+      <ns0:c r="AV42" t="n">
+        <ns0:v>1140</ns0:v>
+      </ns0:c>
+      <ns0:c r="AW42"/>
+      <ns0:c r="AX42" t="str">
+        <ns0:v>Нет</ns0:v>
+      </ns0:c>
+      <ns0:c r="AY42"/>
+      <ns0:c r="AZ42"/>
+      <ns0:c r="BA42"/>
+      <ns0:c r="BB42"/>
+      <ns0:c r="BC42"/>
+      <ns0:c r="BD42"/>
+      <ns0:c r="BE42"/>
+      <ns0:c r="BF42"/>
+    </ns0:row>
+    <ns0:row r="43">
+      <ns0:c r="A43" t="inlineStr">
+        <ns0:is>
+          <ns0:t>adamar-vlg-FOGLINE_DARK_DECOR</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="B43"/>
+      <ns0:c r="C43"/>
+      <ns0:c r="D43"/>
+      <ns0:c r="E43"/>
+      <ns0:c r="F43"/>
+      <ns0:c r="G43" t="str">
+        <ns0:v>Adamar Group</ns0:v>
+      </ns0:c>
+      <ns0:c r="H43" t="str">
+        <ns0:v>79996244489</ns0:v>
+      </ns0:c>
+      <ns0:c r="I43" t="inlineStr">
+        <ns0:is>
+          <ns0:t>Гибкий мрамор 114х280 см — FOGLINE DARK DECOR</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="J43" t="inlineStr">
+        <ns0:is>
+          <ns0:t xml:space="preserve">Гибкий мрамор «FOGLINE DARK DECOR» — выразительная отделка для современного интерьера ✨
+Это широкоформатные панели 114×280 см, которые также называют гибким камнем и микрокальцитными панелями. Материал подходит для кухни, ванной, прихожей, гостиной, офиса и коммерческих помещений. Панели легко режутся и быстро монтируются на прочное основание.
+✅ Есть в наличии в Волгограде.
+🤝 Дилерам и монтажным бригадам предоставляем специальные скидки.
+📍 Приходите в шоурум: ТЦ «Новосрой», 2 этаж, г. Волгоград, ул. 25-летия Октября, д. 1, стр. 3. Посмотрите декоры вживую и получите расчёт количества панелей.</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="K43" t="inlineStr">
+        <ns0:is>
+          <ns0:t>https://avatars.mds.yandex.net/get-yastore/21012869/cj2dchd64njtpqzmwj9qlzgpz4npk7t4/orig | https://avatars.mds.yandex.net/get-yastore/21055393/dptk7k9x749w2bqflqxctk2qqnndkzjv/orig | https://avatars.mds.yandex.net/get-yastore/21012869/8t4gz8wgtjrr969pd4rgm8xxdfhtgp5m/orig</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="L43"/>
+      <ns0:c r="M43" t="str">
+        <ns0:v>По телефону и в сообщениях</ns0:v>
+      </ns0:c>
+      <ns0:c r="N43"/>
+      <ns0:c r="O43"/>
+      <ns0:c r="P43"/>
+      <ns0:c r="Q43" t="str">
+        <ns0:v>Ремонт и строительство</ns0:v>
+      </ns0:c>
+      <ns0:c r="R43" t="inlineStr">
+        <ns0:is>
+          <ns0:t>г. Волгоград, ул. 25-летия Октября, д. 1, стр. 3</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="S43"/>
+      <ns0:c r="T43"/>
+      <ns0:c r="U43"/>
+      <ns0:c r="V43" t="str">
+        <ns0:v>Поштучно</ns0:v>
+      </ns0:c>
+      <ns0:c r="W43">
+        <ns0:v>200</ns0:v>
+      </ns0:c>
+      <ns0:c r="X43" t="n">
+        <ns0:v>1</ns0:v>
+      </ns0:c>
+      <ns0:c r="Y43" t="n">
+        <ns0:v>1</ns0:v>
+      </ns0:c>
+      <ns0:c r="Z43" t="str">
+        <ns0:v>Штуку</ns0:v>
+      </ns0:c>
+      <ns0:c r="AA43"/>
+      <ns0:c r="AB43"/>
+      <ns0:c r="AC43"/>
+      <ns0:c r="AD43">
+        <ns0:v>6.5</ns0:v>
+      </ns0:c>
+      <ns0:c r="AE43">
+        <ns0:v>15</ns0:v>
+      </ns0:c>
+      <ns0:c r="AF43">
+        <ns0:v>120</ns0:v>
+      </ns0:c>
+      <ns0:c r="AG43">
+        <ns0:v>15</ns0:v>
+      </ns0:c>
+      <ns0:c r="AH43"/>
+      <ns0:c r="AI43">
+        <ns0:v>4900</ns0:v>
+      </ns0:c>
+      <ns0:c r="AJ43" t="str">
+        <ns0:v>Стройматериалы</ns0:v>
+      </ns0:c>
+      <ns0:c r="AK43" t="str">
+        <ns0:v>Товар от производителя</ns0:v>
+      </ns0:c>
+      <ns0:c r="AL43" t="str">
+        <ns0:v>Новое</ns0:v>
+      </ns0:c>
+      <ns0:c r="AM43" t="inlineStr">
+        <ns0:is>
+          <ns0:t>В наличии</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="AN43" t="str">
+        <ns0:v>Отделка</ns0:v>
+      </ns0:c>
+      <ns0:c r="AO43"/>
+      <ns0:c r="AP43" t="str">
+        <ns0:v>Стеновые панели, рейки и элементы декора</ns0:v>
+      </ns0:c>
+      <ns0:c r="AQ43" t="str">
+        <ns0:v>Стеновые панели</ns0:v>
+      </ns0:c>
+      <ns0:c r="AR43" t="str">
+        <ns0:v>ПВХ</ns0:v>
+      </ns0:c>
+      <ns0:c r="AS43" t="str">
+        <ns0:v>Стены | Двери</ns0:v>
+      </ns0:c>
+      <ns0:c r="AT43" t="str">
+        <ns0:v>Нет</ns0:v>
+      </ns0:c>
+      <ns0:c r="AU43" t="n">
+        <ns0:v>2800</ns0:v>
+      </ns0:c>
+      <ns0:c r="AV43" t="n">
+        <ns0:v>1140</ns0:v>
+      </ns0:c>
+      <ns0:c r="AW43"/>
+      <ns0:c r="AX43" t="str">
+        <ns0:v>Нет</ns0:v>
+      </ns0:c>
+      <ns0:c r="AY43"/>
+      <ns0:c r="AZ43"/>
+      <ns0:c r="BA43"/>
+      <ns0:c r="BB43"/>
+      <ns0:c r="BC43"/>
+      <ns0:c r="BD43"/>
+      <ns0:c r="BE43"/>
+      <ns0:c r="BF43"/>
+    </ns0:row>
+    <ns0:row r="44">
+      <ns0:c r="A44" t="inlineStr">
+        <ns0:is>
+          <ns0:t>adamar-vlg-AQUAMARINA</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="B44"/>
+      <ns0:c r="C44"/>
+      <ns0:c r="D44"/>
+      <ns0:c r="E44"/>
+      <ns0:c r="F44"/>
+      <ns0:c r="G44" t="str">
+        <ns0:v>Adamar Group</ns0:v>
+      </ns0:c>
+      <ns0:c r="H44" t="str">
+        <ns0:v>79996244489</ns0:v>
+      </ns0:c>
+      <ns0:c r="I44" t="inlineStr">
+        <ns0:is>
+          <ns0:t>Гибкий мрамор 114х280 см — AQUAMARINA</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="J44" t="inlineStr">
+        <ns0:is>
+          <ns0:t xml:space="preserve">Гибкий мрамор «AQUAMARINA» — выразительная отделка для современного интерьера ✨
+Это широкоформатные панели 114×280 см, которые также называют гибким камнем и микрокальцитными панелями. Материал подходит для кухни, ванной, прихожей, гостиной, офиса и коммерческих помещений. Панели легко режутся и быстро монтируются на прочное основание.
+✅ Есть в наличии в Волгограде.
+🤝 Дилерам и монтажным бригадам предоставляем специальные скидки.
+📍 Приходите в шоурум: ТЦ «Новосрой», 2 этаж, г. Волгоград, ул. 25-летия Октября, д. 1, стр. 3. Посмотрите декоры вживую и получите расчёт количества панелей.</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="K44" t="inlineStr">
+        <ns0:is>
+          <ns0:t>https://avatars.mds.yandex.net/get-yastore/20274467/8jjl4tvr5qt8cfcpgtpcvs7vdmfhbbbh/orig | https://avatars.mds.yandex.net/get-yastore/21012869/4svk8hgjggmvdlr6tkjctqv75l626cgx/orig | https://avatars.mds.yandex.net/get-yastore/21055393/btsqjz68cxdj8268kcm64lqznwk8bnff/orig</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="L44"/>
+      <ns0:c r="M44" t="str">
+        <ns0:v>По телефону и в сообщениях</ns0:v>
+      </ns0:c>
+      <ns0:c r="N44"/>
+      <ns0:c r="O44"/>
+      <ns0:c r="P44"/>
+      <ns0:c r="Q44" t="str">
+        <ns0:v>Ремонт и строительство</ns0:v>
+      </ns0:c>
+      <ns0:c r="R44" t="inlineStr">
+        <ns0:is>
+          <ns0:t>г. Волгоград, ул. 25-летия Октября, д. 1, стр. 3</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="S44"/>
+      <ns0:c r="T44"/>
+      <ns0:c r="U44"/>
+      <ns0:c r="V44" t="str">
+        <ns0:v>Поштучно</ns0:v>
+      </ns0:c>
+      <ns0:c r="W44">
+        <ns0:v>200</ns0:v>
+      </ns0:c>
+      <ns0:c r="X44" t="n">
+        <ns0:v>1</ns0:v>
+      </ns0:c>
+      <ns0:c r="Y44" t="n">
+        <ns0:v>1</ns0:v>
+      </ns0:c>
+      <ns0:c r="Z44" t="str">
+        <ns0:v>Штуку</ns0:v>
+      </ns0:c>
+      <ns0:c r="AA44"/>
+      <ns0:c r="AB44"/>
+      <ns0:c r="AC44"/>
+      <ns0:c r="AD44">
+        <ns0:v>6.5</ns0:v>
+      </ns0:c>
+      <ns0:c r="AE44">
+        <ns0:v>15</ns0:v>
+      </ns0:c>
+      <ns0:c r="AF44">
+        <ns0:v>120</ns0:v>
+      </ns0:c>
+      <ns0:c r="AG44">
+        <ns0:v>15</ns0:v>
+      </ns0:c>
+      <ns0:c r="AH44"/>
+      <ns0:c r="AI44">
+        <ns0:v>4900</ns0:v>
+      </ns0:c>
+      <ns0:c r="AJ44" t="str">
+        <ns0:v>Стройматериалы</ns0:v>
+      </ns0:c>
+      <ns0:c r="AK44" t="str">
+        <ns0:v>Товар от производителя</ns0:v>
+      </ns0:c>
+      <ns0:c r="AL44" t="str">
+        <ns0:v>Новое</ns0:v>
+      </ns0:c>
+      <ns0:c r="AM44" t="inlineStr">
+        <ns0:is>
+          <ns0:t>В наличии</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="AN44" t="str">
+        <ns0:v>Отделка</ns0:v>
+      </ns0:c>
+      <ns0:c r="AO44"/>
+      <ns0:c r="AP44" t="str">
+        <ns0:v>Стеновые панели, рейки и элементы декора</ns0:v>
+      </ns0:c>
+      <ns0:c r="AQ44" t="str">
+        <ns0:v>Стеновые панели</ns0:v>
+      </ns0:c>
+      <ns0:c r="AR44" t="str">
+        <ns0:v>ПВХ</ns0:v>
+      </ns0:c>
+      <ns0:c r="AS44" t="str">
+        <ns0:v>Стены | Двери</ns0:v>
+      </ns0:c>
+      <ns0:c r="AT44" t="str">
+        <ns0:v>Нет</ns0:v>
+      </ns0:c>
+      <ns0:c r="AU44" t="n">
+        <ns0:v>2800</ns0:v>
+      </ns0:c>
+      <ns0:c r="AV44" t="n">
+        <ns0:v>1140</ns0:v>
+      </ns0:c>
+      <ns0:c r="AW44"/>
+      <ns0:c r="AX44" t="str">
+        <ns0:v>Нет</ns0:v>
+      </ns0:c>
+      <ns0:c r="AY44"/>
+      <ns0:c r="AZ44"/>
+      <ns0:c r="BA44"/>
+      <ns0:c r="BB44"/>
+      <ns0:c r="BC44"/>
+      <ns0:c r="BD44"/>
+      <ns0:c r="BE44"/>
+      <ns0:c r="BF44"/>
+    </ns0:row>
+    <ns0:row r="45">
+      <ns0:c r="A45" t="inlineStr">
+        <ns0:is>
+          <ns0:t>adamar-vlg-Glossy_Aeon</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="B45"/>
+      <ns0:c r="C45"/>
+      <ns0:c r="D45"/>
+      <ns0:c r="E45"/>
+      <ns0:c r="F45"/>
+      <ns0:c r="G45" t="str">
+        <ns0:v>Adamar Group</ns0:v>
+      </ns0:c>
+      <ns0:c r="H45" t="str">
+        <ns0:v>79996244489</ns0:v>
+      </ns0:c>
+      <ns0:c r="I45" t="inlineStr">
+        <ns0:is>
+          <ns0:t>Гибкий мрамор 114х280 см — Glossy Aeon</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="J45" t="inlineStr">
+        <ns0:is>
+          <ns0:t xml:space="preserve">Гибкий мрамор «Glossy Aeon» — выразительная отделка для современного интерьера ✨
+Это широкоформатные панели 114×280 см, которые также называют гибким камнем и микрокальцитными панелями. Материал подходит для кухни, ванной, прихожей, гостиной, офиса и коммерческих помещений. Панели легко режутся и быстро монтируются на прочное основание.
+✅ Есть в наличии в Волгограде.
+🤝 Дилерам и монтажным бригадам предоставляем специальные скидки.
+📍 Приходите в шоурум: ТЦ «Новосрой», 2 этаж, г. Волгоград, ул. 25-летия Октября, д. 1, стр. 3. Посмотрите декоры вживую и получите расчёт количества панелей.</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="K45" t="inlineStr">
+        <ns0:is>
+          <ns0:t>https://avatars.mds.yandex.net/get-yastore/20918687/tmk9rwz8kng4n27wvvcktqzcnrlpbggc/orig | https://avatars.mds.yandex.net/get-yastore/21553739/sqd6smwdkhwd6bfw89x4b5bj7b842792/orig | https://avatars.mds.yandex.net/get-yastore/21580234/z5wln5tlhxncngcvgxb4ddtl4txks6gx/orig | https://avatars.mds.yandex.net/get-yastore/20493671/8tpjzlztjtl6cdpd55z2z5b4nnvncz6l/orig</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="L45"/>
+      <ns0:c r="M45" t="str">
+        <ns0:v>По телефону и в сообщениях</ns0:v>
+      </ns0:c>
+      <ns0:c r="N45"/>
+      <ns0:c r="O45"/>
+      <ns0:c r="P45"/>
+      <ns0:c r="Q45" t="str">
+        <ns0:v>Ремонт и строительство</ns0:v>
+      </ns0:c>
+      <ns0:c r="R45" t="inlineStr">
+        <ns0:is>
+          <ns0:t>г. Волгоград, ул. 25-летия Октября, д. 1, стр. 3</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="S45"/>
+      <ns0:c r="T45"/>
+      <ns0:c r="U45"/>
+      <ns0:c r="V45" t="str">
+        <ns0:v>Поштучно</ns0:v>
+      </ns0:c>
+      <ns0:c r="W45">
+        <ns0:v>200</ns0:v>
+      </ns0:c>
+      <ns0:c r="X45" t="n">
+        <ns0:v>1</ns0:v>
+      </ns0:c>
+      <ns0:c r="Y45" t="n">
+        <ns0:v>1</ns0:v>
+      </ns0:c>
+      <ns0:c r="Z45" t="str">
+        <ns0:v>Штуку</ns0:v>
+      </ns0:c>
+      <ns0:c r="AA45"/>
+      <ns0:c r="AB45"/>
+      <ns0:c r="AC45"/>
+      <ns0:c r="AD45">
+        <ns0:v>6.5</ns0:v>
+      </ns0:c>
+      <ns0:c r="AE45">
+        <ns0:v>15</ns0:v>
+      </ns0:c>
+      <ns0:c r="AF45">
+        <ns0:v>120</ns0:v>
+      </ns0:c>
+      <ns0:c r="AG45">
+        <ns0:v>15</ns0:v>
+      </ns0:c>
+      <ns0:c r="AH45"/>
+      <ns0:c r="AI45">
+        <ns0:v>4900</ns0:v>
+      </ns0:c>
+      <ns0:c r="AJ45" t="str">
+        <ns0:v>Стройматериалы</ns0:v>
+      </ns0:c>
+      <ns0:c r="AK45" t="str">
+        <ns0:v>Товар от производителя</ns0:v>
+      </ns0:c>
+      <ns0:c r="AL45" t="str">
+        <ns0:v>Новое</ns0:v>
+      </ns0:c>
+      <ns0:c r="AM45" t="inlineStr">
+        <ns0:is>
+          <ns0:t>В наличии</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="AN45" t="str">
+        <ns0:v>Отделка</ns0:v>
+      </ns0:c>
+      <ns0:c r="AO45"/>
+      <ns0:c r="AP45" t="str">
+        <ns0:v>Стеновые панели, рейки и элементы декора</ns0:v>
+      </ns0:c>
+      <ns0:c r="AQ45" t="str">
+        <ns0:v>Стеновые панели</ns0:v>
+      </ns0:c>
+      <ns0:c r="AR45" t="str">
+        <ns0:v>ПВХ</ns0:v>
+      </ns0:c>
+      <ns0:c r="AS45" t="str">
+        <ns0:v>Стены | Двери</ns0:v>
+      </ns0:c>
+      <ns0:c r="AT45" t="str">
+        <ns0:v>Нет</ns0:v>
+      </ns0:c>
+      <ns0:c r="AU45" t="n">
+        <ns0:v>2800</ns0:v>
+      </ns0:c>
+      <ns0:c r="AV45" t="n">
+        <ns0:v>1140</ns0:v>
+      </ns0:c>
+      <ns0:c r="AW45"/>
+      <ns0:c r="AX45" t="str">
+        <ns0:v>Нет</ns0:v>
+      </ns0:c>
+      <ns0:c r="AY45"/>
+      <ns0:c r="AZ45"/>
+      <ns0:c r="BA45"/>
+      <ns0:c r="BB45"/>
+      <ns0:c r="BC45"/>
+      <ns0:c r="BD45"/>
+      <ns0:c r="BE45"/>
+      <ns0:c r="BF45"/>
+    </ns0:row>
+    <ns0:row r="46">
+      <ns0:c r="A46" t="inlineStr">
+        <ns0:is>
+          <ns0:t>adamar-vlg-BETON FERONI DECOR</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="B46"/>
+      <ns0:c r="C46"/>
+      <ns0:c r="D46"/>
+      <ns0:c r="E46"/>
+      <ns0:c r="F46"/>
+      <ns0:c r="G46" t="str">
+        <ns0:v>Adamar Group</ns0:v>
+      </ns0:c>
+      <ns0:c r="H46" t="str">
+        <ns0:v>79996244489</ns0:v>
+      </ns0:c>
+      <ns0:c r="I46" t="inlineStr">
+        <ns0:is>
+          <ns0:t>Гибкий мрамор 114х280 см — BETON FERONI DECOR</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="J46" t="inlineStr">
+        <ns0:is>
+          <ns0:t xml:space="preserve">Гибкий мрамор «BETON FERONI DECOR» — выразительная отделка для современного интерьера ✨
+Это широкоформатные панели 114×280 см, которые также называют гибким камнем и микрокальцитными панелями. Материал подходит для кухни, ванной, прихожей, гостиной, офиса и коммерческих помещений. Панели легко режутся и быстро монтируются на прочное основание.
+✅ Есть в наличии в Волгограде.
+🤝 Дилерам и монтажным бригадам предоставляем специальные скидки.
+📍 Приходите в шоурум: ТЦ «Новосрой», 2 этаж, г. Волгоград, ул. 25-летия Октября, д. 1, стр. 3. Посмотрите декоры вживую и получите расчёт количества панелей.</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="K46" t="inlineStr">
+        <ns0:is>
+          <ns0:t>https://avatars.mds.yandex.net/get-yastore/20274467/6px2n4894ncdd8gnntg4mnh2tp4wmwtz/orig | https://avatars.mds.yandex.net/get-yastore/21055393/zcsklcdmdsdss7v2vd58vkzbqjwwl6gp/orig | https://avatars.mds.yandex.net/get-yastore/21055393/9pv62jp5flt8rjpmpzdmlvqkqxvdvl9x/orig</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="L46"/>
+      <ns0:c r="M46" t="str">
+        <ns0:v>По телефону и в сообщениях</ns0:v>
+      </ns0:c>
+      <ns0:c r="N46"/>
+      <ns0:c r="O46"/>
+      <ns0:c r="P46"/>
+      <ns0:c r="Q46" t="str">
+        <ns0:v>Ремонт и строительство</ns0:v>
+      </ns0:c>
+      <ns0:c r="R46" t="inlineStr">
+        <ns0:is>
+          <ns0:t>г. Волгоград, ул. 25-летия Октября, д. 1, стр. 3</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="S46"/>
+      <ns0:c r="T46"/>
+      <ns0:c r="U46"/>
+      <ns0:c r="V46" t="str">
+        <ns0:v>Поштучно</ns0:v>
+      </ns0:c>
+      <ns0:c r="W46">
+        <ns0:v>200</ns0:v>
+      </ns0:c>
+      <ns0:c r="X46" t="n">
+        <ns0:v>1</ns0:v>
+      </ns0:c>
+      <ns0:c r="Y46" t="n">
+        <ns0:v>1</ns0:v>
+      </ns0:c>
+      <ns0:c r="Z46" t="str">
+        <ns0:v>Штуку</ns0:v>
+      </ns0:c>
+      <ns0:c r="AA46"/>
+      <ns0:c r="AB46"/>
+      <ns0:c r="AC46"/>
+      <ns0:c r="AD46">
+        <ns0:v>6.5</ns0:v>
+      </ns0:c>
+      <ns0:c r="AE46">
+        <ns0:v>15</ns0:v>
+      </ns0:c>
+      <ns0:c r="AF46">
+        <ns0:v>120</ns0:v>
+      </ns0:c>
+      <ns0:c r="AG46">
+        <ns0:v>15</ns0:v>
+      </ns0:c>
+      <ns0:c r="AH46"/>
+      <ns0:c r="AI46">
+        <ns0:v>4900</ns0:v>
+      </ns0:c>
+      <ns0:c r="AJ46" t="str">
+        <ns0:v>Стройматериалы</ns0:v>
+      </ns0:c>
+      <ns0:c r="AK46" t="str">
+        <ns0:v>Товар от производителя</ns0:v>
+      </ns0:c>
+      <ns0:c r="AL46" t="str">
+        <ns0:v>Новое</ns0:v>
+      </ns0:c>
+      <ns0:c r="AM46" t="inlineStr">
+        <ns0:is>
+          <ns0:t>В наличии</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="AN46" t="str">
+        <ns0:v>Отделка</ns0:v>
+      </ns0:c>
+      <ns0:c r="AO46"/>
+      <ns0:c r="AP46" t="str">
+        <ns0:v>Стеновые панели, рейки и элементы декора</ns0:v>
+      </ns0:c>
+      <ns0:c r="AQ46" t="str">
+        <ns0:v>Стеновые панели</ns0:v>
+      </ns0:c>
+      <ns0:c r="AR46" t="str">
+        <ns0:v>ПВХ</ns0:v>
+      </ns0:c>
+      <ns0:c r="AS46" t="str">
+        <ns0:v>Стены | Двери</ns0:v>
+      </ns0:c>
+      <ns0:c r="AT46" t="str">
+        <ns0:v>Нет</ns0:v>
+      </ns0:c>
+      <ns0:c r="AU46" t="n">
+        <ns0:v>2800</ns0:v>
+      </ns0:c>
+      <ns0:c r="AV46" t="n">
+        <ns0:v>1140</ns0:v>
+      </ns0:c>
+      <ns0:c r="AW46"/>
+      <ns0:c r="AX46" t="str">
+        <ns0:v>Нет</ns0:v>
+      </ns0:c>
+      <ns0:c r="AY46"/>
+      <ns0:c r="AZ46"/>
+      <ns0:c r="BA46"/>
+      <ns0:c r="BB46"/>
+      <ns0:c r="BC46"/>
+      <ns0:c r="BD46"/>
+      <ns0:c r="BE46"/>
+      <ns0:c r="BF46"/>
+    </ns0:row>
+    <ns0:row r="47">
+      <ns0:c r="A47" t="inlineStr">
+        <ns0:is>
+          <ns0:t>adamar-vlg-MARBLE SNOW</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="B47"/>
+      <ns0:c r="C47"/>
+      <ns0:c r="D47"/>
+      <ns0:c r="E47"/>
+      <ns0:c r="F47"/>
+      <ns0:c r="G47" t="str">
+        <ns0:v>Adamar Group</ns0:v>
+      </ns0:c>
+      <ns0:c r="H47" t="str">
+        <ns0:v>79996244489</ns0:v>
+      </ns0:c>
+      <ns0:c r="I47" t="inlineStr">
+        <ns0:is>
+          <ns0:t>Гибкий мрамор 114х280 см — MARBLE SNOW</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="J47" t="inlineStr">
+        <ns0:is>
+          <ns0:t xml:space="preserve">Гибкий мрамор «MARBLE SNOW» — выразительная отделка для современного интерьера ✨
+Это широкоформатные панели 114×280 см, которые также называют гибким камнем и микрокальцитными панелями. Материал подходит для кухни, ванной, прихожей, гостиной, офиса и коммерческих помещений. Панели легко режутся и быстро монтируются на прочное основание.
+✅ Есть в наличии в Волгограде.
+🤝 Дилерам и монтажным бригадам предоставляем специальные скидки.
+📍 Приходите в шоурум: ТЦ «Новосрой», 2 этаж, г. Волгоград, ул. 25-летия Октября, д. 1, стр. 3. Посмотрите декоры вживую и получите расчёт количества панелей.</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="K47" t="inlineStr">
+        <ns0:is>
+          <ns0:t>https://avatars.mds.yandex.net/get-yastore/20760651/jwgbjlfl42fnkjffz562n4fr9rbh2cq5/orig | https://avatars.mds.yandex.net/get-yastore/21055393/ztjk7m8czvrwj4jln7rxdtbwgsqm5r4h/orig | https://avatars.mds.yandex.net/get-yastore/20918687/xfx29vfprqmhdwmm4jkf8stk5lg5mzzm/orig | https://avatars.mds.yandex.net/get-yastore/20918687/4gxlq64mknmr4ghq62n7xd4pp44k9gng/orig</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="L47"/>
+      <ns0:c r="M47" t="str">
+        <ns0:v>По телефону и в сообщениях</ns0:v>
+      </ns0:c>
+      <ns0:c r="N47"/>
+      <ns0:c r="O47"/>
+      <ns0:c r="P47"/>
+      <ns0:c r="Q47" t="str">
+        <ns0:v>Ремонт и строительство</ns0:v>
+      </ns0:c>
+      <ns0:c r="R47" t="inlineStr">
+        <ns0:is>
+          <ns0:t>г. Волгоград, ул. 25-летия Октября, д. 1, стр. 3</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="S47"/>
+      <ns0:c r="T47"/>
+      <ns0:c r="U47"/>
+      <ns0:c r="V47" t="str">
+        <ns0:v>Поштучно</ns0:v>
+      </ns0:c>
+      <ns0:c r="W47">
+        <ns0:v>200</ns0:v>
+      </ns0:c>
+      <ns0:c r="X47" t="n">
+        <ns0:v>1</ns0:v>
+      </ns0:c>
+      <ns0:c r="Y47" t="n">
+        <ns0:v>1</ns0:v>
+      </ns0:c>
+      <ns0:c r="Z47" t="str">
+        <ns0:v>Штуку</ns0:v>
+      </ns0:c>
+      <ns0:c r="AA47"/>
+      <ns0:c r="AB47"/>
+      <ns0:c r="AC47"/>
+      <ns0:c r="AD47">
+        <ns0:v>6.5</ns0:v>
+      </ns0:c>
+      <ns0:c r="AE47">
+        <ns0:v>15</ns0:v>
+      </ns0:c>
+      <ns0:c r="AF47">
+        <ns0:v>120</ns0:v>
+      </ns0:c>
+      <ns0:c r="AG47">
+        <ns0:v>15</ns0:v>
+      </ns0:c>
+      <ns0:c r="AH47"/>
+      <ns0:c r="AI47">
+        <ns0:v>4900</ns0:v>
+      </ns0:c>
+      <ns0:c r="AJ47" t="str">
+        <ns0:v>Стройматериалы</ns0:v>
+      </ns0:c>
+      <ns0:c r="AK47" t="str">
+        <ns0:v>Товар от производителя</ns0:v>
+      </ns0:c>
+      <ns0:c r="AL47" t="str">
+        <ns0:v>Новое</ns0:v>
+      </ns0:c>
+      <ns0:c r="AM47" t="inlineStr">
+        <ns0:is>
+          <ns0:t>В наличии</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="AN47" t="str">
+        <ns0:v>Отделка</ns0:v>
+      </ns0:c>
+      <ns0:c r="AO47"/>
+      <ns0:c r="AP47" t="str">
+        <ns0:v>Стеновые панели, рейки и элементы декора</ns0:v>
+      </ns0:c>
+      <ns0:c r="AQ47" t="str">
+        <ns0:v>Стеновые панели</ns0:v>
+      </ns0:c>
+      <ns0:c r="AR47" t="str">
+        <ns0:v>ПВХ</ns0:v>
+      </ns0:c>
+      <ns0:c r="AS47" t="str">
+        <ns0:v>Стены | Двери</ns0:v>
+      </ns0:c>
+      <ns0:c r="AT47" t="str">
+        <ns0:v>Нет</ns0:v>
+      </ns0:c>
+      <ns0:c r="AU47" t="n">
+        <ns0:v>2800</ns0:v>
+      </ns0:c>
+      <ns0:c r="AV47" t="n">
+        <ns0:v>1140</ns0:v>
+      </ns0:c>
+      <ns0:c r="AW47"/>
+      <ns0:c r="AX47" t="str">
+        <ns0:v>Нет</ns0:v>
+      </ns0:c>
+      <ns0:c r="AY47"/>
+      <ns0:c r="AZ47"/>
+      <ns0:c r="BA47"/>
+      <ns0:c r="BB47"/>
+      <ns0:c r="BC47"/>
+      <ns0:c r="BD47"/>
+      <ns0:c r="BE47"/>
+      <ns0:c r="BF47"/>
+    </ns0:row>
+    <ns0:row r="48">
+      <ns0:c r="A48" t="inlineStr">
+        <ns0:is>
+          <ns0:t>adamar-vlg-AQUA SKY</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="B48"/>
+      <ns0:c r="C48"/>
+      <ns0:c r="D48"/>
+      <ns0:c r="E48"/>
+      <ns0:c r="F48"/>
+      <ns0:c r="G48" t="str">
+        <ns0:v>Adamar Group</ns0:v>
+      </ns0:c>
+      <ns0:c r="H48" t="str">
+        <ns0:v>79996244489</ns0:v>
+      </ns0:c>
+      <ns0:c r="I48" t="inlineStr">
+        <ns0:is>
+          <ns0:t>Гибкий мрамор 114х280 см — AQUA SKY</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="J48" t="inlineStr">
+        <ns0:is>
+          <ns0:t xml:space="preserve">Гибкий мрамор «AQUA SKY» — выразительная отделка для современного интерьера ✨
+Это широкоформатные панели 114×280 см, которые также называют гибким камнем и микрокальцитными панелями. Материал подходит для кухни, ванной, прихожей, гостиной, офиса и коммерческих помещений. Панели легко режутся и быстро монтируются на прочное основание.
+✅ Есть в наличии в Волгограде.
+🤝 Дилерам и монтажным бригадам предоставляем специальные скидки.
+📍 Приходите в шоурум: ТЦ «Новосрой», 2 этаж, г. Волгоград, ул. 25-летия Октября, д. 1, стр. 3. Посмотрите декоры вживую и получите расчёт количества панелей.</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="K48" t="inlineStr">
+        <ns0:is>
+          <ns0:t>https://avatars.mds.yandex.net/get-yastore/21696355/h8vjxk9l24ql7h8r9hkj9xxbp4dcdbcl/orig | https://avatars.mds.yandex.net/get-yastore/21580234/djvzdqhcfxx9vvssckcscrxkq24fr4w5/orig | https://avatars.mds.yandex.net/get-yastore/21580234/r769fllkdt8htpkcl8vdtrc78jvl6pxk/orig</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="L48"/>
+      <ns0:c r="M48" t="str">
+        <ns0:v>По телефону и в сообщениях</ns0:v>
+      </ns0:c>
+      <ns0:c r="N48"/>
+      <ns0:c r="O48"/>
+      <ns0:c r="P48"/>
+      <ns0:c r="Q48" t="str">
+        <ns0:v>Ремонт и строительство</ns0:v>
+      </ns0:c>
+      <ns0:c r="R48" t="inlineStr">
+        <ns0:is>
+          <ns0:t>г. Волгоград, ул. 25-летия Октября, д. 1, стр. 3</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="S48"/>
+      <ns0:c r="T48"/>
+      <ns0:c r="U48"/>
+      <ns0:c r="V48" t="str">
+        <ns0:v>Поштучно</ns0:v>
+      </ns0:c>
+      <ns0:c r="W48">
+        <ns0:v>200</ns0:v>
+      </ns0:c>
+      <ns0:c r="X48" t="n">
+        <ns0:v>1</ns0:v>
+      </ns0:c>
+      <ns0:c r="Y48" t="n">
+        <ns0:v>1</ns0:v>
+      </ns0:c>
+      <ns0:c r="Z48" t="str">
+        <ns0:v>Штуку</ns0:v>
+      </ns0:c>
+      <ns0:c r="AA48"/>
+      <ns0:c r="AB48"/>
+      <ns0:c r="AC48"/>
+      <ns0:c r="AD48">
+        <ns0:v>6.5</ns0:v>
+      </ns0:c>
+      <ns0:c r="AE48">
+        <ns0:v>15</ns0:v>
+      </ns0:c>
+      <ns0:c r="AF48">
+        <ns0:v>120</ns0:v>
+      </ns0:c>
+      <ns0:c r="AG48">
+        <ns0:v>15</ns0:v>
+      </ns0:c>
+      <ns0:c r="AH48"/>
+      <ns0:c r="AI48">
+        <ns0:v>4900</ns0:v>
+      </ns0:c>
+      <ns0:c r="AJ48" t="str">
+        <ns0:v>Стройматериалы</ns0:v>
+      </ns0:c>
+      <ns0:c r="AK48" t="str">
+        <ns0:v>Товар от производителя</ns0:v>
+      </ns0:c>
+      <ns0:c r="AL48" t="str">
+        <ns0:v>Новое</ns0:v>
+      </ns0:c>
+      <ns0:c r="AM48" t="inlineStr">
+        <ns0:is>
+          <ns0:t>В наличии</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="AN48" t="str">
+        <ns0:v>Отделка</ns0:v>
+      </ns0:c>
+      <ns0:c r="AO48"/>
+      <ns0:c r="AP48" t="str">
+        <ns0:v>Стеновые панели, рейки и элементы декора</ns0:v>
+      </ns0:c>
+      <ns0:c r="AQ48" t="str">
+        <ns0:v>Стеновые панели</ns0:v>
+      </ns0:c>
+      <ns0:c r="AR48" t="str">
+        <ns0:v>ПВХ</ns0:v>
+      </ns0:c>
+      <ns0:c r="AS48" t="str">
+        <ns0:v>Стены | Двери</ns0:v>
+      </ns0:c>
+      <ns0:c r="AT48" t="str">
+        <ns0:v>Нет</ns0:v>
+      </ns0:c>
+      <ns0:c r="AU48" t="n">
+        <ns0:v>2800</ns0:v>
+      </ns0:c>
+      <ns0:c r="AV48" t="n">
+        <ns0:v>1140</ns0:v>
+      </ns0:c>
+      <ns0:c r="AW48"/>
+      <ns0:c r="AX48" t="str">
+        <ns0:v>Нет</ns0:v>
+      </ns0:c>
+      <ns0:c r="AY48"/>
+      <ns0:c r="AZ48"/>
+      <ns0:c r="BA48"/>
+      <ns0:c r="BB48"/>
+      <ns0:c r="BC48"/>
+      <ns0:c r="BD48"/>
+      <ns0:c r="BE48"/>
+      <ns0:c r="BF48"/>
+    </ns0:row>
+    <ns0:row r="49">
+      <ns0:c r="A49" t="inlineStr">
+        <ns0:is>
+          <ns0:t>adamar-vlg-Matte_MuccaBlack</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="B49"/>
+      <ns0:c r="C49"/>
+      <ns0:c r="D49"/>
+      <ns0:c r="E49"/>
+      <ns0:c r="F49"/>
+      <ns0:c r="G49" t="str">
+        <ns0:v>Adamar Group</ns0:v>
+      </ns0:c>
+      <ns0:c r="H49" t="str">
+        <ns0:v>79996244489</ns0:v>
+      </ns0:c>
+      <ns0:c r="I49" t="inlineStr">
+        <ns0:is>
+          <ns0:t>Гибкий мрамор 114х280 см — Matte MuccaBlack</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="J49" t="inlineStr">
+        <ns0:is>
+          <ns0:t xml:space="preserve">Гибкий мрамор «Matte MuccaBlack» — выразительная отделка для современного интерьера ✨
+Это широкоформатные панели 114×280 см, которые также называют гибким камнем и микрокальцитными панелями. Материал подходит для кухни, ванной, прихожей, гостиной, офиса и коммерческих помещений. Панели легко режутся и быстро монтируются на прочное основание.
+✅ Есть в наличии в Волгограде.
+🤝 Дилерам и монтажным бригадам предоставляем специальные скидки.
+📍 Приходите в шоурум: ТЦ «Новосрой», 2 этаж, г. Волгоград, ул. 25-летия Октября, д. 1, стр. 3. Посмотрите декоры вживую и получите расчёт количества панелей.</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="K49" t="inlineStr">
+        <ns0:is>
+          <ns0:t>https://avatars.mds.yandex.net/get-yastore/20918687/nmmvrkqblbptwv6rtcmcr46mt58dvzlp/orig | https://avatars.mds.yandex.net/get-yastore/17664496/ldwhvtmm74npzgx2m4q82vrd6fbgqcjr/orig | https://avatars.mds.yandex.net/get-yastore/17664496/qsxth74wj7q6jf62fcfnnjvkfw4kx9bg/orig</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="L49"/>
+      <ns0:c r="M49" t="str">
+        <ns0:v>По телефону и в сообщениях</ns0:v>
+      </ns0:c>
+      <ns0:c r="N49"/>
+      <ns0:c r="O49"/>
+      <ns0:c r="P49"/>
+      <ns0:c r="Q49" t="str">
+        <ns0:v>Ремонт и строительство</ns0:v>
+      </ns0:c>
+      <ns0:c r="R49" t="inlineStr">
+        <ns0:is>
+          <ns0:t>г. Волгоград, ул. 25-летия Октября, д. 1, стр. 3</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="S49"/>
+      <ns0:c r="T49"/>
+      <ns0:c r="U49"/>
+      <ns0:c r="V49" t="str">
+        <ns0:v>Поштучно</ns0:v>
+      </ns0:c>
+      <ns0:c r="W49">
+        <ns0:v>200</ns0:v>
+      </ns0:c>
+      <ns0:c r="X49" t="n">
+        <ns0:v>1</ns0:v>
+      </ns0:c>
+      <ns0:c r="Y49" t="n">
+        <ns0:v>1</ns0:v>
+      </ns0:c>
+      <ns0:c r="Z49" t="str">
+        <ns0:v>Штуку</ns0:v>
+      </ns0:c>
+      <ns0:c r="AA49"/>
+      <ns0:c r="AB49"/>
+      <ns0:c r="AC49"/>
+      <ns0:c r="AD49">
+        <ns0:v>6.5</ns0:v>
+      </ns0:c>
+      <ns0:c r="AE49">
+        <ns0:v>15</ns0:v>
+      </ns0:c>
+      <ns0:c r="AF49">
+        <ns0:v>120</ns0:v>
+      </ns0:c>
+      <ns0:c r="AG49">
+        <ns0:v>15</ns0:v>
+      </ns0:c>
+      <ns0:c r="AH49"/>
+      <ns0:c r="AI49">
+        <ns0:v>4900</ns0:v>
+      </ns0:c>
+      <ns0:c r="AJ49" t="str">
+        <ns0:v>Стройматериалы</ns0:v>
+      </ns0:c>
+      <ns0:c r="AK49" t="str">
+        <ns0:v>Товар от производителя</ns0:v>
+      </ns0:c>
+      <ns0:c r="AL49" t="str">
+        <ns0:v>Новое</ns0:v>
+      </ns0:c>
+      <ns0:c r="AM49" t="inlineStr">
+        <ns0:is>
+          <ns0:t>В наличии</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="AN49" t="str">
+        <ns0:v>Отделка</ns0:v>
+      </ns0:c>
+      <ns0:c r="AO49"/>
+      <ns0:c r="AP49" t="str">
+        <ns0:v>Стеновые панели, рейки и элементы декора</ns0:v>
+      </ns0:c>
+      <ns0:c r="AQ49" t="str">
+        <ns0:v>Стеновые панели</ns0:v>
+      </ns0:c>
+      <ns0:c r="AR49" t="str">
+        <ns0:v>ПВХ</ns0:v>
+      </ns0:c>
+      <ns0:c r="AS49" t="str">
+        <ns0:v>Стены | Двери</ns0:v>
+      </ns0:c>
+      <ns0:c r="AT49" t="str">
+        <ns0:v>Нет</ns0:v>
+      </ns0:c>
+      <ns0:c r="AU49" t="n">
+        <ns0:v>2800</ns0:v>
+      </ns0:c>
+      <ns0:c r="AV49" t="n">
+        <ns0:v>1140</ns0:v>
+      </ns0:c>
+      <ns0:c r="AW49"/>
+      <ns0:c r="AX49" t="str">
+        <ns0:v>Нет</ns0:v>
+      </ns0:c>
+      <ns0:c r="AY49"/>
+      <ns0:c r="AZ49"/>
+      <ns0:c r="BA49"/>
+      <ns0:c r="BB49"/>
+      <ns0:c r="BC49"/>
+      <ns0:c r="BD49"/>
+      <ns0:c r="BE49"/>
+      <ns0:c r="BF49"/>
+    </ns0:row>
+    <ns0:row r="50">
+      <ns0:c r="A50" t="inlineStr">
+        <ns0:is>
+          <ns0:t>adamar-vlg-Glossy_ Lumiere</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="B50"/>
+      <ns0:c r="C50"/>
+      <ns0:c r="D50"/>
+      <ns0:c r="E50"/>
+      <ns0:c r="F50"/>
+      <ns0:c r="G50" t="str">
+        <ns0:v>Adamar Group</ns0:v>
+      </ns0:c>
+      <ns0:c r="H50" t="str">
+        <ns0:v>79996244489</ns0:v>
+      </ns0:c>
+      <ns0:c r="I50" t="inlineStr">
+        <ns0:is>
+          <ns0:t>Гибкий мрамор 114х280 см — Glossy  Lumiere</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="J50" t="inlineStr">
+        <ns0:is>
+          <ns0:t xml:space="preserve">Гибкий мрамор «Glossy  Lumiere» — выразительная отделка для современного интерьера ✨
+Это широкоформатные панели 114×280 см, которые также называют гибким камнем и микрокальцитными панелями. Материал подходит для кухни, ванной, прихожей, гостиной, офиса и коммерческих помещений. Панели легко режутся и быстро монтируются на прочное основание.
+✅ Есть в наличии в Волгограде.
+🤝 Дилерам и монтажным бригадам предоставляем специальные скидки.
+📍 Приходите в шоурум: ТЦ «Новосрой», 2 этаж, г. Волгоград, ул. 25-летия Октября, д. 1, стр. 3. Посмотрите декоры вживую и получите расчёт количества панелей.</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="K50" t="inlineStr">
+        <ns0:is>
+          <ns0:t>https://avatars.mds.yandex.net/get-yastore/20760651/zw47h9dtkpgkfvkjqc4ttccbhpl5n9k2/orig | https://avatars.mds.yandex.net/get-yastore/21104660/4pscxf7dfpxsj5npxhgmbjvnrp7nhjnm/orig | https://avatars.mds.yandex.net/get-yastore/20760651/ph9zczmpmvjmzdph7kh2nmvw8jn4l8z7/orig | https://avatars.mds.yandex.net/get-yastore/14319028/7m482xvxpmnsmnkg667bptv52qxcv2dj/orig</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="L50"/>
+      <ns0:c r="M50" t="str">
+        <ns0:v>По телефону и в сообщениях</ns0:v>
+      </ns0:c>
+      <ns0:c r="N50"/>
+      <ns0:c r="O50"/>
+      <ns0:c r="P50"/>
+      <ns0:c r="Q50" t="str">
+        <ns0:v>Ремонт и строительство</ns0:v>
+      </ns0:c>
+      <ns0:c r="R50" t="inlineStr">
+        <ns0:is>
+          <ns0:t>г. Волгоград, ул. 25-летия Октября, д. 1, стр. 3</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="S50"/>
+      <ns0:c r="T50"/>
+      <ns0:c r="U50"/>
+      <ns0:c r="V50" t="str">
+        <ns0:v>Поштучно</ns0:v>
+      </ns0:c>
+      <ns0:c r="W50">
+        <ns0:v>200</ns0:v>
+      </ns0:c>
+      <ns0:c r="X50" t="n">
+        <ns0:v>1</ns0:v>
+      </ns0:c>
+      <ns0:c r="Y50" t="n">
+        <ns0:v>1</ns0:v>
+      </ns0:c>
+      <ns0:c r="Z50" t="str">
+        <ns0:v>Штуку</ns0:v>
+      </ns0:c>
+      <ns0:c r="AA50"/>
+      <ns0:c r="AB50"/>
+      <ns0:c r="AC50"/>
+      <ns0:c r="AD50">
+        <ns0:v>6.5</ns0:v>
+      </ns0:c>
+      <ns0:c r="AE50">
+        <ns0:v>15</ns0:v>
+      </ns0:c>
+      <ns0:c r="AF50">
+        <ns0:v>120</ns0:v>
+      </ns0:c>
+      <ns0:c r="AG50">
+        <ns0:v>15</ns0:v>
+      </ns0:c>
+      <ns0:c r="AH50"/>
+      <ns0:c r="AI50">
+        <ns0:v>4900</ns0:v>
+      </ns0:c>
+      <ns0:c r="AJ50" t="str">
+        <ns0:v>Стройматериалы</ns0:v>
+      </ns0:c>
+      <ns0:c r="AK50" t="str">
+        <ns0:v>Товар от производителя</ns0:v>
+      </ns0:c>
+      <ns0:c r="AL50" t="str">
+        <ns0:v>Новое</ns0:v>
+      </ns0:c>
+      <ns0:c r="AM50" t="inlineStr">
+        <ns0:is>
+          <ns0:t>В наличии</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="AN50" t="str">
+        <ns0:v>Отделка</ns0:v>
+      </ns0:c>
+      <ns0:c r="AO50"/>
+      <ns0:c r="AP50" t="str">
+        <ns0:v>Стеновые панели, рейки и элементы декора</ns0:v>
+      </ns0:c>
+      <ns0:c r="AQ50" t="str">
+        <ns0:v>Стеновые панели</ns0:v>
+      </ns0:c>
+      <ns0:c r="AR50" t="str">
+        <ns0:v>ПВХ</ns0:v>
+      </ns0:c>
+      <ns0:c r="AS50" t="str">
+        <ns0:v>Стены | Двери</ns0:v>
+      </ns0:c>
+      <ns0:c r="AT50" t="str">
+        <ns0:v>Нет</ns0:v>
+      </ns0:c>
+      <ns0:c r="AU50" t="n">
+        <ns0:v>2800</ns0:v>
+      </ns0:c>
+      <ns0:c r="AV50" t="n">
+        <ns0:v>1140</ns0:v>
+      </ns0:c>
+      <ns0:c r="AW50"/>
+      <ns0:c r="AX50" t="str">
+        <ns0:v>Нет</ns0:v>
+      </ns0:c>
+      <ns0:c r="AY50"/>
+      <ns0:c r="AZ50"/>
+      <ns0:c r="BA50"/>
+      <ns0:c r="BB50"/>
+      <ns0:c r="BC50"/>
+      <ns0:c r="BD50"/>
+      <ns0:c r="BE50"/>
+      <ns0:c r="BF50"/>
+    </ns0:row>
+    <ns0:row r="51">
+      <ns0:c r="A51" t="inlineStr">
+        <ns0:is>
+          <ns0:t>adamar-vlg-BETON GREYSON DECOR</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="B51"/>
+      <ns0:c r="C51"/>
+      <ns0:c r="D51"/>
+      <ns0:c r="E51"/>
+      <ns0:c r="F51"/>
+      <ns0:c r="G51" t="str">
+        <ns0:v>Adamar Group</ns0:v>
+      </ns0:c>
+      <ns0:c r="H51" t="str">
+        <ns0:v>79996244489</ns0:v>
+      </ns0:c>
+      <ns0:c r="I51" t="inlineStr">
+        <ns0:is>
+          <ns0:t>Гибкий мрамор 114х280 см — BETON GREYSON DECOR</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="J51" t="inlineStr">
+        <ns0:is>
+          <ns0:t xml:space="preserve">Гибкий мрамор «BETON GREYSON DECOR» — выразительная отделка для современного интерьера ✨
+Это широкоформатные панели 114×280 см, которые также называют гибким камнем и микрокальцитными панелями. Материал подходит для кухни, ванной, прихожей, гостиной, офиса и коммерческих помещений. Панели легко режутся и быстро монтируются на прочное основание.
+✅ Есть в наличии в Волгограде.
+🤝 Дилерам и монтажным бригадам предоставляем специальные скидки.
+📍 Приходите в шоурум: ТЦ «Новосрой», 2 этаж, г. Волгоград, ул. 25-летия Октября, д. 1, стр. 3. Посмотрите декоры вживую и получите расчёт количества панелей.</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="K51" t="inlineStr">
+        <ns0:is>
+          <ns0:t>https://avatars.mds.yandex.net/get-yastore/20274467/s5lt5gh8ccv6w6876txv5q4rbw2lzmgw/orig | https://avatars.mds.yandex.net/get-yastore/21055393/7x8qzz9s7vqkbkdk675nlwgbpmc66bxt/orig | https://avatars.mds.yandex.net/get-yastore/21055393/qh5k9txzdvknvhw7cl9m9n2sdrcnzljq/orig</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="L51"/>
+      <ns0:c r="M51" t="str">
+        <ns0:v>По телефону и в сообщениях</ns0:v>
+      </ns0:c>
+      <ns0:c r="N51"/>
+      <ns0:c r="O51"/>
+      <ns0:c r="P51"/>
+      <ns0:c r="Q51" t="str">
+        <ns0:v>Ремонт и строительство</ns0:v>
+      </ns0:c>
+      <ns0:c r="R51" t="inlineStr">
+        <ns0:is>
+          <ns0:t>г. Волгоград, ул. 25-летия Октября, д. 1, стр. 3</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="S51"/>
+      <ns0:c r="T51"/>
+      <ns0:c r="U51"/>
+      <ns0:c r="V51" t="str">
+        <ns0:v>Поштучно</ns0:v>
+      </ns0:c>
+      <ns0:c r="W51">
+        <ns0:v>200</ns0:v>
+      </ns0:c>
+      <ns0:c r="X51" t="n">
+        <ns0:v>1</ns0:v>
+      </ns0:c>
+      <ns0:c r="Y51" t="n">
+        <ns0:v>1</ns0:v>
+      </ns0:c>
+      <ns0:c r="Z51" t="str">
+        <ns0:v>Штуку</ns0:v>
+      </ns0:c>
+      <ns0:c r="AA51"/>
+      <ns0:c r="AB51"/>
+      <ns0:c r="AC51"/>
+      <ns0:c r="AD51">
+        <ns0:v>6.5</ns0:v>
+      </ns0:c>
+      <ns0:c r="AE51">
+        <ns0:v>15</ns0:v>
+      </ns0:c>
+      <ns0:c r="AF51">
+        <ns0:v>120</ns0:v>
+      </ns0:c>
+      <ns0:c r="AG51">
+        <ns0:v>15</ns0:v>
+      </ns0:c>
+      <ns0:c r="AH51"/>
+      <ns0:c r="AI51">
+        <ns0:v>4900</ns0:v>
+      </ns0:c>
+      <ns0:c r="AJ51" t="str">
+        <ns0:v>Стройматериалы</ns0:v>
+      </ns0:c>
+      <ns0:c r="AK51" t="str">
+        <ns0:v>Товар от производителя</ns0:v>
+      </ns0:c>
+      <ns0:c r="AL51" t="str">
+        <ns0:v>Новое</ns0:v>
+      </ns0:c>
+      <ns0:c r="AM51" t="inlineStr">
+        <ns0:is>
+          <ns0:t>В наличии</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="AN51" t="str">
+        <ns0:v>Отделка</ns0:v>
+      </ns0:c>
+      <ns0:c r="AO51"/>
+      <ns0:c r="AP51" t="str">
+        <ns0:v>Стеновые панели, рейки и элементы декора</ns0:v>
+      </ns0:c>
+      <ns0:c r="AQ51" t="str">
+        <ns0:v>Стеновые панели</ns0:v>
+      </ns0:c>
+      <ns0:c r="AR51" t="str">
+        <ns0:v>ПВХ</ns0:v>
+      </ns0:c>
+      <ns0:c r="AS51" t="str">
+        <ns0:v>Стены | Двери</ns0:v>
+      </ns0:c>
+      <ns0:c r="AT51" t="str">
+        <ns0:v>Нет</ns0:v>
+      </ns0:c>
+      <ns0:c r="AU51" t="n">
+        <ns0:v>2800</ns0:v>
+      </ns0:c>
+      <ns0:c r="AV51" t="n">
+        <ns0:v>1140</ns0:v>
+      </ns0:c>
+      <ns0:c r="AW51"/>
+      <ns0:c r="AX51" t="str">
+        <ns0:v>Нет</ns0:v>
+      </ns0:c>
+      <ns0:c r="AY51"/>
+      <ns0:c r="AZ51"/>
+      <ns0:c r="BA51"/>
+      <ns0:c r="BB51"/>
+      <ns0:c r="BC51"/>
+      <ns0:c r="BD51"/>
+      <ns0:c r="BE51"/>
+      <ns0:c r="BF51"/>
+    </ns0:row>
+    <ns0:row r="52">
+      <ns0:c r="A52" t="inlineStr">
+        <ns0:is>
+          <ns0:t>adamar-vlg-MARBLE VEIL</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="B52"/>
+      <ns0:c r="C52"/>
+      <ns0:c r="D52"/>
+      <ns0:c r="E52"/>
+      <ns0:c r="F52"/>
+      <ns0:c r="G52" t="str">
+        <ns0:v>Adamar Group</ns0:v>
+      </ns0:c>
+      <ns0:c r="H52" t="str">
+        <ns0:v>79996244489</ns0:v>
+      </ns0:c>
+      <ns0:c r="I52" t="inlineStr">
+        <ns0:is>
+          <ns0:t>Гибкий мрамор 114х280 см — MARBLE VEIL</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="J52" t="inlineStr">
+        <ns0:is>
+          <ns0:t xml:space="preserve">Гибкий мрамор «MARBLE VEIL» — выразительная отделка для современного интерьера ✨
+Это широкоформатные панели 114×280 см, которые также называют гибким камнем и микрокальцитными панелями. Материал подходит для кухни, ванной, прихожей, гостиной, офиса и коммерческих помещений. Панели легко режутся и быстро монтируются на прочное основание.
+✅ Есть в наличии в Волгограде.
+🤝 Дилерам и монтажным бригадам предоставляем специальные скидки.
+📍 Приходите в шоурум: ТЦ «Новосрой», 2 этаж, г. Волгоград, ул. 25-летия Октября, д. 1, стр. 3. Посмотрите декоры вживую и получите расчёт количества панелей.</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="K52" t="inlineStr">
+        <ns0:is>
+          <ns0:t>https://avatars.mds.yandex.net/get-yastore/21012869/5fhjbvfv7lctbpm924m982rdxnpbcnzh/orig | https://avatars.mds.yandex.net/get-yastore/20900992/52ck6jvdlvlk4v8548t7b6cvmknxvp5n/orig | https://avatars.mds.yandex.net/get-yastore/20274467/fp2w4gn8d9gkbsfwxn8t64b57b56s8f2/orig | https://avatars.mds.yandex.net/get-yastore/20274467/llk8s5ztv2tx8657t68wf66qqtn7vd94/orig</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="L52"/>
+      <ns0:c r="M52" t="str">
+        <ns0:v>По телефону и в сообщениях</ns0:v>
+      </ns0:c>
+      <ns0:c r="N52"/>
+      <ns0:c r="O52"/>
+      <ns0:c r="P52"/>
+      <ns0:c r="Q52" t="str">
+        <ns0:v>Ремонт и строительство</ns0:v>
+      </ns0:c>
+      <ns0:c r="R52" t="inlineStr">
+        <ns0:is>
+          <ns0:t>г. Волгоград, ул. 25-летия Октября, д. 1, стр. 3</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="S52"/>
+      <ns0:c r="T52"/>
+      <ns0:c r="U52"/>
+      <ns0:c r="V52" t="str">
+        <ns0:v>Поштучно</ns0:v>
+      </ns0:c>
+      <ns0:c r="W52">
+        <ns0:v>200</ns0:v>
+      </ns0:c>
+      <ns0:c r="X52" t="n">
+        <ns0:v>1</ns0:v>
+      </ns0:c>
+      <ns0:c r="Y52" t="n">
+        <ns0:v>1</ns0:v>
+      </ns0:c>
+      <ns0:c r="Z52" t="str">
+        <ns0:v>Штуку</ns0:v>
+      </ns0:c>
+      <ns0:c r="AA52"/>
+      <ns0:c r="AB52"/>
+      <ns0:c r="AC52"/>
+      <ns0:c r="AD52">
+        <ns0:v>6.5</ns0:v>
+      </ns0:c>
+      <ns0:c r="AE52">
+        <ns0:v>15</ns0:v>
+      </ns0:c>
+      <ns0:c r="AF52">
+        <ns0:v>120</ns0:v>
+      </ns0:c>
+      <ns0:c r="AG52">
+        <ns0:v>15</ns0:v>
+      </ns0:c>
+      <ns0:c r="AH52"/>
+      <ns0:c r="AI52">
+        <ns0:v>4900</ns0:v>
+      </ns0:c>
+      <ns0:c r="AJ52" t="str">
+        <ns0:v>Стройматериалы</ns0:v>
+      </ns0:c>
+      <ns0:c r="AK52" t="str">
+        <ns0:v>Товар от производителя</ns0:v>
+      </ns0:c>
+      <ns0:c r="AL52" t="str">
+        <ns0:v>Новое</ns0:v>
+      </ns0:c>
+      <ns0:c r="AM52" t="inlineStr">
+        <ns0:is>
+          <ns0:t>В наличии</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="AN52" t="str">
+        <ns0:v>Отделка</ns0:v>
+      </ns0:c>
+      <ns0:c r="AO52"/>
+      <ns0:c r="AP52" t="str">
+        <ns0:v>Стеновые панели, рейки и элементы декора</ns0:v>
+      </ns0:c>
+      <ns0:c r="AQ52" t="str">
+        <ns0:v>Стеновые панели</ns0:v>
+      </ns0:c>
+      <ns0:c r="AR52" t="str">
+        <ns0:v>ПВХ</ns0:v>
+      </ns0:c>
+      <ns0:c r="AS52" t="str">
+        <ns0:v>Стены | Двери</ns0:v>
+      </ns0:c>
+      <ns0:c r="AT52" t="str">
+        <ns0:v>Нет</ns0:v>
+      </ns0:c>
+      <ns0:c r="AU52" t="n">
+        <ns0:v>2800</ns0:v>
+      </ns0:c>
+      <ns0:c r="AV52" t="n">
+        <ns0:v>1140</ns0:v>
+      </ns0:c>
+      <ns0:c r="AW52"/>
+      <ns0:c r="AX52" t="str">
+        <ns0:v>Нет</ns0:v>
+      </ns0:c>
+      <ns0:c r="AY52"/>
+      <ns0:c r="AZ52"/>
+      <ns0:c r="BA52"/>
+      <ns0:c r="BB52"/>
+      <ns0:c r="BC52"/>
+      <ns0:c r="BD52"/>
+      <ns0:c r="BE52"/>
+      <ns0:c r="BF52"/>
     </ns0:row>
   </ns0:sheetData>
   <ns0:dataValidations count="24">

--- a/avito.xlsx
+++ b/avito.xlsx
@@ -2,9 +2,9 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Инструкция" sheetId="1" r:id="R595ca59ab20144c3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Объявления" sheetId="2" r:id="R5aaa42581b6341ca"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Справочники" sheetId="3" r:id="Ref9e40d10f2a4e8f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Инструкция" sheetId="1" r:id="R840612ec3319472d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Объявления" sheetId="2" r:id="R0ec6555926174044"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Справочники" sheetId="3" r:id="Ra02fa7e921694175"/>
   </x:sheets>
   <x:definedNames>
     <x:definedName name="Instructions" localSheetId="0">Инструкция!$1:$50</x:definedName>
@@ -1913,13 +1913,13 @@
     </x:row>
   </x:sheetData>
   <x:hyperlinks>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B4" r:id="Re0314bd1e381475d"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B5" r:id="Rfbd5a29e8ba44557"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B20" r:id="R9e672130433d4a1d"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B21" r:id="Rae64f50c9d2840f1"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B25" r:id="R00cf6bac6b3048c6"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B31" r:id="Rea834097c3524eeb"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B34" r:id="Ra5f06f0b28614024"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B4" r:id="R4ec80864efd64b8c"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B5" r:id="R722d6521ecbb49a7"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B20" r:id="Rfdad2617063e4117"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B21" r:id="Rebd9e863d8b44611"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B25" r:id="R38d41b2af63749a3"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B31" r:id="R2e05cc0911ee4478"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B34" r:id="Rbcb02398b74b4464"/>
   </x:hyperlinks>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
@@ -2640,11 +2640,11 @@
       <x:c r="A5" t="str">
         <x:v>adamar-vlg-WHITE CONCRETE_1</x:v>
       </x:c>
-      <x:c r="B5" t="str"/>
-      <x:c r="C5" t="str"/>
-      <x:c r="D5" t="str"/>
-      <x:c r="E5" t="str"/>
-      <x:c r="F5" t="str"/>
+      <x:c r="B5"/>
+      <x:c r="C5"/>
+      <x:c r="D5"/>
+      <x:c r="E5"/>
+      <x:c r="F5"/>
       <x:c r="G5" t="str">
         <x:v>Adamar Group</x:v>
       </x:c>
@@ -2671,22 +2671,22 @@
       <x:c r="K5" t="str">
         <x:v>https://avatars.mds.yandex.net/get-yastore/20760651/hzcnmmgxsdvr4ml8wdnjqmffft5jhjtc/orig | https://avatars.mds.yandex.net/get-yastore/21044143/r4bpdkc7m46nn5nx2brwptjdqctlhk7t/orig | https://avatars.mds.yandex.net/get-yastore/21044143/dsfdgrdk2k2q2hvk56cf8v2g2z8kw4bb/orig | https://avatars.mds.yandex.net/get-yastore/20274467/dd25xxsshglhg7tztjqg92qhnc5f9g7r/orig | https://avatars.mds.yandex.net/get-yastore/20760651/xcw6762ckjtd79pkgxkcnc4mhlgk66f2/orig</x:v>
       </x:c>
-      <x:c r="L5" t="str"/>
+      <x:c r="L5"/>
       <x:c r="M5" t="str">
         <x:v>По телефону и в сообщениях</x:v>
       </x:c>
-      <x:c r="N5" t="str"/>
-      <x:c r="O5" t="str"/>
-      <x:c r="P5" t="str"/>
+      <x:c r="N5"/>
+      <x:c r="O5"/>
+      <x:c r="P5"/>
       <x:c r="Q5" t="str">
         <x:v>Ремонт и строительство</x:v>
       </x:c>
       <x:c r="R5" t="str">
         <x:v>г. Волгоград, ул. 25-летия Октября, д. 1, стр. 3</x:v>
       </x:c>
-      <x:c r="S5" t="str"/>
-      <x:c r="T5" t="str"/>
-      <x:c r="U5" t="str"/>
+      <x:c r="S5"/>
+      <x:c r="T5"/>
+      <x:c r="U5"/>
       <x:c r="V5" t="str">
         <x:v>Поштучно</x:v>
       </x:c>
@@ -2702,9 +2702,9 @@
       <x:c r="Z5" t="str">
         <x:v>Штуку</x:v>
       </x:c>
-      <x:c r="AA5" t="str"/>
-      <x:c r="AB5" t="str"/>
-      <x:c r="AC5" t="str"/>
+      <x:c r="AA5"/>
+      <x:c r="AB5"/>
+      <x:c r="AC5"/>
       <x:c r="AD5" t="n">
         <x:v>7</x:v>
       </x:c>
@@ -2717,26 +2717,24 @@
       <x:c r="AG5" t="n">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="AH5" t="str"/>
+      <x:c r="AH5"/>
       <x:c r="AI5" t="str">
         <x:v>3921120000</x:v>
       </x:c>
-      <x:c r="AJ5" t="str">
-        <x:v>22.21.42.110</x:v>
-      </x:c>
-      <x:c r="AK5" t="str"/>
-      <x:c r="AL5" t="str"/>
-      <x:c r="AM5" t="str"/>
-      <x:c r="AN5" t="str"/>
-      <x:c r="AO5" t="str"/>
-      <x:c r="AP5" t="str"/>
-      <x:c r="AQ5" t="str"/>
-      <x:c r="AR5" t="str"/>
-      <x:c r="AS5" t="str"/>
-      <x:c r="AT5" t="str"/>
-      <x:c r="AU5" t="str"/>
-      <x:c r="AV5" t="str"/>
-      <x:c r="AW5" t="str"/>
+      <x:c r="AJ5" t="str"/>
+      <x:c r="AK5"/>
+      <x:c r="AL5"/>
+      <x:c r="AM5"/>
+      <x:c r="AN5"/>
+      <x:c r="AO5"/>
+      <x:c r="AP5"/>
+      <x:c r="AQ5"/>
+      <x:c r="AR5"/>
+      <x:c r="AS5"/>
+      <x:c r="AT5"/>
+      <x:c r="AU5"/>
+      <x:c r="AV5"/>
+      <x:c r="AW5"/>
       <x:c r="AX5" t="str">
         <x:v>3921</x:v>
       </x:c>
@@ -2755,7 +2753,7 @@
       <x:c r="BC5" t="str">
         <x:v>Отделка</x:v>
       </x:c>
-      <x:c r="BD5" t="str"/>
+      <x:c r="BD5"/>
       <x:c r="BE5" t="str">
         <x:v>Стеновые панели, рейки и элементы декора</x:v>
       </x:c>
@@ -2777,28 +2775,28 @@
       <x:c r="BK5" t="str">
         <x:v>1140</x:v>
       </x:c>
-      <x:c r="BL5" t="str"/>
+      <x:c r="BL5"/>
       <x:c r="BM5" t="str">
         <x:v>Нет</x:v>
       </x:c>
-      <x:c r="BN5" t="str"/>
-      <x:c r="BO5" t="str"/>
-      <x:c r="BP5" t="str"/>
-      <x:c r="BQ5" t="str"/>
-      <x:c r="BR5" t="str"/>
-      <x:c r="BS5" t="str"/>
-      <x:c r="BT5" t="str"/>
-      <x:c r="BU5" t="str"/>
+      <x:c r="BN5"/>
+      <x:c r="BO5"/>
+      <x:c r="BP5"/>
+      <x:c r="BQ5"/>
+      <x:c r="BR5"/>
+      <x:c r="BS5"/>
+      <x:c r="BT5"/>
+      <x:c r="BU5"/>
     </x:row>
     <x:row r="6">
       <x:c r="A6" t="str">
         <x:v>adamar-vlg-ДУБ СОНОМА</x:v>
       </x:c>
-      <x:c r="B6" t="str"/>
-      <x:c r="C6" t="str"/>
-      <x:c r="D6" t="str"/>
-      <x:c r="E6" t="str"/>
-      <x:c r="F6" t="str"/>
+      <x:c r="B6"/>
+      <x:c r="C6"/>
+      <x:c r="D6"/>
+      <x:c r="E6"/>
+      <x:c r="F6"/>
       <x:c r="G6" t="str">
         <x:v>Adamar Group</x:v>
       </x:c>
@@ -2825,22 +2823,22 @@
       <x:c r="K6" t="str">
         <x:v>https://avatars.mds.yandex.net/get-yastore/18919159/p7r2b4mtds77d6lzdjz6ksgbcd9kgcx9/orig | https://avatars.mds.yandex.net/get-yastore/18919159/m8dvrkghm7lh2jpg5v76928tc56xbllp/orig | https://avatars.mds.yandex.net/get-yastore/21598990/nm66rkbzrndqsp86grkbf5w6rqlfpp27/orig | https://avatars.mds.yandex.net/get-yastore/19034732/9vf677trzvspc2bpjpbhzgv6ph79w6sf/orig | https://avatars.mds.yandex.net/get-yastore/18919159/bdz5sbrvkr2z6wxw626w5jrxx6shbvwq/orig</x:v>
       </x:c>
-      <x:c r="L6" t="str"/>
+      <x:c r="L6"/>
       <x:c r="M6" t="str">
         <x:v>По телефону и в сообщениях</x:v>
       </x:c>
-      <x:c r="N6" t="str"/>
-      <x:c r="O6" t="str"/>
-      <x:c r="P6" t="str"/>
+      <x:c r="N6"/>
+      <x:c r="O6"/>
+      <x:c r="P6"/>
       <x:c r="Q6" t="str">
         <x:v>Ремонт и строительство</x:v>
       </x:c>
       <x:c r="R6" t="str">
         <x:v>г. Волгоград, ул. 25-летия Октября, д. 1, стр. 3</x:v>
       </x:c>
-      <x:c r="S6" t="str"/>
-      <x:c r="T6" t="str"/>
-      <x:c r="U6" t="str"/>
+      <x:c r="S6"/>
+      <x:c r="T6"/>
+      <x:c r="U6"/>
       <x:c r="V6" t="str">
         <x:v>Поштучно</x:v>
       </x:c>
@@ -2856,9 +2854,9 @@
       <x:c r="Z6" t="str">
         <x:v>Штуку</x:v>
       </x:c>
-      <x:c r="AA6" t="str"/>
-      <x:c r="AB6" t="str"/>
-      <x:c r="AC6" t="str"/>
+      <x:c r="AA6"/>
+      <x:c r="AB6"/>
+      <x:c r="AC6"/>
       <x:c r="AD6" t="n">
         <x:v>7</x:v>
       </x:c>
@@ -2871,26 +2869,24 @@
       <x:c r="AG6" t="n">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="AH6" t="str"/>
+      <x:c r="AH6"/>
       <x:c r="AI6" t="str">
         <x:v>3921120000</x:v>
       </x:c>
-      <x:c r="AJ6" t="str">
-        <x:v>22.21.42.110</x:v>
-      </x:c>
-      <x:c r="AK6" t="str"/>
-      <x:c r="AL6" t="str"/>
-      <x:c r="AM6" t="str"/>
-      <x:c r="AN6" t="str"/>
-      <x:c r="AO6" t="str"/>
-      <x:c r="AP6" t="str"/>
-      <x:c r="AQ6" t="str"/>
-      <x:c r="AR6" t="str"/>
-      <x:c r="AS6" t="str"/>
-      <x:c r="AT6" t="str"/>
-      <x:c r="AU6" t="str"/>
-      <x:c r="AV6" t="str"/>
-      <x:c r="AW6" t="str"/>
+      <x:c r="AJ6" t="str"/>
+      <x:c r="AK6"/>
+      <x:c r="AL6"/>
+      <x:c r="AM6"/>
+      <x:c r="AN6"/>
+      <x:c r="AO6"/>
+      <x:c r="AP6"/>
+      <x:c r="AQ6"/>
+      <x:c r="AR6"/>
+      <x:c r="AS6"/>
+      <x:c r="AT6"/>
+      <x:c r="AU6"/>
+      <x:c r="AV6"/>
+      <x:c r="AW6"/>
       <x:c r="AX6" t="str">
         <x:v>3921</x:v>
       </x:c>
@@ -2909,7 +2905,7 @@
       <x:c r="BC6" t="str">
         <x:v>Отделка</x:v>
       </x:c>
-      <x:c r="BD6" t="str"/>
+      <x:c r="BD6"/>
       <x:c r="BE6" t="str">
         <x:v>Стеновые панели, рейки и элементы декора</x:v>
       </x:c>
@@ -2931,28 +2927,28 @@
       <x:c r="BK6" t="str">
         <x:v>1140</x:v>
       </x:c>
-      <x:c r="BL6" t="str"/>
+      <x:c r="BL6"/>
       <x:c r="BM6" t="str">
         <x:v>Нет</x:v>
       </x:c>
-      <x:c r="BN6" t="str"/>
-      <x:c r="BO6" t="str"/>
-      <x:c r="BP6" t="str"/>
-      <x:c r="BQ6" t="str"/>
-      <x:c r="BR6" t="str"/>
-      <x:c r="BS6" t="str"/>
-      <x:c r="BT6" t="str"/>
-      <x:c r="BU6" t="str"/>
+      <x:c r="BN6"/>
+      <x:c r="BO6"/>
+      <x:c r="BP6"/>
+      <x:c r="BQ6"/>
+      <x:c r="BR6"/>
+      <x:c r="BS6"/>
+      <x:c r="BT6"/>
+      <x:c r="BU6"/>
     </x:row>
     <x:row r="7">
       <x:c r="A7" t="str">
         <x:v>adamar-vlg-WHITE CONCRETE FON</x:v>
       </x:c>
-      <x:c r="B7" t="str"/>
-      <x:c r="C7" t="str"/>
-      <x:c r="D7" t="str"/>
-      <x:c r="E7" t="str"/>
-      <x:c r="F7" t="str"/>
+      <x:c r="B7"/>
+      <x:c r="C7"/>
+      <x:c r="D7"/>
+      <x:c r="E7"/>
+      <x:c r="F7"/>
       <x:c r="G7" t="str">
         <x:v>Adamar Group</x:v>
       </x:c>
@@ -2979,22 +2975,22 @@
       <x:c r="K7" t="str">
         <x:v>https://avatars.mds.yandex.net/get-yastore/20760651/jxvfhrwn5qgx4v29kj74p2wknsjtqjl5/orig | https://avatars.mds.yandex.net/get-yastore/20760651/xmsrjq5wl6dpz7gq6v98f4vcwxvc692s/orig | https://avatars.mds.yandex.net/get-yastore/20760651/x8lfdrwhmtgbsnqkbj5cb6chhvvntlwl/orig | https://avatars.mds.yandex.net/get-yastore/20760651/87jmpptxgkltrl79k95488prdfqjn2w6/orig | https://avatars.mds.yandex.net/get-yastore/20760651/xcw6762ckjtd79pkgxkcnc4mhlgk66f2/orig</x:v>
       </x:c>
-      <x:c r="L7" t="str"/>
+      <x:c r="L7"/>
       <x:c r="M7" t="str">
         <x:v>По телефону и в сообщениях</x:v>
       </x:c>
-      <x:c r="N7" t="str"/>
-      <x:c r="O7" t="str"/>
-      <x:c r="P7" t="str"/>
+      <x:c r="N7"/>
+      <x:c r="O7"/>
+      <x:c r="P7"/>
       <x:c r="Q7" t="str">
         <x:v>Ремонт и строительство</x:v>
       </x:c>
       <x:c r="R7" t="str">
         <x:v>г. Волгоград, ул. 25-летия Октября, д. 1, стр. 3</x:v>
       </x:c>
-      <x:c r="S7" t="str"/>
-      <x:c r="T7" t="str"/>
-      <x:c r="U7" t="str"/>
+      <x:c r="S7"/>
+      <x:c r="T7"/>
+      <x:c r="U7"/>
       <x:c r="V7" t="str">
         <x:v>Поштучно</x:v>
       </x:c>
@@ -3010,9 +3006,9 @@
       <x:c r="Z7" t="str">
         <x:v>Штуку</x:v>
       </x:c>
-      <x:c r="AA7" t="str"/>
-      <x:c r="AB7" t="str"/>
-      <x:c r="AC7" t="str"/>
+      <x:c r="AA7"/>
+      <x:c r="AB7"/>
+      <x:c r="AC7"/>
       <x:c r="AD7" t="n">
         <x:v>7</x:v>
       </x:c>
@@ -3025,26 +3021,24 @@
       <x:c r="AG7" t="n">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="AH7" t="str"/>
+      <x:c r="AH7"/>
       <x:c r="AI7" t="str">
         <x:v>3921120000</x:v>
       </x:c>
-      <x:c r="AJ7" t="str">
-        <x:v>22.21.42.110</x:v>
-      </x:c>
-      <x:c r="AK7" t="str"/>
-      <x:c r="AL7" t="str"/>
-      <x:c r="AM7" t="str"/>
-      <x:c r="AN7" t="str"/>
-      <x:c r="AO7" t="str"/>
-      <x:c r="AP7" t="str"/>
-      <x:c r="AQ7" t="str"/>
-      <x:c r="AR7" t="str"/>
-      <x:c r="AS7" t="str"/>
-      <x:c r="AT7" t="str"/>
-      <x:c r="AU7" t="str"/>
-      <x:c r="AV7" t="str"/>
-      <x:c r="AW7" t="str"/>
+      <x:c r="AJ7" t="str"/>
+      <x:c r="AK7"/>
+      <x:c r="AL7"/>
+      <x:c r="AM7"/>
+      <x:c r="AN7"/>
+      <x:c r="AO7"/>
+      <x:c r="AP7"/>
+      <x:c r="AQ7"/>
+      <x:c r="AR7"/>
+      <x:c r="AS7"/>
+      <x:c r="AT7"/>
+      <x:c r="AU7"/>
+      <x:c r="AV7"/>
+      <x:c r="AW7"/>
       <x:c r="AX7" t="str">
         <x:v>3921</x:v>
       </x:c>
@@ -3063,7 +3057,7 @@
       <x:c r="BC7" t="str">
         <x:v>Отделка</x:v>
       </x:c>
-      <x:c r="BD7" t="str"/>
+      <x:c r="BD7"/>
       <x:c r="BE7" t="str">
         <x:v>Стеновые панели, рейки и элементы декора</x:v>
       </x:c>
@@ -3085,28 +3079,28 @@
       <x:c r="BK7" t="str">
         <x:v>1140</x:v>
       </x:c>
-      <x:c r="BL7" t="str"/>
+      <x:c r="BL7"/>
       <x:c r="BM7" t="str">
         <x:v>Нет</x:v>
       </x:c>
-      <x:c r="BN7" t="str"/>
-      <x:c r="BO7" t="str"/>
-      <x:c r="BP7" t="str"/>
-      <x:c r="BQ7" t="str"/>
-      <x:c r="BR7" t="str"/>
-      <x:c r="BS7" t="str"/>
-      <x:c r="BT7" t="str"/>
-      <x:c r="BU7" t="str"/>
+      <x:c r="BN7"/>
+      <x:c r="BO7"/>
+      <x:c r="BP7"/>
+      <x:c r="BQ7"/>
+      <x:c r="BR7"/>
+      <x:c r="BS7"/>
+      <x:c r="BT7"/>
+      <x:c r="BU7"/>
     </x:row>
     <x:row r="8">
       <x:c r="A8" t="str">
         <x:v>adamar-vlg-GREY LORD_1</x:v>
       </x:c>
-      <x:c r="B8" t="str"/>
-      <x:c r="C8" t="str"/>
-      <x:c r="D8" t="str"/>
-      <x:c r="E8" t="str"/>
-      <x:c r="F8" t="str"/>
+      <x:c r="B8"/>
+      <x:c r="C8"/>
+      <x:c r="D8"/>
+      <x:c r="E8"/>
+      <x:c r="F8"/>
       <x:c r="G8" t="str">
         <x:v>Adamar Group</x:v>
       </x:c>
@@ -3133,22 +3127,22 @@
       <x:c r="K8" t="str">
         <x:v>https://avatars.mds.yandex.net/get-yastore/21044143/zchqpmj7gl7k4c5lz72mxv5cr8n6mms7/orig | https://avatars.mds.yandex.net/get-yastore/20918687/4pznjgzkm2wf9qbtrbz4xfn7hg8mhm4j/orig | https://avatars.mds.yandex.net/get-yastore/20918687/7l568nzcwmdvm6jwwgd7srnfxvl8c6p8/orig | https://avatars.mds.yandex.net/get-yastore/20274467/4qvg5mb65w8ptttxbbj8qch54784c4d5/orig</x:v>
       </x:c>
-      <x:c r="L8" t="str"/>
+      <x:c r="L8"/>
       <x:c r="M8" t="str">
         <x:v>По телефону и в сообщениях</x:v>
       </x:c>
-      <x:c r="N8" t="str"/>
-      <x:c r="O8" t="str"/>
-      <x:c r="P8" t="str"/>
+      <x:c r="N8"/>
+      <x:c r="O8"/>
+      <x:c r="P8"/>
       <x:c r="Q8" t="str">
         <x:v>Ремонт и строительство</x:v>
       </x:c>
       <x:c r="R8" t="str">
         <x:v>г. Волгоград, ул. 25-летия Октября, д. 1, стр. 3</x:v>
       </x:c>
-      <x:c r="S8" t="str"/>
-      <x:c r="T8" t="str"/>
-      <x:c r="U8" t="str"/>
+      <x:c r="S8"/>
+      <x:c r="T8"/>
+      <x:c r="U8"/>
       <x:c r="V8" t="str">
         <x:v>Поштучно</x:v>
       </x:c>
@@ -3164,9 +3158,9 @@
       <x:c r="Z8" t="str">
         <x:v>Штуку</x:v>
       </x:c>
-      <x:c r="AA8" t="str"/>
-      <x:c r="AB8" t="str"/>
-      <x:c r="AC8" t="str"/>
+      <x:c r="AA8"/>
+      <x:c r="AB8"/>
+      <x:c r="AC8"/>
       <x:c r="AD8" t="n">
         <x:v>7</x:v>
       </x:c>
@@ -3179,26 +3173,24 @@
       <x:c r="AG8" t="n">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="AH8" t="str"/>
+      <x:c r="AH8"/>
       <x:c r="AI8" t="str">
         <x:v>3921120000</x:v>
       </x:c>
-      <x:c r="AJ8" t="str">
-        <x:v>22.21.42.110</x:v>
-      </x:c>
-      <x:c r="AK8" t="str"/>
-      <x:c r="AL8" t="str"/>
-      <x:c r="AM8" t="str"/>
-      <x:c r="AN8" t="str"/>
-      <x:c r="AO8" t="str"/>
-      <x:c r="AP8" t="str"/>
-      <x:c r="AQ8" t="str"/>
-      <x:c r="AR8" t="str"/>
-      <x:c r="AS8" t="str"/>
-      <x:c r="AT8" t="str"/>
-      <x:c r="AU8" t="str"/>
-      <x:c r="AV8" t="str"/>
-      <x:c r="AW8" t="str"/>
+      <x:c r="AJ8" t="str"/>
+      <x:c r="AK8"/>
+      <x:c r="AL8"/>
+      <x:c r="AM8"/>
+      <x:c r="AN8"/>
+      <x:c r="AO8"/>
+      <x:c r="AP8"/>
+      <x:c r="AQ8"/>
+      <x:c r="AR8"/>
+      <x:c r="AS8"/>
+      <x:c r="AT8"/>
+      <x:c r="AU8"/>
+      <x:c r="AV8"/>
+      <x:c r="AW8"/>
       <x:c r="AX8" t="str">
         <x:v>3921</x:v>
       </x:c>
@@ -3217,7 +3209,7 @@
       <x:c r="BC8" t="str">
         <x:v>Отделка</x:v>
       </x:c>
-      <x:c r="BD8" t="str"/>
+      <x:c r="BD8"/>
       <x:c r="BE8" t="str">
         <x:v>Стеновые панели, рейки и элементы декора</x:v>
       </x:c>
@@ -3239,28 +3231,28 @@
       <x:c r="BK8" t="str">
         <x:v>1140</x:v>
       </x:c>
-      <x:c r="BL8" t="str"/>
+      <x:c r="BL8"/>
       <x:c r="BM8" t="str">
         <x:v>Нет</x:v>
       </x:c>
-      <x:c r="BN8" t="str"/>
-      <x:c r="BO8" t="str"/>
-      <x:c r="BP8" t="str"/>
-      <x:c r="BQ8" t="str"/>
-      <x:c r="BR8" t="str"/>
-      <x:c r="BS8" t="str"/>
-      <x:c r="BT8" t="str"/>
-      <x:c r="BU8" t="str"/>
+      <x:c r="BN8"/>
+      <x:c r="BO8"/>
+      <x:c r="BP8"/>
+      <x:c r="BQ8"/>
+      <x:c r="BR8"/>
+      <x:c r="BS8"/>
+      <x:c r="BT8"/>
+      <x:c r="BU8"/>
     </x:row>
     <x:row r="9">
       <x:c r="A9" t="str">
         <x:v>adamar-vlg-WHITE ROCK</x:v>
       </x:c>
-      <x:c r="B9" t="str"/>
-      <x:c r="C9" t="str"/>
-      <x:c r="D9" t="str"/>
-      <x:c r="E9" t="str"/>
-      <x:c r="F9" t="str"/>
+      <x:c r="B9"/>
+      <x:c r="C9"/>
+      <x:c r="D9"/>
+      <x:c r="E9"/>
+      <x:c r="F9"/>
       <x:c r="G9" t="str">
         <x:v>Adamar Group</x:v>
       </x:c>
@@ -3287,22 +3279,22 @@
       <x:c r="K9" t="str">
         <x:v>https://avatars.mds.yandex.net/get-yastore/20811730/cqpzstj9nzd8wrbprll9frnrl6x9g4wp/orig | https://avatars.mds.yandex.net/get-yastore/21497181/nwc5cp78n76vn97z555g2zlbvfmf22kl/orig | https://avatars.mds.yandex.net/get-yastore/21598990/6cxjqfncddsz5hcd72mb8mc7nlplxd5h/orig | https://avatars.mds.yandex.net/get-yastore/19034732/s67p8kgt597xq9kzwvdhs9x4k4knk4b5/orig | https://avatars.mds.yandex.net/get-yastore/19034732/d95z2nt8lmf8rvq68qtgvmvdskjnj665/orig</x:v>
       </x:c>
-      <x:c r="L9" t="str"/>
+      <x:c r="L9"/>
       <x:c r="M9" t="str">
         <x:v>По телефону и в сообщениях</x:v>
       </x:c>
-      <x:c r="N9" t="str"/>
-      <x:c r="O9" t="str"/>
-      <x:c r="P9" t="str"/>
+      <x:c r="N9"/>
+      <x:c r="O9"/>
+      <x:c r="P9"/>
       <x:c r="Q9" t="str">
         <x:v>Ремонт и строительство</x:v>
       </x:c>
       <x:c r="R9" t="str">
         <x:v>г. Волгоград, ул. 25-летия Октября, д. 1, стр. 3</x:v>
       </x:c>
-      <x:c r="S9" t="str"/>
-      <x:c r="T9" t="str"/>
-      <x:c r="U9" t="str"/>
+      <x:c r="S9"/>
+      <x:c r="T9"/>
+      <x:c r="U9"/>
       <x:c r="V9" t="str">
         <x:v>Поштучно</x:v>
       </x:c>
@@ -3318,9 +3310,9 @@
       <x:c r="Z9" t="str">
         <x:v>Штуку</x:v>
       </x:c>
-      <x:c r="AA9" t="str"/>
-      <x:c r="AB9" t="str"/>
-      <x:c r="AC9" t="str"/>
+      <x:c r="AA9"/>
+      <x:c r="AB9"/>
+      <x:c r="AC9"/>
       <x:c r="AD9" t="n">
         <x:v>7</x:v>
       </x:c>
@@ -3333,26 +3325,24 @@
       <x:c r="AG9" t="n">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="AH9" t="str"/>
+      <x:c r="AH9"/>
       <x:c r="AI9" t="str">
         <x:v>3921120000</x:v>
       </x:c>
-      <x:c r="AJ9" t="str">
-        <x:v>22.21.42.110</x:v>
-      </x:c>
-      <x:c r="AK9" t="str"/>
-      <x:c r="AL9" t="str"/>
-      <x:c r="AM9" t="str"/>
-      <x:c r="AN9" t="str"/>
-      <x:c r="AO9" t="str"/>
-      <x:c r="AP9" t="str"/>
-      <x:c r="AQ9" t="str"/>
-      <x:c r="AR9" t="str"/>
-      <x:c r="AS9" t="str"/>
-      <x:c r="AT9" t="str"/>
-      <x:c r="AU9" t="str"/>
-      <x:c r="AV9" t="str"/>
-      <x:c r="AW9" t="str"/>
+      <x:c r="AJ9" t="str"/>
+      <x:c r="AK9"/>
+      <x:c r="AL9"/>
+      <x:c r="AM9"/>
+      <x:c r="AN9"/>
+      <x:c r="AO9"/>
+      <x:c r="AP9"/>
+      <x:c r="AQ9"/>
+      <x:c r="AR9"/>
+      <x:c r="AS9"/>
+      <x:c r="AT9"/>
+      <x:c r="AU9"/>
+      <x:c r="AV9"/>
+      <x:c r="AW9"/>
       <x:c r="AX9" t="str">
         <x:v>3921</x:v>
       </x:c>
@@ -3371,7 +3361,7 @@
       <x:c r="BC9" t="str">
         <x:v>Отделка</x:v>
       </x:c>
-      <x:c r="BD9" t="str"/>
+      <x:c r="BD9"/>
       <x:c r="BE9" t="str">
         <x:v>Стеновые панели, рейки и элементы декора</x:v>
       </x:c>
@@ -3393,28 +3383,28 @@
       <x:c r="BK9" t="str">
         <x:v>1140</x:v>
       </x:c>
-      <x:c r="BL9" t="str"/>
+      <x:c r="BL9"/>
       <x:c r="BM9" t="str">
         <x:v>Нет</x:v>
       </x:c>
-      <x:c r="BN9" t="str"/>
-      <x:c r="BO9" t="str"/>
-      <x:c r="BP9" t="str"/>
-      <x:c r="BQ9" t="str"/>
-      <x:c r="BR9" t="str"/>
-      <x:c r="BS9" t="str"/>
-      <x:c r="BT9" t="str"/>
-      <x:c r="BU9" t="str"/>
+      <x:c r="BN9"/>
+      <x:c r="BO9"/>
+      <x:c r="BP9"/>
+      <x:c r="BQ9"/>
+      <x:c r="BR9"/>
+      <x:c r="BS9"/>
+      <x:c r="BT9"/>
+      <x:c r="BU9"/>
     </x:row>
     <x:row r="10">
       <x:c r="A10" t="str">
         <x:v>adamar-vlg-ОРЕХ ТЕМНЫЙ</x:v>
       </x:c>
-      <x:c r="B10" t="str"/>
-      <x:c r="C10" t="str"/>
-      <x:c r="D10" t="str"/>
-      <x:c r="E10" t="str"/>
-      <x:c r="F10" t="str"/>
+      <x:c r="B10"/>
+      <x:c r="C10"/>
+      <x:c r="D10"/>
+      <x:c r="E10"/>
+      <x:c r="F10"/>
       <x:c r="G10" t="str">
         <x:v>Adamar Group</x:v>
       </x:c>
@@ -3441,22 +3431,22 @@
       <x:c r="K10" t="str">
         <x:v>https://avatars.mds.yandex.net/get-yastore/21580234/kqljphlmrr8v4ftp5q7fgnc7m2x6mwxg/orig | https://avatars.mds.yandex.net/get-yastore/20811730/z2jfrv44x46kw2xnqxjdmcjlkjjkc7qt/orig | https://avatars.mds.yandex.net/get-yastore/19782553/gqwpd5z6k62dbtwxtm4dptjtf2jmqpdz/orig | https://avatars.mds.yandex.net/get-yastore/18919159/bvccxxtwvgdx2f6l9vjgxn94s2jrzrwk/orig</x:v>
       </x:c>
-      <x:c r="L10" t="str"/>
+      <x:c r="L10"/>
       <x:c r="M10" t="str">
         <x:v>По телефону и в сообщениях</x:v>
       </x:c>
-      <x:c r="N10" t="str"/>
-      <x:c r="O10" t="str"/>
-      <x:c r="P10" t="str"/>
+      <x:c r="N10"/>
+      <x:c r="O10"/>
+      <x:c r="P10"/>
       <x:c r="Q10" t="str">
         <x:v>Ремонт и строительство</x:v>
       </x:c>
       <x:c r="R10" t="str">
         <x:v>г. Волгоград, ул. 25-летия Октября, д. 1, стр. 3</x:v>
       </x:c>
-      <x:c r="S10" t="str"/>
-      <x:c r="T10" t="str"/>
-      <x:c r="U10" t="str"/>
+      <x:c r="S10"/>
+      <x:c r="T10"/>
+      <x:c r="U10"/>
       <x:c r="V10" t="str">
         <x:v>Поштучно</x:v>
       </x:c>
@@ -3472,9 +3462,9 @@
       <x:c r="Z10" t="str">
         <x:v>Штуку</x:v>
       </x:c>
-      <x:c r="AA10" t="str"/>
-      <x:c r="AB10" t="str"/>
-      <x:c r="AC10" t="str"/>
+      <x:c r="AA10"/>
+      <x:c r="AB10"/>
+      <x:c r="AC10"/>
       <x:c r="AD10" t="n">
         <x:v>7</x:v>
       </x:c>
@@ -3487,26 +3477,24 @@
       <x:c r="AG10" t="n">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="AH10" t="str"/>
+      <x:c r="AH10"/>
       <x:c r="AI10" t="str">
         <x:v>3921120000</x:v>
       </x:c>
-      <x:c r="AJ10" t="str">
-        <x:v>22.21.42.110</x:v>
-      </x:c>
-      <x:c r="AK10" t="str"/>
-      <x:c r="AL10" t="str"/>
-      <x:c r="AM10" t="str"/>
-      <x:c r="AN10" t="str"/>
-      <x:c r="AO10" t="str"/>
-      <x:c r="AP10" t="str"/>
-      <x:c r="AQ10" t="str"/>
-      <x:c r="AR10" t="str"/>
-      <x:c r="AS10" t="str"/>
-      <x:c r="AT10" t="str"/>
-      <x:c r="AU10" t="str"/>
-      <x:c r="AV10" t="str"/>
-      <x:c r="AW10" t="str"/>
+      <x:c r="AJ10" t="str"/>
+      <x:c r="AK10"/>
+      <x:c r="AL10"/>
+      <x:c r="AM10"/>
+      <x:c r="AN10"/>
+      <x:c r="AO10"/>
+      <x:c r="AP10"/>
+      <x:c r="AQ10"/>
+      <x:c r="AR10"/>
+      <x:c r="AS10"/>
+      <x:c r="AT10"/>
+      <x:c r="AU10"/>
+      <x:c r="AV10"/>
+      <x:c r="AW10"/>
       <x:c r="AX10" t="str">
         <x:v>3921</x:v>
       </x:c>
@@ -3525,7 +3513,7 @@
       <x:c r="BC10" t="str">
         <x:v>Отделка</x:v>
       </x:c>
-      <x:c r="BD10" t="str"/>
+      <x:c r="BD10"/>
       <x:c r="BE10" t="str">
         <x:v>Стеновые панели, рейки и элементы декора</x:v>
       </x:c>
@@ -3547,28 +3535,28 @@
       <x:c r="BK10" t="str">
         <x:v>1140</x:v>
       </x:c>
-      <x:c r="BL10" t="str"/>
+      <x:c r="BL10"/>
       <x:c r="BM10" t="str">
         <x:v>Нет</x:v>
       </x:c>
-      <x:c r="BN10" t="str"/>
-      <x:c r="BO10" t="str"/>
-      <x:c r="BP10" t="str"/>
-      <x:c r="BQ10" t="str"/>
-      <x:c r="BR10" t="str"/>
-      <x:c r="BS10" t="str"/>
-      <x:c r="BT10" t="str"/>
-      <x:c r="BU10" t="str"/>
+      <x:c r="BN10"/>
+      <x:c r="BO10"/>
+      <x:c r="BP10"/>
+      <x:c r="BQ10"/>
+      <x:c r="BR10"/>
+      <x:c r="BS10"/>
+      <x:c r="BT10"/>
+      <x:c r="BU10"/>
     </x:row>
     <x:row r="11">
       <x:c r="A11" t="str">
         <x:v>adamar-vlg-SCANDI_1</x:v>
       </x:c>
-      <x:c r="B11" t="str"/>
-      <x:c r="C11" t="str"/>
-      <x:c r="D11" t="str"/>
-      <x:c r="E11" t="str"/>
-      <x:c r="F11" t="str"/>
+      <x:c r="B11"/>
+      <x:c r="C11"/>
+      <x:c r="D11"/>
+      <x:c r="E11"/>
+      <x:c r="F11"/>
       <x:c r="G11" t="str">
         <x:v>Adamar Group</x:v>
       </x:c>
@@ -3595,22 +3583,22 @@
       <x:c r="K11" t="str">
         <x:v>https://avatars.mds.yandex.net/get-yastore/21044143/9hcv6xhdxnfjrwwd98qg92wl4v5lgz6f/orig | https://avatars.mds.yandex.net/get-yastore/20274467/jsx9k6l9fsmls57rbgv52zbzcrt5zwq5/orig | https://avatars.mds.yandex.net/get-yastore/21012869/rfbzjh69f6cqw8bnk645qlv9f2vwwz8s/orig | https://avatars.mds.yandex.net/get-yastore/20274467/zswsl6dwvnc6b8gfs6xnbcdxvxm22p5j/orig</x:v>
       </x:c>
-      <x:c r="L11" t="str"/>
+      <x:c r="L11"/>
       <x:c r="M11" t="str">
         <x:v>По телефону и в сообщениях</x:v>
       </x:c>
-      <x:c r="N11" t="str"/>
-      <x:c r="O11" t="str"/>
-      <x:c r="P11" t="str"/>
+      <x:c r="N11"/>
+      <x:c r="O11"/>
+      <x:c r="P11"/>
       <x:c r="Q11" t="str">
         <x:v>Ремонт и строительство</x:v>
       </x:c>
       <x:c r="R11" t="str">
         <x:v>г. Волгоград, ул. 25-летия Октября, д. 1, стр. 3</x:v>
       </x:c>
-      <x:c r="S11" t="str"/>
-      <x:c r="T11" t="str"/>
-      <x:c r="U11" t="str"/>
+      <x:c r="S11"/>
+      <x:c r="T11"/>
+      <x:c r="U11"/>
       <x:c r="V11" t="str">
         <x:v>Поштучно</x:v>
       </x:c>
@@ -3626,9 +3614,9 @@
       <x:c r="Z11" t="str">
         <x:v>Штуку</x:v>
       </x:c>
-      <x:c r="AA11" t="str"/>
-      <x:c r="AB11" t="str"/>
-      <x:c r="AC11" t="str"/>
+      <x:c r="AA11"/>
+      <x:c r="AB11"/>
+      <x:c r="AC11"/>
       <x:c r="AD11" t="n">
         <x:v>7</x:v>
       </x:c>
@@ -3641,26 +3629,24 @@
       <x:c r="AG11" t="n">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="AH11" t="str"/>
+      <x:c r="AH11"/>
       <x:c r="AI11" t="str">
         <x:v>3921120000</x:v>
       </x:c>
-      <x:c r="AJ11" t="str">
-        <x:v>22.21.42.110</x:v>
-      </x:c>
-      <x:c r="AK11" t="str"/>
-      <x:c r="AL11" t="str"/>
-      <x:c r="AM11" t="str"/>
-      <x:c r="AN11" t="str"/>
-      <x:c r="AO11" t="str"/>
-      <x:c r="AP11" t="str"/>
-      <x:c r="AQ11" t="str"/>
-      <x:c r="AR11" t="str"/>
-      <x:c r="AS11" t="str"/>
-      <x:c r="AT11" t="str"/>
-      <x:c r="AU11" t="str"/>
-      <x:c r="AV11" t="str"/>
-      <x:c r="AW11" t="str"/>
+      <x:c r="AJ11" t="str"/>
+      <x:c r="AK11"/>
+      <x:c r="AL11"/>
+      <x:c r="AM11"/>
+      <x:c r="AN11"/>
+      <x:c r="AO11"/>
+      <x:c r="AP11"/>
+      <x:c r="AQ11"/>
+      <x:c r="AR11"/>
+      <x:c r="AS11"/>
+      <x:c r="AT11"/>
+      <x:c r="AU11"/>
+      <x:c r="AV11"/>
+      <x:c r="AW11"/>
       <x:c r="AX11" t="str">
         <x:v>3921</x:v>
       </x:c>
@@ -3679,7 +3665,7 @@
       <x:c r="BC11" t="str">
         <x:v>Отделка</x:v>
       </x:c>
-      <x:c r="BD11" t="str"/>
+      <x:c r="BD11"/>
       <x:c r="BE11" t="str">
         <x:v>Стеновые панели, рейки и элементы декора</x:v>
       </x:c>
@@ -3701,28 +3687,28 @@
       <x:c r="BK11" t="str">
         <x:v>1140</x:v>
       </x:c>
-      <x:c r="BL11" t="str"/>
+      <x:c r="BL11"/>
       <x:c r="BM11" t="str">
         <x:v>Нет</x:v>
       </x:c>
-      <x:c r="BN11" t="str"/>
-      <x:c r="BO11" t="str"/>
-      <x:c r="BP11" t="str"/>
-      <x:c r="BQ11" t="str"/>
-      <x:c r="BR11" t="str"/>
-      <x:c r="BS11" t="str"/>
-      <x:c r="BT11" t="str"/>
-      <x:c r="BU11" t="str"/>
+      <x:c r="BN11"/>
+      <x:c r="BO11"/>
+      <x:c r="BP11"/>
+      <x:c r="BQ11"/>
+      <x:c r="BR11"/>
+      <x:c r="BS11"/>
+      <x:c r="BT11"/>
+      <x:c r="BU11"/>
     </x:row>
     <x:row r="12">
       <x:c r="A12" t="str">
         <x:v>adamar-vlg-ДУБ ВИНТАЖ</x:v>
       </x:c>
-      <x:c r="B12" t="str"/>
-      <x:c r="C12" t="str"/>
-      <x:c r="D12" t="str"/>
-      <x:c r="E12" t="str"/>
-      <x:c r="F12" t="str"/>
+      <x:c r="B12"/>
+      <x:c r="C12"/>
+      <x:c r="D12"/>
+      <x:c r="E12"/>
+      <x:c r="F12"/>
       <x:c r="G12" t="str">
         <x:v>Adamar Group</x:v>
       </x:c>
@@ -3749,22 +3735,22 @@
       <x:c r="K12" t="str">
         <x:v>https://avatars.mds.yandex.net/get-yastore/20918687/wtqtqnntvvsh8zrsnh7mgg4psnkmxb7b/orig | https://avatars.mds.yandex.net/get-yastore/20918687/mb526z5xgklm9k4529xjjs8kj8rlkckk/orig | https://avatars.mds.yandex.net/get-yastore/21044143/ftcjlr95jm5nhlr6b7tq9sknh5q4nc72/orig</x:v>
       </x:c>
-      <x:c r="L12" t="str"/>
+      <x:c r="L12"/>
       <x:c r="M12" t="str">
         <x:v>По телефону и в сообщениях</x:v>
       </x:c>
-      <x:c r="N12" t="str"/>
-      <x:c r="O12" t="str"/>
-      <x:c r="P12" t="str"/>
+      <x:c r="N12"/>
+      <x:c r="O12"/>
+      <x:c r="P12"/>
       <x:c r="Q12" t="str">
         <x:v>Ремонт и строительство</x:v>
       </x:c>
       <x:c r="R12" t="str">
         <x:v>г. Волгоград, ул. 25-летия Октября, д. 1, стр. 3</x:v>
       </x:c>
-      <x:c r="S12" t="str"/>
-      <x:c r="T12" t="str"/>
-      <x:c r="U12" t="str"/>
+      <x:c r="S12"/>
+      <x:c r="T12"/>
+      <x:c r="U12"/>
       <x:c r="V12" t="str">
         <x:v>Поштучно</x:v>
       </x:c>
@@ -3780,9 +3766,9 @@
       <x:c r="Z12" t="str">
         <x:v>Штуку</x:v>
       </x:c>
-      <x:c r="AA12" t="str"/>
-      <x:c r="AB12" t="str"/>
-      <x:c r="AC12" t="str"/>
+      <x:c r="AA12"/>
+      <x:c r="AB12"/>
+      <x:c r="AC12"/>
       <x:c r="AD12" t="n">
         <x:v>7</x:v>
       </x:c>
@@ -3795,26 +3781,24 @@
       <x:c r="AG12" t="n">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="AH12" t="str"/>
+      <x:c r="AH12"/>
       <x:c r="AI12" t="str">
         <x:v>3921120000</x:v>
       </x:c>
-      <x:c r="AJ12" t="str">
-        <x:v>22.21.42.110</x:v>
-      </x:c>
-      <x:c r="AK12" t="str"/>
-      <x:c r="AL12" t="str"/>
-      <x:c r="AM12" t="str"/>
-      <x:c r="AN12" t="str"/>
-      <x:c r="AO12" t="str"/>
-      <x:c r="AP12" t="str"/>
-      <x:c r="AQ12" t="str"/>
-      <x:c r="AR12" t="str"/>
-      <x:c r="AS12" t="str"/>
-      <x:c r="AT12" t="str"/>
-      <x:c r="AU12" t="str"/>
-      <x:c r="AV12" t="str"/>
-      <x:c r="AW12" t="str"/>
+      <x:c r="AJ12" t="str"/>
+      <x:c r="AK12"/>
+      <x:c r="AL12"/>
+      <x:c r="AM12"/>
+      <x:c r="AN12"/>
+      <x:c r="AO12"/>
+      <x:c r="AP12"/>
+      <x:c r="AQ12"/>
+      <x:c r="AR12"/>
+      <x:c r="AS12"/>
+      <x:c r="AT12"/>
+      <x:c r="AU12"/>
+      <x:c r="AV12"/>
+      <x:c r="AW12"/>
       <x:c r="AX12" t="str">
         <x:v>3921</x:v>
       </x:c>
@@ -3833,7 +3817,7 @@
       <x:c r="BC12" t="str">
         <x:v>Отделка</x:v>
       </x:c>
-      <x:c r="BD12" t="str"/>
+      <x:c r="BD12"/>
       <x:c r="BE12" t="str">
         <x:v>Стеновые панели, рейки и элементы декора</x:v>
       </x:c>
@@ -3855,28 +3839,28 @@
       <x:c r="BK12" t="str">
         <x:v>1140</x:v>
       </x:c>
-      <x:c r="BL12" t="str"/>
+      <x:c r="BL12"/>
       <x:c r="BM12" t="str">
         <x:v>Нет</x:v>
       </x:c>
-      <x:c r="BN12" t="str"/>
-      <x:c r="BO12" t="str"/>
-      <x:c r="BP12" t="str"/>
-      <x:c r="BQ12" t="str"/>
-      <x:c r="BR12" t="str"/>
-      <x:c r="BS12" t="str"/>
-      <x:c r="BT12" t="str"/>
-      <x:c r="BU12" t="str"/>
+      <x:c r="BN12"/>
+      <x:c r="BO12"/>
+      <x:c r="BP12"/>
+      <x:c r="BQ12"/>
+      <x:c r="BR12"/>
+      <x:c r="BS12"/>
+      <x:c r="BT12"/>
+      <x:c r="BU12"/>
     </x:row>
     <x:row r="13">
       <x:c r="A13" t="str">
         <x:v>adamar-vlg-BEIGE CONCRETE</x:v>
       </x:c>
-      <x:c r="B13" t="str"/>
-      <x:c r="C13" t="str"/>
-      <x:c r="D13" t="str"/>
-      <x:c r="E13" t="str"/>
-      <x:c r="F13" t="str"/>
+      <x:c r="B13"/>
+      <x:c r="C13"/>
+      <x:c r="D13"/>
+      <x:c r="E13"/>
+      <x:c r="F13"/>
       <x:c r="G13" t="str">
         <x:v>Adamar Group</x:v>
       </x:c>
@@ -3903,22 +3887,22 @@
       <x:c r="K13" t="str">
         <x:v>https://avatars.mds.yandex.net/get-yastore/20760651/8qw2qwg2v87gsqggrf2qlbjll858zxkf/orig | https://avatars.mds.yandex.net/get-yastore/21104660/zvcjwnpn7l4b6bvrxq9m5k7j87gv2w95/orig | https://avatars.mds.yandex.net/get-yastore/21012869/jv4xmtjhk8cq5zmkj2klxhg9dfrn6vlm/orig | https://avatars.mds.yandex.net/get-yastore/20760651/f6fd5rqmkhs4r9qbjs8nb45rrqckvmlg/orig</x:v>
       </x:c>
-      <x:c r="L13" t="str"/>
+      <x:c r="L13"/>
       <x:c r="M13" t="str">
         <x:v>По телефону и в сообщениях</x:v>
       </x:c>
-      <x:c r="N13" t="str"/>
-      <x:c r="O13" t="str"/>
-      <x:c r="P13" t="str"/>
+      <x:c r="N13"/>
+      <x:c r="O13"/>
+      <x:c r="P13"/>
       <x:c r="Q13" t="str">
         <x:v>Ремонт и строительство</x:v>
       </x:c>
       <x:c r="R13" t="str">
         <x:v>г. Волгоград, ул. 25-летия Октября, д. 1, стр. 3</x:v>
       </x:c>
-      <x:c r="S13" t="str"/>
-      <x:c r="T13" t="str"/>
-      <x:c r="U13" t="str"/>
+      <x:c r="S13"/>
+      <x:c r="T13"/>
+      <x:c r="U13"/>
       <x:c r="V13" t="str">
         <x:v>Поштучно</x:v>
       </x:c>
@@ -3934,9 +3918,9 @@
       <x:c r="Z13" t="str">
         <x:v>Штуку</x:v>
       </x:c>
-      <x:c r="AA13" t="str"/>
-      <x:c r="AB13" t="str"/>
-      <x:c r="AC13" t="str"/>
+      <x:c r="AA13"/>
+      <x:c r="AB13"/>
+      <x:c r="AC13"/>
       <x:c r="AD13" t="n">
         <x:v>7</x:v>
       </x:c>
@@ -3949,26 +3933,24 @@
       <x:c r="AG13" t="n">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="AH13" t="str"/>
+      <x:c r="AH13"/>
       <x:c r="AI13" t="str">
         <x:v>3921120000</x:v>
       </x:c>
-      <x:c r="AJ13" t="str">
-        <x:v>22.21.42.110</x:v>
-      </x:c>
-      <x:c r="AK13" t="str"/>
-      <x:c r="AL13" t="str"/>
-      <x:c r="AM13" t="str"/>
-      <x:c r="AN13" t="str"/>
-      <x:c r="AO13" t="str"/>
-      <x:c r="AP13" t="str"/>
-      <x:c r="AQ13" t="str"/>
-      <x:c r="AR13" t="str"/>
-      <x:c r="AS13" t="str"/>
-      <x:c r="AT13" t="str"/>
-      <x:c r="AU13" t="str"/>
-      <x:c r="AV13" t="str"/>
-      <x:c r="AW13" t="str"/>
+      <x:c r="AJ13" t="str"/>
+      <x:c r="AK13"/>
+      <x:c r="AL13"/>
+      <x:c r="AM13"/>
+      <x:c r="AN13"/>
+      <x:c r="AO13"/>
+      <x:c r="AP13"/>
+      <x:c r="AQ13"/>
+      <x:c r="AR13"/>
+      <x:c r="AS13"/>
+      <x:c r="AT13"/>
+      <x:c r="AU13"/>
+      <x:c r="AV13"/>
+      <x:c r="AW13"/>
       <x:c r="AX13" t="str">
         <x:v>3921</x:v>
       </x:c>
@@ -3987,7 +3969,7 @@
       <x:c r="BC13" t="str">
         <x:v>Отделка</x:v>
       </x:c>
-      <x:c r="BD13" t="str"/>
+      <x:c r="BD13"/>
       <x:c r="BE13" t="str">
         <x:v>Стеновые панели, рейки и элементы декора</x:v>
       </x:c>
@@ -4009,28 +3991,28 @@
       <x:c r="BK13" t="str">
         <x:v>1140</x:v>
       </x:c>
-      <x:c r="BL13" t="str"/>
+      <x:c r="BL13"/>
       <x:c r="BM13" t="str">
         <x:v>Нет</x:v>
       </x:c>
-      <x:c r="BN13" t="str"/>
-      <x:c r="BO13" t="str"/>
-      <x:c r="BP13" t="str"/>
-      <x:c r="BQ13" t="str"/>
-      <x:c r="BR13" t="str"/>
-      <x:c r="BS13" t="str"/>
-      <x:c r="BT13" t="str"/>
-      <x:c r="BU13" t="str"/>
+      <x:c r="BN13"/>
+      <x:c r="BO13"/>
+      <x:c r="BP13"/>
+      <x:c r="BQ13"/>
+      <x:c r="BR13"/>
+      <x:c r="BS13"/>
+      <x:c r="BT13"/>
+      <x:c r="BU13"/>
     </x:row>
     <x:row r="14">
       <x:c r="A14" t="str">
         <x:v>adamar-vlg-TERRAZZO WHITE</x:v>
       </x:c>
-      <x:c r="B14" t="str"/>
-      <x:c r="C14" t="str"/>
-      <x:c r="D14" t="str"/>
-      <x:c r="E14" t="str"/>
-      <x:c r="F14" t="str"/>
+      <x:c r="B14"/>
+      <x:c r="C14"/>
+      <x:c r="D14"/>
+      <x:c r="E14"/>
+      <x:c r="F14"/>
       <x:c r="G14" t="str">
         <x:v>Adamar Group</x:v>
       </x:c>
@@ -4057,22 +4039,22 @@
       <x:c r="K14" t="str">
         <x:v>https://avatars.mds.yandex.net/get-yastore/21012869/zvg5c7xvfp27vb94x8dgw6nw8hrkzgs8/orig | https://avatars.mds.yandex.net/get-yastore/20900992/qf62gg7v6c79zx5nz7bbkffmx542n4ws/orig | https://avatars.mds.yandex.net/get-yastore/20900992/j8c85d75scqcql2tbc6z56sfwncft7gd/orig</x:v>
       </x:c>
-      <x:c r="L14" t="str"/>
+      <x:c r="L14"/>
       <x:c r="M14" t="str">
         <x:v>По телефону и в сообщениях</x:v>
       </x:c>
-      <x:c r="N14" t="str"/>
-      <x:c r="O14" t="str"/>
-      <x:c r="P14" t="str"/>
+      <x:c r="N14"/>
+      <x:c r="O14"/>
+      <x:c r="P14"/>
       <x:c r="Q14" t="str">
         <x:v>Ремонт и строительство</x:v>
       </x:c>
       <x:c r="R14" t="str">
         <x:v>г. Волгоград, ул. 25-летия Октября, д. 1, стр. 3</x:v>
       </x:c>
-      <x:c r="S14" t="str"/>
-      <x:c r="T14" t="str"/>
-      <x:c r="U14" t="str"/>
+      <x:c r="S14"/>
+      <x:c r="T14"/>
+      <x:c r="U14"/>
       <x:c r="V14" t="str">
         <x:v>Поштучно</x:v>
       </x:c>
@@ -4088,9 +4070,9 @@
       <x:c r="Z14" t="str">
         <x:v>Штуку</x:v>
       </x:c>
-      <x:c r="AA14" t="str"/>
-      <x:c r="AB14" t="str"/>
-      <x:c r="AC14" t="str"/>
+      <x:c r="AA14"/>
+      <x:c r="AB14"/>
+      <x:c r="AC14"/>
       <x:c r="AD14" t="n">
         <x:v>7</x:v>
       </x:c>
@@ -4103,26 +4085,24 @@
       <x:c r="AG14" t="n">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="AH14" t="str"/>
+      <x:c r="AH14"/>
       <x:c r="AI14" t="str">
         <x:v>3921120000</x:v>
       </x:c>
-      <x:c r="AJ14" t="str">
-        <x:v>22.21.42.110</x:v>
-      </x:c>
-      <x:c r="AK14" t="str"/>
-      <x:c r="AL14" t="str"/>
-      <x:c r="AM14" t="str"/>
-      <x:c r="AN14" t="str"/>
-      <x:c r="AO14" t="str"/>
-      <x:c r="AP14" t="str"/>
-      <x:c r="AQ14" t="str"/>
-      <x:c r="AR14" t="str"/>
-      <x:c r="AS14" t="str"/>
-      <x:c r="AT14" t="str"/>
-      <x:c r="AU14" t="str"/>
-      <x:c r="AV14" t="str"/>
-      <x:c r="AW14" t="str"/>
+      <x:c r="AJ14" t="str"/>
+      <x:c r="AK14"/>
+      <x:c r="AL14"/>
+      <x:c r="AM14"/>
+      <x:c r="AN14"/>
+      <x:c r="AO14"/>
+      <x:c r="AP14"/>
+      <x:c r="AQ14"/>
+      <x:c r="AR14"/>
+      <x:c r="AS14"/>
+      <x:c r="AT14"/>
+      <x:c r="AU14"/>
+      <x:c r="AV14"/>
+      <x:c r="AW14"/>
       <x:c r="AX14" t="str">
         <x:v>3921</x:v>
       </x:c>
@@ -4141,7 +4121,7 @@
       <x:c r="BC14" t="str">
         <x:v>Отделка</x:v>
       </x:c>
-      <x:c r="BD14" t="str"/>
+      <x:c r="BD14"/>
       <x:c r="BE14" t="str">
         <x:v>Стеновые панели, рейки и элементы декора</x:v>
       </x:c>
@@ -4163,28 +4143,28 @@
       <x:c r="BK14" t="str">
         <x:v>1140</x:v>
       </x:c>
-      <x:c r="BL14" t="str"/>
+      <x:c r="BL14"/>
       <x:c r="BM14" t="str">
         <x:v>Нет</x:v>
       </x:c>
-      <x:c r="BN14" t="str"/>
-      <x:c r="BO14" t="str"/>
-      <x:c r="BP14" t="str"/>
-      <x:c r="BQ14" t="str"/>
-      <x:c r="BR14" t="str"/>
-      <x:c r="BS14" t="str"/>
-      <x:c r="BT14" t="str"/>
-      <x:c r="BU14" t="str"/>
+      <x:c r="BN14"/>
+      <x:c r="BO14"/>
+      <x:c r="BP14"/>
+      <x:c r="BQ14"/>
+      <x:c r="BR14"/>
+      <x:c r="BS14"/>
+      <x:c r="BT14"/>
+      <x:c r="BU14"/>
     </x:row>
     <x:row r="15">
       <x:c r="A15" t="str">
         <x:v>adamar-vlg-SOTY LIGHT GRAY</x:v>
       </x:c>
-      <x:c r="B15" t="str"/>
-      <x:c r="C15" t="str"/>
-      <x:c r="D15" t="str"/>
-      <x:c r="E15" t="str"/>
-      <x:c r="F15" t="str"/>
+      <x:c r="B15"/>
+      <x:c r="C15"/>
+      <x:c r="D15"/>
+      <x:c r="E15"/>
+      <x:c r="F15"/>
       <x:c r="G15" t="str">
         <x:v>Adamar Group</x:v>
       </x:c>
@@ -4204,22 +4184,22 @@
       <x:c r="K15" t="str">
         <x:v>https://avatars.mds.yandex.net/get-yastore/20918687/vcdsrg87hjghbb7rrqjsgg9lk4xwxfbd/orig | https://avatars.mds.yandex.net/get-yastore/20918687/r4mxrbl2hwf49p5l4g54r4vpwrxvzgj8/orig | https://avatars.mds.yandex.net/get-yastore/20760651/hsnpdljqjs775bgcd6dksw96qvt8m2mg/orig</x:v>
       </x:c>
-      <x:c r="L15" t="str"/>
+      <x:c r="L15"/>
       <x:c r="M15" t="str">
         <x:v>По телефону и в сообщениях</x:v>
       </x:c>
-      <x:c r="N15" t="str"/>
-      <x:c r="O15" t="str"/>
-      <x:c r="P15" t="str"/>
+      <x:c r="N15"/>
+      <x:c r="O15"/>
+      <x:c r="P15"/>
       <x:c r="Q15" t="str">
         <x:v>Ремонт и строительство</x:v>
       </x:c>
       <x:c r="R15" t="str">
         <x:v>г. Волгоград, ул. 25-летия Октября, д. 1, стр. 3</x:v>
       </x:c>
-      <x:c r="S15" t="str"/>
-      <x:c r="T15" t="str"/>
-      <x:c r="U15" t="str"/>
+      <x:c r="S15"/>
+      <x:c r="T15"/>
+      <x:c r="U15"/>
       <x:c r="V15" t="str">
         <x:v>Поштучно</x:v>
       </x:c>
@@ -4235,9 +4215,9 @@
       <x:c r="Z15" t="str">
         <x:v>Штуку</x:v>
       </x:c>
-      <x:c r="AA15" t="str"/>
-      <x:c r="AB15" t="str"/>
-      <x:c r="AC15" t="str"/>
+      <x:c r="AA15"/>
+      <x:c r="AB15"/>
+      <x:c r="AC15"/>
       <x:c r="AD15" t="n">
         <x:v>7</x:v>
       </x:c>
@@ -4250,26 +4230,24 @@
       <x:c r="AG15" t="n">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="AH15" t="str"/>
+      <x:c r="AH15"/>
       <x:c r="AI15" t="str">
         <x:v>3921120000</x:v>
       </x:c>
-      <x:c r="AJ15" t="str">
-        <x:v>22.21.42.110</x:v>
-      </x:c>
-      <x:c r="AK15" t="str"/>
-      <x:c r="AL15" t="str"/>
-      <x:c r="AM15" t="str"/>
-      <x:c r="AN15" t="str"/>
-      <x:c r="AO15" t="str"/>
-      <x:c r="AP15" t="str"/>
-      <x:c r="AQ15" t="str"/>
-      <x:c r="AR15" t="str"/>
-      <x:c r="AS15" t="str"/>
-      <x:c r="AT15" t="str"/>
-      <x:c r="AU15" t="str"/>
-      <x:c r="AV15" t="str"/>
-      <x:c r="AW15" t="str"/>
+      <x:c r="AJ15" t="str"/>
+      <x:c r="AK15"/>
+      <x:c r="AL15"/>
+      <x:c r="AM15"/>
+      <x:c r="AN15"/>
+      <x:c r="AO15"/>
+      <x:c r="AP15"/>
+      <x:c r="AQ15"/>
+      <x:c r="AR15"/>
+      <x:c r="AS15"/>
+      <x:c r="AT15"/>
+      <x:c r="AU15"/>
+      <x:c r="AV15"/>
+      <x:c r="AW15"/>
       <x:c r="AX15" t="str">
         <x:v>3921</x:v>
       </x:c>
@@ -4288,7 +4266,7 @@
       <x:c r="BC15" t="str">
         <x:v>Отделка</x:v>
       </x:c>
-      <x:c r="BD15" t="str"/>
+      <x:c r="BD15"/>
       <x:c r="BE15" t="str">
         <x:v>Стеновые панели, рейки и элементы декора</x:v>
       </x:c>
@@ -4310,28 +4288,28 @@
       <x:c r="BK15" t="str">
         <x:v>1140</x:v>
       </x:c>
-      <x:c r="BL15" t="str"/>
+      <x:c r="BL15"/>
       <x:c r="BM15" t="str">
         <x:v>Нет</x:v>
       </x:c>
-      <x:c r="BN15" t="str"/>
-      <x:c r="BO15" t="str"/>
-      <x:c r="BP15" t="str"/>
-      <x:c r="BQ15" t="str"/>
-      <x:c r="BR15" t="str"/>
-      <x:c r="BS15" t="str"/>
-      <x:c r="BT15" t="str"/>
-      <x:c r="BU15" t="str"/>
+      <x:c r="BN15"/>
+      <x:c r="BO15"/>
+      <x:c r="BP15"/>
+      <x:c r="BQ15"/>
+      <x:c r="BR15"/>
+      <x:c r="BS15"/>
+      <x:c r="BT15"/>
+      <x:c r="BU15"/>
     </x:row>
     <x:row r="16">
       <x:c r="A16" t="str">
         <x:v>adamar-vlg-SOTY GRAY</x:v>
       </x:c>
-      <x:c r="B16" t="str"/>
-      <x:c r="C16" t="str"/>
-      <x:c r="D16" t="str"/>
-      <x:c r="E16" t="str"/>
-      <x:c r="F16" t="str"/>
+      <x:c r="B16"/>
+      <x:c r="C16"/>
+      <x:c r="D16"/>
+      <x:c r="E16"/>
+      <x:c r="F16"/>
       <x:c r="G16" t="str">
         <x:v>Adamar Group</x:v>
       </x:c>
@@ -4351,22 +4329,22 @@
       <x:c r="K16" t="str">
         <x:v>https://avatars.mds.yandex.net/get-yastore/21012869/kpgrt7s5ptkwtl6j7dj59rb9hwkrwrnq/orig | https://avatars.mds.yandex.net/get-yastore/20918687/mh6lzzxbg8wmr87qjrnd52g9qc28btrs/orig | https://avatars.mds.yandex.net/get-yastore/21012869/zr9xw2rzqbkj45skkmgmlw4zlbz8wpfr/orig</x:v>
       </x:c>
-      <x:c r="L16" t="str"/>
+      <x:c r="L16"/>
       <x:c r="M16" t="str">
         <x:v>По телефону и в сообщениях</x:v>
       </x:c>
-      <x:c r="N16" t="str"/>
-      <x:c r="O16" t="str"/>
-      <x:c r="P16" t="str"/>
+      <x:c r="N16"/>
+      <x:c r="O16"/>
+      <x:c r="P16"/>
       <x:c r="Q16" t="str">
         <x:v>Ремонт и строительство</x:v>
       </x:c>
       <x:c r="R16" t="str">
         <x:v>г. Волгоград, ул. 25-летия Октября, д. 1, стр. 3</x:v>
       </x:c>
-      <x:c r="S16" t="str"/>
-      <x:c r="T16" t="str"/>
-      <x:c r="U16" t="str"/>
+      <x:c r="S16"/>
+      <x:c r="T16"/>
+      <x:c r="U16"/>
       <x:c r="V16" t="str">
         <x:v>Поштучно</x:v>
       </x:c>
@@ -4382,9 +4360,9 @@
       <x:c r="Z16" t="str">
         <x:v>Штуку</x:v>
       </x:c>
-      <x:c r="AA16" t="str"/>
-      <x:c r="AB16" t="str"/>
-      <x:c r="AC16" t="str"/>
+      <x:c r="AA16"/>
+      <x:c r="AB16"/>
+      <x:c r="AC16"/>
       <x:c r="AD16" t="n">
         <x:v>7</x:v>
       </x:c>
@@ -4397,26 +4375,24 @@
       <x:c r="AG16" t="n">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="AH16" t="str"/>
+      <x:c r="AH16"/>
       <x:c r="AI16" t="str">
         <x:v>3921120000</x:v>
       </x:c>
-      <x:c r="AJ16" t="str">
-        <x:v>22.21.42.110</x:v>
-      </x:c>
-      <x:c r="AK16" t="str"/>
-      <x:c r="AL16" t="str"/>
-      <x:c r="AM16" t="str"/>
-      <x:c r="AN16" t="str"/>
-      <x:c r="AO16" t="str"/>
-      <x:c r="AP16" t="str"/>
-      <x:c r="AQ16" t="str"/>
-      <x:c r="AR16" t="str"/>
-      <x:c r="AS16" t="str"/>
-      <x:c r="AT16" t="str"/>
-      <x:c r="AU16" t="str"/>
-      <x:c r="AV16" t="str"/>
-      <x:c r="AW16" t="str"/>
+      <x:c r="AJ16" t="str"/>
+      <x:c r="AK16"/>
+      <x:c r="AL16"/>
+      <x:c r="AM16"/>
+      <x:c r="AN16"/>
+      <x:c r="AO16"/>
+      <x:c r="AP16"/>
+      <x:c r="AQ16"/>
+      <x:c r="AR16"/>
+      <x:c r="AS16"/>
+      <x:c r="AT16"/>
+      <x:c r="AU16"/>
+      <x:c r="AV16"/>
+      <x:c r="AW16"/>
       <x:c r="AX16" t="str">
         <x:v>3921</x:v>
       </x:c>
@@ -4435,7 +4411,7 @@
       <x:c r="BC16" t="str">
         <x:v>Отделка</x:v>
       </x:c>
-      <x:c r="BD16" t="str"/>
+      <x:c r="BD16"/>
       <x:c r="BE16" t="str">
         <x:v>Стеновые панели, рейки и элементы декора</x:v>
       </x:c>
@@ -4457,28 +4433,28 @@
       <x:c r="BK16" t="str">
         <x:v>1140</x:v>
       </x:c>
-      <x:c r="BL16" t="str"/>
+      <x:c r="BL16"/>
       <x:c r="BM16" t="str">
         <x:v>Нет</x:v>
       </x:c>
-      <x:c r="BN16" t="str"/>
-      <x:c r="BO16" t="str"/>
-      <x:c r="BP16" t="str"/>
-      <x:c r="BQ16" t="str"/>
-      <x:c r="BR16" t="str"/>
-      <x:c r="BS16" t="str"/>
-      <x:c r="BT16" t="str"/>
-      <x:c r="BU16" t="str"/>
+      <x:c r="BN16"/>
+      <x:c r="BO16"/>
+      <x:c r="BP16"/>
+      <x:c r="BQ16"/>
+      <x:c r="BR16"/>
+      <x:c r="BS16"/>
+      <x:c r="BT16"/>
+      <x:c r="BU16"/>
     </x:row>
     <x:row r="17">
       <x:c r="A17" t="str">
         <x:v>adamar-vlg-ДУБ ТОСКАНА</x:v>
       </x:c>
-      <x:c r="B17" t="str"/>
-      <x:c r="C17" t="str"/>
-      <x:c r="D17" t="str"/>
-      <x:c r="E17" t="str"/>
-      <x:c r="F17" t="str"/>
+      <x:c r="B17"/>
+      <x:c r="C17"/>
+      <x:c r="D17"/>
+      <x:c r="E17"/>
+      <x:c r="F17"/>
       <x:c r="G17" t="str">
         <x:v>Adamar Group</x:v>
       </x:c>
@@ -4498,22 +4474,22 @@
       <x:c r="K17" t="str">
         <x:v>https://avatars.mds.yandex.net/get-yastore/21044143/gq6tvnvv2hzmnl4ht9t68h4t5pfqmrc5/orig | https://avatars.mds.yandex.net/get-yastore/20918687/zd7zwc559bblwrw59c8wdcqv5kfgpmgd/orig | https://avatars.mds.yandex.net/get-yastore/20918687/mg4chd67l2fkgf89lg5tgxh2mv74zd94/orig</x:v>
       </x:c>
-      <x:c r="L17" t="str"/>
+      <x:c r="L17"/>
       <x:c r="M17" t="str">
         <x:v>По телефону и в сообщениях</x:v>
       </x:c>
-      <x:c r="N17" t="str"/>
-      <x:c r="O17" t="str"/>
-      <x:c r="P17" t="str"/>
+      <x:c r="N17"/>
+      <x:c r="O17"/>
+      <x:c r="P17"/>
       <x:c r="Q17" t="str">
         <x:v>Ремонт и строительство</x:v>
       </x:c>
       <x:c r="R17" t="str">
         <x:v>г. Волгоград, ул. 25-летия Октября, д. 1, стр. 3</x:v>
       </x:c>
-      <x:c r="S17" t="str"/>
-      <x:c r="T17" t="str"/>
-      <x:c r="U17" t="str"/>
+      <x:c r="S17"/>
+      <x:c r="T17"/>
+      <x:c r="U17"/>
       <x:c r="V17" t="str">
         <x:v>Поштучно</x:v>
       </x:c>
@@ -4529,9 +4505,9 @@
       <x:c r="Z17" t="str">
         <x:v>Штуку</x:v>
       </x:c>
-      <x:c r="AA17" t="str"/>
-      <x:c r="AB17" t="str"/>
-      <x:c r="AC17" t="str"/>
+      <x:c r="AA17"/>
+      <x:c r="AB17"/>
+      <x:c r="AC17"/>
       <x:c r="AD17" t="n">
         <x:v>7</x:v>
       </x:c>
@@ -4544,26 +4520,24 @@
       <x:c r="AG17" t="n">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="AH17" t="str"/>
+      <x:c r="AH17"/>
       <x:c r="AI17" t="str">
         <x:v>3921120000</x:v>
       </x:c>
-      <x:c r="AJ17" t="str">
-        <x:v>22.21.42.110</x:v>
-      </x:c>
-      <x:c r="AK17" t="str"/>
-      <x:c r="AL17" t="str"/>
-      <x:c r="AM17" t="str"/>
-      <x:c r="AN17" t="str"/>
-      <x:c r="AO17" t="str"/>
-      <x:c r="AP17" t="str"/>
-      <x:c r="AQ17" t="str"/>
-      <x:c r="AR17" t="str"/>
-      <x:c r="AS17" t="str"/>
-      <x:c r="AT17" t="str"/>
-      <x:c r="AU17" t="str"/>
-      <x:c r="AV17" t="str"/>
-      <x:c r="AW17" t="str"/>
+      <x:c r="AJ17" t="str"/>
+      <x:c r="AK17"/>
+      <x:c r="AL17"/>
+      <x:c r="AM17"/>
+      <x:c r="AN17"/>
+      <x:c r="AO17"/>
+      <x:c r="AP17"/>
+      <x:c r="AQ17"/>
+      <x:c r="AR17"/>
+      <x:c r="AS17"/>
+      <x:c r="AT17"/>
+      <x:c r="AU17"/>
+      <x:c r="AV17"/>
+      <x:c r="AW17"/>
       <x:c r="AX17" t="str">
         <x:v>3950</x:v>
       </x:c>
@@ -4582,7 +4556,7 @@
       <x:c r="BC17" t="str">
         <x:v>Отделка</x:v>
       </x:c>
-      <x:c r="BD17" t="str"/>
+      <x:c r="BD17"/>
       <x:c r="BE17" t="str">
         <x:v>Стеновые панели, рейки и элементы декора</x:v>
       </x:c>
@@ -4604,28 +4578,28 @@
       <x:c r="BK17" t="str">
         <x:v>1140</x:v>
       </x:c>
-      <x:c r="BL17" t="str"/>
+      <x:c r="BL17"/>
       <x:c r="BM17" t="str">
         <x:v>Нет</x:v>
       </x:c>
-      <x:c r="BN17" t="str"/>
-      <x:c r="BO17" t="str"/>
-      <x:c r="BP17" t="str"/>
-      <x:c r="BQ17" t="str"/>
-      <x:c r="BR17" t="str"/>
-      <x:c r="BS17" t="str"/>
-      <x:c r="BT17" t="str"/>
-      <x:c r="BU17" t="str"/>
+      <x:c r="BN17"/>
+      <x:c r="BO17"/>
+      <x:c r="BP17"/>
+      <x:c r="BQ17"/>
+      <x:c r="BR17"/>
+      <x:c r="BS17"/>
+      <x:c r="BT17"/>
+      <x:c r="BU17"/>
     </x:row>
     <x:row r="18">
       <x:c r="A18" t="str">
         <x:v>adamar-vlg-Дуб ВЕНГЕ</x:v>
       </x:c>
-      <x:c r="B18" t="str"/>
-      <x:c r="C18" t="str"/>
-      <x:c r="D18" t="str"/>
-      <x:c r="E18" t="str"/>
-      <x:c r="F18" t="str"/>
+      <x:c r="B18"/>
+      <x:c r="C18"/>
+      <x:c r="D18"/>
+      <x:c r="E18"/>
+      <x:c r="F18"/>
       <x:c r="G18" t="str">
         <x:v>Adamar Group</x:v>
       </x:c>
@@ -4645,22 +4619,22 @@
       <x:c r="K18" t="str">
         <x:v>https://avatars.mds.yandex.net/get-yastore/21044143/ccr9kp4dn8qxz5lfbt94ngtpxnhv8xn8/orig | https://avatars.mds.yandex.net/get-yastore/20918687/szzkvp9tp5zhh2npwxfvk88hpnzfb7qb/orig | https://avatars.mds.yandex.net/get-yastore/20918687/89rm5qdrppnc4vsgpww5hzfqpfkz8hwj/orig</x:v>
       </x:c>
-      <x:c r="L18" t="str"/>
+      <x:c r="L18"/>
       <x:c r="M18" t="str">
         <x:v>По телефону и в сообщениях</x:v>
       </x:c>
-      <x:c r="N18" t="str"/>
-      <x:c r="O18" t="str"/>
-      <x:c r="P18" t="str"/>
+      <x:c r="N18"/>
+      <x:c r="O18"/>
+      <x:c r="P18"/>
       <x:c r="Q18" t="str">
         <x:v>Ремонт и строительство</x:v>
       </x:c>
       <x:c r="R18" t="str">
         <x:v>г. Волгоград, ул. 25-летия Октября, д. 1, стр. 3</x:v>
       </x:c>
-      <x:c r="S18" t="str"/>
-      <x:c r="T18" t="str"/>
-      <x:c r="U18" t="str"/>
+      <x:c r="S18"/>
+      <x:c r="T18"/>
+      <x:c r="U18"/>
       <x:c r="V18" t="str">
         <x:v>Поштучно</x:v>
       </x:c>
@@ -4676,9 +4650,9 @@
       <x:c r="Z18" t="str">
         <x:v>Штуку</x:v>
       </x:c>
-      <x:c r="AA18" t="str"/>
-      <x:c r="AB18" t="str"/>
-      <x:c r="AC18" t="str"/>
+      <x:c r="AA18"/>
+      <x:c r="AB18"/>
+      <x:c r="AC18"/>
       <x:c r="AD18" t="n">
         <x:v>7</x:v>
       </x:c>
@@ -4691,26 +4665,24 @@
       <x:c r="AG18" t="n">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="AH18" t="str"/>
+      <x:c r="AH18"/>
       <x:c r="AI18" t="str">
         <x:v>3921120000</x:v>
       </x:c>
-      <x:c r="AJ18" t="str">
-        <x:v>22.21.42.110</x:v>
-      </x:c>
-      <x:c r="AK18" t="str"/>
-      <x:c r="AL18" t="str"/>
-      <x:c r="AM18" t="str"/>
-      <x:c r="AN18" t="str"/>
-      <x:c r="AO18" t="str"/>
-      <x:c r="AP18" t="str"/>
-      <x:c r="AQ18" t="str"/>
-      <x:c r="AR18" t="str"/>
-      <x:c r="AS18" t="str"/>
-      <x:c r="AT18" t="str"/>
-      <x:c r="AU18" t="str"/>
-      <x:c r="AV18" t="str"/>
-      <x:c r="AW18" t="str"/>
+      <x:c r="AJ18" t="str"/>
+      <x:c r="AK18"/>
+      <x:c r="AL18"/>
+      <x:c r="AM18"/>
+      <x:c r="AN18"/>
+      <x:c r="AO18"/>
+      <x:c r="AP18"/>
+      <x:c r="AQ18"/>
+      <x:c r="AR18"/>
+      <x:c r="AS18"/>
+      <x:c r="AT18"/>
+      <x:c r="AU18"/>
+      <x:c r="AV18"/>
+      <x:c r="AW18"/>
       <x:c r="AX18" t="str">
         <x:v>3950</x:v>
       </x:c>
@@ -4729,7 +4701,7 @@
       <x:c r="BC18" t="str">
         <x:v>Отделка</x:v>
       </x:c>
-      <x:c r="BD18" t="str"/>
+      <x:c r="BD18"/>
       <x:c r="BE18" t="str">
         <x:v>Стеновые панели, рейки и элементы декора</x:v>
       </x:c>
@@ -4751,28 +4723,28 @@
       <x:c r="BK18" t="str">
         <x:v>1140</x:v>
       </x:c>
-      <x:c r="BL18" t="str"/>
+      <x:c r="BL18"/>
       <x:c r="BM18" t="str">
         <x:v>Нет</x:v>
       </x:c>
-      <x:c r="BN18" t="str"/>
-      <x:c r="BO18" t="str"/>
-      <x:c r="BP18" t="str"/>
-      <x:c r="BQ18" t="str"/>
-      <x:c r="BR18" t="str"/>
-      <x:c r="BS18" t="str"/>
-      <x:c r="BT18" t="str"/>
-      <x:c r="BU18" t="str"/>
+      <x:c r="BN18"/>
+      <x:c r="BO18"/>
+      <x:c r="BP18"/>
+      <x:c r="BQ18"/>
+      <x:c r="BR18"/>
+      <x:c r="BS18"/>
+      <x:c r="BT18"/>
+      <x:c r="BU18"/>
     </x:row>
     <x:row r="19">
       <x:c r="A19" t="str">
         <x:v>adamar-vlg-SIENA_1</x:v>
       </x:c>
-      <x:c r="B19" t="str"/>
-      <x:c r="C19" t="str"/>
-      <x:c r="D19" t="str"/>
-      <x:c r="E19" t="str"/>
-      <x:c r="F19" t="str"/>
+      <x:c r="B19"/>
+      <x:c r="C19"/>
+      <x:c r="D19"/>
+      <x:c r="E19"/>
+      <x:c r="F19"/>
       <x:c r="G19" t="str">
         <x:v>Adamar Group</x:v>
       </x:c>
@@ -4792,22 +4764,22 @@
       <x:c r="K19" t="str">
         <x:v>https://avatars.mds.yandex.net/get-yastore/21055393/pjtzf4v2ggn2jxf82mp8lqzlvlldscds/orig | https://avatars.mds.yandex.net/get-yastore/21055393/xcf2khnk2t24n6gnm2vfd9ngqbmwpvbk/orig | https://avatars.mds.yandex.net/get-yastore/21055393/xzdmtpdldr9v6rgb8lsjq8v8bf4rtvm5/orig | https://avatars.mds.yandex.net/get-yastore/20274467/f5vddlgqd8qvnlh57ckqfc7wgbtjnjkz/orig</x:v>
       </x:c>
-      <x:c r="L19" t="str"/>
+      <x:c r="L19"/>
       <x:c r="M19" t="str">
         <x:v>По телефону и в сообщениях</x:v>
       </x:c>
-      <x:c r="N19" t="str"/>
-      <x:c r="O19" t="str"/>
-      <x:c r="P19" t="str"/>
+      <x:c r="N19"/>
+      <x:c r="O19"/>
+      <x:c r="P19"/>
       <x:c r="Q19" t="str">
         <x:v>Ремонт и строительство</x:v>
       </x:c>
       <x:c r="R19" t="str">
         <x:v>г. Волгоград, ул. 25-летия Октября, д. 1, стр. 3</x:v>
       </x:c>
-      <x:c r="S19" t="str"/>
-      <x:c r="T19" t="str"/>
-      <x:c r="U19" t="str"/>
+      <x:c r="S19"/>
+      <x:c r="T19"/>
+      <x:c r="U19"/>
       <x:c r="V19" t="str">
         <x:v>Поштучно</x:v>
       </x:c>
@@ -4823,9 +4795,9 @@
       <x:c r="Z19" t="str">
         <x:v>Штуку</x:v>
       </x:c>
-      <x:c r="AA19" t="str"/>
-      <x:c r="AB19" t="str"/>
-      <x:c r="AC19" t="str"/>
+      <x:c r="AA19"/>
+      <x:c r="AB19"/>
+      <x:c r="AC19"/>
       <x:c r="AD19" t="n">
         <x:v>7</x:v>
       </x:c>
@@ -4838,26 +4810,24 @@
       <x:c r="AG19" t="n">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="AH19" t="str"/>
+      <x:c r="AH19"/>
       <x:c r="AI19" t="str">
         <x:v>3921120000</x:v>
       </x:c>
-      <x:c r="AJ19" t="str">
-        <x:v>22.21.42.110</x:v>
-      </x:c>
-      <x:c r="AK19" t="str"/>
-      <x:c r="AL19" t="str"/>
-      <x:c r="AM19" t="str"/>
-      <x:c r="AN19" t="str"/>
-      <x:c r="AO19" t="str"/>
-      <x:c r="AP19" t="str"/>
-      <x:c r="AQ19" t="str"/>
-      <x:c r="AR19" t="str"/>
-      <x:c r="AS19" t="str"/>
-      <x:c r="AT19" t="str"/>
-      <x:c r="AU19" t="str"/>
-      <x:c r="AV19" t="str"/>
-      <x:c r="AW19" t="str"/>
+      <x:c r="AJ19" t="str"/>
+      <x:c r="AK19"/>
+      <x:c r="AL19"/>
+      <x:c r="AM19"/>
+      <x:c r="AN19"/>
+      <x:c r="AO19"/>
+      <x:c r="AP19"/>
+      <x:c r="AQ19"/>
+      <x:c r="AR19"/>
+      <x:c r="AS19"/>
+      <x:c r="AT19"/>
+      <x:c r="AU19"/>
+      <x:c r="AV19"/>
+      <x:c r="AW19"/>
       <x:c r="AX19" t="str">
         <x:v>3950</x:v>
       </x:c>
@@ -4876,7 +4846,7 @@
       <x:c r="BC19" t="str">
         <x:v>Отделка</x:v>
       </x:c>
-      <x:c r="BD19" t="str"/>
+      <x:c r="BD19"/>
       <x:c r="BE19" t="str">
         <x:v>Стеновые панели, рейки и элементы декора</x:v>
       </x:c>
@@ -4898,28 +4868,28 @@
       <x:c r="BK19" t="str">
         <x:v>1140</x:v>
       </x:c>
-      <x:c r="BL19" t="str"/>
+      <x:c r="BL19"/>
       <x:c r="BM19" t="str">
         <x:v>Нет</x:v>
       </x:c>
-      <x:c r="BN19" t="str"/>
-      <x:c r="BO19" t="str"/>
-      <x:c r="BP19" t="str"/>
-      <x:c r="BQ19" t="str"/>
-      <x:c r="BR19" t="str"/>
-      <x:c r="BS19" t="str"/>
-      <x:c r="BT19" t="str"/>
-      <x:c r="BU19" t="str"/>
+      <x:c r="BN19"/>
+      <x:c r="BO19"/>
+      <x:c r="BP19"/>
+      <x:c r="BQ19"/>
+      <x:c r="BR19"/>
+      <x:c r="BS19"/>
+      <x:c r="BT19"/>
+      <x:c r="BU19"/>
     </x:row>
     <x:row r="20">
       <x:c r="A20" t="str">
         <x:v>adamar-vlg-MILANO_1</x:v>
       </x:c>
-      <x:c r="B20" t="str"/>
-      <x:c r="C20" t="str"/>
-      <x:c r="D20" t="str"/>
-      <x:c r="E20" t="str"/>
-      <x:c r="F20" t="str"/>
+      <x:c r="B20"/>
+      <x:c r="C20"/>
+      <x:c r="D20"/>
+      <x:c r="E20"/>
+      <x:c r="F20"/>
       <x:c r="G20" t="str">
         <x:v>Adamar Group</x:v>
       </x:c>
@@ -4939,22 +4909,22 @@
       <x:c r="K20" t="str">
         <x:v>https://avatars.mds.yandex.net/get-yastore/21055393/kpbckqnvj9tcxkv52ghp294zxplqctsw/orig | https://avatars.mds.yandex.net/get-yastore/20918687/v78snp6r8vvcqjg6dx4vndhbfbl6gvqn/orig | https://avatars.mds.yandex.net/get-yastore/20918687/86gvwsn2bgr7stcvwcrxjpx5ljjk6nld/orig | https://avatars.mds.yandex.net/get-yastore/20918687/dwpwsscw86tqq958wmbjc8hpzsp92cbf/orig</x:v>
       </x:c>
-      <x:c r="L20" t="str"/>
+      <x:c r="L20"/>
       <x:c r="M20" t="str">
         <x:v>По телефону и в сообщениях</x:v>
       </x:c>
-      <x:c r="N20" t="str"/>
-      <x:c r="O20" t="str"/>
-      <x:c r="P20" t="str"/>
+      <x:c r="N20"/>
+      <x:c r="O20"/>
+      <x:c r="P20"/>
       <x:c r="Q20" t="str">
         <x:v>Ремонт и строительство</x:v>
       </x:c>
       <x:c r="R20" t="str">
         <x:v>г. Волгоград, ул. 25-летия Октября, д. 1, стр. 3</x:v>
       </x:c>
-      <x:c r="S20" t="str"/>
-      <x:c r="T20" t="str"/>
-      <x:c r="U20" t="str"/>
+      <x:c r="S20"/>
+      <x:c r="T20"/>
+      <x:c r="U20"/>
       <x:c r="V20" t="str">
         <x:v>Поштучно</x:v>
       </x:c>
@@ -4970,9 +4940,9 @@
       <x:c r="Z20" t="str">
         <x:v>Штуку</x:v>
       </x:c>
-      <x:c r="AA20" t="str"/>
-      <x:c r="AB20" t="str"/>
-      <x:c r="AC20" t="str"/>
+      <x:c r="AA20"/>
+      <x:c r="AB20"/>
+      <x:c r="AC20"/>
       <x:c r="AD20" t="n">
         <x:v>7</x:v>
       </x:c>
@@ -4985,26 +4955,24 @@
       <x:c r="AG20" t="n">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="AH20" t="str"/>
+      <x:c r="AH20"/>
       <x:c r="AI20" t="str">
         <x:v>3921120000</x:v>
       </x:c>
-      <x:c r="AJ20" t="str">
-        <x:v>22.21.42.110</x:v>
-      </x:c>
-      <x:c r="AK20" t="str"/>
-      <x:c r="AL20" t="str"/>
-      <x:c r="AM20" t="str"/>
-      <x:c r="AN20" t="str"/>
-      <x:c r="AO20" t="str"/>
-      <x:c r="AP20" t="str"/>
-      <x:c r="AQ20" t="str"/>
-      <x:c r="AR20" t="str"/>
-      <x:c r="AS20" t="str"/>
-      <x:c r="AT20" t="str"/>
-      <x:c r="AU20" t="str"/>
-      <x:c r="AV20" t="str"/>
-      <x:c r="AW20" t="str"/>
+      <x:c r="AJ20" t="str"/>
+      <x:c r="AK20"/>
+      <x:c r="AL20"/>
+      <x:c r="AM20"/>
+      <x:c r="AN20"/>
+      <x:c r="AO20"/>
+      <x:c r="AP20"/>
+      <x:c r="AQ20"/>
+      <x:c r="AR20"/>
+      <x:c r="AS20"/>
+      <x:c r="AT20"/>
+      <x:c r="AU20"/>
+      <x:c r="AV20"/>
+      <x:c r="AW20"/>
       <x:c r="AX20" t="str">
         <x:v>3950</x:v>
       </x:c>
@@ -5023,7 +4991,7 @@
       <x:c r="BC20" t="str">
         <x:v>Отделка</x:v>
       </x:c>
-      <x:c r="BD20" t="str"/>
+      <x:c r="BD20"/>
       <x:c r="BE20" t="str">
         <x:v>Стеновые панели, рейки и элементы декора</x:v>
       </x:c>
@@ -5045,28 +5013,28 @@
       <x:c r="BK20" t="str">
         <x:v>1140</x:v>
       </x:c>
-      <x:c r="BL20" t="str"/>
+      <x:c r="BL20"/>
       <x:c r="BM20" t="str">
         <x:v>Нет</x:v>
       </x:c>
-      <x:c r="BN20" t="str"/>
-      <x:c r="BO20" t="str"/>
-      <x:c r="BP20" t="str"/>
-      <x:c r="BQ20" t="str"/>
-      <x:c r="BR20" t="str"/>
-      <x:c r="BS20" t="str"/>
-      <x:c r="BT20" t="str"/>
-      <x:c r="BU20" t="str"/>
+      <x:c r="BN20"/>
+      <x:c r="BO20"/>
+      <x:c r="BP20"/>
+      <x:c r="BQ20"/>
+      <x:c r="BR20"/>
+      <x:c r="BS20"/>
+      <x:c r="BT20"/>
+      <x:c r="BU20"/>
     </x:row>
     <x:row r="21">
       <x:c r="A21" t="str">
         <x:v>adamar-vlg-FONDAMENTO_DECOR_2</x:v>
       </x:c>
-      <x:c r="B21" t="str"/>
-      <x:c r="C21" t="str"/>
-      <x:c r="D21" t="str"/>
-      <x:c r="E21" t="str"/>
-      <x:c r="F21" t="str"/>
+      <x:c r="B21"/>
+      <x:c r="C21"/>
+      <x:c r="D21"/>
+      <x:c r="E21"/>
+      <x:c r="F21"/>
       <x:c r="G21" t="str">
         <x:v>Adamar Group</x:v>
       </x:c>
@@ -5086,22 +5054,22 @@
       <x:c r="K21" t="str">
         <x:v>https://avatars.mds.yandex.net/get-yastore/21012869/ljdlf7jj44xvmtzkm8nzzdpql6m64x5l/orig | https://avatars.mds.yandex.net/get-yastore/20274467/8svljtp6jjcrd7s79x7l6mx84ft582xb/orig | https://avatars.mds.yandex.net/get-yastore/21012869/x68jbrttlkgfg2tx9zf9lzmxfg65wcnl/orig</x:v>
       </x:c>
-      <x:c r="L21" t="str"/>
+      <x:c r="L21"/>
       <x:c r="M21" t="str">
         <x:v>По телефону и в сообщениях</x:v>
       </x:c>
-      <x:c r="N21" t="str"/>
-      <x:c r="O21" t="str"/>
-      <x:c r="P21" t="str"/>
+      <x:c r="N21"/>
+      <x:c r="O21"/>
+      <x:c r="P21"/>
       <x:c r="Q21" t="str">
         <x:v>Ремонт и строительство</x:v>
       </x:c>
       <x:c r="R21" t="str">
         <x:v>г. Волгоград, ул. 25-летия Октября, д. 1, стр. 3</x:v>
       </x:c>
-      <x:c r="S21" t="str"/>
-      <x:c r="T21" t="str"/>
-      <x:c r="U21" t="str"/>
+      <x:c r="S21"/>
+      <x:c r="T21"/>
+      <x:c r="U21"/>
       <x:c r="V21" t="str">
         <x:v>Поштучно</x:v>
       </x:c>
@@ -5117,9 +5085,9 @@
       <x:c r="Z21" t="str">
         <x:v>Штуку</x:v>
       </x:c>
-      <x:c r="AA21" t="str"/>
-      <x:c r="AB21" t="str"/>
-      <x:c r="AC21" t="str"/>
+      <x:c r="AA21"/>
+      <x:c r="AB21"/>
+      <x:c r="AC21"/>
       <x:c r="AD21" t="n">
         <x:v>7</x:v>
       </x:c>
@@ -5132,26 +5100,24 @@
       <x:c r="AG21" t="n">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="AH21" t="str"/>
+      <x:c r="AH21"/>
       <x:c r="AI21" t="str">
         <x:v>3921120000</x:v>
       </x:c>
-      <x:c r="AJ21" t="str">
-        <x:v>22.21.42.110</x:v>
-      </x:c>
-      <x:c r="AK21" t="str"/>
-      <x:c r="AL21" t="str"/>
-      <x:c r="AM21" t="str"/>
-      <x:c r="AN21" t="str"/>
-      <x:c r="AO21" t="str"/>
-      <x:c r="AP21" t="str"/>
-      <x:c r="AQ21" t="str"/>
-      <x:c r="AR21" t="str"/>
-      <x:c r="AS21" t="str"/>
-      <x:c r="AT21" t="str"/>
-      <x:c r="AU21" t="str"/>
-      <x:c r="AV21" t="str"/>
-      <x:c r="AW21" t="str"/>
+      <x:c r="AJ21" t="str"/>
+      <x:c r="AK21"/>
+      <x:c r="AL21"/>
+      <x:c r="AM21"/>
+      <x:c r="AN21"/>
+      <x:c r="AO21"/>
+      <x:c r="AP21"/>
+      <x:c r="AQ21"/>
+      <x:c r="AR21"/>
+      <x:c r="AS21"/>
+      <x:c r="AT21"/>
+      <x:c r="AU21"/>
+      <x:c r="AV21"/>
+      <x:c r="AW21"/>
       <x:c r="AX21" t="str">
         <x:v>3950</x:v>
       </x:c>
@@ -5170,7 +5136,7 @@
       <x:c r="BC21" t="str">
         <x:v>Отделка</x:v>
       </x:c>
-      <x:c r="BD21" t="str"/>
+      <x:c r="BD21"/>
       <x:c r="BE21" t="str">
         <x:v>Стеновые панели, рейки и элементы декора</x:v>
       </x:c>
@@ -5192,28 +5158,28 @@
       <x:c r="BK21" t="str">
         <x:v>1140</x:v>
       </x:c>
-      <x:c r="BL21" t="str"/>
+      <x:c r="BL21"/>
       <x:c r="BM21" t="str">
         <x:v>Нет</x:v>
       </x:c>
-      <x:c r="BN21" t="str"/>
-      <x:c r="BO21" t="str"/>
-      <x:c r="BP21" t="str"/>
-      <x:c r="BQ21" t="str"/>
-      <x:c r="BR21" t="str"/>
-      <x:c r="BS21" t="str"/>
-      <x:c r="BT21" t="str"/>
-      <x:c r="BU21" t="str"/>
+      <x:c r="BN21"/>
+      <x:c r="BO21"/>
+      <x:c r="BP21"/>
+      <x:c r="BQ21"/>
+      <x:c r="BR21"/>
+      <x:c r="BS21"/>
+      <x:c r="BT21"/>
+      <x:c r="BU21"/>
     </x:row>
     <x:row r="22">
       <x:c r="A22" t="str">
         <x:v>adamar-vlg-Diagonal Wood</x:v>
       </x:c>
-      <x:c r="B22" t="str"/>
-      <x:c r="C22" t="str"/>
-      <x:c r="D22" t="str"/>
-      <x:c r="E22" t="str"/>
-      <x:c r="F22" t="str"/>
+      <x:c r="B22"/>
+      <x:c r="C22"/>
+      <x:c r="D22"/>
+      <x:c r="E22"/>
+      <x:c r="F22"/>
       <x:c r="G22" t="str">
         <x:v>Adamar Group</x:v>
       </x:c>
@@ -5233,22 +5199,22 @@
       <x:c r="K22" t="str">
         <x:v>https://avatars.mds.yandex.net/get-yastore/20900992/8rr4hmg2ccgglvmmfrsv4j6xsvxhr2tc/orig | https://avatars.mds.yandex.net/get-yastore/20900992/dz64p4phw87hprkkwtxfsgk7m2fgvcqm/orig | https://avatars.mds.yandex.net/get-yastore/20760651/ld56wsf2t6f9wpct7px28bvwtqxp7wc5/orig</x:v>
       </x:c>
-      <x:c r="L22" t="str"/>
+      <x:c r="L22"/>
       <x:c r="M22" t="str">
         <x:v>По телефону и в сообщениях</x:v>
       </x:c>
-      <x:c r="N22" t="str"/>
-      <x:c r="O22" t="str"/>
-      <x:c r="P22" t="str"/>
+      <x:c r="N22"/>
+      <x:c r="O22"/>
+      <x:c r="P22"/>
       <x:c r="Q22" t="str">
         <x:v>Ремонт и строительство</x:v>
       </x:c>
       <x:c r="R22" t="str">
         <x:v>г. Волгоград, ул. 25-летия Октября, д. 1, стр. 3</x:v>
       </x:c>
-      <x:c r="S22" t="str"/>
-      <x:c r="T22" t="str"/>
-      <x:c r="U22" t="str"/>
+      <x:c r="S22"/>
+      <x:c r="T22"/>
+      <x:c r="U22"/>
       <x:c r="V22" t="str">
         <x:v>Поштучно</x:v>
       </x:c>
@@ -5264,9 +5230,9 @@
       <x:c r="Z22" t="str">
         <x:v>Штуку</x:v>
       </x:c>
-      <x:c r="AA22" t="str"/>
-      <x:c r="AB22" t="str"/>
-      <x:c r="AC22" t="str"/>
+      <x:c r="AA22"/>
+      <x:c r="AB22"/>
+      <x:c r="AC22"/>
       <x:c r="AD22" t="n">
         <x:v>7</x:v>
       </x:c>
@@ -5279,26 +5245,24 @@
       <x:c r="AG22" t="n">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="AH22" t="str"/>
+      <x:c r="AH22"/>
       <x:c r="AI22" t="str">
         <x:v>3921120000</x:v>
       </x:c>
-      <x:c r="AJ22" t="str">
-        <x:v>22.21.42.110</x:v>
-      </x:c>
-      <x:c r="AK22" t="str"/>
-      <x:c r="AL22" t="str"/>
-      <x:c r="AM22" t="str"/>
-      <x:c r="AN22" t="str"/>
-      <x:c r="AO22" t="str"/>
-      <x:c r="AP22" t="str"/>
-      <x:c r="AQ22" t="str"/>
-      <x:c r="AR22" t="str"/>
-      <x:c r="AS22" t="str"/>
-      <x:c r="AT22" t="str"/>
-      <x:c r="AU22" t="str"/>
-      <x:c r="AV22" t="str"/>
-      <x:c r="AW22" t="str"/>
+      <x:c r="AJ22" t="str"/>
+      <x:c r="AK22"/>
+      <x:c r="AL22"/>
+      <x:c r="AM22"/>
+      <x:c r="AN22"/>
+      <x:c r="AO22"/>
+      <x:c r="AP22"/>
+      <x:c r="AQ22"/>
+      <x:c r="AR22"/>
+      <x:c r="AS22"/>
+      <x:c r="AT22"/>
+      <x:c r="AU22"/>
+      <x:c r="AV22"/>
+      <x:c r="AW22"/>
       <x:c r="AX22" t="str">
         <x:v>3950</x:v>
       </x:c>
@@ -5317,7 +5281,7 @@
       <x:c r="BC22" t="str">
         <x:v>Отделка</x:v>
       </x:c>
-      <x:c r="BD22" t="str"/>
+      <x:c r="BD22"/>
       <x:c r="BE22" t="str">
         <x:v>Стеновые панели, рейки и элементы декора</x:v>
       </x:c>
@@ -5339,28 +5303,28 @@
       <x:c r="BK22" t="str">
         <x:v>1140</x:v>
       </x:c>
-      <x:c r="BL22" t="str"/>
+      <x:c r="BL22"/>
       <x:c r="BM22" t="str">
         <x:v>Нет</x:v>
       </x:c>
-      <x:c r="BN22" t="str"/>
-      <x:c r="BO22" t="str"/>
-      <x:c r="BP22" t="str"/>
-      <x:c r="BQ22" t="str"/>
-      <x:c r="BR22" t="str"/>
-      <x:c r="BS22" t="str"/>
-      <x:c r="BT22" t="str"/>
-      <x:c r="BU22" t="str"/>
+      <x:c r="BN22"/>
+      <x:c r="BO22"/>
+      <x:c r="BP22"/>
+      <x:c r="BQ22"/>
+      <x:c r="BR22"/>
+      <x:c r="BS22"/>
+      <x:c r="BT22"/>
+      <x:c r="BU22"/>
     </x:row>
     <x:row r="23">
       <x:c r="A23" t="str">
         <x:v>adamar-vlg-BETON FERONI</x:v>
       </x:c>
-      <x:c r="B23" t="str"/>
-      <x:c r="C23" t="str"/>
-      <x:c r="D23" t="str"/>
-      <x:c r="E23" t="str"/>
-      <x:c r="F23" t="str"/>
+      <x:c r="B23"/>
+      <x:c r="C23"/>
+      <x:c r="D23"/>
+      <x:c r="E23"/>
+      <x:c r="F23"/>
       <x:c r="G23" t="str">
         <x:v>Adamar Group</x:v>
       </x:c>
@@ -5380,22 +5344,22 @@
       <x:c r="K23" t="str">
         <x:v>https://avatars.mds.yandex.net/get-yastore/20274467/q775nsnhfv9dfb2486f2f9qtd9rmffpb/orig | https://avatars.mds.yandex.net/get-yastore/20918687/q5ttswrk7xrxnfn6z4c9x9wp2hfxs566/orig | https://avatars.mds.yandex.net/get-yastore/21055393/77zplgmjgc72rls96628pdkfckft46dp/orig | https://avatars.mds.yandex.net/get-yastore/20760651/wdk2qsr69dxrvvtkjxccs5gslllbnzkc/orig</x:v>
       </x:c>
-      <x:c r="L23" t="str"/>
+      <x:c r="L23"/>
       <x:c r="M23" t="str">
         <x:v>По телефону и в сообщениях</x:v>
       </x:c>
-      <x:c r="N23" t="str"/>
-      <x:c r="O23" t="str"/>
-      <x:c r="P23" t="str"/>
+      <x:c r="N23"/>
+      <x:c r="O23"/>
+      <x:c r="P23"/>
       <x:c r="Q23" t="str">
         <x:v>Ремонт и строительство</x:v>
       </x:c>
       <x:c r="R23" t="str">
         <x:v>г. Волгоград, ул. 25-летия Октября, д. 1, стр. 3</x:v>
       </x:c>
-      <x:c r="S23" t="str"/>
-      <x:c r="T23" t="str"/>
-      <x:c r="U23" t="str"/>
+      <x:c r="S23"/>
+      <x:c r="T23"/>
+      <x:c r="U23"/>
       <x:c r="V23" t="str">
         <x:v>Поштучно</x:v>
       </x:c>
@@ -5411,9 +5375,9 @@
       <x:c r="Z23" t="str">
         <x:v>Штуку</x:v>
       </x:c>
-      <x:c r="AA23" t="str"/>
-      <x:c r="AB23" t="str"/>
-      <x:c r="AC23" t="str"/>
+      <x:c r="AA23"/>
+      <x:c r="AB23"/>
+      <x:c r="AC23"/>
       <x:c r="AD23" t="n">
         <x:v>7</x:v>
       </x:c>
@@ -5426,26 +5390,24 @@
       <x:c r="AG23" t="n">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="AH23" t="str"/>
+      <x:c r="AH23"/>
       <x:c r="AI23" t="str">
         <x:v>3921120000</x:v>
       </x:c>
-      <x:c r="AJ23" t="str">
-        <x:v>22.21.42.110</x:v>
-      </x:c>
-      <x:c r="AK23" t="str"/>
-      <x:c r="AL23" t="str"/>
-      <x:c r="AM23" t="str"/>
-      <x:c r="AN23" t="str"/>
-      <x:c r="AO23" t="str"/>
-      <x:c r="AP23" t="str"/>
-      <x:c r="AQ23" t="str"/>
-      <x:c r="AR23" t="str"/>
-      <x:c r="AS23" t="str"/>
-      <x:c r="AT23" t="str"/>
-      <x:c r="AU23" t="str"/>
-      <x:c r="AV23" t="str"/>
-      <x:c r="AW23" t="str"/>
+      <x:c r="AJ23" t="str"/>
+      <x:c r="AK23"/>
+      <x:c r="AL23"/>
+      <x:c r="AM23"/>
+      <x:c r="AN23"/>
+      <x:c r="AO23"/>
+      <x:c r="AP23"/>
+      <x:c r="AQ23"/>
+      <x:c r="AR23"/>
+      <x:c r="AS23"/>
+      <x:c r="AT23"/>
+      <x:c r="AU23"/>
+      <x:c r="AV23"/>
+      <x:c r="AW23"/>
       <x:c r="AX23" t="str">
         <x:v>3950</x:v>
       </x:c>
@@ -5464,7 +5426,7 @@
       <x:c r="BC23" t="str">
         <x:v>Отделка</x:v>
       </x:c>
-      <x:c r="BD23" t="str"/>
+      <x:c r="BD23"/>
       <x:c r="BE23" t="str">
         <x:v>Стеновые панели, рейки и элементы декора</x:v>
       </x:c>
@@ -5486,28 +5448,28 @@
       <x:c r="BK23" t="str">
         <x:v>1140</x:v>
       </x:c>
-      <x:c r="BL23" t="str"/>
+      <x:c r="BL23"/>
       <x:c r="BM23" t="str">
         <x:v>Нет</x:v>
       </x:c>
-      <x:c r="BN23" t="str"/>
-      <x:c r="BO23" t="str"/>
-      <x:c r="BP23" t="str"/>
-      <x:c r="BQ23" t="str"/>
-      <x:c r="BR23" t="str"/>
-      <x:c r="BS23" t="str"/>
-      <x:c r="BT23" t="str"/>
-      <x:c r="BU23" t="str"/>
+      <x:c r="BN23"/>
+      <x:c r="BO23"/>
+      <x:c r="BP23"/>
+      <x:c r="BQ23"/>
+      <x:c r="BR23"/>
+      <x:c r="BS23"/>
+      <x:c r="BT23"/>
+      <x:c r="BU23"/>
     </x:row>
     <x:row r="24">
       <x:c r="A24" t="str">
         <x:v>adamar-vlg-COLORED MARBLE 7</x:v>
       </x:c>
-      <x:c r="B24" t="str"/>
-      <x:c r="C24" t="str"/>
-      <x:c r="D24" t="str"/>
-      <x:c r="E24" t="str"/>
-      <x:c r="F24" t="str"/>
+      <x:c r="B24"/>
+      <x:c r="C24"/>
+      <x:c r="D24"/>
+      <x:c r="E24"/>
+      <x:c r="F24"/>
       <x:c r="G24" t="str">
         <x:v>Adamar Group</x:v>
       </x:c>
@@ -5527,22 +5489,22 @@
       <x:c r="K24" t="str">
         <x:v>https://avatars.mds.yandex.net/get-yastore/20274467/zrcg6w7hg548jtbwpd6lb5qv95plg5hw/orig | https://avatars.mds.yandex.net/get-yastore/20274467/gdmk94hv9bwkq7fpmsxqcvbpkflczrxt/orig | https://avatars.mds.yandex.net/get-yastore/20274467/wp28gth8f8h9bjdw9n9jz55c8xkrqrnx/orig | https://avatars.mds.yandex.net/get-yastore/20274467/r2p69stwgdp78tcw5fsnngrb5l72fkb9/orig</x:v>
       </x:c>
-      <x:c r="L24" t="str"/>
+      <x:c r="L24"/>
       <x:c r="M24" t="str">
         <x:v>По телефону и в сообщениях</x:v>
       </x:c>
-      <x:c r="N24" t="str"/>
-      <x:c r="O24" t="str"/>
-      <x:c r="P24" t="str"/>
+      <x:c r="N24"/>
+      <x:c r="O24"/>
+      <x:c r="P24"/>
       <x:c r="Q24" t="str">
         <x:v>Ремонт и строительство</x:v>
       </x:c>
       <x:c r="R24" t="str">
         <x:v>г. Волгоград, ул. 25-летия Октября, д. 1, стр. 3</x:v>
       </x:c>
-      <x:c r="S24" t="str"/>
-      <x:c r="T24" t="str"/>
-      <x:c r="U24" t="str"/>
+      <x:c r="S24"/>
+      <x:c r="T24"/>
+      <x:c r="U24"/>
       <x:c r="V24" t="str">
         <x:v>Поштучно</x:v>
       </x:c>
@@ -5558,9 +5520,9 @@
       <x:c r="Z24" t="str">
         <x:v>Штуку</x:v>
       </x:c>
-      <x:c r="AA24" t="str"/>
-      <x:c r="AB24" t="str"/>
-      <x:c r="AC24" t="str"/>
+      <x:c r="AA24"/>
+      <x:c r="AB24"/>
+      <x:c r="AC24"/>
       <x:c r="AD24" t="n">
         <x:v>7</x:v>
       </x:c>
@@ -5573,26 +5535,24 @@
       <x:c r="AG24" t="n">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="AH24" t="str"/>
+      <x:c r="AH24"/>
       <x:c r="AI24" t="str">
         <x:v>3921120000</x:v>
       </x:c>
-      <x:c r="AJ24" t="str">
-        <x:v>22.21.42.110</x:v>
-      </x:c>
-      <x:c r="AK24" t="str"/>
-      <x:c r="AL24" t="str"/>
-      <x:c r="AM24" t="str"/>
-      <x:c r="AN24" t="str"/>
-      <x:c r="AO24" t="str"/>
-      <x:c r="AP24" t="str"/>
-      <x:c r="AQ24" t="str"/>
-      <x:c r="AR24" t="str"/>
-      <x:c r="AS24" t="str"/>
-      <x:c r="AT24" t="str"/>
-      <x:c r="AU24" t="str"/>
-      <x:c r="AV24" t="str"/>
-      <x:c r="AW24" t="str"/>
+      <x:c r="AJ24" t="str"/>
+      <x:c r="AK24"/>
+      <x:c r="AL24"/>
+      <x:c r="AM24"/>
+      <x:c r="AN24"/>
+      <x:c r="AO24"/>
+      <x:c r="AP24"/>
+      <x:c r="AQ24"/>
+      <x:c r="AR24"/>
+      <x:c r="AS24"/>
+      <x:c r="AT24"/>
+      <x:c r="AU24"/>
+      <x:c r="AV24"/>
+      <x:c r="AW24"/>
       <x:c r="AX24" t="str">
         <x:v>3950</x:v>
       </x:c>
@@ -5611,7 +5571,7 @@
       <x:c r="BC24" t="str">
         <x:v>Отделка</x:v>
       </x:c>
-      <x:c r="BD24" t="str"/>
+      <x:c r="BD24"/>
       <x:c r="BE24" t="str">
         <x:v>Стеновые панели, рейки и элементы декора</x:v>
       </x:c>
@@ -5633,28 +5593,28 @@
       <x:c r="BK24" t="str">
         <x:v>1140</x:v>
       </x:c>
-      <x:c r="BL24" t="str"/>
+      <x:c r="BL24"/>
       <x:c r="BM24" t="str">
         <x:v>Нет</x:v>
       </x:c>
-      <x:c r="BN24" t="str"/>
-      <x:c r="BO24" t="str"/>
-      <x:c r="BP24" t="str"/>
-      <x:c r="BQ24" t="str"/>
-      <x:c r="BR24" t="str"/>
-      <x:c r="BS24" t="str"/>
-      <x:c r="BT24" t="str"/>
-      <x:c r="BU24" t="str"/>
+      <x:c r="BN24"/>
+      <x:c r="BO24"/>
+      <x:c r="BP24"/>
+      <x:c r="BQ24"/>
+      <x:c r="BR24"/>
+      <x:c r="BS24"/>
+      <x:c r="BT24"/>
+      <x:c r="BU24"/>
     </x:row>
     <x:row r="25">
       <x:c r="A25" t="str">
         <x:v>adamar-vlg-Glossy_Vanila_Sky</x:v>
       </x:c>
-      <x:c r="B25" t="str"/>
-      <x:c r="C25" t="str"/>
-      <x:c r="D25" t="str"/>
-      <x:c r="E25" t="str"/>
-      <x:c r="F25" t="str"/>
+      <x:c r="B25"/>
+      <x:c r="C25"/>
+      <x:c r="D25"/>
+      <x:c r="E25"/>
+      <x:c r="F25"/>
       <x:c r="G25" t="str">
         <x:v>Adamar Group</x:v>
       </x:c>
@@ -5674,22 +5634,22 @@
       <x:c r="K25" t="str">
         <x:v>https://avatars.mds.yandex.net/get-yastore/20274467/4zjf6j8qllw66k8mc2kjkpkrzbtpdvhx/orig | https://avatars.mds.yandex.net/get-yastore/20918687/t6ll57zcx7swtqkgrsshnhplcsb8qx7n/orig | https://avatars.mds.yandex.net/get-yastore/21055393/cjs7kt22xn4n5dctndxkkr47hl76bv29/orig | https://avatars.mds.yandex.net/get-yastore/18125838/bw72zxhq46m5s5rb6dbnsln7cdpbwkp2/orig</x:v>
       </x:c>
-      <x:c r="L25" t="str"/>
+      <x:c r="L25"/>
       <x:c r="M25" t="str">
         <x:v>По телефону и в сообщениях</x:v>
       </x:c>
-      <x:c r="N25" t="str"/>
-      <x:c r="O25" t="str"/>
-      <x:c r="P25" t="str"/>
+      <x:c r="N25"/>
+      <x:c r="O25"/>
+      <x:c r="P25"/>
       <x:c r="Q25" t="str">
         <x:v>Ремонт и строительство</x:v>
       </x:c>
       <x:c r="R25" t="str">
         <x:v>г. Волгоград, ул. 25-летия Октября, д. 1, стр. 3</x:v>
       </x:c>
-      <x:c r="S25" t="str"/>
-      <x:c r="T25" t="str"/>
-      <x:c r="U25" t="str"/>
+      <x:c r="S25"/>
+      <x:c r="T25"/>
+      <x:c r="U25"/>
       <x:c r="V25" t="str">
         <x:v>Поштучно</x:v>
       </x:c>
@@ -5705,9 +5665,9 @@
       <x:c r="Z25" t="str">
         <x:v>Штуку</x:v>
       </x:c>
-      <x:c r="AA25" t="str"/>
-      <x:c r="AB25" t="str"/>
-      <x:c r="AC25" t="str"/>
+      <x:c r="AA25"/>
+      <x:c r="AB25"/>
+      <x:c r="AC25"/>
       <x:c r="AD25" t="n">
         <x:v>7</x:v>
       </x:c>
@@ -5720,26 +5680,24 @@
       <x:c r="AG25" t="n">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="AH25" t="str"/>
+      <x:c r="AH25"/>
       <x:c r="AI25" t="str">
         <x:v>3921120000</x:v>
       </x:c>
-      <x:c r="AJ25" t="str">
-        <x:v>22.21.42.110</x:v>
-      </x:c>
-      <x:c r="AK25" t="str"/>
-      <x:c r="AL25" t="str"/>
-      <x:c r="AM25" t="str"/>
-      <x:c r="AN25" t="str"/>
-      <x:c r="AO25" t="str"/>
-      <x:c r="AP25" t="str"/>
-      <x:c r="AQ25" t="str"/>
-      <x:c r="AR25" t="str"/>
-      <x:c r="AS25" t="str"/>
-      <x:c r="AT25" t="str"/>
-      <x:c r="AU25" t="str"/>
-      <x:c r="AV25" t="str"/>
-      <x:c r="AW25" t="str"/>
+      <x:c r="AJ25" t="str"/>
+      <x:c r="AK25"/>
+      <x:c r="AL25"/>
+      <x:c r="AM25"/>
+      <x:c r="AN25"/>
+      <x:c r="AO25"/>
+      <x:c r="AP25"/>
+      <x:c r="AQ25"/>
+      <x:c r="AR25"/>
+      <x:c r="AS25"/>
+      <x:c r="AT25"/>
+      <x:c r="AU25"/>
+      <x:c r="AV25"/>
+      <x:c r="AW25"/>
       <x:c r="AX25" t="str">
         <x:v>3950</x:v>
       </x:c>
@@ -5758,7 +5716,7 @@
       <x:c r="BC25" t="str">
         <x:v>Отделка</x:v>
       </x:c>
-      <x:c r="BD25" t="str"/>
+      <x:c r="BD25"/>
       <x:c r="BE25" t="str">
         <x:v>Стеновые панели, рейки и элементы декора</x:v>
       </x:c>
@@ -5780,28 +5738,28 @@
       <x:c r="BK25" t="str">
         <x:v>1140</x:v>
       </x:c>
-      <x:c r="BL25" t="str"/>
+      <x:c r="BL25"/>
       <x:c r="BM25" t="str">
         <x:v>Нет</x:v>
       </x:c>
-      <x:c r="BN25" t="str"/>
-      <x:c r="BO25" t="str"/>
-      <x:c r="BP25" t="str"/>
-      <x:c r="BQ25" t="str"/>
-      <x:c r="BR25" t="str"/>
-      <x:c r="BS25" t="str"/>
-      <x:c r="BT25" t="str"/>
-      <x:c r="BU25" t="str"/>
+      <x:c r="BN25"/>
+      <x:c r="BO25"/>
+      <x:c r="BP25"/>
+      <x:c r="BQ25"/>
+      <x:c r="BR25"/>
+      <x:c r="BS25"/>
+      <x:c r="BT25"/>
+      <x:c r="BU25"/>
     </x:row>
     <x:row r="26">
       <x:c r="A26" t="str">
         <x:v>adamar-vlg-SCRIBBLE GRAY_1</x:v>
       </x:c>
-      <x:c r="B26" t="str"/>
-      <x:c r="C26" t="str"/>
-      <x:c r="D26" t="str"/>
-      <x:c r="E26" t="str"/>
-      <x:c r="F26" t="str"/>
+      <x:c r="B26"/>
+      <x:c r="C26"/>
+      <x:c r="D26"/>
+      <x:c r="E26"/>
+      <x:c r="F26"/>
       <x:c r="G26" t="str">
         <x:v>Adamar Group</x:v>
       </x:c>
@@ -5821,22 +5779,22 @@
       <x:c r="K26" t="str">
         <x:v>https://avatars.mds.yandex.net/get-yastore/21055393/9kkt59pv4mdn66w5bq7ts4s5s2zwvdcl/orig | https://avatars.mds.yandex.net/get-yastore/21055393/v89g7vkm4fpkcph8q5576xhg95kcchld/orig | https://avatars.mds.yandex.net/get-yastore/20918687/jfwnzj7czzdm72hsftfvfk5pzpwnjj2b/orig | https://avatars.mds.yandex.net/get-yastore/21055393/bk2tdvhntmz7zl25g9pzsxx2clkzxmwx/orig</x:v>
       </x:c>
-      <x:c r="L26" t="str"/>
+      <x:c r="L26"/>
       <x:c r="M26" t="str">
         <x:v>По телефону и в сообщениях</x:v>
       </x:c>
-      <x:c r="N26" t="str"/>
-      <x:c r="O26" t="str"/>
-      <x:c r="P26" t="str"/>
+      <x:c r="N26"/>
+      <x:c r="O26"/>
+      <x:c r="P26"/>
       <x:c r="Q26" t="str">
         <x:v>Ремонт и строительство</x:v>
       </x:c>
       <x:c r="R26" t="str">
         <x:v>г. Волгоград, ул. 25-летия Октября, д. 1, стр. 3</x:v>
       </x:c>
-      <x:c r="S26" t="str"/>
-      <x:c r="T26" t="str"/>
-      <x:c r="U26" t="str"/>
+      <x:c r="S26"/>
+      <x:c r="T26"/>
+      <x:c r="U26"/>
       <x:c r="V26" t="str">
         <x:v>Поштучно</x:v>
       </x:c>
@@ -5852,9 +5810,9 @@
       <x:c r="Z26" t="str">
         <x:v>Штуку</x:v>
       </x:c>
-      <x:c r="AA26" t="str"/>
-      <x:c r="AB26" t="str"/>
-      <x:c r="AC26" t="str"/>
+      <x:c r="AA26"/>
+      <x:c r="AB26"/>
+      <x:c r="AC26"/>
       <x:c r="AD26" t="n">
         <x:v>7</x:v>
       </x:c>
@@ -5867,26 +5825,24 @@
       <x:c r="AG26" t="n">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="AH26" t="str"/>
+      <x:c r="AH26"/>
       <x:c r="AI26" t="str">
         <x:v>3921120000</x:v>
       </x:c>
-      <x:c r="AJ26" t="str">
-        <x:v>22.21.42.110</x:v>
-      </x:c>
-      <x:c r="AK26" t="str"/>
-      <x:c r="AL26" t="str"/>
-      <x:c r="AM26" t="str"/>
-      <x:c r="AN26" t="str"/>
-      <x:c r="AO26" t="str"/>
-      <x:c r="AP26" t="str"/>
-      <x:c r="AQ26" t="str"/>
-      <x:c r="AR26" t="str"/>
-      <x:c r="AS26" t="str"/>
-      <x:c r="AT26" t="str"/>
-      <x:c r="AU26" t="str"/>
-      <x:c r="AV26" t="str"/>
-      <x:c r="AW26" t="str"/>
+      <x:c r="AJ26" t="str"/>
+      <x:c r="AK26"/>
+      <x:c r="AL26"/>
+      <x:c r="AM26"/>
+      <x:c r="AN26"/>
+      <x:c r="AO26"/>
+      <x:c r="AP26"/>
+      <x:c r="AQ26"/>
+      <x:c r="AR26"/>
+      <x:c r="AS26"/>
+      <x:c r="AT26"/>
+      <x:c r="AU26"/>
+      <x:c r="AV26"/>
+      <x:c r="AW26"/>
       <x:c r="AX26" t="str">
         <x:v>3950</x:v>
       </x:c>
@@ -5905,7 +5861,7 @@
       <x:c r="BC26" t="str">
         <x:v>Отделка</x:v>
       </x:c>
-      <x:c r="BD26" t="str"/>
+      <x:c r="BD26"/>
       <x:c r="BE26" t="str">
         <x:v>Стеновые панели, рейки и элементы декора</x:v>
       </x:c>
@@ -5927,28 +5883,28 @@
       <x:c r="BK26" t="str">
         <x:v>1140</x:v>
       </x:c>
-      <x:c r="BL26" t="str"/>
+      <x:c r="BL26"/>
       <x:c r="BM26" t="str">
         <x:v>Нет</x:v>
       </x:c>
-      <x:c r="BN26" t="str"/>
-      <x:c r="BO26" t="str"/>
-      <x:c r="BP26" t="str"/>
-      <x:c r="BQ26" t="str"/>
-      <x:c r="BR26" t="str"/>
-      <x:c r="BS26" t="str"/>
-      <x:c r="BT26" t="str"/>
-      <x:c r="BU26" t="str"/>
+      <x:c r="BN26"/>
+      <x:c r="BO26"/>
+      <x:c r="BP26"/>
+      <x:c r="BQ26"/>
+      <x:c r="BR26"/>
+      <x:c r="BS26"/>
+      <x:c r="BT26"/>
+      <x:c r="BU26"/>
     </x:row>
     <x:row r="27">
       <x:c r="A27" t="str">
         <x:v>adamar-vlg-Glossy_ Emperador Gold</x:v>
       </x:c>
-      <x:c r="B27" t="str"/>
-      <x:c r="C27" t="str"/>
-      <x:c r="D27" t="str"/>
-      <x:c r="E27" t="str"/>
-      <x:c r="F27" t="str"/>
+      <x:c r="B27"/>
+      <x:c r="C27"/>
+      <x:c r="D27"/>
+      <x:c r="E27"/>
+      <x:c r="F27"/>
       <x:c r="G27" t="str">
         <x:v>Adamar Group</x:v>
       </x:c>
@@ -5968,22 +5924,22 @@
       <x:c r="K27" t="str">
         <x:v>https://avatars.mds.yandex.net/get-yastore/20760651/g8zk8w4pxtbvqw4kv4pdcbp9rjqj6rxm/orig | https://avatars.mds.yandex.net/get-yastore/20760651/s9z96jw5d2bwd5pwvpwp7rzmxn4j7nx9/orig | https://avatars.mds.yandex.net/get-yastore/20760651/hs5zlsdcqp92f54bvt7scfmdfx6p9bzm/orig | https://avatars.mds.yandex.net/get-yastore/20760651/cgwq5zxnjsnwnpnrc8cn7d8brfwx96pp/orig</x:v>
       </x:c>
-      <x:c r="L27" t="str"/>
+      <x:c r="L27"/>
       <x:c r="M27" t="str">
         <x:v>По телефону и в сообщениях</x:v>
       </x:c>
-      <x:c r="N27" t="str"/>
-      <x:c r="O27" t="str"/>
-      <x:c r="P27" t="str"/>
+      <x:c r="N27"/>
+      <x:c r="O27"/>
+      <x:c r="P27"/>
       <x:c r="Q27" t="str">
         <x:v>Ремонт и строительство</x:v>
       </x:c>
       <x:c r="R27" t="str">
         <x:v>г. Волгоград, ул. 25-летия Октября, д. 1, стр. 3</x:v>
       </x:c>
-      <x:c r="S27" t="str"/>
-      <x:c r="T27" t="str"/>
-      <x:c r="U27" t="str"/>
+      <x:c r="S27"/>
+      <x:c r="T27"/>
+      <x:c r="U27"/>
       <x:c r="V27" t="str">
         <x:v>Поштучно</x:v>
       </x:c>
@@ -5999,9 +5955,9 @@
       <x:c r="Z27" t="str">
         <x:v>Штуку</x:v>
       </x:c>
-      <x:c r="AA27" t="str"/>
-      <x:c r="AB27" t="str"/>
-      <x:c r="AC27" t="str"/>
+      <x:c r="AA27"/>
+      <x:c r="AB27"/>
+      <x:c r="AC27"/>
       <x:c r="AD27" t="n">
         <x:v>7</x:v>
       </x:c>
@@ -6014,26 +5970,24 @@
       <x:c r="AG27" t="n">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="AH27" t="str"/>
+      <x:c r="AH27"/>
       <x:c r="AI27" t="str">
         <x:v>3921120000</x:v>
       </x:c>
-      <x:c r="AJ27" t="str">
-        <x:v>22.21.42.110</x:v>
-      </x:c>
-      <x:c r="AK27" t="str"/>
-      <x:c r="AL27" t="str"/>
-      <x:c r="AM27" t="str"/>
-      <x:c r="AN27" t="str"/>
-      <x:c r="AO27" t="str"/>
-      <x:c r="AP27" t="str"/>
-      <x:c r="AQ27" t="str"/>
-      <x:c r="AR27" t="str"/>
-      <x:c r="AS27" t="str"/>
-      <x:c r="AT27" t="str"/>
-      <x:c r="AU27" t="str"/>
-      <x:c r="AV27" t="str"/>
-      <x:c r="AW27" t="str"/>
+      <x:c r="AJ27" t="str"/>
+      <x:c r="AK27"/>
+      <x:c r="AL27"/>
+      <x:c r="AM27"/>
+      <x:c r="AN27"/>
+      <x:c r="AO27"/>
+      <x:c r="AP27"/>
+      <x:c r="AQ27"/>
+      <x:c r="AR27"/>
+      <x:c r="AS27"/>
+      <x:c r="AT27"/>
+      <x:c r="AU27"/>
+      <x:c r="AV27"/>
+      <x:c r="AW27"/>
       <x:c r="AX27" t="str">
         <x:v>3950</x:v>
       </x:c>
@@ -6052,7 +6006,7 @@
       <x:c r="BC27" t="str">
         <x:v>Отделка</x:v>
       </x:c>
-      <x:c r="BD27" t="str"/>
+      <x:c r="BD27"/>
       <x:c r="BE27" t="str">
         <x:v>Стеновые панели, рейки и элементы декора</x:v>
       </x:c>
@@ -6074,28 +6028,28 @@
       <x:c r="BK27" t="str">
         <x:v>1140</x:v>
       </x:c>
-      <x:c r="BL27" t="str"/>
+      <x:c r="BL27"/>
       <x:c r="BM27" t="str">
         <x:v>Нет</x:v>
       </x:c>
-      <x:c r="BN27" t="str"/>
-      <x:c r="BO27" t="str"/>
-      <x:c r="BP27" t="str"/>
-      <x:c r="BQ27" t="str"/>
-      <x:c r="BR27" t="str"/>
-      <x:c r="BS27" t="str"/>
-      <x:c r="BT27" t="str"/>
-      <x:c r="BU27" t="str"/>
+      <x:c r="BN27"/>
+      <x:c r="BO27"/>
+      <x:c r="BP27"/>
+      <x:c r="BQ27"/>
+      <x:c r="BR27"/>
+      <x:c r="BS27"/>
+      <x:c r="BT27"/>
+      <x:c r="BU27"/>
     </x:row>
     <x:row r="28">
       <x:c r="A28" t="str">
         <x:v>adamar-vlg-Onyx Sonara_1RESCALE</x:v>
       </x:c>
-      <x:c r="B28" t="str"/>
-      <x:c r="C28" t="str"/>
-      <x:c r="D28" t="str"/>
-      <x:c r="E28" t="str"/>
-      <x:c r="F28" t="str"/>
+      <x:c r="B28"/>
+      <x:c r="C28"/>
+      <x:c r="D28"/>
+      <x:c r="E28"/>
+      <x:c r="F28"/>
       <x:c r="G28" t="str">
         <x:v>Adamar Group</x:v>
       </x:c>
@@ -6115,22 +6069,22 @@
       <x:c r="K28" t="str">
         <x:v>https://avatars.mds.yandex.net/get-yastore/21055393/dlshdvlqg4tlg6rtvlcvm8p8ktt99c9f/orig | https://avatars.mds.yandex.net/get-yastore/20918687/mr4n22wvwmjmmp4pg6n4bpqkkcpc28jf/orig | https://avatars.mds.yandex.net/get-yastore/20918687/489478v5kpn5hqncffc4fn7lcmxttlmf/orig | https://avatars.mds.yandex.net/get-yastore/20918687/qjdnd5cbc5pv5lqx7rtgph64mpwsmvrw/orig | https://avatars.mds.yandex.net/get-yastore/20918687/jhnhd8x8m4kgccgtkr9kql8h2mqjzf42/orig</x:v>
       </x:c>
-      <x:c r="L28" t="str"/>
+      <x:c r="L28"/>
       <x:c r="M28" t="str">
         <x:v>По телефону и в сообщениях</x:v>
       </x:c>
-      <x:c r="N28" t="str"/>
-      <x:c r="O28" t="str"/>
-      <x:c r="P28" t="str"/>
+      <x:c r="N28"/>
+      <x:c r="O28"/>
+      <x:c r="P28"/>
       <x:c r="Q28" t="str">
         <x:v>Ремонт и строительство</x:v>
       </x:c>
       <x:c r="R28" t="str">
         <x:v>г. Волгоград, ул. 25-летия Октября, д. 1, стр. 3</x:v>
       </x:c>
-      <x:c r="S28" t="str"/>
-      <x:c r="T28" t="str"/>
-      <x:c r="U28" t="str"/>
+      <x:c r="S28"/>
+      <x:c r="T28"/>
+      <x:c r="U28"/>
       <x:c r="V28" t="str">
         <x:v>Поштучно</x:v>
       </x:c>
@@ -6146,9 +6100,9 @@
       <x:c r="Z28" t="str">
         <x:v>Штуку</x:v>
       </x:c>
-      <x:c r="AA28" t="str"/>
-      <x:c r="AB28" t="str"/>
-      <x:c r="AC28" t="str"/>
+      <x:c r="AA28"/>
+      <x:c r="AB28"/>
+      <x:c r="AC28"/>
       <x:c r="AD28" t="n">
         <x:v>7</x:v>
       </x:c>
@@ -6161,26 +6115,24 @@
       <x:c r="AG28" t="n">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="AH28" t="str"/>
+      <x:c r="AH28"/>
       <x:c r="AI28" t="str">
         <x:v>3921120000</x:v>
       </x:c>
-      <x:c r="AJ28" t="str">
-        <x:v>22.21.42.110</x:v>
-      </x:c>
-      <x:c r="AK28" t="str"/>
-      <x:c r="AL28" t="str"/>
-      <x:c r="AM28" t="str"/>
-      <x:c r="AN28" t="str"/>
-      <x:c r="AO28" t="str"/>
-      <x:c r="AP28" t="str"/>
-      <x:c r="AQ28" t="str"/>
-      <x:c r="AR28" t="str"/>
-      <x:c r="AS28" t="str"/>
-      <x:c r="AT28" t="str"/>
-      <x:c r="AU28" t="str"/>
-      <x:c r="AV28" t="str"/>
-      <x:c r="AW28" t="str"/>
+      <x:c r="AJ28" t="str"/>
+      <x:c r="AK28"/>
+      <x:c r="AL28"/>
+      <x:c r="AM28"/>
+      <x:c r="AN28"/>
+      <x:c r="AO28"/>
+      <x:c r="AP28"/>
+      <x:c r="AQ28"/>
+      <x:c r="AR28"/>
+      <x:c r="AS28"/>
+      <x:c r="AT28"/>
+      <x:c r="AU28"/>
+      <x:c r="AV28"/>
+      <x:c r="AW28"/>
       <x:c r="AX28" t="str">
         <x:v>3950</x:v>
       </x:c>
@@ -6199,7 +6151,7 @@
       <x:c r="BC28" t="str">
         <x:v>Отделка</x:v>
       </x:c>
-      <x:c r="BD28" t="str"/>
+      <x:c r="BD28"/>
       <x:c r="BE28" t="str">
         <x:v>Стеновые панели, рейки и элементы декора</x:v>
       </x:c>
@@ -6221,28 +6173,28 @@
       <x:c r="BK28" t="str">
         <x:v>1140</x:v>
       </x:c>
-      <x:c r="BL28" t="str"/>
+      <x:c r="BL28"/>
       <x:c r="BM28" t="str">
         <x:v>Нет</x:v>
       </x:c>
-      <x:c r="BN28" t="str"/>
-      <x:c r="BO28" t="str"/>
-      <x:c r="BP28" t="str"/>
-      <x:c r="BQ28" t="str"/>
-      <x:c r="BR28" t="str"/>
-      <x:c r="BS28" t="str"/>
-      <x:c r="BT28" t="str"/>
-      <x:c r="BU28" t="str"/>
+      <x:c r="BN28"/>
+      <x:c r="BO28"/>
+      <x:c r="BP28"/>
+      <x:c r="BQ28"/>
+      <x:c r="BR28"/>
+      <x:c r="BS28"/>
+      <x:c r="BT28"/>
+      <x:c r="BU28"/>
     </x:row>
     <x:row r="29">
       <x:c r="A29" t="str">
         <x:v>adamar-vlg-Tile Wood</x:v>
       </x:c>
-      <x:c r="B29" t="str"/>
-      <x:c r="C29" t="str"/>
-      <x:c r="D29" t="str"/>
-      <x:c r="E29" t="str"/>
-      <x:c r="F29" t="str"/>
+      <x:c r="B29"/>
+      <x:c r="C29"/>
+      <x:c r="D29"/>
+      <x:c r="E29"/>
+      <x:c r="F29"/>
       <x:c r="G29" t="str">
         <x:v>Adamar Group</x:v>
       </x:c>
@@ -6262,22 +6214,22 @@
       <x:c r="K29" t="str">
         <x:v>https://avatars.mds.yandex.net/get-yastore/20900992/tgk654kbhhjcm7h45nqnr2gg962p6677/orig | https://avatars.mds.yandex.net/get-yastore/20900992/gpkckjhdffg525crqsz9scntw9bf5kwj/orig | https://avatars.mds.yandex.net/get-yastore/20900992/kl9x9jrkl7z7lqxkmsxlm5nfql88zc8b/orig</x:v>
       </x:c>
-      <x:c r="L29" t="str"/>
+      <x:c r="L29"/>
       <x:c r="M29" t="str">
         <x:v>По телефону и в сообщениях</x:v>
       </x:c>
-      <x:c r="N29" t="str"/>
-      <x:c r="O29" t="str"/>
-      <x:c r="P29" t="str"/>
+      <x:c r="N29"/>
+      <x:c r="O29"/>
+      <x:c r="P29"/>
       <x:c r="Q29" t="str">
         <x:v>Ремонт и строительство</x:v>
       </x:c>
       <x:c r="R29" t="str">
         <x:v>г. Волгоград, ул. 25-летия Октября, д. 1, стр. 3</x:v>
       </x:c>
-      <x:c r="S29" t="str"/>
-      <x:c r="T29" t="str"/>
-      <x:c r="U29" t="str"/>
+      <x:c r="S29"/>
+      <x:c r="T29"/>
+      <x:c r="U29"/>
       <x:c r="V29" t="str">
         <x:v>Поштучно</x:v>
       </x:c>
@@ -6293,9 +6245,9 @@
       <x:c r="Z29" t="str">
         <x:v>Штуку</x:v>
       </x:c>
-      <x:c r="AA29" t="str"/>
-      <x:c r="AB29" t="str"/>
-      <x:c r="AC29" t="str"/>
+      <x:c r="AA29"/>
+      <x:c r="AB29"/>
+      <x:c r="AC29"/>
       <x:c r="AD29" t="n">
         <x:v>7</x:v>
       </x:c>
@@ -6308,26 +6260,24 @@
       <x:c r="AG29" t="n">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="AH29" t="str"/>
+      <x:c r="AH29"/>
       <x:c r="AI29" t="str">
         <x:v>3921120000</x:v>
       </x:c>
-      <x:c r="AJ29" t="str">
-        <x:v>22.21.42.110</x:v>
-      </x:c>
-      <x:c r="AK29" t="str"/>
-      <x:c r="AL29" t="str"/>
-      <x:c r="AM29" t="str"/>
-      <x:c r="AN29" t="str"/>
-      <x:c r="AO29" t="str"/>
-      <x:c r="AP29" t="str"/>
-      <x:c r="AQ29" t="str"/>
-      <x:c r="AR29" t="str"/>
-      <x:c r="AS29" t="str"/>
-      <x:c r="AT29" t="str"/>
-      <x:c r="AU29" t="str"/>
-      <x:c r="AV29" t="str"/>
-      <x:c r="AW29" t="str"/>
+      <x:c r="AJ29" t="str"/>
+      <x:c r="AK29"/>
+      <x:c r="AL29"/>
+      <x:c r="AM29"/>
+      <x:c r="AN29"/>
+      <x:c r="AO29"/>
+      <x:c r="AP29"/>
+      <x:c r="AQ29"/>
+      <x:c r="AR29"/>
+      <x:c r="AS29"/>
+      <x:c r="AT29"/>
+      <x:c r="AU29"/>
+      <x:c r="AV29"/>
+      <x:c r="AW29"/>
       <x:c r="AX29" t="str">
         <x:v>3950</x:v>
       </x:c>
@@ -6346,7 +6296,7 @@
       <x:c r="BC29" t="str">
         <x:v>Отделка</x:v>
       </x:c>
-      <x:c r="BD29" t="str"/>
+      <x:c r="BD29"/>
       <x:c r="BE29" t="str">
         <x:v>Стеновые панели, рейки и элементы декора</x:v>
       </x:c>
@@ -6368,28 +6318,28 @@
       <x:c r="BK29" t="str">
         <x:v>1140</x:v>
       </x:c>
-      <x:c r="BL29" t="str"/>
+      <x:c r="BL29"/>
       <x:c r="BM29" t="str">
         <x:v>Нет</x:v>
       </x:c>
-      <x:c r="BN29" t="str"/>
-      <x:c r="BO29" t="str"/>
-      <x:c r="BP29" t="str"/>
-      <x:c r="BQ29" t="str"/>
-      <x:c r="BR29" t="str"/>
-      <x:c r="BS29" t="str"/>
-      <x:c r="BT29" t="str"/>
-      <x:c r="BU29" t="str"/>
+      <x:c r="BN29"/>
+      <x:c r="BO29"/>
+      <x:c r="BP29"/>
+      <x:c r="BQ29"/>
+      <x:c r="BR29"/>
+      <x:c r="BS29"/>
+      <x:c r="BT29"/>
+      <x:c r="BU29"/>
     </x:row>
     <x:row r="30">
       <x:c r="A30" t="str">
         <x:v>adamar-vlg-BETON GREYSON_2</x:v>
       </x:c>
-      <x:c r="B30" t="str"/>
-      <x:c r="C30" t="str"/>
-      <x:c r="D30" t="str"/>
-      <x:c r="E30" t="str"/>
-      <x:c r="F30" t="str"/>
+      <x:c r="B30"/>
+      <x:c r="C30"/>
+      <x:c r="D30"/>
+      <x:c r="E30"/>
+      <x:c r="F30"/>
       <x:c r="G30" t="str">
         <x:v>Adamar Group</x:v>
       </x:c>
@@ -6409,22 +6359,22 @@
       <x:c r="K30" t="str">
         <x:v>https://avatars.mds.yandex.net/get-yastore/20918687/d8c667nvxvfrknpnsnbc5dqlclssppfm/orig | https://avatars.mds.yandex.net/get-yastore/20274467/x95jrn2jjbtlqk4lrdptcsf7p8fbmgrs/orig | https://avatars.mds.yandex.net/get-yastore/20274467/shmhnrqg5gbtwl994l2rlprv2tg27mb7/orig | https://avatars.mds.yandex.net/get-yastore/20918687/vfcwt5qh4nlsz6npz6td9hxpxqpbcccz/orig</x:v>
       </x:c>
-      <x:c r="L30" t="str"/>
+      <x:c r="L30"/>
       <x:c r="M30" t="str">
         <x:v>По телефону и в сообщениях</x:v>
       </x:c>
-      <x:c r="N30" t="str"/>
-      <x:c r="O30" t="str"/>
-      <x:c r="P30" t="str"/>
+      <x:c r="N30"/>
+      <x:c r="O30"/>
+      <x:c r="P30"/>
       <x:c r="Q30" t="str">
         <x:v>Ремонт и строительство</x:v>
       </x:c>
       <x:c r="R30" t="str">
         <x:v>г. Волгоград, ул. 25-летия Октября, д. 1, стр. 3</x:v>
       </x:c>
-      <x:c r="S30" t="str"/>
-      <x:c r="T30" t="str"/>
-      <x:c r="U30" t="str"/>
+      <x:c r="S30"/>
+      <x:c r="T30"/>
+      <x:c r="U30"/>
       <x:c r="V30" t="str">
         <x:v>Поштучно</x:v>
       </x:c>
@@ -6440,9 +6390,9 @@
       <x:c r="Z30" t="str">
         <x:v>Штуку</x:v>
       </x:c>
-      <x:c r="AA30" t="str"/>
-      <x:c r="AB30" t="str"/>
-      <x:c r="AC30" t="str"/>
+      <x:c r="AA30"/>
+      <x:c r="AB30"/>
+      <x:c r="AC30"/>
       <x:c r="AD30" t="n">
         <x:v>7</x:v>
       </x:c>
@@ -6455,26 +6405,24 @@
       <x:c r="AG30" t="n">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="AH30" t="str"/>
+      <x:c r="AH30"/>
       <x:c r="AI30" t="str">
         <x:v>3921120000</x:v>
       </x:c>
-      <x:c r="AJ30" t="str">
-        <x:v>22.21.42.110</x:v>
-      </x:c>
-      <x:c r="AK30" t="str"/>
-      <x:c r="AL30" t="str"/>
-      <x:c r="AM30" t="str"/>
-      <x:c r="AN30" t="str"/>
-      <x:c r="AO30" t="str"/>
-      <x:c r="AP30" t="str"/>
-      <x:c r="AQ30" t="str"/>
-      <x:c r="AR30" t="str"/>
-      <x:c r="AS30" t="str"/>
-      <x:c r="AT30" t="str"/>
-      <x:c r="AU30" t="str"/>
-      <x:c r="AV30" t="str"/>
-      <x:c r="AW30" t="str"/>
+      <x:c r="AJ30" t="str"/>
+      <x:c r="AK30"/>
+      <x:c r="AL30"/>
+      <x:c r="AM30"/>
+      <x:c r="AN30"/>
+      <x:c r="AO30"/>
+      <x:c r="AP30"/>
+      <x:c r="AQ30"/>
+      <x:c r="AR30"/>
+      <x:c r="AS30"/>
+      <x:c r="AT30"/>
+      <x:c r="AU30"/>
+      <x:c r="AV30"/>
+      <x:c r="AW30"/>
       <x:c r="AX30" t="str">
         <x:v>3950</x:v>
       </x:c>
@@ -6493,7 +6441,7 @@
       <x:c r="BC30" t="str">
         <x:v>Отделка</x:v>
       </x:c>
-      <x:c r="BD30" t="str"/>
+      <x:c r="BD30"/>
       <x:c r="BE30" t="str">
         <x:v>Стеновые панели, рейки и элементы декора</x:v>
       </x:c>
@@ -6515,28 +6463,28 @@
       <x:c r="BK30" t="str">
         <x:v>1140</x:v>
       </x:c>
-      <x:c r="BL30" t="str"/>
+      <x:c r="BL30"/>
       <x:c r="BM30" t="str">
         <x:v>Нет</x:v>
       </x:c>
-      <x:c r="BN30" t="str"/>
-      <x:c r="BO30" t="str"/>
-      <x:c r="BP30" t="str"/>
-      <x:c r="BQ30" t="str"/>
-      <x:c r="BR30" t="str"/>
-      <x:c r="BS30" t="str"/>
-      <x:c r="BT30" t="str"/>
-      <x:c r="BU30" t="str"/>
+      <x:c r="BN30"/>
+      <x:c r="BO30"/>
+      <x:c r="BP30"/>
+      <x:c r="BQ30"/>
+      <x:c r="BR30"/>
+      <x:c r="BS30"/>
+      <x:c r="BT30"/>
+      <x:c r="BU30"/>
     </x:row>
     <x:row r="31">
       <x:c r="A31" t="str">
         <x:v>adamar-vlg-Glossy_ColoredMarble_12</x:v>
       </x:c>
-      <x:c r="B31" t="str"/>
-      <x:c r="C31" t="str"/>
-      <x:c r="D31" t="str"/>
-      <x:c r="E31" t="str"/>
-      <x:c r="F31" t="str"/>
+      <x:c r="B31"/>
+      <x:c r="C31"/>
+      <x:c r="D31"/>
+      <x:c r="E31"/>
+      <x:c r="F31"/>
       <x:c r="G31" t="str">
         <x:v>Adamar Group</x:v>
       </x:c>
@@ -6556,22 +6504,22 @@
       <x:c r="K31" t="str">
         <x:v>https://avatars.mds.yandex.net/get-yastore/20918687/mqnvdhj4pf7xszrl94qz75mxk47n9tjd/orig | https://avatars.mds.yandex.net/get-yastore/20811730/95dwnhrcxkhbg6nzbb4wl5r95zmtrb54/orig | https://avatars.mds.yandex.net/get-yastore/21580234/5dg2vv677zl8rlt75nx5s9zzh2hr5fhz/orig | https://avatars.mds.yandex.net/get-yastore/18125838/h2k7jt5f775hrbcx6xtl2p5dbp6m2642/orig</x:v>
       </x:c>
-      <x:c r="L31" t="str"/>
+      <x:c r="L31"/>
       <x:c r="M31" t="str">
         <x:v>По телефону и в сообщениях</x:v>
       </x:c>
-      <x:c r="N31" t="str"/>
-      <x:c r="O31" t="str"/>
-      <x:c r="P31" t="str"/>
+      <x:c r="N31"/>
+      <x:c r="O31"/>
+      <x:c r="P31"/>
       <x:c r="Q31" t="str">
         <x:v>Ремонт и строительство</x:v>
       </x:c>
       <x:c r="R31" t="str">
         <x:v>г. Волгоград, ул. 25-летия Октября, д. 1, стр. 3</x:v>
       </x:c>
-      <x:c r="S31" t="str"/>
-      <x:c r="T31" t="str"/>
-      <x:c r="U31" t="str"/>
+      <x:c r="S31"/>
+      <x:c r="T31"/>
+      <x:c r="U31"/>
       <x:c r="V31" t="str">
         <x:v>Поштучно</x:v>
       </x:c>
@@ -6587,9 +6535,9 @@
       <x:c r="Z31" t="str">
         <x:v>Штуку</x:v>
       </x:c>
-      <x:c r="AA31" t="str"/>
-      <x:c r="AB31" t="str"/>
-      <x:c r="AC31" t="str"/>
+      <x:c r="AA31"/>
+      <x:c r="AB31"/>
+      <x:c r="AC31"/>
       <x:c r="AD31" t="n">
         <x:v>7</x:v>
       </x:c>
@@ -6602,26 +6550,24 @@
       <x:c r="AG31" t="n">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="AH31" t="str"/>
+      <x:c r="AH31"/>
       <x:c r="AI31" t="str">
         <x:v>3921120000</x:v>
       </x:c>
-      <x:c r="AJ31" t="str">
-        <x:v>22.21.42.110</x:v>
-      </x:c>
-      <x:c r="AK31" t="str"/>
-      <x:c r="AL31" t="str"/>
-      <x:c r="AM31" t="str"/>
-      <x:c r="AN31" t="str"/>
-      <x:c r="AO31" t="str"/>
-      <x:c r="AP31" t="str"/>
-      <x:c r="AQ31" t="str"/>
-      <x:c r="AR31" t="str"/>
-      <x:c r="AS31" t="str"/>
-      <x:c r="AT31" t="str"/>
-      <x:c r="AU31" t="str"/>
-      <x:c r="AV31" t="str"/>
-      <x:c r="AW31" t="str"/>
+      <x:c r="AJ31" t="str"/>
+      <x:c r="AK31"/>
+      <x:c r="AL31"/>
+      <x:c r="AM31"/>
+      <x:c r="AN31"/>
+      <x:c r="AO31"/>
+      <x:c r="AP31"/>
+      <x:c r="AQ31"/>
+      <x:c r="AR31"/>
+      <x:c r="AS31"/>
+      <x:c r="AT31"/>
+      <x:c r="AU31"/>
+      <x:c r="AV31"/>
+      <x:c r="AW31"/>
       <x:c r="AX31" t="str">
         <x:v>3950</x:v>
       </x:c>
@@ -6640,7 +6586,7 @@
       <x:c r="BC31" t="str">
         <x:v>Отделка</x:v>
       </x:c>
-      <x:c r="BD31" t="str"/>
+      <x:c r="BD31"/>
       <x:c r="BE31" t="str">
         <x:v>Стеновые панели, рейки и элементы декора</x:v>
       </x:c>
@@ -6662,28 +6608,28 @@
       <x:c r="BK31" t="str">
         <x:v>1140</x:v>
       </x:c>
-      <x:c r="BL31" t="str"/>
+      <x:c r="BL31"/>
       <x:c r="BM31" t="str">
         <x:v>Нет</x:v>
       </x:c>
-      <x:c r="BN31" t="str"/>
-      <x:c r="BO31" t="str"/>
-      <x:c r="BP31" t="str"/>
-      <x:c r="BQ31" t="str"/>
-      <x:c r="BR31" t="str"/>
-      <x:c r="BS31" t="str"/>
-      <x:c r="BT31" t="str"/>
-      <x:c r="BU31" t="str"/>
+      <x:c r="BN31"/>
+      <x:c r="BO31"/>
+      <x:c r="BP31"/>
+      <x:c r="BQ31"/>
+      <x:c r="BR31"/>
+      <x:c r="BS31"/>
+      <x:c r="BT31"/>
+      <x:c r="BU31"/>
     </x:row>
     <x:row r="32">
       <x:c r="A32" t="str">
         <x:v>adamar-vlg-Жидкие гвозди_290мл</x:v>
       </x:c>
-      <x:c r="B32" t="str"/>
-      <x:c r="C32" t="str"/>
-      <x:c r="D32" t="str"/>
-      <x:c r="E32" t="str"/>
-      <x:c r="F32" t="str"/>
+      <x:c r="B32"/>
+      <x:c r="C32"/>
+      <x:c r="D32"/>
+      <x:c r="E32"/>
+      <x:c r="F32"/>
       <x:c r="G32" t="str">
         <x:v>Adamar Group</x:v>
       </x:c>
@@ -6703,22 +6649,22 @@
       <x:c r="K32" t="str">
         <x:v>https://avatars.mds.yandex.net/get-yastore/21012869/rb8t5498jj2657gnvgwbv4gnzgcvhwx4/orig</x:v>
       </x:c>
-      <x:c r="L32" t="str"/>
+      <x:c r="L32"/>
       <x:c r="M32" t="str">
         <x:v>По телефону и в сообщениях</x:v>
       </x:c>
-      <x:c r="N32" t="str"/>
-      <x:c r="O32" t="str"/>
-      <x:c r="P32" t="str"/>
+      <x:c r="N32"/>
+      <x:c r="O32"/>
+      <x:c r="P32"/>
       <x:c r="Q32" t="str">
         <x:v>Ремонт и строительство</x:v>
       </x:c>
       <x:c r="R32" t="str">
         <x:v>г. Волгоград, ул. 25-летия Октября, д. 1, стр. 3</x:v>
       </x:c>
-      <x:c r="S32" t="str"/>
-      <x:c r="T32" t="str"/>
-      <x:c r="U32" t="str"/>
+      <x:c r="S32"/>
+      <x:c r="T32"/>
+      <x:c r="U32"/>
       <x:c r="V32" t="str">
         <x:v>Поштучно</x:v>
       </x:c>
@@ -6734,29 +6680,29 @@
       <x:c r="Z32" t="str">
         <x:v>Штуку</x:v>
       </x:c>
-      <x:c r="AA32" t="str"/>
-      <x:c r="AB32" t="str"/>
-      <x:c r="AC32" t="str"/>
-      <x:c r="AD32" t="str"/>
-      <x:c r="AE32" t="str"/>
-      <x:c r="AF32" t="str"/>
-      <x:c r="AG32" t="str"/>
-      <x:c r="AH32" t="str"/>
-      <x:c r="AI32" t="str"/>
-      <x:c r="AJ32" t="str"/>
-      <x:c r="AK32" t="str"/>
-      <x:c r="AL32" t="str"/>
-      <x:c r="AM32" t="str"/>
-      <x:c r="AN32" t="str"/>
-      <x:c r="AO32" t="str"/>
-      <x:c r="AP32" t="str"/>
-      <x:c r="AQ32" t="str"/>
-      <x:c r="AR32" t="str"/>
-      <x:c r="AS32" t="str"/>
-      <x:c r="AT32" t="str"/>
-      <x:c r="AU32" t="str"/>
-      <x:c r="AV32" t="str"/>
-      <x:c r="AW32" t="str"/>
+      <x:c r="AA32"/>
+      <x:c r="AB32"/>
+      <x:c r="AC32"/>
+      <x:c r="AD32"/>
+      <x:c r="AE32"/>
+      <x:c r="AF32"/>
+      <x:c r="AG32"/>
+      <x:c r="AH32"/>
+      <x:c r="AI32"/>
+      <x:c r="AJ32"/>
+      <x:c r="AK32"/>
+      <x:c r="AL32"/>
+      <x:c r="AM32"/>
+      <x:c r="AN32"/>
+      <x:c r="AO32"/>
+      <x:c r="AP32"/>
+      <x:c r="AQ32"/>
+      <x:c r="AR32"/>
+      <x:c r="AS32"/>
+      <x:c r="AT32"/>
+      <x:c r="AU32"/>
+      <x:c r="AV32"/>
+      <x:c r="AW32"/>
       <x:c r="AX32" t="str">
         <x:v>490</x:v>
       </x:c>
@@ -6775,7 +6721,7 @@
       <x:c r="BC32" t="str">
         <x:v>Отделка</x:v>
       </x:c>
-      <x:c r="BD32" t="str"/>
+      <x:c r="BD32"/>
       <x:c r="BE32" t="str">
         <x:v>Стеновые панели, рейки и элементы декора</x:v>
       </x:c>
@@ -6797,28 +6743,28 @@
       <x:c r="BK32" t="str">
         <x:v>1140</x:v>
       </x:c>
-      <x:c r="BL32" t="str"/>
+      <x:c r="BL32"/>
       <x:c r="BM32" t="str">
         <x:v>Нет</x:v>
       </x:c>
-      <x:c r="BN32" t="str"/>
-      <x:c r="BO32" t="str"/>
-      <x:c r="BP32" t="str"/>
-      <x:c r="BQ32" t="str"/>
-      <x:c r="BR32" t="str"/>
-      <x:c r="BS32" t="str"/>
-      <x:c r="BT32" t="str"/>
-      <x:c r="BU32" t="str"/>
+      <x:c r="BN32"/>
+      <x:c r="BO32"/>
+      <x:c r="BP32"/>
+      <x:c r="BQ32"/>
+      <x:c r="BR32"/>
+      <x:c r="BS32"/>
+      <x:c r="BT32"/>
+      <x:c r="BU32"/>
     </x:row>
     <x:row r="33">
       <x:c r="A33" t="str">
         <x:v>adamar-vlg-ДУБ БЕЛЕНЫЙ</x:v>
       </x:c>
-      <x:c r="B33" t="str"/>
-      <x:c r="C33" t="str"/>
-      <x:c r="D33" t="str"/>
-      <x:c r="E33" t="str"/>
-      <x:c r="F33" t="str"/>
+      <x:c r="B33"/>
+      <x:c r="C33"/>
+      <x:c r="D33"/>
+      <x:c r="E33"/>
+      <x:c r="F33"/>
       <x:c r="G33" t="str">
         <x:v>Adamar Group</x:v>
       </x:c>
@@ -6838,22 +6784,22 @@
       <x:c r="K33" t="str">
         <x:v>https://avatars.mds.yandex.net/get-yastore/21044143/9vjbw4hhj7cjqzcb4qwft87tm7bdlb5d/orig | https://avatars.mds.yandex.net/get-yastore/20918687/lfck5pdxflgh5jxjvhj59x6584zgqtrd/orig | https://avatars.mds.yandex.net/get-yastore/20918687/4nxrrq9q62cwnv68swfhtmk546k8ktrl/orig</x:v>
       </x:c>
-      <x:c r="L33" t="str"/>
+      <x:c r="L33"/>
       <x:c r="M33" t="str">
         <x:v>По телефону и в сообщениях</x:v>
       </x:c>
-      <x:c r="N33" t="str"/>
-      <x:c r="O33" t="str"/>
-      <x:c r="P33" t="str"/>
+      <x:c r="N33"/>
+      <x:c r="O33"/>
+      <x:c r="P33"/>
       <x:c r="Q33" t="str">
         <x:v>Ремонт и строительство</x:v>
       </x:c>
       <x:c r="R33" t="str">
         <x:v>г. Волгоград, ул. 25-летия Октября, д. 1, стр. 3</x:v>
       </x:c>
-      <x:c r="S33" t="str"/>
-      <x:c r="T33" t="str"/>
-      <x:c r="U33" t="str"/>
+      <x:c r="S33"/>
+      <x:c r="T33"/>
+      <x:c r="U33"/>
       <x:c r="V33" t="str">
         <x:v>Поштучно</x:v>
       </x:c>
@@ -6869,9 +6815,9 @@
       <x:c r="Z33" t="str">
         <x:v>Штуку</x:v>
       </x:c>
-      <x:c r="AA33" t="str"/>
-      <x:c r="AB33" t="str"/>
-      <x:c r="AC33" t="str"/>
+      <x:c r="AA33"/>
+      <x:c r="AB33"/>
+      <x:c r="AC33"/>
       <x:c r="AD33" t="n">
         <x:v>7</x:v>
       </x:c>
@@ -6884,26 +6830,24 @@
       <x:c r="AG33" t="n">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="AH33" t="str"/>
+      <x:c r="AH33"/>
       <x:c r="AI33" t="str">
         <x:v>3921120000</x:v>
       </x:c>
-      <x:c r="AJ33" t="str">
-        <x:v>22.21.42.110</x:v>
-      </x:c>
-      <x:c r="AK33" t="str"/>
-      <x:c r="AL33" t="str"/>
-      <x:c r="AM33" t="str"/>
-      <x:c r="AN33" t="str"/>
-      <x:c r="AO33" t="str"/>
-      <x:c r="AP33" t="str"/>
-      <x:c r="AQ33" t="str"/>
-      <x:c r="AR33" t="str"/>
-      <x:c r="AS33" t="str"/>
-      <x:c r="AT33" t="str"/>
-      <x:c r="AU33" t="str"/>
-      <x:c r="AV33" t="str"/>
-      <x:c r="AW33" t="str"/>
+      <x:c r="AJ33" t="str"/>
+      <x:c r="AK33"/>
+      <x:c r="AL33"/>
+      <x:c r="AM33"/>
+      <x:c r="AN33"/>
+      <x:c r="AO33"/>
+      <x:c r="AP33"/>
+      <x:c r="AQ33"/>
+      <x:c r="AR33"/>
+      <x:c r="AS33"/>
+      <x:c r="AT33"/>
+      <x:c r="AU33"/>
+      <x:c r="AV33"/>
+      <x:c r="AW33"/>
       <x:c r="AX33" t="str">
         <x:v>4900</x:v>
       </x:c>
@@ -6922,7 +6866,7 @@
       <x:c r="BC33" t="str">
         <x:v>Отделка</x:v>
       </x:c>
-      <x:c r="BD33" t="str"/>
+      <x:c r="BD33"/>
       <x:c r="BE33" t="str">
         <x:v>Стеновые панели, рейки и элементы декора</x:v>
       </x:c>
@@ -6944,28 +6888,28 @@
       <x:c r="BK33" t="str">
         <x:v>1140</x:v>
       </x:c>
-      <x:c r="BL33" t="str"/>
+      <x:c r="BL33"/>
       <x:c r="BM33" t="str">
         <x:v>Нет</x:v>
       </x:c>
-      <x:c r="BN33" t="str"/>
-      <x:c r="BO33" t="str"/>
-      <x:c r="BP33" t="str"/>
-      <x:c r="BQ33" t="str"/>
-      <x:c r="BR33" t="str"/>
-      <x:c r="BS33" t="str"/>
-      <x:c r="BT33" t="str"/>
-      <x:c r="BU33" t="str"/>
+      <x:c r="BN33"/>
+      <x:c r="BO33"/>
+      <x:c r="BP33"/>
+      <x:c r="BQ33"/>
+      <x:c r="BR33"/>
+      <x:c r="BS33"/>
+      <x:c r="BT33"/>
+      <x:c r="BU33"/>
     </x:row>
     <x:row r="34">
       <x:c r="A34" t="str">
         <x:v>adamar-vlg-FONDAMENTO BLUE</x:v>
       </x:c>
-      <x:c r="B34" t="str"/>
-      <x:c r="C34" t="str"/>
-      <x:c r="D34" t="str"/>
-      <x:c r="E34" t="str"/>
-      <x:c r="F34" t="str"/>
+      <x:c r="B34"/>
+      <x:c r="C34"/>
+      <x:c r="D34"/>
+      <x:c r="E34"/>
+      <x:c r="F34"/>
       <x:c r="G34" t="str">
         <x:v>Adamar Group</x:v>
       </x:c>
@@ -6985,22 +6929,22 @@
       <x:c r="K34" t="str">
         <x:v>https://avatars.mds.yandex.net/get-yastore/20760651/znswqj9q9pd95zkm6477mrhc86wgbxkf/orig | https://avatars.mds.yandex.net/get-yastore/20760651/k9tgsvwpl7fdnkgqnzmfscrrvfxrff2j/orig | https://avatars.mds.yandex.net/get-yastore/21104660/w28jjl9k4mbx5rz2hf4j9cf7rttmjpwh/orig | https://avatars.mds.yandex.net/get-yastore/20760651/gmb7ddls4m2mwzk8blt4rgchgfn9ntp2/orig</x:v>
       </x:c>
-      <x:c r="L34" t="str"/>
+      <x:c r="L34"/>
       <x:c r="M34" t="str">
         <x:v>По телефону и в сообщениях</x:v>
       </x:c>
-      <x:c r="N34" t="str"/>
-      <x:c r="O34" t="str"/>
-      <x:c r="P34" t="str"/>
+      <x:c r="N34"/>
+      <x:c r="O34"/>
+      <x:c r="P34"/>
       <x:c r="Q34" t="str">
         <x:v>Ремонт и строительство</x:v>
       </x:c>
       <x:c r="R34" t="str">
         <x:v>г. Волгоград, ул. 25-летия Октября, д. 1, стр. 3</x:v>
       </x:c>
-      <x:c r="S34" t="str"/>
-      <x:c r="T34" t="str"/>
-      <x:c r="U34" t="str"/>
+      <x:c r="S34"/>
+      <x:c r="T34"/>
+      <x:c r="U34"/>
       <x:c r="V34" t="str">
         <x:v>Поштучно</x:v>
       </x:c>
@@ -7016,9 +6960,9 @@
       <x:c r="Z34" t="str">
         <x:v>Штуку</x:v>
       </x:c>
-      <x:c r="AA34" t="str"/>
-      <x:c r="AB34" t="str"/>
-      <x:c r="AC34" t="str"/>
+      <x:c r="AA34"/>
+      <x:c r="AB34"/>
+      <x:c r="AC34"/>
       <x:c r="AD34" t="n">
         <x:v>7</x:v>
       </x:c>
@@ -7031,26 +6975,24 @@
       <x:c r="AG34" t="n">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="AH34" t="str"/>
+      <x:c r="AH34"/>
       <x:c r="AI34" t="str">
         <x:v>3921120000</x:v>
       </x:c>
-      <x:c r="AJ34" t="str">
-        <x:v>22.21.42.110</x:v>
-      </x:c>
-      <x:c r="AK34" t="str"/>
-      <x:c r="AL34" t="str"/>
-      <x:c r="AM34" t="str"/>
-      <x:c r="AN34" t="str"/>
-      <x:c r="AO34" t="str"/>
-      <x:c r="AP34" t="str"/>
-      <x:c r="AQ34" t="str"/>
-      <x:c r="AR34" t="str"/>
-      <x:c r="AS34" t="str"/>
-      <x:c r="AT34" t="str"/>
-      <x:c r="AU34" t="str"/>
-      <x:c r="AV34" t="str"/>
-      <x:c r="AW34" t="str"/>
+      <x:c r="AJ34" t="str"/>
+      <x:c r="AK34"/>
+      <x:c r="AL34"/>
+      <x:c r="AM34"/>
+      <x:c r="AN34"/>
+      <x:c r="AO34"/>
+      <x:c r="AP34"/>
+      <x:c r="AQ34"/>
+      <x:c r="AR34"/>
+      <x:c r="AS34"/>
+      <x:c r="AT34"/>
+      <x:c r="AU34"/>
+      <x:c r="AV34"/>
+      <x:c r="AW34"/>
       <x:c r="AX34" t="str">
         <x:v>4900</x:v>
       </x:c>
@@ -7069,7 +7011,7 @@
       <x:c r="BC34" t="str">
         <x:v>Отделка</x:v>
       </x:c>
-      <x:c r="BD34" t="str"/>
+      <x:c r="BD34"/>
       <x:c r="BE34" t="str">
         <x:v>Стеновые панели, рейки и элементы декора</x:v>
       </x:c>
@@ -7091,28 +7033,28 @@
       <x:c r="BK34" t="str">
         <x:v>1140</x:v>
       </x:c>
-      <x:c r="BL34" t="str"/>
+      <x:c r="BL34"/>
       <x:c r="BM34" t="str">
         <x:v>Нет</x:v>
       </x:c>
-      <x:c r="BN34" t="str"/>
-      <x:c r="BO34" t="str"/>
-      <x:c r="BP34" t="str"/>
-      <x:c r="BQ34" t="str"/>
-      <x:c r="BR34" t="str"/>
-      <x:c r="BS34" t="str"/>
-      <x:c r="BT34" t="str"/>
-      <x:c r="BU34" t="str"/>
+      <x:c r="BN34"/>
+      <x:c r="BO34"/>
+      <x:c r="BP34"/>
+      <x:c r="BQ34"/>
+      <x:c r="BR34"/>
+      <x:c r="BS34"/>
+      <x:c r="BT34"/>
+      <x:c r="BU34"/>
     </x:row>
     <x:row r="35">
       <x:c r="A35" t="str">
         <x:v>adamar-vlg-Glossy_MARBLE_FLORENCE</x:v>
       </x:c>
-      <x:c r="B35" t="str"/>
-      <x:c r="C35" t="str"/>
-      <x:c r="D35" t="str"/>
-      <x:c r="E35" t="str"/>
-      <x:c r="F35" t="str"/>
+      <x:c r="B35"/>
+      <x:c r="C35"/>
+      <x:c r="D35"/>
+      <x:c r="E35"/>
+      <x:c r="F35"/>
       <x:c r="G35" t="str">
         <x:v>Adamar Group</x:v>
       </x:c>
@@ -7132,22 +7074,22 @@
       <x:c r="K35" t="str">
         <x:v>https://avatars.mds.yandex.net/get-yastore/20760651/bjcwtcqtz6kcrwlg45pc2zv4sc4tmzr4/orig | https://avatars.mds.yandex.net/get-yastore/21069123/gt8fs88vhfp7c4p897jqvfbp8vjfdgq8/orig | https://avatars.mds.yandex.net/get-yastore/21069123/kkd64w7s64tbxd9f4jmbdtl42krkxqr6/orig | https://avatars.mds.yandex.net/get-yastore/16104656/8rjb7dc2wxpbw6fpcz9b9n8g6lcs2q9v/orig</x:v>
       </x:c>
-      <x:c r="L35" t="str"/>
+      <x:c r="L35"/>
       <x:c r="M35" t="str">
         <x:v>По телефону и в сообщениях</x:v>
       </x:c>
-      <x:c r="N35" t="str"/>
-      <x:c r="O35" t="str"/>
-      <x:c r="P35" t="str"/>
+      <x:c r="N35"/>
+      <x:c r="O35"/>
+      <x:c r="P35"/>
       <x:c r="Q35" t="str">
         <x:v>Ремонт и строительство</x:v>
       </x:c>
       <x:c r="R35" t="str">
         <x:v>г. Волгоград, ул. 25-летия Октября, д. 1, стр. 3</x:v>
       </x:c>
-      <x:c r="S35" t="str"/>
-      <x:c r="T35" t="str"/>
-      <x:c r="U35" t="str"/>
+      <x:c r="S35"/>
+      <x:c r="T35"/>
+      <x:c r="U35"/>
       <x:c r="V35" t="str">
         <x:v>Поштучно</x:v>
       </x:c>
@@ -7163,9 +7105,9 @@
       <x:c r="Z35" t="str">
         <x:v>Штуку</x:v>
       </x:c>
-      <x:c r="AA35" t="str"/>
-      <x:c r="AB35" t="str"/>
-      <x:c r="AC35" t="str"/>
+      <x:c r="AA35"/>
+      <x:c r="AB35"/>
+      <x:c r="AC35"/>
       <x:c r="AD35" t="n">
         <x:v>7</x:v>
       </x:c>
@@ -7178,26 +7120,24 @@
       <x:c r="AG35" t="n">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="AH35" t="str"/>
+      <x:c r="AH35"/>
       <x:c r="AI35" t="str">
         <x:v>3921120000</x:v>
       </x:c>
-      <x:c r="AJ35" t="str">
-        <x:v>22.21.42.110</x:v>
-      </x:c>
-      <x:c r="AK35" t="str"/>
-      <x:c r="AL35" t="str"/>
-      <x:c r="AM35" t="str"/>
-      <x:c r="AN35" t="str"/>
-      <x:c r="AO35" t="str"/>
-      <x:c r="AP35" t="str"/>
-      <x:c r="AQ35" t="str"/>
-      <x:c r="AR35" t="str"/>
-      <x:c r="AS35" t="str"/>
-      <x:c r="AT35" t="str"/>
-      <x:c r="AU35" t="str"/>
-      <x:c r="AV35" t="str"/>
-      <x:c r="AW35" t="str"/>
+      <x:c r="AJ35" t="str"/>
+      <x:c r="AK35"/>
+      <x:c r="AL35"/>
+      <x:c r="AM35"/>
+      <x:c r="AN35"/>
+      <x:c r="AO35"/>
+      <x:c r="AP35"/>
+      <x:c r="AQ35"/>
+      <x:c r="AR35"/>
+      <x:c r="AS35"/>
+      <x:c r="AT35"/>
+      <x:c r="AU35"/>
+      <x:c r="AV35"/>
+      <x:c r="AW35"/>
       <x:c r="AX35" t="str">
         <x:v>4900</x:v>
       </x:c>
@@ -7216,7 +7156,7 @@
       <x:c r="BC35" t="str">
         <x:v>Отделка</x:v>
       </x:c>
-      <x:c r="BD35" t="str"/>
+      <x:c r="BD35"/>
       <x:c r="BE35" t="str">
         <x:v>Стеновые панели, рейки и элементы декора</x:v>
       </x:c>
@@ -7238,28 +7178,28 @@
       <x:c r="BK35" t="str">
         <x:v>1140</x:v>
       </x:c>
-      <x:c r="BL35" t="str"/>
+      <x:c r="BL35"/>
       <x:c r="BM35" t="str">
         <x:v>Нет</x:v>
       </x:c>
-      <x:c r="BN35" t="str"/>
-      <x:c r="BO35" t="str"/>
-      <x:c r="BP35" t="str"/>
-      <x:c r="BQ35" t="str"/>
-      <x:c r="BR35" t="str"/>
-      <x:c r="BS35" t="str"/>
-      <x:c r="BT35" t="str"/>
-      <x:c r="BU35" t="str"/>
+      <x:c r="BN35"/>
+      <x:c r="BO35"/>
+      <x:c r="BP35"/>
+      <x:c r="BQ35"/>
+      <x:c r="BR35"/>
+      <x:c r="BS35"/>
+      <x:c r="BT35"/>
+      <x:c r="BU35"/>
     </x:row>
     <x:row r="36">
       <x:c r="A36" t="str">
         <x:v>adamar-vlg-SKY</x:v>
       </x:c>
-      <x:c r="B36" t="str"/>
-      <x:c r="C36" t="str"/>
-      <x:c r="D36" t="str"/>
-      <x:c r="E36" t="str"/>
-      <x:c r="F36" t="str"/>
+      <x:c r="B36"/>
+      <x:c r="C36"/>
+      <x:c r="D36"/>
+      <x:c r="E36"/>
+      <x:c r="F36"/>
       <x:c r="G36" t="str">
         <x:v>Adamar Group</x:v>
       </x:c>
@@ -7279,22 +7219,22 @@
       <x:c r="K36" t="str">
         <x:v>https://avatars.mds.yandex.net/get-yastore/20760651/v6dqzkbdpvjbhxhnwnxzdvnddd9w68pf/orig | https://avatars.mds.yandex.net/get-yastore/21104660/9cq7lxgsc2dgcmrzkxrbs4dwcbkhfv6s/orig | https://avatars.mds.yandex.net/get-yastore/21104660/gjvvs4vfb7b54s9trbvmxbt8468l2fft/orig | https://avatars.mds.yandex.net/get-yastore/21104660/gcbxfclzcc76zrlhdk68qrjqd8qz9772/orig</x:v>
       </x:c>
-      <x:c r="L36" t="str"/>
+      <x:c r="L36"/>
       <x:c r="M36" t="str">
         <x:v>По телефону и в сообщениях</x:v>
       </x:c>
-      <x:c r="N36" t="str"/>
-      <x:c r="O36" t="str"/>
-      <x:c r="P36" t="str"/>
+      <x:c r="N36"/>
+      <x:c r="O36"/>
+      <x:c r="P36"/>
       <x:c r="Q36" t="str">
         <x:v>Ремонт и строительство</x:v>
       </x:c>
       <x:c r="R36" t="str">
         <x:v>г. Волгоград, ул. 25-летия Октября, д. 1, стр. 3</x:v>
       </x:c>
-      <x:c r="S36" t="str"/>
-      <x:c r="T36" t="str"/>
-      <x:c r="U36" t="str"/>
+      <x:c r="S36"/>
+      <x:c r="T36"/>
+      <x:c r="U36"/>
       <x:c r="V36" t="str">
         <x:v>Поштучно</x:v>
       </x:c>
@@ -7310,9 +7250,9 @@
       <x:c r="Z36" t="str">
         <x:v>Штуку</x:v>
       </x:c>
-      <x:c r="AA36" t="str"/>
-      <x:c r="AB36" t="str"/>
-      <x:c r="AC36" t="str"/>
+      <x:c r="AA36"/>
+      <x:c r="AB36"/>
+      <x:c r="AC36"/>
       <x:c r="AD36" t="n">
         <x:v>7</x:v>
       </x:c>
@@ -7325,26 +7265,24 @@
       <x:c r="AG36" t="n">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="AH36" t="str"/>
+      <x:c r="AH36"/>
       <x:c r="AI36" t="str">
         <x:v>3921120000</x:v>
       </x:c>
-      <x:c r="AJ36" t="str">
-        <x:v>22.21.42.110</x:v>
-      </x:c>
-      <x:c r="AK36" t="str"/>
-      <x:c r="AL36" t="str"/>
-      <x:c r="AM36" t="str"/>
-      <x:c r="AN36" t="str"/>
-      <x:c r="AO36" t="str"/>
-      <x:c r="AP36" t="str"/>
-      <x:c r="AQ36" t="str"/>
-      <x:c r="AR36" t="str"/>
-      <x:c r="AS36" t="str"/>
-      <x:c r="AT36" t="str"/>
-      <x:c r="AU36" t="str"/>
-      <x:c r="AV36" t="str"/>
-      <x:c r="AW36" t="str"/>
+      <x:c r="AJ36" t="str"/>
+      <x:c r="AK36"/>
+      <x:c r="AL36"/>
+      <x:c r="AM36"/>
+      <x:c r="AN36"/>
+      <x:c r="AO36"/>
+      <x:c r="AP36"/>
+      <x:c r="AQ36"/>
+      <x:c r="AR36"/>
+      <x:c r="AS36"/>
+      <x:c r="AT36"/>
+      <x:c r="AU36"/>
+      <x:c r="AV36"/>
+      <x:c r="AW36"/>
       <x:c r="AX36" t="str">
         <x:v>4900</x:v>
       </x:c>
@@ -7363,7 +7301,7 @@
       <x:c r="BC36" t="str">
         <x:v>Отделка</x:v>
       </x:c>
-      <x:c r="BD36" t="str"/>
+      <x:c r="BD36"/>
       <x:c r="BE36" t="str">
         <x:v>Стеновые панели, рейки и элементы декора</x:v>
       </x:c>
@@ -7385,28 +7323,28 @@
       <x:c r="BK36" t="str">
         <x:v>1140</x:v>
       </x:c>
-      <x:c r="BL36" t="str"/>
+      <x:c r="BL36"/>
       <x:c r="BM36" t="str">
         <x:v>Нет</x:v>
       </x:c>
-      <x:c r="BN36" t="str"/>
-      <x:c r="BO36" t="str"/>
-      <x:c r="BP36" t="str"/>
-      <x:c r="BQ36" t="str"/>
-      <x:c r="BR36" t="str"/>
-      <x:c r="BS36" t="str"/>
-      <x:c r="BT36" t="str"/>
-      <x:c r="BU36" t="str"/>
+      <x:c r="BN36"/>
+      <x:c r="BO36"/>
+      <x:c r="BP36"/>
+      <x:c r="BQ36"/>
+      <x:c r="BR36"/>
+      <x:c r="BS36"/>
+      <x:c r="BT36"/>
+      <x:c r="BU36"/>
     </x:row>
     <x:row r="37">
       <x:c r="A37" t="str">
         <x:v>adamar-vlg-SCRIBBLE GRAY</x:v>
       </x:c>
-      <x:c r="B37" t="str"/>
-      <x:c r="C37" t="str"/>
-      <x:c r="D37" t="str"/>
-      <x:c r="E37" t="str"/>
-      <x:c r="F37" t="str"/>
+      <x:c r="B37"/>
+      <x:c r="C37"/>
+      <x:c r="D37"/>
+      <x:c r="E37"/>
+      <x:c r="F37"/>
       <x:c r="G37" t="str">
         <x:v>Adamar Group</x:v>
       </x:c>
@@ -7426,22 +7364,22 @@
       <x:c r="K37" t="str">
         <x:v>https://avatars.mds.yandex.net/get-yastore/21055393/9kkt59pv4mdn66w5bq7ts4s5s2zwvdcl/orig | https://avatars.mds.yandex.net/get-yastore/21055393/v89g7vkm4fpkcph8q5576xhg95kcchld/orig | https://avatars.mds.yandex.net/get-yastore/20918687/jfwnzj7czzdm72hsftfvfk5pzpwnjj2b/orig | https://avatars.mds.yandex.net/get-yastore/21055393/bk2tdvhntmz7zl25g9pzsxx2clkzxmwx/orig</x:v>
       </x:c>
-      <x:c r="L37" t="str"/>
+      <x:c r="L37"/>
       <x:c r="M37" t="str">
         <x:v>По телефону и в сообщениях</x:v>
       </x:c>
-      <x:c r="N37" t="str"/>
-      <x:c r="O37" t="str"/>
-      <x:c r="P37" t="str"/>
+      <x:c r="N37"/>
+      <x:c r="O37"/>
+      <x:c r="P37"/>
       <x:c r="Q37" t="str">
         <x:v>Ремонт и строительство</x:v>
       </x:c>
       <x:c r="R37" t="str">
         <x:v>г. Волгоград, ул. 25-летия Октября, д. 1, стр. 3</x:v>
       </x:c>
-      <x:c r="S37" t="str"/>
-      <x:c r="T37" t="str"/>
-      <x:c r="U37" t="str"/>
+      <x:c r="S37"/>
+      <x:c r="T37"/>
+      <x:c r="U37"/>
       <x:c r="V37" t="str">
         <x:v>Поштучно</x:v>
       </x:c>
@@ -7457,9 +7395,9 @@
       <x:c r="Z37" t="str">
         <x:v>Штуку</x:v>
       </x:c>
-      <x:c r="AA37" t="str"/>
-      <x:c r="AB37" t="str"/>
-      <x:c r="AC37" t="str"/>
+      <x:c r="AA37"/>
+      <x:c r="AB37"/>
+      <x:c r="AC37"/>
       <x:c r="AD37" t="n">
         <x:v>7</x:v>
       </x:c>
@@ -7472,26 +7410,24 @@
       <x:c r="AG37" t="n">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="AH37" t="str"/>
+      <x:c r="AH37"/>
       <x:c r="AI37" t="str">
         <x:v>3921120000</x:v>
       </x:c>
-      <x:c r="AJ37" t="str">
-        <x:v>22.21.42.110</x:v>
-      </x:c>
-      <x:c r="AK37" t="str"/>
-      <x:c r="AL37" t="str"/>
-      <x:c r="AM37" t="str"/>
-      <x:c r="AN37" t="str"/>
-      <x:c r="AO37" t="str"/>
-      <x:c r="AP37" t="str"/>
-      <x:c r="AQ37" t="str"/>
-      <x:c r="AR37" t="str"/>
-      <x:c r="AS37" t="str"/>
-      <x:c r="AT37" t="str"/>
-      <x:c r="AU37" t="str"/>
-      <x:c r="AV37" t="str"/>
-      <x:c r="AW37" t="str"/>
+      <x:c r="AJ37" t="str"/>
+      <x:c r="AK37"/>
+      <x:c r="AL37"/>
+      <x:c r="AM37"/>
+      <x:c r="AN37"/>
+      <x:c r="AO37"/>
+      <x:c r="AP37"/>
+      <x:c r="AQ37"/>
+      <x:c r="AR37"/>
+      <x:c r="AS37"/>
+      <x:c r="AT37"/>
+      <x:c r="AU37"/>
+      <x:c r="AV37"/>
+      <x:c r="AW37"/>
       <x:c r="AX37" t="str">
         <x:v>4900</x:v>
       </x:c>
@@ -7510,7 +7446,7 @@
       <x:c r="BC37" t="str">
         <x:v>Отделка</x:v>
       </x:c>
-      <x:c r="BD37" t="str"/>
+      <x:c r="BD37"/>
       <x:c r="BE37" t="str">
         <x:v>Стеновые панели, рейки и элементы декора</x:v>
       </x:c>
@@ -7532,28 +7468,28 @@
       <x:c r="BK37" t="str">
         <x:v>1140</x:v>
       </x:c>
-      <x:c r="BL37" t="str"/>
+      <x:c r="BL37"/>
       <x:c r="BM37" t="str">
         <x:v>Нет</x:v>
       </x:c>
-      <x:c r="BN37" t="str"/>
-      <x:c r="BO37" t="str"/>
-      <x:c r="BP37" t="str"/>
-      <x:c r="BQ37" t="str"/>
-      <x:c r="BR37" t="str"/>
-      <x:c r="BS37" t="str"/>
-      <x:c r="BT37" t="str"/>
-      <x:c r="BU37" t="str"/>
+      <x:c r="BN37"/>
+      <x:c r="BO37"/>
+      <x:c r="BP37"/>
+      <x:c r="BQ37"/>
+      <x:c r="BR37"/>
+      <x:c r="BS37"/>
+      <x:c r="BT37"/>
+      <x:c r="BU37"/>
     </x:row>
     <x:row r="38">
       <x:c r="A38" t="str">
         <x:v>adamar-vlg-OCEAN_1</x:v>
       </x:c>
-      <x:c r="B38" t="str"/>
-      <x:c r="C38" t="str"/>
-      <x:c r="D38" t="str"/>
-      <x:c r="E38" t="str"/>
-      <x:c r="F38" t="str"/>
+      <x:c r="B38"/>
+      <x:c r="C38"/>
+      <x:c r="D38"/>
+      <x:c r="E38"/>
+      <x:c r="F38"/>
       <x:c r="G38" t="str">
         <x:v>Adamar Group</x:v>
       </x:c>
@@ -7573,22 +7509,22 @@
       <x:c r="K38" t="str">
         <x:v>https://avatars.mds.yandex.net/get-yastore/21012869/qqd2bp2fsxjqbqnm75kwbsq9mlkqjxtp/orig | https://avatars.mds.yandex.net/get-yastore/20274467/btsmj4xjltbnxvml826r8wxbrhhlzrxn/orig | https://avatars.mds.yandex.net/get-yastore/20760651/czxdrm24dr9plkqp6h8k9wt9fjjx2gn8/orig | https://avatars.mds.yandex.net/get-yastore/20274467/zkkls5t6wlljhblwjvwpr8tnbwwz2hxk/orig</x:v>
       </x:c>
-      <x:c r="L38" t="str"/>
+      <x:c r="L38"/>
       <x:c r="M38" t="str">
         <x:v>По телефону и в сообщениях</x:v>
       </x:c>
-      <x:c r="N38" t="str"/>
-      <x:c r="O38" t="str"/>
-      <x:c r="P38" t="str"/>
+      <x:c r="N38"/>
+      <x:c r="O38"/>
+      <x:c r="P38"/>
       <x:c r="Q38" t="str">
         <x:v>Ремонт и строительство</x:v>
       </x:c>
       <x:c r="R38" t="str">
         <x:v>г. Волгоград, ул. 25-летия Октября, д. 1, стр. 3</x:v>
       </x:c>
-      <x:c r="S38" t="str"/>
-      <x:c r="T38" t="str"/>
-      <x:c r="U38" t="str"/>
+      <x:c r="S38"/>
+      <x:c r="T38"/>
+      <x:c r="U38"/>
       <x:c r="V38" t="str">
         <x:v>Поштучно</x:v>
       </x:c>
@@ -7604,9 +7540,9 @@
       <x:c r="Z38" t="str">
         <x:v>Штуку</x:v>
       </x:c>
-      <x:c r="AA38" t="str"/>
-      <x:c r="AB38" t="str"/>
-      <x:c r="AC38" t="str"/>
+      <x:c r="AA38"/>
+      <x:c r="AB38"/>
+      <x:c r="AC38"/>
       <x:c r="AD38" t="n">
         <x:v>7</x:v>
       </x:c>
@@ -7619,26 +7555,24 @@
       <x:c r="AG38" t="n">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="AH38" t="str"/>
+      <x:c r="AH38"/>
       <x:c r="AI38" t="str">
         <x:v>3921120000</x:v>
       </x:c>
-      <x:c r="AJ38" t="str">
-        <x:v>22.21.42.110</x:v>
-      </x:c>
-      <x:c r="AK38" t="str"/>
-      <x:c r="AL38" t="str"/>
-      <x:c r="AM38" t="str"/>
-      <x:c r="AN38" t="str"/>
-      <x:c r="AO38" t="str"/>
-      <x:c r="AP38" t="str"/>
-      <x:c r="AQ38" t="str"/>
-      <x:c r="AR38" t="str"/>
-      <x:c r="AS38" t="str"/>
-      <x:c r="AT38" t="str"/>
-      <x:c r="AU38" t="str"/>
-      <x:c r="AV38" t="str"/>
-      <x:c r="AW38" t="str"/>
+      <x:c r="AJ38" t="str"/>
+      <x:c r="AK38"/>
+      <x:c r="AL38"/>
+      <x:c r="AM38"/>
+      <x:c r="AN38"/>
+      <x:c r="AO38"/>
+      <x:c r="AP38"/>
+      <x:c r="AQ38"/>
+      <x:c r="AR38"/>
+      <x:c r="AS38"/>
+      <x:c r="AT38"/>
+      <x:c r="AU38"/>
+      <x:c r="AV38"/>
+      <x:c r="AW38"/>
       <x:c r="AX38" t="str">
         <x:v>4900</x:v>
       </x:c>
@@ -7657,7 +7591,7 @@
       <x:c r="BC38" t="str">
         <x:v>Отделка</x:v>
       </x:c>
-      <x:c r="BD38" t="str"/>
+      <x:c r="BD38"/>
       <x:c r="BE38" t="str">
         <x:v>Стеновые панели, рейки и элементы декора</x:v>
       </x:c>
@@ -7679,28 +7613,28 @@
       <x:c r="BK38" t="str">
         <x:v>1140</x:v>
       </x:c>
-      <x:c r="BL38" t="str"/>
+      <x:c r="BL38"/>
       <x:c r="BM38" t="str">
         <x:v>Нет</x:v>
       </x:c>
-      <x:c r="BN38" t="str"/>
-      <x:c r="BO38" t="str"/>
-      <x:c r="BP38" t="str"/>
-      <x:c r="BQ38" t="str"/>
-      <x:c r="BR38" t="str"/>
-      <x:c r="BS38" t="str"/>
-      <x:c r="BT38" t="str"/>
-      <x:c r="BU38" t="str"/>
+      <x:c r="BN38"/>
+      <x:c r="BO38"/>
+      <x:c r="BP38"/>
+      <x:c r="BQ38"/>
+      <x:c r="BR38"/>
+      <x:c r="BS38"/>
+      <x:c r="BT38"/>
+      <x:c r="BU38"/>
     </x:row>
     <x:row r="39">
       <x:c r="A39" t="str">
         <x:v>adamar-vlg-Gerda_1</x:v>
       </x:c>
-      <x:c r="B39" t="str"/>
-      <x:c r="C39" t="str"/>
-      <x:c r="D39" t="str"/>
-      <x:c r="E39" t="str"/>
-      <x:c r="F39" t="str"/>
+      <x:c r="B39"/>
+      <x:c r="C39"/>
+      <x:c r="D39"/>
+      <x:c r="E39"/>
+      <x:c r="F39"/>
       <x:c r="G39" t="str">
         <x:v>Adamar Group</x:v>
       </x:c>
@@ -7720,22 +7654,22 @@
       <x:c r="K39" t="str">
         <x:v>https://avatars.mds.yandex.net/get-yastore/20274467/vgf9tn8bz9zf6bvf79jwttbd8lgvrl87/orig | https://avatars.mds.yandex.net/get-yastore/20274467/86nfrzr9gmk4ct8c62pbk282lclqmrpg/orig | https://avatars.mds.yandex.net/get-yastore/20274467/grkksnr7rlmv9445rwt5prw2ht2hbc8p/orig | https://avatars.mds.yandex.net/get-yastore/20274467/lp2jlgpz7wv6nds9crs9pcslw4rgrwfv/orig</x:v>
       </x:c>
-      <x:c r="L39" t="str"/>
+      <x:c r="L39"/>
       <x:c r="M39" t="str">
         <x:v>По телефону и в сообщениях</x:v>
       </x:c>
-      <x:c r="N39" t="str"/>
-      <x:c r="O39" t="str"/>
-      <x:c r="P39" t="str"/>
+      <x:c r="N39"/>
+      <x:c r="O39"/>
+      <x:c r="P39"/>
       <x:c r="Q39" t="str">
         <x:v>Ремонт и строительство</x:v>
       </x:c>
       <x:c r="R39" t="str">
         <x:v>г. Волгоград, ул. 25-летия Октября, д. 1, стр. 3</x:v>
       </x:c>
-      <x:c r="S39" t="str"/>
-      <x:c r="T39" t="str"/>
-      <x:c r="U39" t="str"/>
+      <x:c r="S39"/>
+      <x:c r="T39"/>
+      <x:c r="U39"/>
       <x:c r="V39" t="str">
         <x:v>Поштучно</x:v>
       </x:c>
@@ -7751,9 +7685,9 @@
       <x:c r="Z39" t="str">
         <x:v>Штуку</x:v>
       </x:c>
-      <x:c r="AA39" t="str"/>
-      <x:c r="AB39" t="str"/>
-      <x:c r="AC39" t="str"/>
+      <x:c r="AA39"/>
+      <x:c r="AB39"/>
+      <x:c r="AC39"/>
       <x:c r="AD39" t="n">
         <x:v>7</x:v>
       </x:c>
@@ -7766,26 +7700,24 @@
       <x:c r="AG39" t="n">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="AH39" t="str"/>
+      <x:c r="AH39"/>
       <x:c r="AI39" t="str">
         <x:v>3921120000</x:v>
       </x:c>
-      <x:c r="AJ39" t="str">
-        <x:v>22.21.42.110</x:v>
-      </x:c>
-      <x:c r="AK39" t="str"/>
-      <x:c r="AL39" t="str"/>
-      <x:c r="AM39" t="str"/>
-      <x:c r="AN39" t="str"/>
-      <x:c r="AO39" t="str"/>
-      <x:c r="AP39" t="str"/>
-      <x:c r="AQ39" t="str"/>
-      <x:c r="AR39" t="str"/>
-      <x:c r="AS39" t="str"/>
-      <x:c r="AT39" t="str"/>
-      <x:c r="AU39" t="str"/>
-      <x:c r="AV39" t="str"/>
-      <x:c r="AW39" t="str"/>
+      <x:c r="AJ39" t="str"/>
+      <x:c r="AK39"/>
+      <x:c r="AL39"/>
+      <x:c r="AM39"/>
+      <x:c r="AN39"/>
+      <x:c r="AO39"/>
+      <x:c r="AP39"/>
+      <x:c r="AQ39"/>
+      <x:c r="AR39"/>
+      <x:c r="AS39"/>
+      <x:c r="AT39"/>
+      <x:c r="AU39"/>
+      <x:c r="AV39"/>
+      <x:c r="AW39"/>
       <x:c r="AX39" t="str">
         <x:v>4900</x:v>
       </x:c>
@@ -7804,7 +7736,7 @@
       <x:c r="BC39" t="str">
         <x:v>Отделка</x:v>
       </x:c>
-      <x:c r="BD39" t="str"/>
+      <x:c r="BD39"/>
       <x:c r="BE39" t="str">
         <x:v>Стеновые панели, рейки и элементы декора</x:v>
       </x:c>
@@ -7826,28 +7758,28 @@
       <x:c r="BK39" t="str">
         <x:v>1140</x:v>
       </x:c>
-      <x:c r="BL39" t="str"/>
+      <x:c r="BL39"/>
       <x:c r="BM39" t="str">
         <x:v>Нет</x:v>
       </x:c>
-      <x:c r="BN39" t="str"/>
-      <x:c r="BO39" t="str"/>
-      <x:c r="BP39" t="str"/>
-      <x:c r="BQ39" t="str"/>
-      <x:c r="BR39" t="str"/>
-      <x:c r="BS39" t="str"/>
-      <x:c r="BT39" t="str"/>
-      <x:c r="BU39" t="str"/>
+      <x:c r="BN39"/>
+      <x:c r="BO39"/>
+      <x:c r="BP39"/>
+      <x:c r="BQ39"/>
+      <x:c r="BR39"/>
+      <x:c r="BS39"/>
+      <x:c r="BT39"/>
+      <x:c r="BU39"/>
     </x:row>
     <x:row r="40">
       <x:c r="A40" t="str">
         <x:v>adamar-vlg-Beton Blurry_1</x:v>
       </x:c>
-      <x:c r="B40" t="str"/>
-      <x:c r="C40" t="str"/>
-      <x:c r="D40" t="str"/>
-      <x:c r="E40" t="str"/>
-      <x:c r="F40" t="str"/>
+      <x:c r="B40"/>
+      <x:c r="C40"/>
+      <x:c r="D40"/>
+      <x:c r="E40"/>
+      <x:c r="F40"/>
       <x:c r="G40" t="str">
         <x:v>Adamar Group</x:v>
       </x:c>
@@ -7867,22 +7799,22 @@
       <x:c r="K40" t="str">
         <x:v>https://avatars.mds.yandex.net/get-yastore/20918687/65tfpzcmtfgh2nw54b54phkjth8pfmdt/orig | https://avatars.mds.yandex.net/get-yastore/21055393/9j56s4dxrz9lp5xtqpm2wfjspjk54nvd/orig | https://avatars.mds.yandex.net/get-yastore/20918687/pfzrxv5stbw7prlfmsghplrcwk67mc47/orig</x:v>
       </x:c>
-      <x:c r="L40" t="str"/>
+      <x:c r="L40"/>
       <x:c r="M40" t="str">
         <x:v>По телефону и в сообщениях</x:v>
       </x:c>
-      <x:c r="N40" t="str"/>
-      <x:c r="O40" t="str"/>
-      <x:c r="P40" t="str"/>
+      <x:c r="N40"/>
+      <x:c r="O40"/>
+      <x:c r="P40"/>
       <x:c r="Q40" t="str">
         <x:v>Ремонт и строительство</x:v>
       </x:c>
       <x:c r="R40" t="str">
         <x:v>г. Волгоград, ул. 25-летия Октября, д. 1, стр. 3</x:v>
       </x:c>
-      <x:c r="S40" t="str"/>
-      <x:c r="T40" t="str"/>
-      <x:c r="U40" t="str"/>
+      <x:c r="S40"/>
+      <x:c r="T40"/>
+      <x:c r="U40"/>
       <x:c r="V40" t="str">
         <x:v>Поштучно</x:v>
       </x:c>
@@ -7898,9 +7830,9 @@
       <x:c r="Z40" t="str">
         <x:v>Штуку</x:v>
       </x:c>
-      <x:c r="AA40" t="str"/>
-      <x:c r="AB40" t="str"/>
-      <x:c r="AC40" t="str"/>
+      <x:c r="AA40"/>
+      <x:c r="AB40"/>
+      <x:c r="AC40"/>
       <x:c r="AD40" t="n">
         <x:v>7</x:v>
       </x:c>
@@ -7913,26 +7845,24 @@
       <x:c r="AG40" t="n">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="AH40" t="str"/>
+      <x:c r="AH40"/>
       <x:c r="AI40" t="str">
         <x:v>3921120000</x:v>
       </x:c>
-      <x:c r="AJ40" t="str">
-        <x:v>22.21.42.110</x:v>
-      </x:c>
-      <x:c r="AK40" t="str"/>
-      <x:c r="AL40" t="str"/>
-      <x:c r="AM40" t="str"/>
-      <x:c r="AN40" t="str"/>
-      <x:c r="AO40" t="str"/>
-      <x:c r="AP40" t="str"/>
-      <x:c r="AQ40" t="str"/>
-      <x:c r="AR40" t="str"/>
-      <x:c r="AS40" t="str"/>
-      <x:c r="AT40" t="str"/>
-      <x:c r="AU40" t="str"/>
-      <x:c r="AV40" t="str"/>
-      <x:c r="AW40" t="str"/>
+      <x:c r="AJ40" t="str"/>
+      <x:c r="AK40"/>
+      <x:c r="AL40"/>
+      <x:c r="AM40"/>
+      <x:c r="AN40"/>
+      <x:c r="AO40"/>
+      <x:c r="AP40"/>
+      <x:c r="AQ40"/>
+      <x:c r="AR40"/>
+      <x:c r="AS40"/>
+      <x:c r="AT40"/>
+      <x:c r="AU40"/>
+      <x:c r="AV40"/>
+      <x:c r="AW40"/>
       <x:c r="AX40" t="str">
         <x:v>4900</x:v>
       </x:c>
@@ -7951,7 +7881,7 @@
       <x:c r="BC40" t="str">
         <x:v>Отделка</x:v>
       </x:c>
-      <x:c r="BD40" t="str"/>
+      <x:c r="BD40"/>
       <x:c r="BE40" t="str">
         <x:v>Стеновые панели, рейки и элементы декора</x:v>
       </x:c>
@@ -7973,28 +7903,28 @@
       <x:c r="BK40" t="str">
         <x:v>1140</x:v>
       </x:c>
-      <x:c r="BL40" t="str"/>
+      <x:c r="BL40"/>
       <x:c r="BM40" t="str">
         <x:v>Нет</x:v>
       </x:c>
-      <x:c r="BN40" t="str"/>
-      <x:c r="BO40" t="str"/>
-      <x:c r="BP40" t="str"/>
-      <x:c r="BQ40" t="str"/>
-      <x:c r="BR40" t="str"/>
-      <x:c r="BS40" t="str"/>
-      <x:c r="BT40" t="str"/>
-      <x:c r="BU40" t="str"/>
+      <x:c r="BN40"/>
+      <x:c r="BO40"/>
+      <x:c r="BP40"/>
+      <x:c r="BQ40"/>
+      <x:c r="BR40"/>
+      <x:c r="BS40"/>
+      <x:c r="BT40"/>
+      <x:c r="BU40"/>
     </x:row>
     <x:row r="41">
       <x:c r="A41" t="str">
         <x:v>adamar-vlg-MARBLE 10</x:v>
       </x:c>
-      <x:c r="B41" t="str"/>
-      <x:c r="C41" t="str"/>
-      <x:c r="D41" t="str"/>
-      <x:c r="E41" t="str"/>
-      <x:c r="F41" t="str"/>
+      <x:c r="B41"/>
+      <x:c r="C41"/>
+      <x:c r="D41"/>
+      <x:c r="E41"/>
+      <x:c r="F41"/>
       <x:c r="G41" t="str">
         <x:v>Adamar Group</x:v>
       </x:c>
@@ -8014,22 +7944,22 @@
       <x:c r="K41" t="str">
         <x:v>https://avatars.mds.yandex.net/get-yastore/20760651/jdgk94lggnz2mdjcdxvlv8v9jt2fv4qs/orig | https://avatars.mds.yandex.net/get-yastore/20918687/fc6f786fxq9nhx4n2wwhzg7z2d97h6ld/orig | https://avatars.mds.yandex.net/get-yastore/20274467/fd4pj5crklkgv7dz6jxq2fq7qvmjfc47/orig | https://avatars.mds.yandex.net/get-yastore/20760651/zqfffdb4thrz2rmcqhvlbkb7swv5rj46/orig</x:v>
       </x:c>
-      <x:c r="L41" t="str"/>
+      <x:c r="L41"/>
       <x:c r="M41" t="str">
         <x:v>По телефону и в сообщениях</x:v>
       </x:c>
-      <x:c r="N41" t="str"/>
-      <x:c r="O41" t="str"/>
-      <x:c r="P41" t="str"/>
+      <x:c r="N41"/>
+      <x:c r="O41"/>
+      <x:c r="P41"/>
       <x:c r="Q41" t="str">
         <x:v>Ремонт и строительство</x:v>
       </x:c>
       <x:c r="R41" t="str">
         <x:v>г. Волгоград, ул. 25-летия Октября, д. 1, стр. 3</x:v>
       </x:c>
-      <x:c r="S41" t="str"/>
-      <x:c r="T41" t="str"/>
-      <x:c r="U41" t="str"/>
+      <x:c r="S41"/>
+      <x:c r="T41"/>
+      <x:c r="U41"/>
       <x:c r="V41" t="str">
         <x:v>Поштучно</x:v>
       </x:c>
@@ -8045,9 +7975,9 @@
       <x:c r="Z41" t="str">
         <x:v>Штуку</x:v>
       </x:c>
-      <x:c r="AA41" t="str"/>
-      <x:c r="AB41" t="str"/>
-      <x:c r="AC41" t="str"/>
+      <x:c r="AA41"/>
+      <x:c r="AB41"/>
+      <x:c r="AC41"/>
       <x:c r="AD41" t="n">
         <x:v>7</x:v>
       </x:c>
@@ -8060,26 +7990,24 @@
       <x:c r="AG41" t="n">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="AH41" t="str"/>
+      <x:c r="AH41"/>
       <x:c r="AI41" t="str">
         <x:v>3921120000</x:v>
       </x:c>
-      <x:c r="AJ41" t="str">
-        <x:v>22.21.42.110</x:v>
-      </x:c>
-      <x:c r="AK41" t="str"/>
-      <x:c r="AL41" t="str"/>
-      <x:c r="AM41" t="str"/>
-      <x:c r="AN41" t="str"/>
-      <x:c r="AO41" t="str"/>
-      <x:c r="AP41" t="str"/>
-      <x:c r="AQ41" t="str"/>
-      <x:c r="AR41" t="str"/>
-      <x:c r="AS41" t="str"/>
-      <x:c r="AT41" t="str"/>
-      <x:c r="AU41" t="str"/>
-      <x:c r="AV41" t="str"/>
-      <x:c r="AW41" t="str"/>
+      <x:c r="AJ41" t="str"/>
+      <x:c r="AK41"/>
+      <x:c r="AL41"/>
+      <x:c r="AM41"/>
+      <x:c r="AN41"/>
+      <x:c r="AO41"/>
+      <x:c r="AP41"/>
+      <x:c r="AQ41"/>
+      <x:c r="AR41"/>
+      <x:c r="AS41"/>
+      <x:c r="AT41"/>
+      <x:c r="AU41"/>
+      <x:c r="AV41"/>
+      <x:c r="AW41"/>
       <x:c r="AX41" t="str">
         <x:v>4900</x:v>
       </x:c>
@@ -8098,7 +8026,7 @@
       <x:c r="BC41" t="str">
         <x:v>Отделка</x:v>
       </x:c>
-      <x:c r="BD41" t="str"/>
+      <x:c r="BD41"/>
       <x:c r="BE41" t="str">
         <x:v>Стеновые панели, рейки и элементы декора</x:v>
       </x:c>
@@ -8120,28 +8048,28 @@
       <x:c r="BK41" t="str">
         <x:v>1140</x:v>
       </x:c>
-      <x:c r="BL41" t="str"/>
+      <x:c r="BL41"/>
       <x:c r="BM41" t="str">
         <x:v>Нет</x:v>
       </x:c>
-      <x:c r="BN41" t="str"/>
-      <x:c r="BO41" t="str"/>
-      <x:c r="BP41" t="str"/>
-      <x:c r="BQ41" t="str"/>
-      <x:c r="BR41" t="str"/>
-      <x:c r="BS41" t="str"/>
-      <x:c r="BT41" t="str"/>
-      <x:c r="BU41" t="str"/>
+      <x:c r="BN41"/>
+      <x:c r="BO41"/>
+      <x:c r="BP41"/>
+      <x:c r="BQ41"/>
+      <x:c r="BR41"/>
+      <x:c r="BS41"/>
+      <x:c r="BT41"/>
+      <x:c r="BU41"/>
     </x:row>
     <x:row r="42">
       <x:c r="A42" t="str">
         <x:v>adamar-vlg-WHITE NIGHT</x:v>
       </x:c>
-      <x:c r="B42" t="str"/>
-      <x:c r="C42" t="str"/>
-      <x:c r="D42" t="str"/>
-      <x:c r="E42" t="str"/>
-      <x:c r="F42" t="str"/>
+      <x:c r="B42"/>
+      <x:c r="C42"/>
+      <x:c r="D42"/>
+      <x:c r="E42"/>
+      <x:c r="F42"/>
       <x:c r="G42" t="str">
         <x:v>Adamar Group</x:v>
       </x:c>
@@ -8161,22 +8089,22 @@
       <x:c r="K42" t="str">
         <x:v>https://avatars.mds.yandex.net/get-yastore/20274467/vmk77jq2ks4hmzjfx4vv6dblzrswm4rl/orig | https://avatars.mds.yandex.net/get-yastore/20274467/677wqq2wb8s2cwhkckssh4d9g2lrxmsl/orig | https://avatars.mds.yandex.net/get-yastore/20274467/pkh99898g7qsc95krlm8mgt9q856mhjq/orig | https://avatars.mds.yandex.net/get-yastore/20274467/q8wjzqsrfqnbsr9qf68mnrf52xs5tfjd/orig</x:v>
       </x:c>
-      <x:c r="L42" t="str"/>
+      <x:c r="L42"/>
       <x:c r="M42" t="str">
         <x:v>По телефону и в сообщениях</x:v>
       </x:c>
-      <x:c r="N42" t="str"/>
-      <x:c r="O42" t="str"/>
-      <x:c r="P42" t="str"/>
+      <x:c r="N42"/>
+      <x:c r="O42"/>
+      <x:c r="P42"/>
       <x:c r="Q42" t="str">
         <x:v>Ремонт и строительство</x:v>
       </x:c>
       <x:c r="R42" t="str">
         <x:v>г. Волгоград, ул. 25-летия Октября, д. 1, стр. 3</x:v>
       </x:c>
-      <x:c r="S42" t="str"/>
-      <x:c r="T42" t="str"/>
-      <x:c r="U42" t="str"/>
+      <x:c r="S42"/>
+      <x:c r="T42"/>
+      <x:c r="U42"/>
       <x:c r="V42" t="str">
         <x:v>Поштучно</x:v>
       </x:c>
@@ -8192,9 +8120,9 @@
       <x:c r="Z42" t="str">
         <x:v>Штуку</x:v>
       </x:c>
-      <x:c r="AA42" t="str"/>
-      <x:c r="AB42" t="str"/>
-      <x:c r="AC42" t="str"/>
+      <x:c r="AA42"/>
+      <x:c r="AB42"/>
+      <x:c r="AC42"/>
       <x:c r="AD42" t="n">
         <x:v>7</x:v>
       </x:c>
@@ -8207,26 +8135,24 @@
       <x:c r="AG42" t="n">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="AH42" t="str"/>
+      <x:c r="AH42"/>
       <x:c r="AI42" t="str">
         <x:v>3921120000</x:v>
       </x:c>
-      <x:c r="AJ42" t="str">
-        <x:v>22.21.42.110</x:v>
-      </x:c>
-      <x:c r="AK42" t="str"/>
-      <x:c r="AL42" t="str"/>
-      <x:c r="AM42" t="str"/>
-      <x:c r="AN42" t="str"/>
-      <x:c r="AO42" t="str"/>
-      <x:c r="AP42" t="str"/>
-      <x:c r="AQ42" t="str"/>
-      <x:c r="AR42" t="str"/>
-      <x:c r="AS42" t="str"/>
-      <x:c r="AT42" t="str"/>
-      <x:c r="AU42" t="str"/>
-      <x:c r="AV42" t="str"/>
-      <x:c r="AW42" t="str"/>
+      <x:c r="AJ42" t="str"/>
+      <x:c r="AK42"/>
+      <x:c r="AL42"/>
+      <x:c r="AM42"/>
+      <x:c r="AN42"/>
+      <x:c r="AO42"/>
+      <x:c r="AP42"/>
+      <x:c r="AQ42"/>
+      <x:c r="AR42"/>
+      <x:c r="AS42"/>
+      <x:c r="AT42"/>
+      <x:c r="AU42"/>
+      <x:c r="AV42"/>
+      <x:c r="AW42"/>
       <x:c r="AX42" t="str">
         <x:v>4900</x:v>
       </x:c>
@@ -8245,7 +8171,7 @@
       <x:c r="BC42" t="str">
         <x:v>Отделка</x:v>
       </x:c>
-      <x:c r="BD42" t="str"/>
+      <x:c r="BD42"/>
       <x:c r="BE42" t="str">
         <x:v>Стеновые панели, рейки и элементы декора</x:v>
       </x:c>
@@ -8267,28 +8193,28 @@
       <x:c r="BK42" t="str">
         <x:v>1140</x:v>
       </x:c>
-      <x:c r="BL42" t="str"/>
+      <x:c r="BL42"/>
       <x:c r="BM42" t="str">
         <x:v>Нет</x:v>
       </x:c>
-      <x:c r="BN42" t="str"/>
-      <x:c r="BO42" t="str"/>
-      <x:c r="BP42" t="str"/>
-      <x:c r="BQ42" t="str"/>
-      <x:c r="BR42" t="str"/>
-      <x:c r="BS42" t="str"/>
-      <x:c r="BT42" t="str"/>
-      <x:c r="BU42" t="str"/>
+      <x:c r="BN42"/>
+      <x:c r="BO42"/>
+      <x:c r="BP42"/>
+      <x:c r="BQ42"/>
+      <x:c r="BR42"/>
+      <x:c r="BS42"/>
+      <x:c r="BT42"/>
+      <x:c r="BU42"/>
     </x:row>
     <x:row r="43">
       <x:c r="A43" t="str">
         <x:v>adamar-vlg-FOGLINE_DARK_DECOR</x:v>
       </x:c>
-      <x:c r="B43" t="str"/>
-      <x:c r="C43" t="str"/>
-      <x:c r="D43" t="str"/>
-      <x:c r="E43" t="str"/>
-      <x:c r="F43" t="str"/>
+      <x:c r="B43"/>
+      <x:c r="C43"/>
+      <x:c r="D43"/>
+      <x:c r="E43"/>
+      <x:c r="F43"/>
       <x:c r="G43" t="str">
         <x:v>Adamar Group</x:v>
       </x:c>
@@ -8308,22 +8234,22 @@
       <x:c r="K43" t="str">
         <x:v>https://avatars.mds.yandex.net/get-yastore/21012869/cj2dchd64njtpqzmwj9qlzgpz4npk7t4/orig | https://avatars.mds.yandex.net/get-yastore/21055393/dptk7k9x749w2bqflqxctk2qqnndkzjv/orig | https://avatars.mds.yandex.net/get-yastore/21012869/8t4gz8wgtjrr969pd4rgm8xxdfhtgp5m/orig</x:v>
       </x:c>
-      <x:c r="L43" t="str"/>
+      <x:c r="L43"/>
       <x:c r="M43" t="str">
         <x:v>По телефону и в сообщениях</x:v>
       </x:c>
-      <x:c r="N43" t="str"/>
-      <x:c r="O43" t="str"/>
-      <x:c r="P43" t="str"/>
+      <x:c r="N43"/>
+      <x:c r="O43"/>
+      <x:c r="P43"/>
       <x:c r="Q43" t="str">
         <x:v>Ремонт и строительство</x:v>
       </x:c>
       <x:c r="R43" t="str">
         <x:v>г. Волгоград, ул. 25-летия Октября, д. 1, стр. 3</x:v>
       </x:c>
-      <x:c r="S43" t="str"/>
-      <x:c r="T43" t="str"/>
-      <x:c r="U43" t="str"/>
+      <x:c r="S43"/>
+      <x:c r="T43"/>
+      <x:c r="U43"/>
       <x:c r="V43" t="str">
         <x:v>Поштучно</x:v>
       </x:c>
@@ -8339,9 +8265,9 @@
       <x:c r="Z43" t="str">
         <x:v>Штуку</x:v>
       </x:c>
-      <x:c r="AA43" t="str"/>
-      <x:c r="AB43" t="str"/>
-      <x:c r="AC43" t="str"/>
+      <x:c r="AA43"/>
+      <x:c r="AB43"/>
+      <x:c r="AC43"/>
       <x:c r="AD43" t="n">
         <x:v>7</x:v>
       </x:c>
@@ -8354,26 +8280,24 @@
       <x:c r="AG43" t="n">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="AH43" t="str"/>
+      <x:c r="AH43"/>
       <x:c r="AI43" t="str">
         <x:v>3921120000</x:v>
       </x:c>
-      <x:c r="AJ43" t="str">
-        <x:v>22.21.42.110</x:v>
-      </x:c>
-      <x:c r="AK43" t="str"/>
-      <x:c r="AL43" t="str"/>
-      <x:c r="AM43" t="str"/>
-      <x:c r="AN43" t="str"/>
-      <x:c r="AO43" t="str"/>
-      <x:c r="AP43" t="str"/>
-      <x:c r="AQ43" t="str"/>
-      <x:c r="AR43" t="str"/>
-      <x:c r="AS43" t="str"/>
-      <x:c r="AT43" t="str"/>
-      <x:c r="AU43" t="str"/>
-      <x:c r="AV43" t="str"/>
-      <x:c r="AW43" t="str"/>
+      <x:c r="AJ43" t="str"/>
+      <x:c r="AK43"/>
+      <x:c r="AL43"/>
+      <x:c r="AM43"/>
+      <x:c r="AN43"/>
+      <x:c r="AO43"/>
+      <x:c r="AP43"/>
+      <x:c r="AQ43"/>
+      <x:c r="AR43"/>
+      <x:c r="AS43"/>
+      <x:c r="AT43"/>
+      <x:c r="AU43"/>
+      <x:c r="AV43"/>
+      <x:c r="AW43"/>
       <x:c r="AX43" t="str">
         <x:v>4900</x:v>
       </x:c>
@@ -8392,7 +8316,7 @@
       <x:c r="BC43" t="str">
         <x:v>Отделка</x:v>
       </x:c>
-      <x:c r="BD43" t="str"/>
+      <x:c r="BD43"/>
       <x:c r="BE43" t="str">
         <x:v>Стеновые панели, рейки и элементы декора</x:v>
       </x:c>
@@ -8414,28 +8338,28 @@
       <x:c r="BK43" t="str">
         <x:v>1140</x:v>
       </x:c>
-      <x:c r="BL43" t="str"/>
+      <x:c r="BL43"/>
       <x:c r="BM43" t="str">
         <x:v>Нет</x:v>
       </x:c>
-      <x:c r="BN43" t="str"/>
-      <x:c r="BO43" t="str"/>
-      <x:c r="BP43" t="str"/>
-      <x:c r="BQ43" t="str"/>
-      <x:c r="BR43" t="str"/>
-      <x:c r="BS43" t="str"/>
-      <x:c r="BT43" t="str"/>
-      <x:c r="BU43" t="str"/>
+      <x:c r="BN43"/>
+      <x:c r="BO43"/>
+      <x:c r="BP43"/>
+      <x:c r="BQ43"/>
+      <x:c r="BR43"/>
+      <x:c r="BS43"/>
+      <x:c r="BT43"/>
+      <x:c r="BU43"/>
     </x:row>
     <x:row r="44">
       <x:c r="A44" t="str">
         <x:v>adamar-vlg-AQUAMARINA</x:v>
       </x:c>
-      <x:c r="B44" t="str"/>
-      <x:c r="C44" t="str"/>
-      <x:c r="D44" t="str"/>
-      <x:c r="E44" t="str"/>
-      <x:c r="F44" t="str"/>
+      <x:c r="B44"/>
+      <x:c r="C44"/>
+      <x:c r="D44"/>
+      <x:c r="E44"/>
+      <x:c r="F44"/>
       <x:c r="G44" t="str">
         <x:v>Adamar Group</x:v>
       </x:c>
@@ -8455,22 +8379,22 @@
       <x:c r="K44" t="str">
         <x:v>https://avatars.mds.yandex.net/get-yastore/20274467/8jjl4tvr5qt8cfcpgtpcvs7vdmfhbbbh/orig | https://avatars.mds.yandex.net/get-yastore/21012869/4svk8hgjggmvdlr6tkjctqv75l626cgx/orig | https://avatars.mds.yandex.net/get-yastore/21055393/btsqjz68cxdj8268kcm64lqznwk8bnff/orig</x:v>
       </x:c>
-      <x:c r="L44" t="str"/>
+      <x:c r="L44"/>
       <x:c r="M44" t="str">
         <x:v>По телефону и в сообщениях</x:v>
       </x:c>
-      <x:c r="N44" t="str"/>
-      <x:c r="O44" t="str"/>
-      <x:c r="P44" t="str"/>
+      <x:c r="N44"/>
+      <x:c r="O44"/>
+      <x:c r="P44"/>
       <x:c r="Q44" t="str">
         <x:v>Ремонт и строительство</x:v>
       </x:c>
       <x:c r="R44" t="str">
         <x:v>г. Волгоград, ул. 25-летия Октября, д. 1, стр. 3</x:v>
       </x:c>
-      <x:c r="S44" t="str"/>
-      <x:c r="T44" t="str"/>
-      <x:c r="U44" t="str"/>
+      <x:c r="S44"/>
+      <x:c r="T44"/>
+      <x:c r="U44"/>
       <x:c r="V44" t="str">
         <x:v>Поштучно</x:v>
       </x:c>
@@ -8486,9 +8410,9 @@
       <x:c r="Z44" t="str">
         <x:v>Штуку</x:v>
       </x:c>
-      <x:c r="AA44" t="str"/>
-      <x:c r="AB44" t="str"/>
-      <x:c r="AC44" t="str"/>
+      <x:c r="AA44"/>
+      <x:c r="AB44"/>
+      <x:c r="AC44"/>
       <x:c r="AD44" t="n">
         <x:v>7</x:v>
       </x:c>
@@ -8501,26 +8425,24 @@
       <x:c r="AG44" t="n">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="AH44" t="str"/>
+      <x:c r="AH44"/>
       <x:c r="AI44" t="str">
         <x:v>3921120000</x:v>
       </x:c>
-      <x:c r="AJ44" t="str">
-        <x:v>22.21.42.110</x:v>
-      </x:c>
-      <x:c r="AK44" t="str"/>
-      <x:c r="AL44" t="str"/>
-      <x:c r="AM44" t="str"/>
-      <x:c r="AN44" t="str"/>
-      <x:c r="AO44" t="str"/>
-      <x:c r="AP44" t="str"/>
-      <x:c r="AQ44" t="str"/>
-      <x:c r="AR44" t="str"/>
-      <x:c r="AS44" t="str"/>
-      <x:c r="AT44" t="str"/>
-      <x:c r="AU44" t="str"/>
-      <x:c r="AV44" t="str"/>
-      <x:c r="AW44" t="str"/>
+      <x:c r="AJ44" t="str"/>
+      <x:c r="AK44"/>
+      <x:c r="AL44"/>
+      <x:c r="AM44"/>
+      <x:c r="AN44"/>
+      <x:c r="AO44"/>
+      <x:c r="AP44"/>
+      <x:c r="AQ44"/>
+      <x:c r="AR44"/>
+      <x:c r="AS44"/>
+      <x:c r="AT44"/>
+      <x:c r="AU44"/>
+      <x:c r="AV44"/>
+      <x:c r="AW44"/>
       <x:c r="AX44" t="str">
         <x:v>4900</x:v>
       </x:c>
@@ -8539,7 +8461,7 @@
       <x:c r="BC44" t="str">
         <x:v>Отделка</x:v>
       </x:c>
-      <x:c r="BD44" t="str"/>
+      <x:c r="BD44"/>
       <x:c r="BE44" t="str">
         <x:v>Стеновые панели, рейки и элементы декора</x:v>
       </x:c>
@@ -8561,28 +8483,28 @@
       <x:c r="BK44" t="str">
         <x:v>1140</x:v>
       </x:c>
-      <x:c r="BL44" t="str"/>
+      <x:c r="BL44"/>
       <x:c r="BM44" t="str">
         <x:v>Нет</x:v>
       </x:c>
-      <x:c r="BN44" t="str"/>
-      <x:c r="BO44" t="str"/>
-      <x:c r="BP44" t="str"/>
-      <x:c r="BQ44" t="str"/>
-      <x:c r="BR44" t="str"/>
-      <x:c r="BS44" t="str"/>
-      <x:c r="BT44" t="str"/>
-      <x:c r="BU44" t="str"/>
+      <x:c r="BN44"/>
+      <x:c r="BO44"/>
+      <x:c r="BP44"/>
+      <x:c r="BQ44"/>
+      <x:c r="BR44"/>
+      <x:c r="BS44"/>
+      <x:c r="BT44"/>
+      <x:c r="BU44"/>
     </x:row>
     <x:row r="45">
       <x:c r="A45" t="str">
         <x:v>adamar-vlg-Glossy_Aeon</x:v>
       </x:c>
-      <x:c r="B45" t="str"/>
-      <x:c r="C45" t="str"/>
-      <x:c r="D45" t="str"/>
-      <x:c r="E45" t="str"/>
-      <x:c r="F45" t="str"/>
+      <x:c r="B45"/>
+      <x:c r="C45"/>
+      <x:c r="D45"/>
+      <x:c r="E45"/>
+      <x:c r="F45"/>
       <x:c r="G45" t="str">
         <x:v>Adamar Group</x:v>
       </x:c>
@@ -8602,22 +8524,22 @@
       <x:c r="K45" t="str">
         <x:v>https://avatars.mds.yandex.net/get-yastore/20918687/tmk9rwz8kng4n27wvvcktqzcnrlpbggc/orig | https://avatars.mds.yandex.net/get-yastore/21553739/sqd6smwdkhwd6bfw89x4b5bj7b842792/orig | https://avatars.mds.yandex.net/get-yastore/21580234/z5wln5tlhxncngcvgxb4ddtl4txks6gx/orig | https://avatars.mds.yandex.net/get-yastore/20493671/8tpjzlztjtl6cdpd55z2z5b4nnvncz6l/orig</x:v>
       </x:c>
-      <x:c r="L45" t="str"/>
+      <x:c r="L45"/>
       <x:c r="M45" t="str">
         <x:v>По телефону и в сообщениях</x:v>
       </x:c>
-      <x:c r="N45" t="str"/>
-      <x:c r="O45" t="str"/>
-      <x:c r="P45" t="str"/>
+      <x:c r="N45"/>
+      <x:c r="O45"/>
+      <x:c r="P45"/>
       <x:c r="Q45" t="str">
         <x:v>Ремонт и строительство</x:v>
       </x:c>
       <x:c r="R45" t="str">
         <x:v>г. Волгоград, ул. 25-летия Октября, д. 1, стр. 3</x:v>
       </x:c>
-      <x:c r="S45" t="str"/>
-      <x:c r="T45" t="str"/>
-      <x:c r="U45" t="str"/>
+      <x:c r="S45"/>
+      <x:c r="T45"/>
+      <x:c r="U45"/>
       <x:c r="V45" t="str">
         <x:v>Поштучно</x:v>
       </x:c>
@@ -8633,9 +8555,9 @@
       <x:c r="Z45" t="str">
         <x:v>Штуку</x:v>
       </x:c>
-      <x:c r="AA45" t="str"/>
-      <x:c r="AB45" t="str"/>
-      <x:c r="AC45" t="str"/>
+      <x:c r="AA45"/>
+      <x:c r="AB45"/>
+      <x:c r="AC45"/>
       <x:c r="AD45" t="n">
         <x:v>7</x:v>
       </x:c>
@@ -8648,26 +8570,24 @@
       <x:c r="AG45" t="n">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="AH45" t="str"/>
+      <x:c r="AH45"/>
       <x:c r="AI45" t="str">
         <x:v>3921120000</x:v>
       </x:c>
-      <x:c r="AJ45" t="str">
-        <x:v>22.21.42.110</x:v>
-      </x:c>
-      <x:c r="AK45" t="str"/>
-      <x:c r="AL45" t="str"/>
-      <x:c r="AM45" t="str"/>
-      <x:c r="AN45" t="str"/>
-      <x:c r="AO45" t="str"/>
-      <x:c r="AP45" t="str"/>
-      <x:c r="AQ45" t="str"/>
-      <x:c r="AR45" t="str"/>
-      <x:c r="AS45" t="str"/>
-      <x:c r="AT45" t="str"/>
-      <x:c r="AU45" t="str"/>
-      <x:c r="AV45" t="str"/>
-      <x:c r="AW45" t="str"/>
+      <x:c r="AJ45" t="str"/>
+      <x:c r="AK45"/>
+      <x:c r="AL45"/>
+      <x:c r="AM45"/>
+      <x:c r="AN45"/>
+      <x:c r="AO45"/>
+      <x:c r="AP45"/>
+      <x:c r="AQ45"/>
+      <x:c r="AR45"/>
+      <x:c r="AS45"/>
+      <x:c r="AT45"/>
+      <x:c r="AU45"/>
+      <x:c r="AV45"/>
+      <x:c r="AW45"/>
       <x:c r="AX45" t="str">
         <x:v>4900</x:v>
       </x:c>
@@ -8686,7 +8606,7 @@
       <x:c r="BC45" t="str">
         <x:v>Отделка</x:v>
       </x:c>
-      <x:c r="BD45" t="str"/>
+      <x:c r="BD45"/>
       <x:c r="BE45" t="str">
         <x:v>Стеновые панели, рейки и элементы декора</x:v>
       </x:c>
@@ -8708,28 +8628,28 @@
       <x:c r="BK45" t="str">
         <x:v>1140</x:v>
       </x:c>
-      <x:c r="BL45" t="str"/>
+      <x:c r="BL45"/>
       <x:c r="BM45" t="str">
         <x:v>Нет</x:v>
       </x:c>
-      <x:c r="BN45" t="str"/>
-      <x:c r="BO45" t="str"/>
-      <x:c r="BP45" t="str"/>
-      <x:c r="BQ45" t="str"/>
-      <x:c r="BR45" t="str"/>
-      <x:c r="BS45" t="str"/>
-      <x:c r="BT45" t="str"/>
-      <x:c r="BU45" t="str"/>
+      <x:c r="BN45"/>
+      <x:c r="BO45"/>
+      <x:c r="BP45"/>
+      <x:c r="BQ45"/>
+      <x:c r="BR45"/>
+      <x:c r="BS45"/>
+      <x:c r="BT45"/>
+      <x:c r="BU45"/>
     </x:row>
     <x:row r="46">
       <x:c r="A46" t="str">
         <x:v>adamar-vlg-BETON FERONI DECOR</x:v>
       </x:c>
-      <x:c r="B46" t="str"/>
-      <x:c r="C46" t="str"/>
-      <x:c r="D46" t="str"/>
-      <x:c r="E46" t="str"/>
-      <x:c r="F46" t="str"/>
+      <x:c r="B46"/>
+      <x:c r="C46"/>
+      <x:c r="D46"/>
+      <x:c r="E46"/>
+      <x:c r="F46"/>
       <x:c r="G46" t="str">
         <x:v>Adamar Group</x:v>
       </x:c>
@@ -8749,22 +8669,22 @@
       <x:c r="K46" t="str">
         <x:v>https://avatars.mds.yandex.net/get-yastore/20274467/6px2n4894ncdd8gnntg4mnh2tp4wmwtz/orig | https://avatars.mds.yandex.net/get-yastore/21055393/zcsklcdmdsdss7v2vd58vkzbqjwwl6gp/orig | https://avatars.mds.yandex.net/get-yastore/21055393/9pv62jp5flt8rjpmpzdmlvqkqxvdvl9x/orig</x:v>
       </x:c>
-      <x:c r="L46" t="str"/>
+      <x:c r="L46"/>
       <x:c r="M46" t="str">
         <x:v>По телефону и в сообщениях</x:v>
       </x:c>
-      <x:c r="N46" t="str"/>
-      <x:c r="O46" t="str"/>
-      <x:c r="P46" t="str"/>
+      <x:c r="N46"/>
+      <x:c r="O46"/>
+      <x:c r="P46"/>
       <x:c r="Q46" t="str">
         <x:v>Ремонт и строительство</x:v>
       </x:c>
       <x:c r="R46" t="str">
         <x:v>г. Волгоград, ул. 25-летия Октября, д. 1, стр. 3</x:v>
       </x:c>
-      <x:c r="S46" t="str"/>
-      <x:c r="T46" t="str"/>
-      <x:c r="U46" t="str"/>
+      <x:c r="S46"/>
+      <x:c r="T46"/>
+      <x:c r="U46"/>
       <x:c r="V46" t="str">
         <x:v>Поштучно</x:v>
       </x:c>
@@ -8780,9 +8700,9 @@
       <x:c r="Z46" t="str">
         <x:v>Штуку</x:v>
       </x:c>
-      <x:c r="AA46" t="str"/>
-      <x:c r="AB46" t="str"/>
-      <x:c r="AC46" t="str"/>
+      <x:c r="AA46"/>
+      <x:c r="AB46"/>
+      <x:c r="AC46"/>
       <x:c r="AD46" t="n">
         <x:v>7</x:v>
       </x:c>
@@ -8795,26 +8715,24 @@
       <x:c r="AG46" t="n">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="AH46" t="str"/>
+      <x:c r="AH46"/>
       <x:c r="AI46" t="str">
         <x:v>3921120000</x:v>
       </x:c>
-      <x:c r="AJ46" t="str">
-        <x:v>22.21.42.110</x:v>
-      </x:c>
-      <x:c r="AK46" t="str"/>
-      <x:c r="AL46" t="str"/>
-      <x:c r="AM46" t="str"/>
-      <x:c r="AN46" t="str"/>
-      <x:c r="AO46" t="str"/>
-      <x:c r="AP46" t="str"/>
-      <x:c r="AQ46" t="str"/>
-      <x:c r="AR46" t="str"/>
-      <x:c r="AS46" t="str"/>
-      <x:c r="AT46" t="str"/>
-      <x:c r="AU46" t="str"/>
-      <x:c r="AV46" t="str"/>
-      <x:c r="AW46" t="str"/>
+      <x:c r="AJ46" t="str"/>
+      <x:c r="AK46"/>
+      <x:c r="AL46"/>
+      <x:c r="AM46"/>
+      <x:c r="AN46"/>
+      <x:c r="AO46"/>
+      <x:c r="AP46"/>
+      <x:c r="AQ46"/>
+      <x:c r="AR46"/>
+      <x:c r="AS46"/>
+      <x:c r="AT46"/>
+      <x:c r="AU46"/>
+      <x:c r="AV46"/>
+      <x:c r="AW46"/>
       <x:c r="AX46" t="str">
         <x:v>4900</x:v>
       </x:c>
@@ -8833,7 +8751,7 @@
       <x:c r="BC46" t="str">
         <x:v>Отделка</x:v>
       </x:c>
-      <x:c r="BD46" t="str"/>
+      <x:c r="BD46"/>
       <x:c r="BE46" t="str">
         <x:v>Стеновые панели, рейки и элементы декора</x:v>
       </x:c>
@@ -8855,28 +8773,28 @@
       <x:c r="BK46" t="str">
         <x:v>1140</x:v>
       </x:c>
-      <x:c r="BL46" t="str"/>
+      <x:c r="BL46"/>
       <x:c r="BM46" t="str">
         <x:v>Нет</x:v>
       </x:c>
-      <x:c r="BN46" t="str"/>
-      <x:c r="BO46" t="str"/>
-      <x:c r="BP46" t="str"/>
-      <x:c r="BQ46" t="str"/>
-      <x:c r="BR46" t="str"/>
-      <x:c r="BS46" t="str"/>
-      <x:c r="BT46" t="str"/>
-      <x:c r="BU46" t="str"/>
+      <x:c r="BN46"/>
+      <x:c r="BO46"/>
+      <x:c r="BP46"/>
+      <x:c r="BQ46"/>
+      <x:c r="BR46"/>
+      <x:c r="BS46"/>
+      <x:c r="BT46"/>
+      <x:c r="BU46"/>
     </x:row>
     <x:row r="47">
       <x:c r="A47" t="str">
         <x:v>adamar-vlg-MARBLE SNOW</x:v>
       </x:c>
-      <x:c r="B47" t="str"/>
-      <x:c r="C47" t="str"/>
-      <x:c r="D47" t="str"/>
-      <x:c r="E47" t="str"/>
-      <x:c r="F47" t="str"/>
+      <x:c r="B47"/>
+      <x:c r="C47"/>
+      <x:c r="D47"/>
+      <x:c r="E47"/>
+      <x:c r="F47"/>
       <x:c r="G47" t="str">
         <x:v>Adamar Group</x:v>
       </x:c>
@@ -8896,22 +8814,22 @@
       <x:c r="K47" t="str">
         <x:v>https://avatars.mds.yandex.net/get-yastore/20760651/jwgbjlfl42fnkjffz562n4fr9rbh2cq5/orig | https://avatars.mds.yandex.net/get-yastore/21055393/ztjk7m8czvrwj4jln7rxdtbwgsqm5r4h/orig | https://avatars.mds.yandex.net/get-yastore/20918687/xfx29vfprqmhdwmm4jkf8stk5lg5mzzm/orig | https://avatars.mds.yandex.net/get-yastore/20918687/4gxlq64mknmr4ghq62n7xd4pp44k9gng/orig</x:v>
       </x:c>
-      <x:c r="L47" t="str"/>
+      <x:c r="L47"/>
       <x:c r="M47" t="str">
         <x:v>По телефону и в сообщениях</x:v>
       </x:c>
-      <x:c r="N47" t="str"/>
-      <x:c r="O47" t="str"/>
-      <x:c r="P47" t="str"/>
+      <x:c r="N47"/>
+      <x:c r="O47"/>
+      <x:c r="P47"/>
       <x:c r="Q47" t="str">
         <x:v>Ремонт и строительство</x:v>
       </x:c>
       <x:c r="R47" t="str">
         <x:v>г. Волгоград, ул. 25-летия Октября, д. 1, стр. 3</x:v>
       </x:c>
-      <x:c r="S47" t="str"/>
-      <x:c r="T47" t="str"/>
-      <x:c r="U47" t="str"/>
+      <x:c r="S47"/>
+      <x:c r="T47"/>
+      <x:c r="U47"/>
       <x:c r="V47" t="str">
         <x:v>Поштучно</x:v>
       </x:c>
@@ -8927,9 +8845,9 @@
       <x:c r="Z47" t="str">
         <x:v>Штуку</x:v>
       </x:c>
-      <x:c r="AA47" t="str"/>
-      <x:c r="AB47" t="str"/>
-      <x:c r="AC47" t="str"/>
+      <x:c r="AA47"/>
+      <x:c r="AB47"/>
+      <x:c r="AC47"/>
       <x:c r="AD47" t="n">
         <x:v>7</x:v>
       </x:c>
@@ -8942,26 +8860,24 @@
       <x:c r="AG47" t="n">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="AH47" t="str"/>
+      <x:c r="AH47"/>
       <x:c r="AI47" t="str">
         <x:v>3921120000</x:v>
       </x:c>
-      <x:c r="AJ47" t="str">
-        <x:v>22.21.42.110</x:v>
-      </x:c>
-      <x:c r="AK47" t="str"/>
-      <x:c r="AL47" t="str"/>
-      <x:c r="AM47" t="str"/>
-      <x:c r="AN47" t="str"/>
-      <x:c r="AO47" t="str"/>
-      <x:c r="AP47" t="str"/>
-      <x:c r="AQ47" t="str"/>
-      <x:c r="AR47" t="str"/>
-      <x:c r="AS47" t="str"/>
-      <x:c r="AT47" t="str"/>
-      <x:c r="AU47" t="str"/>
-      <x:c r="AV47" t="str"/>
-      <x:c r="AW47" t="str"/>
+      <x:c r="AJ47" t="str"/>
+      <x:c r="AK47"/>
+      <x:c r="AL47"/>
+      <x:c r="AM47"/>
+      <x:c r="AN47"/>
+      <x:c r="AO47"/>
+      <x:c r="AP47"/>
+      <x:c r="AQ47"/>
+      <x:c r="AR47"/>
+      <x:c r="AS47"/>
+      <x:c r="AT47"/>
+      <x:c r="AU47"/>
+      <x:c r="AV47"/>
+      <x:c r="AW47"/>
       <x:c r="AX47" t="str">
         <x:v>4900</x:v>
       </x:c>
@@ -8980,7 +8896,7 @@
       <x:c r="BC47" t="str">
         <x:v>Отделка</x:v>
       </x:c>
-      <x:c r="BD47" t="str"/>
+      <x:c r="BD47"/>
       <x:c r="BE47" t="str">
         <x:v>Стеновые панели, рейки и элементы декора</x:v>
       </x:c>
@@ -9002,28 +8918,28 @@
       <x:c r="BK47" t="str">
         <x:v>1140</x:v>
       </x:c>
-      <x:c r="BL47" t="str"/>
+      <x:c r="BL47"/>
       <x:c r="BM47" t="str">
         <x:v>Нет</x:v>
       </x:c>
-      <x:c r="BN47" t="str"/>
-      <x:c r="BO47" t="str"/>
-      <x:c r="BP47" t="str"/>
-      <x:c r="BQ47" t="str"/>
-      <x:c r="BR47" t="str"/>
-      <x:c r="BS47" t="str"/>
-      <x:c r="BT47" t="str"/>
-      <x:c r="BU47" t="str"/>
+      <x:c r="BN47"/>
+      <x:c r="BO47"/>
+      <x:c r="BP47"/>
+      <x:c r="BQ47"/>
+      <x:c r="BR47"/>
+      <x:c r="BS47"/>
+      <x:c r="BT47"/>
+      <x:c r="BU47"/>
     </x:row>
     <x:row r="48">
       <x:c r="A48" t="str">
         <x:v>adamar-vlg-AQUA SKY</x:v>
       </x:c>
-      <x:c r="B48" t="str"/>
-      <x:c r="C48" t="str"/>
-      <x:c r="D48" t="str"/>
-      <x:c r="E48" t="str"/>
-      <x:c r="F48" t="str"/>
+      <x:c r="B48"/>
+      <x:c r="C48"/>
+      <x:c r="D48"/>
+      <x:c r="E48"/>
+      <x:c r="F48"/>
       <x:c r="G48" t="str">
         <x:v>Adamar Group</x:v>
       </x:c>
@@ -9043,22 +8959,22 @@
       <x:c r="K48" t="str">
         <x:v>https://avatars.mds.yandex.net/get-yastore/21696355/h8vjxk9l24ql7h8r9hkj9xxbp4dcdbcl/orig | https://avatars.mds.yandex.net/get-yastore/21580234/djvzdqhcfxx9vvssckcscrxkq24fr4w5/orig | https://avatars.mds.yandex.net/get-yastore/21580234/r769fllkdt8htpkcl8vdtrc78jvl6pxk/orig</x:v>
       </x:c>
-      <x:c r="L48" t="str"/>
+      <x:c r="L48"/>
       <x:c r="M48" t="str">
         <x:v>По телефону и в сообщениях</x:v>
       </x:c>
-      <x:c r="N48" t="str"/>
-      <x:c r="O48" t="str"/>
-      <x:c r="P48" t="str"/>
+      <x:c r="N48"/>
+      <x:c r="O48"/>
+      <x:c r="P48"/>
       <x:c r="Q48" t="str">
         <x:v>Ремонт и строительство</x:v>
       </x:c>
       <x:c r="R48" t="str">
         <x:v>г. Волгоград, ул. 25-летия Октября, д. 1, стр. 3</x:v>
       </x:c>
-      <x:c r="S48" t="str"/>
-      <x:c r="T48" t="str"/>
-      <x:c r="U48" t="str"/>
+      <x:c r="S48"/>
+      <x:c r="T48"/>
+      <x:c r="U48"/>
       <x:c r="V48" t="str">
         <x:v>Поштучно</x:v>
       </x:c>
@@ -9074,9 +8990,9 @@
       <x:c r="Z48" t="str">
         <x:v>Штуку</x:v>
       </x:c>
-      <x:c r="AA48" t="str"/>
-      <x:c r="AB48" t="str"/>
-      <x:c r="AC48" t="str"/>
+      <x:c r="AA48"/>
+      <x:c r="AB48"/>
+      <x:c r="AC48"/>
       <x:c r="AD48" t="n">
         <x:v>7</x:v>
       </x:c>
@@ -9089,26 +9005,24 @@
       <x:c r="AG48" t="n">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="AH48" t="str"/>
+      <x:c r="AH48"/>
       <x:c r="AI48" t="str">
         <x:v>3921120000</x:v>
       </x:c>
-      <x:c r="AJ48" t="str">
-        <x:v>22.21.42.110</x:v>
-      </x:c>
-      <x:c r="AK48" t="str"/>
-      <x:c r="AL48" t="str"/>
-      <x:c r="AM48" t="str"/>
-      <x:c r="AN48" t="str"/>
-      <x:c r="AO48" t="str"/>
-      <x:c r="AP48" t="str"/>
-      <x:c r="AQ48" t="str"/>
-      <x:c r="AR48" t="str"/>
-      <x:c r="AS48" t="str"/>
-      <x:c r="AT48" t="str"/>
-      <x:c r="AU48" t="str"/>
-      <x:c r="AV48" t="str"/>
-      <x:c r="AW48" t="str"/>
+      <x:c r="AJ48" t="str"/>
+      <x:c r="AK48"/>
+      <x:c r="AL48"/>
+      <x:c r="AM48"/>
+      <x:c r="AN48"/>
+      <x:c r="AO48"/>
+      <x:c r="AP48"/>
+      <x:c r="AQ48"/>
+      <x:c r="AR48"/>
+      <x:c r="AS48"/>
+      <x:c r="AT48"/>
+      <x:c r="AU48"/>
+      <x:c r="AV48"/>
+      <x:c r="AW48"/>
       <x:c r="AX48" t="str">
         <x:v>4900</x:v>
       </x:c>
@@ -9127,7 +9041,7 @@
       <x:c r="BC48" t="str">
         <x:v>Отделка</x:v>
       </x:c>
-      <x:c r="BD48" t="str"/>
+      <x:c r="BD48"/>
       <x:c r="BE48" t="str">
         <x:v>Стеновые панели, рейки и элементы декора</x:v>
       </x:c>
@@ -9149,28 +9063,28 @@
       <x:c r="BK48" t="str">
         <x:v>1140</x:v>
       </x:c>
-      <x:c r="BL48" t="str"/>
+      <x:c r="BL48"/>
       <x:c r="BM48" t="str">
         <x:v>Нет</x:v>
       </x:c>
-      <x:c r="BN48" t="str"/>
-      <x:c r="BO48" t="str"/>
-      <x:c r="BP48" t="str"/>
-      <x:c r="BQ48" t="str"/>
-      <x:c r="BR48" t="str"/>
-      <x:c r="BS48" t="str"/>
-      <x:c r="BT48" t="str"/>
-      <x:c r="BU48" t="str"/>
+      <x:c r="BN48"/>
+      <x:c r="BO48"/>
+      <x:c r="BP48"/>
+      <x:c r="BQ48"/>
+      <x:c r="BR48"/>
+      <x:c r="BS48"/>
+      <x:c r="BT48"/>
+      <x:c r="BU48"/>
     </x:row>
     <x:row r="49">
       <x:c r="A49" t="str">
         <x:v>adamar-vlg-Matte_MuccaBlack</x:v>
       </x:c>
-      <x:c r="B49" t="str"/>
-      <x:c r="C49" t="str"/>
-      <x:c r="D49" t="str"/>
-      <x:c r="E49" t="str"/>
-      <x:c r="F49" t="str"/>
+      <x:c r="B49"/>
+      <x:c r="C49"/>
+      <x:c r="D49"/>
+      <x:c r="E49"/>
+      <x:c r="F49"/>
       <x:c r="G49" t="str">
         <x:v>Adamar Group</x:v>
       </x:c>
@@ -9190,22 +9104,22 @@
       <x:c r="K49" t="str">
         <x:v>https://avatars.mds.yandex.net/get-yastore/20918687/nmmvrkqblbptwv6rtcmcr46mt58dvzlp/orig | https://avatars.mds.yandex.net/get-yastore/17664496/ldwhvtmm74npzgx2m4q82vrd6fbgqcjr/orig | https://avatars.mds.yandex.net/get-yastore/17664496/qsxth74wj7q6jf62fcfnnjvkfw4kx9bg/orig</x:v>
       </x:c>
-      <x:c r="L49" t="str"/>
+      <x:c r="L49"/>
       <x:c r="M49" t="str">
         <x:v>По телефону и в сообщениях</x:v>
       </x:c>
-      <x:c r="N49" t="str"/>
-      <x:c r="O49" t="str"/>
-      <x:c r="P49" t="str"/>
+      <x:c r="N49"/>
+      <x:c r="O49"/>
+      <x:c r="P49"/>
       <x:c r="Q49" t="str">
         <x:v>Ремонт и строительство</x:v>
       </x:c>
       <x:c r="R49" t="str">
         <x:v>г. Волгоград, ул. 25-летия Октября, д. 1, стр. 3</x:v>
       </x:c>
-      <x:c r="S49" t="str"/>
-      <x:c r="T49" t="str"/>
-      <x:c r="U49" t="str"/>
+      <x:c r="S49"/>
+      <x:c r="T49"/>
+      <x:c r="U49"/>
       <x:c r="V49" t="str">
         <x:v>Поштучно</x:v>
       </x:c>
@@ -9221,9 +9135,9 @@
       <x:c r="Z49" t="str">
         <x:v>Штуку</x:v>
       </x:c>
-      <x:c r="AA49" t="str"/>
-      <x:c r="AB49" t="str"/>
-      <x:c r="AC49" t="str"/>
+      <x:c r="AA49"/>
+      <x:c r="AB49"/>
+      <x:c r="AC49"/>
       <x:c r="AD49" t="n">
         <x:v>7</x:v>
       </x:c>
@@ -9236,26 +9150,24 @@
       <x:c r="AG49" t="n">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="AH49" t="str"/>
+      <x:c r="AH49"/>
       <x:c r="AI49" t="str">
         <x:v>3921120000</x:v>
       </x:c>
-      <x:c r="AJ49" t="str">
-        <x:v>22.21.42.110</x:v>
-      </x:c>
-      <x:c r="AK49" t="str"/>
-      <x:c r="AL49" t="str"/>
-      <x:c r="AM49" t="str"/>
-      <x:c r="AN49" t="str"/>
-      <x:c r="AO49" t="str"/>
-      <x:c r="AP49" t="str"/>
-      <x:c r="AQ49" t="str"/>
-      <x:c r="AR49" t="str"/>
-      <x:c r="AS49" t="str"/>
-      <x:c r="AT49" t="str"/>
-      <x:c r="AU49" t="str"/>
-      <x:c r="AV49" t="str"/>
-      <x:c r="AW49" t="str"/>
+      <x:c r="AJ49" t="str"/>
+      <x:c r="AK49"/>
+      <x:c r="AL49"/>
+      <x:c r="AM49"/>
+      <x:c r="AN49"/>
+      <x:c r="AO49"/>
+      <x:c r="AP49"/>
+      <x:c r="AQ49"/>
+      <x:c r="AR49"/>
+      <x:c r="AS49"/>
+      <x:c r="AT49"/>
+      <x:c r="AU49"/>
+      <x:c r="AV49"/>
+      <x:c r="AW49"/>
       <x:c r="AX49" t="str">
         <x:v>4900</x:v>
       </x:c>
@@ -9274,7 +9186,7 @@
       <x:c r="BC49" t="str">
         <x:v>Отделка</x:v>
       </x:c>
-      <x:c r="BD49" t="str"/>
+      <x:c r="BD49"/>
       <x:c r="BE49" t="str">
         <x:v>Стеновые панели, рейки и элементы декора</x:v>
       </x:c>
@@ -9296,28 +9208,28 @@
       <x:c r="BK49" t="str">
         <x:v>1140</x:v>
       </x:c>
-      <x:c r="BL49" t="str"/>
+      <x:c r="BL49"/>
       <x:c r="BM49" t="str">
         <x:v>Нет</x:v>
       </x:c>
-      <x:c r="BN49" t="str"/>
-      <x:c r="BO49" t="str"/>
-      <x:c r="BP49" t="str"/>
-      <x:c r="BQ49" t="str"/>
-      <x:c r="BR49" t="str"/>
-      <x:c r="BS49" t="str"/>
-      <x:c r="BT49" t="str"/>
-      <x:c r="BU49" t="str"/>
+      <x:c r="BN49"/>
+      <x:c r="BO49"/>
+      <x:c r="BP49"/>
+      <x:c r="BQ49"/>
+      <x:c r="BR49"/>
+      <x:c r="BS49"/>
+      <x:c r="BT49"/>
+      <x:c r="BU49"/>
     </x:row>
     <x:row r="50">
       <x:c r="A50" t="str">
         <x:v>adamar-vlg-Glossy_ Lumiere</x:v>
       </x:c>
-      <x:c r="B50" t="str"/>
-      <x:c r="C50" t="str"/>
-      <x:c r="D50" t="str"/>
-      <x:c r="E50" t="str"/>
-      <x:c r="F50" t="str"/>
+      <x:c r="B50"/>
+      <x:c r="C50"/>
+      <x:c r="D50"/>
+      <x:c r="E50"/>
+      <x:c r="F50"/>
       <x:c r="G50" t="str">
         <x:v>Adamar Group</x:v>
       </x:c>
@@ -9337,22 +9249,22 @@
       <x:c r="K50" t="str">
         <x:v>https://avatars.mds.yandex.net/get-yastore/20760651/zw47h9dtkpgkfvkjqc4ttccbhpl5n9k2/orig | https://avatars.mds.yandex.net/get-yastore/21104660/4pscxf7dfpxsj5npxhgmbjvnrp7nhjnm/orig | https://avatars.mds.yandex.net/get-yastore/20760651/ph9zczmpmvjmzdph7kh2nmvw8jn4l8z7/orig | https://avatars.mds.yandex.net/get-yastore/14319028/7m482xvxpmnsmnkg667bptv52qxcv2dj/orig</x:v>
       </x:c>
-      <x:c r="L50" t="str"/>
+      <x:c r="L50"/>
       <x:c r="M50" t="str">
         <x:v>По телефону и в сообщениях</x:v>
       </x:c>
-      <x:c r="N50" t="str"/>
-      <x:c r="O50" t="str"/>
-      <x:c r="P50" t="str"/>
+      <x:c r="N50"/>
+      <x:c r="O50"/>
+      <x:c r="P50"/>
       <x:c r="Q50" t="str">
         <x:v>Ремонт и строительство</x:v>
       </x:c>
       <x:c r="R50" t="str">
         <x:v>г. Волгоград, ул. 25-летия Октября, д. 1, стр. 3</x:v>
       </x:c>
-      <x:c r="S50" t="str"/>
-      <x:c r="T50" t="str"/>
-      <x:c r="U50" t="str"/>
+      <x:c r="S50"/>
+      <x:c r="T50"/>
+      <x:c r="U50"/>
       <x:c r="V50" t="str">
         <x:v>Поштучно</x:v>
       </x:c>
@@ -9368,9 +9280,9 @@
       <x:c r="Z50" t="str">
         <x:v>Штуку</x:v>
       </x:c>
-      <x:c r="AA50" t="str"/>
-      <x:c r="AB50" t="str"/>
-      <x:c r="AC50" t="str"/>
+      <x:c r="AA50"/>
+      <x:c r="AB50"/>
+      <x:c r="AC50"/>
       <x:c r="AD50" t="n">
         <x:v>7</x:v>
       </x:c>
@@ -9383,26 +9295,24 @@
       <x:c r="AG50" t="n">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="AH50" t="str"/>
+      <x:c r="AH50"/>
       <x:c r="AI50" t="str">
         <x:v>3921120000</x:v>
       </x:c>
-      <x:c r="AJ50" t="str">
-        <x:v>22.21.42.110</x:v>
-      </x:c>
-      <x:c r="AK50" t="str"/>
-      <x:c r="AL50" t="str"/>
-      <x:c r="AM50" t="str"/>
-      <x:c r="AN50" t="str"/>
-      <x:c r="AO50" t="str"/>
-      <x:c r="AP50" t="str"/>
-      <x:c r="AQ50" t="str"/>
-      <x:c r="AR50" t="str"/>
-      <x:c r="AS50" t="str"/>
-      <x:c r="AT50" t="str"/>
-      <x:c r="AU50" t="str"/>
-      <x:c r="AV50" t="str"/>
-      <x:c r="AW50" t="str"/>
+      <x:c r="AJ50" t="str"/>
+      <x:c r="AK50"/>
+      <x:c r="AL50"/>
+      <x:c r="AM50"/>
+      <x:c r="AN50"/>
+      <x:c r="AO50"/>
+      <x:c r="AP50"/>
+      <x:c r="AQ50"/>
+      <x:c r="AR50"/>
+      <x:c r="AS50"/>
+      <x:c r="AT50"/>
+      <x:c r="AU50"/>
+      <x:c r="AV50"/>
+      <x:c r="AW50"/>
       <x:c r="AX50" t="str">
         <x:v>4900</x:v>
       </x:c>
@@ -9421,7 +9331,7 @@
       <x:c r="BC50" t="str">
         <x:v>Отделка</x:v>
       </x:c>
-      <x:c r="BD50" t="str"/>
+      <x:c r="BD50"/>
       <x:c r="BE50" t="str">
         <x:v>Стеновые панели, рейки и элементы декора</x:v>
       </x:c>
@@ -9443,28 +9353,28 @@
       <x:c r="BK50" t="str">
         <x:v>1140</x:v>
       </x:c>
-      <x:c r="BL50" t="str"/>
+      <x:c r="BL50"/>
       <x:c r="BM50" t="str">
         <x:v>Нет</x:v>
       </x:c>
-      <x:c r="BN50" t="str"/>
-      <x:c r="BO50" t="str"/>
-      <x:c r="BP50" t="str"/>
-      <x:c r="BQ50" t="str"/>
-      <x:c r="BR50" t="str"/>
-      <x:c r="BS50" t="str"/>
-      <x:c r="BT50" t="str"/>
-      <x:c r="BU50" t="str"/>
+      <x:c r="BN50"/>
+      <x:c r="BO50"/>
+      <x:c r="BP50"/>
+      <x:c r="BQ50"/>
+      <x:c r="BR50"/>
+      <x:c r="BS50"/>
+      <x:c r="BT50"/>
+      <x:c r="BU50"/>
     </x:row>
     <x:row r="51">
       <x:c r="A51" t="str">
         <x:v>adamar-vlg-BETON GREYSON DECOR</x:v>
       </x:c>
-      <x:c r="B51" t="str"/>
-      <x:c r="C51" t="str"/>
-      <x:c r="D51" t="str"/>
-      <x:c r="E51" t="str"/>
-      <x:c r="F51" t="str"/>
+      <x:c r="B51"/>
+      <x:c r="C51"/>
+      <x:c r="D51"/>
+      <x:c r="E51"/>
+      <x:c r="F51"/>
       <x:c r="G51" t="str">
         <x:v>Adamar Group</x:v>
       </x:c>
@@ -9484,22 +9394,22 @@
       <x:c r="K51" t="str">
         <x:v>https://avatars.mds.yandex.net/get-yastore/20274467/s5lt5gh8ccv6w6876txv5q4rbw2lzmgw/orig | https://avatars.mds.yandex.net/get-yastore/21055393/7x8qzz9s7vqkbkdk675nlwgbpmc66bxt/orig | https://avatars.mds.yandex.net/get-yastore/21055393/qh5k9txzdvknvhw7cl9m9n2sdrcnzljq/orig</x:v>
       </x:c>
-      <x:c r="L51" t="str"/>
+      <x:c r="L51"/>
       <x:c r="M51" t="str">
         <x:v>По телефону и в сообщениях</x:v>
       </x:c>
-      <x:c r="N51" t="str"/>
-      <x:c r="O51" t="str"/>
-      <x:c r="P51" t="str"/>
+      <x:c r="N51"/>
+      <x:c r="O51"/>
+      <x:c r="P51"/>
       <x:c r="Q51" t="str">
         <x:v>Ремонт и строительство</x:v>
       </x:c>
       <x:c r="R51" t="str">
         <x:v>г. Волгоград, ул. 25-летия Октября, д. 1, стр. 3</x:v>
       </x:c>
-      <x:c r="S51" t="str"/>
-      <x:c r="T51" t="str"/>
-      <x:c r="U51" t="str"/>
+      <x:c r="S51"/>
+      <x:c r="T51"/>
+      <x:c r="U51"/>
       <x:c r="V51" t="str">
         <x:v>Поштучно</x:v>
       </x:c>
@@ -9515,9 +9425,9 @@
       <x:c r="Z51" t="str">
         <x:v>Штуку</x:v>
       </x:c>
-      <x:c r="AA51" t="str"/>
-      <x:c r="AB51" t="str"/>
-      <x:c r="AC51" t="str"/>
+      <x:c r="AA51"/>
+      <x:c r="AB51"/>
+      <x:c r="AC51"/>
       <x:c r="AD51" t="n">
         <x:v>7</x:v>
       </x:c>
@@ -9530,26 +9440,24 @@
       <x:c r="AG51" t="n">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="AH51" t="str"/>
+      <x:c r="AH51"/>
       <x:c r="AI51" t="str">
         <x:v>3921120000</x:v>
       </x:c>
-      <x:c r="AJ51" t="str">
-        <x:v>22.21.42.110</x:v>
-      </x:c>
-      <x:c r="AK51" t="str"/>
-      <x:c r="AL51" t="str"/>
-      <x:c r="AM51" t="str"/>
-      <x:c r="AN51" t="str"/>
-      <x:c r="AO51" t="str"/>
-      <x:c r="AP51" t="str"/>
-      <x:c r="AQ51" t="str"/>
-      <x:c r="AR51" t="str"/>
-      <x:c r="AS51" t="str"/>
-      <x:c r="AT51" t="str"/>
-      <x:c r="AU51" t="str"/>
-      <x:c r="AV51" t="str"/>
-      <x:c r="AW51" t="str"/>
+      <x:c r="AJ51" t="str"/>
+      <x:c r="AK51"/>
+      <x:c r="AL51"/>
+      <x:c r="AM51"/>
+      <x:c r="AN51"/>
+      <x:c r="AO51"/>
+      <x:c r="AP51"/>
+      <x:c r="AQ51"/>
+      <x:c r="AR51"/>
+      <x:c r="AS51"/>
+      <x:c r="AT51"/>
+      <x:c r="AU51"/>
+      <x:c r="AV51"/>
+      <x:c r="AW51"/>
       <x:c r="AX51" t="str">
         <x:v>4900</x:v>
       </x:c>
@@ -9568,7 +9476,7 @@
       <x:c r="BC51" t="str">
         <x:v>Отделка</x:v>
       </x:c>
-      <x:c r="BD51" t="str"/>
+      <x:c r="BD51"/>
       <x:c r="BE51" t="str">
         <x:v>Стеновые панели, рейки и элементы декора</x:v>
       </x:c>
@@ -9590,28 +9498,28 @@
       <x:c r="BK51" t="str">
         <x:v>1140</x:v>
       </x:c>
-      <x:c r="BL51" t="str"/>
+      <x:c r="BL51"/>
       <x:c r="BM51" t="str">
         <x:v>Нет</x:v>
       </x:c>
-      <x:c r="BN51" t="str"/>
-      <x:c r="BO51" t="str"/>
-      <x:c r="BP51" t="str"/>
-      <x:c r="BQ51" t="str"/>
-      <x:c r="BR51" t="str"/>
-      <x:c r="BS51" t="str"/>
-      <x:c r="BT51" t="str"/>
-      <x:c r="BU51" t="str"/>
+      <x:c r="BN51"/>
+      <x:c r="BO51"/>
+      <x:c r="BP51"/>
+      <x:c r="BQ51"/>
+      <x:c r="BR51"/>
+      <x:c r="BS51"/>
+      <x:c r="BT51"/>
+      <x:c r="BU51"/>
     </x:row>
     <x:row r="52">
       <x:c r="A52" t="str">
         <x:v>adamar-vlg-MARBLE VEIL</x:v>
       </x:c>
-      <x:c r="B52" t="str"/>
-      <x:c r="C52" t="str"/>
-      <x:c r="D52" t="str"/>
-      <x:c r="E52" t="str"/>
-      <x:c r="F52" t="str"/>
+      <x:c r="B52"/>
+      <x:c r="C52"/>
+      <x:c r="D52"/>
+      <x:c r="E52"/>
+      <x:c r="F52"/>
       <x:c r="G52" t="str">
         <x:v>Adamar Group</x:v>
       </x:c>
@@ -9631,22 +9539,22 @@
       <x:c r="K52" t="str">
         <x:v>https://avatars.mds.yandex.net/get-yastore/21012869/5fhjbvfv7lctbpm924m982rdxnpbcnzh/orig | https://avatars.mds.yandex.net/get-yastore/20900992/52ck6jvdlvlk4v8548t7b6cvmknxvp5n/orig | https://avatars.mds.yandex.net/get-yastore/20274467/fp2w4gn8d9gkbsfwxn8t64b57b56s8f2/orig | https://avatars.mds.yandex.net/get-yastore/20274467/llk8s5ztv2tx8657t68wf66qqtn7vd94/orig</x:v>
       </x:c>
-      <x:c r="L52" t="str"/>
+      <x:c r="L52"/>
       <x:c r="M52" t="str">
         <x:v>По телефону и в сообщениях</x:v>
       </x:c>
-      <x:c r="N52" t="str"/>
-      <x:c r="O52" t="str"/>
-      <x:c r="P52" t="str"/>
+      <x:c r="N52"/>
+      <x:c r="O52"/>
+      <x:c r="P52"/>
       <x:c r="Q52" t="str">
         <x:v>Ремонт и строительство</x:v>
       </x:c>
       <x:c r="R52" t="str">
         <x:v>г. Волгоград, ул. 25-летия Октября, д. 1, стр. 3</x:v>
       </x:c>
-      <x:c r="S52" t="str"/>
-      <x:c r="T52" t="str"/>
-      <x:c r="U52" t="str"/>
+      <x:c r="S52"/>
+      <x:c r="T52"/>
+      <x:c r="U52"/>
       <x:c r="V52" t="str">
         <x:v>Поштучно</x:v>
       </x:c>
@@ -9662,9 +9570,9 @@
       <x:c r="Z52" t="str">
         <x:v>Штуку</x:v>
       </x:c>
-      <x:c r="AA52" t="str"/>
-      <x:c r="AB52" t="str"/>
-      <x:c r="AC52" t="str"/>
+      <x:c r="AA52"/>
+      <x:c r="AB52"/>
+      <x:c r="AC52"/>
       <x:c r="AD52" t="n">
         <x:v>7</x:v>
       </x:c>
@@ -9677,26 +9585,24 @@
       <x:c r="AG52" t="n">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="AH52" t="str"/>
+      <x:c r="AH52"/>
       <x:c r="AI52" t="str">
         <x:v>3921120000</x:v>
       </x:c>
-      <x:c r="AJ52" t="str">
-        <x:v>22.21.42.110</x:v>
-      </x:c>
-      <x:c r="AK52" t="str"/>
-      <x:c r="AL52" t="str"/>
-      <x:c r="AM52" t="str"/>
-      <x:c r="AN52" t="str"/>
-      <x:c r="AO52" t="str"/>
-      <x:c r="AP52" t="str"/>
-      <x:c r="AQ52" t="str"/>
-      <x:c r="AR52" t="str"/>
-      <x:c r="AS52" t="str"/>
-      <x:c r="AT52" t="str"/>
-      <x:c r="AU52" t="str"/>
-      <x:c r="AV52" t="str"/>
-      <x:c r="AW52" t="str"/>
+      <x:c r="AJ52" t="str"/>
+      <x:c r="AK52"/>
+      <x:c r="AL52"/>
+      <x:c r="AM52"/>
+      <x:c r="AN52"/>
+      <x:c r="AO52"/>
+      <x:c r="AP52"/>
+      <x:c r="AQ52"/>
+      <x:c r="AR52"/>
+      <x:c r="AS52"/>
+      <x:c r="AT52"/>
+      <x:c r="AU52"/>
+      <x:c r="AV52"/>
+      <x:c r="AW52"/>
       <x:c r="AX52" t="str">
         <x:v>4900</x:v>
       </x:c>
@@ -9715,7 +9621,7 @@
       <x:c r="BC52" t="str">
         <x:v>Отделка</x:v>
       </x:c>
-      <x:c r="BD52" t="str"/>
+      <x:c r="BD52"/>
       <x:c r="BE52" t="str">
         <x:v>Стеновые панели, рейки и элементы декора</x:v>
       </x:c>
@@ -9737,18 +9643,18 @@
       <x:c r="BK52" t="str">
         <x:v>1140</x:v>
       </x:c>
-      <x:c r="BL52" t="str"/>
+      <x:c r="BL52"/>
       <x:c r="BM52" t="str">
         <x:v>Нет</x:v>
       </x:c>
-      <x:c r="BN52" t="str"/>
-      <x:c r="BO52" t="str"/>
-      <x:c r="BP52" t="str"/>
-      <x:c r="BQ52" t="str"/>
-      <x:c r="BR52" t="str"/>
-      <x:c r="BS52" t="str"/>
-      <x:c r="BT52" t="str"/>
-      <x:c r="BU52" t="str"/>
+      <x:c r="BN52"/>
+      <x:c r="BO52"/>
+      <x:c r="BP52"/>
+      <x:c r="BQ52"/>
+      <x:c r="BR52"/>
+      <x:c r="BS52"/>
+      <x:c r="BT52"/>
+      <x:c r="BU52"/>
     </x:row>
   </x:sheetData>
   <x:dataValidations count="27">
@@ -9835,51 +9741,51 @@
     </x:dataValidation>
   </x:dataValidations>
   <x:hyperlinks>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="BN3" r:id="R58706452e2674ab0"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="BO3" r:id="Rd3f78d767af3484e"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="BP3" r:id="R89c593d4630e416c"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="BS3" r:id="Ra7dc4773cd1b47e6"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="BT3" r:id="Rcfd64058c2c94b1e"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A4" r:id="R5f27da2963bd458b"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B4" r:id="Re09150677a304c18"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C4" r:id="R1ba051f1c74644a3"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F4" r:id="R9f06d2e6abc5439b"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G4" r:id="Rb2a1c4bda8ee4063"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H4" r:id="R75072120b7114892"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K4" r:id="R1e9136819b19449a"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L4" r:id="Rd904d446fa024a1e"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O4" r:id="R429c7e6dbf804165"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P4" r:id="Ra3923dd48f1646d5"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R4" r:id="R0dcb81ad62ea484a"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S4" r:id="Rf986edd7c0104274"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T4" r:id="R0303eee4031d4b35"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U4" r:id="R6fe815d7fa224844"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W4" r:id="R097c24c7e6004f36"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X4" r:id="R7df193bfcfaf467a"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Y4" r:id="Ra23101701a464523"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB4" r:id="Rfab959e996204cba"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AD4" r:id="R3c912490296e4732"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE4" r:id="R8c22b0c788314d2f"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AF4" r:id="R6065fc361af34be1"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AG4" r:id="R9fcaa53c6b8540ca"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AM4" r:id="R5f8ea6007c8e4e69"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AN4" r:id="Rd0234aa01323499c"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AO4" r:id="R53c6413324044f0b"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AP4" r:id="Rf283a9d526b74b7d"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AQ4" r:id="R25d4b96f6a804de9"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AR4" r:id="R45f4c06ecb63422e"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AS4" r:id="R5cefb2f6bdf24b0e"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AT4" r:id="Rc7965216f12d46dd"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AU4" r:id="Rcf96b0eefcad4bac"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AV4" r:id="R861605c0ed3342ec"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AX4" r:id="Rb54264683a0842c8"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="BD4" r:id="R590e4b6645134cda"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="BJ4" r:id="Re8b285525a1f41e2"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="BK4" r:id="R30df98e4ad8b440d"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="BO4" r:id="R121f670855cd4c5e"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="BQ4" r:id="R2801402713164453"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="BT4" r:id="R307011d953b945a2"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="BU4" r:id="Rf4a47188840148ab"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="BN3" r:id="R31572887d7a64165"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="BO3" r:id="R3a9262c1624449d6"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="BP3" r:id="R13b3a8af045d44dc"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="BS3" r:id="Rd6fdbffc54aa4261"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="BT3" r:id="Re65574ab56e54758"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A4" r:id="R0c2eb8438bda4412"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B4" r:id="R5d448fa95f114098"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C4" r:id="R233e5b541a5644f1"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F4" r:id="Rcac5192cf8c94612"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G4" r:id="R58e48a7ca7bb4e7b"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H4" r:id="Rf5b87ed4cdc549f5"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K4" r:id="R8b5567427a9c4ae6"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L4" r:id="Rb98b7b06f0d34422"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O4" r:id="Re7f00653226b44a4"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P4" r:id="Rea7f8cbe73e443c0"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R4" r:id="R5b100cc444dc4808"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S4" r:id="R0f160a00ea11419a"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T4" r:id="R153e6b1d6af54e99"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U4" r:id="R1527d2f664ca46aa"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W4" r:id="R89bd38aaa9d64257"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X4" r:id="Rb4ed0c040eda48e2"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Y4" r:id="R5cebc7c230674c6a"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB4" r:id="R4be8d5d39339405e"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AD4" r:id="R0b048f05987b4b05"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE4" r:id="R4bc89cb6e8644abb"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AF4" r:id="Rf114dc9f502d4200"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AG4" r:id="Rfbe608a983644071"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AM4" r:id="Rb9a9d4fdb7a042af"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AN4" r:id="R4e1b7d6a62954193"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AO4" r:id="R7a294abde11e4129"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AP4" r:id="R0c70d947e6334529"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AQ4" r:id="Re66925fb160e4c1c"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AR4" r:id="R6d6dd6ba065e47ed"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AS4" r:id="Rda32b184a73d408f"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AT4" r:id="Rd6efbfecaa8443a5"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AU4" r:id="Re8cf1a22911c4301"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AV4" r:id="R7d032306b93a4bd3"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AX4" r:id="Rd3abb51587c74eab"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="BD4" r:id="Rbc987d3b799248bf"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="BJ4" r:id="R1eee4749470c48ce"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="BK4" r:id="R947b676f766b47e2"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="BO4" r:id="Rcba0a9f7ec0c4c05"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="BQ4" r:id="R1b35c36f7d66470b"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="BT4" r:id="Rd482a11803614d0c"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="BU4" r:id="Rcc17013c58904bb4"/>
   </x:hyperlinks>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
